--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F72942-A510-4C1C-8312-A22818C3BC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64092B70-20B1-4C38-A1F4-E6F01939C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19425" yWindow="5955" windowWidth="35475" windowHeight="23445" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6608" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6616" uniqueCount="1198">
   <si>
     <t>Patient Inputs</t>
   </si>
@@ -2867,9 +2867,6 @@
   </si>
   <si>
     <t>cala2004vd</t>
-  </si>
-  <si>
-    <t>PositiveEndExpiratoryPressure</t>
   </si>
   <si>
     <t>Positive end-expiratory pressure (PEEP) is the pressure in the lungs (alveolar pressure) above atmospheric pressure (the pressure outside of the body) that exists at the end of expiration. The two types of PEEP are extrinsic PEEP (PEEP applied by a ventilator) and intrinsic PEEP (PEEP caused by an incomplete exhalation). Pressure that is applied or increased during an inspiration is termed pressure support.</t>
@@ -3764,6 +3761,12 @@
   </si>
   <si>
     <t>RespiratoryElastance</t>
+  </si>
+  <si>
+    <t>ExtrinsicPositiveEndExpiratoryPressure</t>
+  </si>
+  <si>
+    <t>TotalPositiveEndExpiratoryPressure</t>
   </si>
 </sst>
 </file>
@@ -4035,7 +4038,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4372,18 +4375,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5005,7 +4996,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -5025,7 +5016,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="9" t="s">
@@ -5075,7 +5066,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="10" t="s">
         <v>851</v>
       </c>
       <c r="B2" s="26" t="s">
@@ -5113,7 +5104,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="36">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="10" t="s">
         <v>856</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -5153,7 +5144,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="36">
-      <c r="A4" s="122" t="s">
+      <c r="A4" s="10" t="s">
         <v>861</v>
       </c>
       <c r="B4" s="17" t="s">
@@ -5197,7 +5188,7 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="10" t="s">
         <v>866</v>
       </c>
       <c r="B5" s="17" t="s">
@@ -5239,7 +5230,7 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="10" t="s">
         <v>869</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -5279,7 +5270,7 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="48" t="s">
         <v>872</v>
       </c>
       <c r="B7" s="17" t="s">
@@ -5309,7 +5300,7 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="48" t="s">
         <v>874</v>
       </c>
       <c r="B8" s="17"/>
@@ -5337,7 +5328,7 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="10" t="s">
         <v>875</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -5377,7 +5368,7 @@
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="124" t="s">
+      <c r="A10" s="48" t="s">
         <v>878</v>
       </c>
       <c r="B10" s="17"/>
@@ -5405,7 +5396,7 @@
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="124" t="s">
+      <c r="A11" s="48" t="s">
         <v>879</v>
       </c>
       <c r="B11" s="17"/>
@@ -5432,27 +5423,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A12" s="122" t="s">
-        <v>880</v>
+    <row r="12" spans="1:16">
+      <c r="A12" s="10" t="s">
+        <v>1196</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>881</v>
+        <v>852</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
-      <c r="F12" s="94">
-        <v>0.44</v>
+      <c r="F12" s="98">
+        <v>0</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>882</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>883</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="17" t="s">
         <v>49</v>
       </c>
@@ -5472,33 +5461,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="122" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>884</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51" t="s">
-        <v>885</v>
+    <row r="13" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>881</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="94">
+        <v>0.44</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>853</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>886</v>
+        <v>882</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>883</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="26"/>
-      <c r="L13" s="95"/>
+      <c r="L13" s="91"/>
       <c r="M13" s="66" t="s">
         <v>855</v>
       </c>
@@ -5513,37 +5502,37 @@
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="122" t="s">
-        <v>887</v>
+      <c r="A14" s="10" t="s">
+        <v>1191</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>17</v>
+        <v>884</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>862</v>
+        <v>46</v>
       </c>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="51">
-        <v>7</v>
+      <c r="F14" s="51" t="s">
+        <v>885</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>888</v>
+        <v>853</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>886</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="26"/>
-      <c r="L14" s="91"/>
+      <c r="L14" s="95"/>
       <c r="M14" s="66" t="s">
         <v>855</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>860</v>
+        <v>101</v>
       </c>
       <c r="O14" s="14" t="s">
         <v>52</v>
@@ -5553,33 +5542,37 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="122" t="s">
-        <v>889</v>
-      </c>
-      <c r="B15" s="17"/>
+      <c r="A15" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" s="51" t="s">
-        <v>46</v>
+        <v>862</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51">
-        <v>0.21</v>
+        <v>7</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="17"/>
+        <v>104</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="I15" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="26"/>
-      <c r="L15" s="95"/>
+      <c r="L15" s="91"/>
       <c r="M15" s="66" t="s">
         <v>855</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>101</v>
+        <v>860</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>52</v>
@@ -5589,34 +5582,28 @@
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="122" t="s">
-        <v>890</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>200</v>
-      </c>
+      <c r="A16" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="B16" s="17"/>
       <c r="C16" s="51" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51">
-        <v>452</v>
-      </c>
-      <c r="G16" s="8" t="s">
+        <v>0.21</v>
+      </c>
+      <c r="G16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>891</v>
-      </c>
+      <c r="H16" s="17"/>
       <c r="I16" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="J16" s="17" t="s">
-        <v>892</v>
-      </c>
+      <c r="J16" s="17"/>
       <c r="K16" s="26"/>
-      <c r="L16" s="92"/>
+      <c r="L16" s="95"/>
       <c r="M16" s="66" t="s">
         <v>855</v>
       </c>
@@ -5631,22 +5618,34 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="124" t="s">
-        <v>893</v>
+      <c r="A17" s="10" t="s">
+        <v>890</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="C17" s="51"/>
+        <v>200</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>46</v>
+      </c>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="F17" s="51">
+        <v>452</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>891</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>892</v>
+      </c>
       <c r="K17" s="26"/>
-      <c r="L17" s="91"/>
+      <c r="L17" s="92"/>
       <c r="M17" s="66" t="s">
         <v>855</v>
       </c>
@@ -5661,11 +5660,11 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="124" t="s">
-        <v>895</v>
+      <c r="A18" s="48" t="s">
+        <v>893</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
@@ -5691,32 +5690,22 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="122" t="s">
-        <v>896</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="51" t="s">
-        <v>46</v>
-      </c>
+      <c r="A19" s="48" t="s">
+        <v>895</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="51" t="s">
-        <v>897</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>49</v>
-      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
       <c r="J19" s="17"/>
-      <c r="K19" s="26" t="s">
-        <v>899</v>
-      </c>
-      <c r="L19" s="95"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="91"/>
       <c r="M19" s="66" t="s">
         <v>855</v>
       </c>
@@ -5731,32 +5720,32 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="122" t="s">
-        <v>900</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>881</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="96">
-        <v>0.4</v>
+      <c r="A20" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51" t="s">
+        <v>897</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>882</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>883</v>
+        <v>104</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>898</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>573</v>
+        <v>49</v>
       </c>
       <c r="J20" s="17"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="91"/>
+      <c r="K20" s="26" t="s">
+        <v>899</v>
+      </c>
+      <c r="L20" s="95"/>
       <c r="M20" s="66" t="s">
         <v>855</v>
       </c>
@@ -5771,32 +5760,32 @@
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="122" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>884</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51" t="s">
-        <v>885</v>
+      <c r="A21" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>881</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="96">
+        <v>0.4</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>853</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>886</v>
+        <v>882</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>883</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>49</v>
+        <v>573</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="26"/>
-      <c r="L21" s="95"/>
+      <c r="L21" s="91"/>
       <c r="M21" s="66" t="s">
         <v>855</v>
       </c>
@@ -5811,37 +5800,37 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="122" t="s">
-        <v>901</v>
+      <c r="A22" s="10" t="s">
+        <v>1192</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>17</v>
+        <v>884</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>862</v>
+        <v>46</v>
       </c>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
-      <c r="F22" s="51">
-        <v>7</v>
+      <c r="F22" s="51" t="s">
+        <v>885</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>888</v>
+        <v>853</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>886</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="26"/>
-      <c r="L22" s="91"/>
+      <c r="L22" s="95"/>
       <c r="M22" s="66" t="s">
         <v>855</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>860</v>
+        <v>101</v>
       </c>
       <c r="O22" s="14" t="s">
         <v>52</v>
@@ -5851,28 +5840,28 @@
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="122" t="s">
-        <v>902</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>852</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="97">
-        <v>-8</v>
+      <c r="A23" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>862</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51">
+        <v>7</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>573</v>
+        <v>49</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="26"/>
@@ -5881,7 +5870,7 @@
         <v>855</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>101</v>
+        <v>860</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>52</v>
@@ -5891,19 +5880,19 @@
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="122" t="s">
+      <c r="A24" s="10" t="s">
         <v>902</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
       <c r="F24" s="97">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>104</v>
@@ -5931,8 +5920,8 @@
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="122" t="s">
-        <v>904</v>
+      <c r="A25" s="10" t="s">
+        <v>902</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>852</v>
@@ -5942,20 +5931,20 @@
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
-      <c r="F25" s="98">
-        <v>5.4</v>
+      <c r="F25" s="97">
+        <v>-5</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="8"/>
+        <v>104</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>903</v>
+      </c>
       <c r="I25" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J25" s="17"/>
-      <c r="K25" s="26" t="s">
-        <v>905</v>
-      </c>
+      <c r="K25" s="26"/>
       <c r="L25" s="91"/>
       <c r="M25" s="66" t="s">
         <v>855</v>
@@ -5971,29 +5960,31 @@
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="122" t="s">
+      <c r="A26" s="10" t="s">
         <v>904</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
       <c r="F26" s="98">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="17" t="s">
-        <v>49</v>
+        <v>573</v>
       </c>
       <c r="J26" s="17"/>
-      <c r="K26" s="26"/>
+      <c r="K26" s="26" t="s">
+        <v>905</v>
+      </c>
       <c r="L26" s="91"/>
       <c r="M26" s="66" t="s">
         <v>855</v>
@@ -6009,8 +6000,8 @@
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="122" t="s">
-        <v>1194</v>
+      <c r="A27" s="10" t="s">
+        <v>904</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>852</v>
@@ -6047,26 +6038,24 @@
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="122" t="s">
-        <v>906</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>870</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="93">
-        <v>0.2</v>
+      <c r="A28" s="10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="98">
+        <v>0</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>871</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H28" s="8"/>
       <c r="I28" s="17" t="s">
         <v>49</v>
       </c>
@@ -6086,34 +6075,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="60">
-      <c r="A29" s="122" t="s">
-        <v>907</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>852</v>
+    <row r="29" spans="1:16">
+      <c r="A29" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>870</v>
       </c>
       <c r="C29" s="51" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
-      <c r="F29" s="6">
-        <v>-1</v>
+      <c r="F29" s="93">
+        <v>0.2</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>908</v>
+        <v>871</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>573</v>
+        <v>49</v>
       </c>
       <c r="J29" s="17"/>
-      <c r="K29" s="26" t="s">
-        <v>909</v>
-      </c>
+      <c r="K29" s="26"/>
       <c r="L29" s="91"/>
       <c r="M29" s="66" t="s">
         <v>855</v>
@@ -6128,9 +6115,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="122" t="s">
-        <v>910</v>
+    <row r="30" spans="1:16" ht="60">
+      <c r="A30" s="10" t="s">
+        <v>907</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>852</v>
@@ -6141,17 +6128,21 @@
       <c r="D30" s="51"/>
       <c r="E30" s="51"/>
       <c r="F30" s="6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>853</v>
-      </c>
-      <c r="H30" s="17"/>
+        <v>104</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>908</v>
+      </c>
       <c r="I30" s="17" t="s">
-        <v>49</v>
+        <v>573</v>
       </c>
       <c r="J30" s="17"/>
-      <c r="K30" s="26"/>
+      <c r="K30" s="26" t="s">
+        <v>909</v>
+      </c>
       <c r="L30" s="91"/>
       <c r="M30" s="66" t="s">
         <v>855</v>
@@ -6167,10 +6158,12 @@
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="122" t="s">
-        <v>911</v>
-      </c>
-      <c r="B31" s="26"/>
+      <c r="A31" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>852</v>
+      </c>
       <c r="C31" s="51" t="s">
         <v>46</v>
       </c>
@@ -6186,9 +6179,7 @@
       <c r="I31" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="J31" s="17" t="s">
-        <v>912</v>
-      </c>
+      <c r="J31" s="17"/>
       <c r="K31" s="26"/>
       <c r="L31" s="91"/>
       <c r="M31" s="66" t="s">
@@ -6205,12 +6196,10 @@
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="122" t="s">
-        <v>913</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>200</v>
-      </c>
+      <c r="A32" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="B32" s="26"/>
       <c r="C32" s="51" t="s">
         <v>46</v>
       </c>
@@ -6227,7 +6216,7 @@
         <v>49</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="K32" s="26"/>
       <c r="L32" s="91"/>
@@ -6245,20 +6234,30 @@
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="124" t="s">
-        <v>915</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="C33" s="51"/>
+      <c r="A33" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>46</v>
+      </c>
       <c r="D33" s="51"/>
       <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="17"/>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>853</v>
+      </c>
       <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
+      <c r="I33" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>914</v>
+      </c>
       <c r="K33" s="26"/>
       <c r="L33" s="91"/>
       <c r="M33" s="66" t="s">
@@ -6275,11 +6274,11 @@
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="124" t="s">
-        <v>916</v>
+      <c r="A34" s="48" t="s">
+        <v>915</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
@@ -6304,32 +6303,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="24">
-      <c r="A35" s="122" t="s">
-        <v>917</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>852</v>
-      </c>
-      <c r="C35" s="51" t="s">
-        <v>46</v>
-      </c>
+    <row r="35" spans="1:16">
+      <c r="A35" s="48" t="s">
+        <v>916</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C35" s="51"/>
       <c r="D35" s="51"/>
       <c r="E35" s="51"/>
-      <c r="F35" s="6">
-        <v>1</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>104</v>
-      </c>
+      <c r="F35" s="51"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="17"/>
-      <c r="I35" s="17" t="s">
-        <v>573</v>
-      </c>
+      <c r="I35" s="17"/>
       <c r="J35" s="17"/>
-      <c r="K35" s="26" t="s">
-        <v>918</v>
-      </c>
+      <c r="K35" s="26"/>
       <c r="L35" s="91"/>
       <c r="M35" s="66" t="s">
         <v>855</v>
@@ -6344,32 +6333,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A36" s="122" t="s">
-        <v>919</v>
+    <row r="36" spans="1:16" ht="24">
+      <c r="A36" s="10" t="s">
+        <v>917</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>17</v>
+        <v>852</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>862</v>
+        <v>46</v>
       </c>
       <c r="D36" s="51"/>
       <c r="E36" s="51"/>
-      <c r="F36" s="5">
-        <v>2</v>
+      <c r="F36" s="6">
+        <v>1</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>888</v>
-      </c>
+      <c r="H36" s="17"/>
       <c r="I36" s="17" t="s">
-        <v>49</v>
+        <v>573</v>
       </c>
       <c r="J36" s="17"/>
-      <c r="K36" s="26"/>
+      <c r="K36" s="26" t="s">
+        <v>918</v>
+      </c>
       <c r="L36" s="91"/>
       <c r="M36" s="66" t="s">
         <v>855</v>
@@ -6384,23 +6373,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="122" t="s">
-        <v>920</v>
-      </c>
-      <c r="B37" s="18"/>
+    <row r="37" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A37" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>17</v>
+      </c>
       <c r="C37" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="51" t="s">
-        <v>921</v>
+        <v>862</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="5">
+        <v>2</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>922</v>
-      </c>
-      <c r="H37" s="17"/>
+        <v>104</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="I37" s="17" t="s">
         <v>49</v>
       </c>
@@ -6420,32 +6413,28 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="108">
-      <c r="A38" s="122" t="s">
-        <v>923</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>852</v>
-      </c>
+    <row r="38" spans="1:16">
+      <c r="A38" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="B38" s="18"/>
       <c r="C38" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="6">
-        <v>0</v>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="51" t="s">
+        <v>921</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>104</v>
+        <v>922</v>
       </c>
       <c r="H38" s="17"/>
       <c r="I38" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="17"/>
-      <c r="K38" s="26" t="s">
-        <v>924</v>
-      </c>
+      <c r="K38" s="26"/>
       <c r="L38" s="91"/>
       <c r="M38" s="66" t="s">
         <v>855</v>
@@ -6461,8 +6450,8 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="96">
-      <c r="A39" s="122" t="s">
-        <v>1195</v>
+      <c r="A39" s="10" t="s">
+        <v>1194</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>870</v>
@@ -6473,20 +6462,20 @@
       <c r="D39" s="51"/>
       <c r="E39" s="51"/>
       <c r="F39" s="17" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="26" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L39" s="95"/>
       <c r="M39" s="66" t="s">
@@ -6503,11 +6492,11 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="122" t="s">
-        <v>1196</v>
+      <c r="A40" s="10" t="s">
+        <v>1195</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C40" s="51" t="s">
         <v>46</v>
@@ -6515,20 +6504,20 @@
       <c r="D40" s="51"/>
       <c r="E40" s="51"/>
       <c r="F40" s="17" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G40" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="26" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L40" s="95"/>
       <c r="M40" s="66" t="s">
@@ -6545,11 +6534,11 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="24">
-      <c r="A41" s="122" t="s">
+      <c r="A41" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="B41" s="18" t="s">
         <v>931</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>932</v>
       </c>
       <c r="C41" s="51" t="s">
         <v>862</v>
@@ -6570,7 +6559,7 @@
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="26" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="66" t="s">
@@ -6587,8 +6576,8 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="124" t="s">
-        <v>934</v>
+      <c r="A42" s="48" t="s">
+        <v>933</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>873</v>
@@ -6617,8 +6606,8 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="124" t="s">
-        <v>935</v>
+      <c r="A43" s="48" t="s">
+        <v>934</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>873</v>
@@ -6647,8 +6636,8 @@
       </c>
     </row>
     <row r="44" spans="1:16" ht="36">
-      <c r="A44" s="122" t="s">
-        <v>936</v>
+      <c r="A44" s="10" t="s">
+        <v>935</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>292</v>
@@ -6659,13 +6648,13 @@
       <c r="D44" s="51"/>
       <c r="E44" s="51"/>
       <c r="F44" s="18" t="s">
+        <v>936</v>
+      </c>
+      <c r="G44" s="99" t="s">
         <v>937</v>
       </c>
-      <c r="G44" s="99" t="s">
+      <c r="H44" s="8" t="s">
         <v>938</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>939</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>49</v>
@@ -6687,8 +6676,8 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="124" t="s">
-        <v>940</v>
+      <c r="A45" s="48" t="s">
+        <v>939</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="51" t="s">
@@ -6700,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
@@ -6721,8 +6710,8 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="124" t="s">
-        <v>942</v>
+      <c r="A46" s="48" t="s">
+        <v>941</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="51"/>
@@ -6749,8 +6738,8 @@
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="122" t="s">
-        <v>943</v>
+      <c r="A47" s="10" t="s">
+        <v>942</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="51" t="s">
@@ -6769,7 +6758,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="K47" s="51"/>
       <c r="L47" s="51"/>
@@ -6787,8 +6776,8 @@
       </c>
     </row>
     <row r="48" spans="1:16" ht="24">
-      <c r="A48" s="122" t="s">
-        <v>945</v>
+      <c r="A48" s="10" t="s">
+        <v>944</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="51" t="s">
@@ -6810,7 +6799,7 @@
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="26" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L48" s="92"/>
       <c r="M48" s="66" t="s">
@@ -6827,8 +6816,8 @@
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="122" t="s">
-        <v>947</v>
+      <c r="A49" s="10" t="s">
+        <v>946</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>17</v>
@@ -6867,11 +6856,11 @@
       </c>
     </row>
     <row r="50" spans="1:16" ht="24">
-      <c r="A50" s="122" t="s">
+      <c r="A50" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="B50" s="17" t="s">
         <v>948</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>949</v>
       </c>
       <c r="C50" s="51" t="s">
         <v>862</v>
@@ -6892,7 +6881,7 @@
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="26" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="L50" s="91"/>
       <c r="M50" s="66" t="s">
@@ -6909,11 +6898,11 @@
       </c>
     </row>
     <row r="51" spans="1:16" ht="24">
-      <c r="A51" s="122" t="s">
-        <v>951</v>
+      <c r="A51" s="10" t="s">
+        <v>950</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C51" s="51" t="s">
         <v>862</v>
@@ -6935,7 +6924,7 @@
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="26" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="L51" s="56"/>
       <c r="M51" s="66" t="s">
@@ -6952,11 +6941,11 @@
       </c>
     </row>
     <row r="52" spans="1:16" ht="36">
-      <c r="A52" s="122" t="s">
-        <v>953</v>
+      <c r="A52" s="10" t="s">
+        <v>952</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C52" s="51" t="s">
         <v>862</v>
@@ -6977,7 +6966,7 @@
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="26" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="L52" s="56"/>
       <c r="M52" s="66" t="s">
@@ -6993,22 +6982,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="124" t="s">
-        <v>955</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="C53" s="51"/>
+    <row r="53" spans="1:16" ht="108">
+      <c r="A53" s="10" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>852</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>46</v>
+      </c>
       <c r="D53" s="51"/>
       <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="17"/>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
+      <c r="I53" s="17" t="s">
+        <v>49</v>
+      </c>
       <c r="J53" s="17"/>
-      <c r="K53" s="26"/>
+      <c r="K53" s="26" t="s">
+        <v>923</v>
+      </c>
       <c r="L53" s="91"/>
       <c r="M53" s="66" t="s">
         <v>855</v>
@@ -7023,35 +7022,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A54" s="122" t="s">
-        <v>956</v>
+    <row r="54" spans="1:16">
+      <c r="A54" s="48" t="s">
+        <v>954</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>949</v>
-      </c>
-      <c r="C54" s="51" t="s">
-        <v>862</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="C54" s="51"/>
       <c r="D54" s="51"/>
       <c r="E54" s="51"/>
-      <c r="F54" s="51">
-        <f>0.007*12</f>
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>888</v>
-      </c>
-      <c r="I54" s="17" t="s">
-        <v>49</v>
-      </c>
+      <c r="F54" s="51"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
       <c r="J54" s="17"/>
-      <c r="K54" s="26" t="s">
-        <v>957</v>
-      </c>
+      <c r="K54" s="26"/>
       <c r="L54" s="91"/>
       <c r="M54" s="66" t="s">
         <v>855</v>
@@ -7066,22 +7052,35 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="124" t="s">
-        <v>958</v>
+    <row r="55" spans="1:16" ht="45.75" customHeight="1">
+      <c r="A55" s="10" t="s">
+        <v>955</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>873</v>
-      </c>
-      <c r="C55" s="51"/>
+        <v>948</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>862</v>
+      </c>
       <c r="D55" s="51"/>
       <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
+      <c r="F55" s="51">
+        <f>0.007*12</f>
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>49</v>
+      </c>
       <c r="J55" s="17"/>
-      <c r="K55" s="26"/>
+      <c r="K55" s="26" t="s">
+        <v>956</v>
+      </c>
       <c r="L55" s="91"/>
       <c r="M55" s="66" t="s">
         <v>855</v>
@@ -7097,29 +7096,19 @@
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="122" t="s">
-        <v>959</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>852</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="51">
-        <v>-1</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>908</v>
-      </c>
-      <c r="I56" s="17" t="s">
-        <v>573</v>
-      </c>
+      <c r="A56" s="48" t="s">
+        <v>957</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C56" s="51"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
       <c r="J56" s="17"/>
       <c r="K56" s="26"/>
       <c r="L56" s="91"/>
@@ -7137,19 +7126,19 @@
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="122" t="s">
-        <v>959</v>
+      <c r="A57" s="10" t="s">
+        <v>958</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="51">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G57" s="17" t="s">
         <v>104</v>
@@ -7177,25 +7166,25 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="122" t="s">
-        <v>960</v>
-      </c>
-      <c r="B58" s="17" t="s">
+      <c r="A58" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="B58" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
       <c r="F58" s="51">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>961</v>
+        <v>908</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>573</v>
@@ -7217,25 +7206,25 @@
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="122" t="s">
-        <v>960</v>
+      <c r="A59" s="10" t="s">
+        <v>959</v>
       </c>
       <c r="B59" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
       <c r="F59" s="51">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="G59" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>573</v>
@@ -7256,34 +7245,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="24">
-      <c r="A60" s="122" t="s">
-        <v>962</v>
-      </c>
-      <c r="B60" s="18" t="s">
+    <row r="60" spans="1:16">
+      <c r="A60" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="B60" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
-      <c r="F60" s="97">
-        <v>-8</v>
+      <c r="F60" s="51">
+        <v>7.2</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>903</v>
+        <v>15</v>
+      </c>
+      <c r="H60" s="17" t="s">
+        <v>960</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J60" s="17"/>
-      <c r="K60" s="26" t="s">
-        <v>963</v>
-      </c>
+      <c r="K60" s="26"/>
       <c r="L60" s="91"/>
       <c r="M60" s="66" t="s">
         <v>855</v>
@@ -7299,19 +7286,19 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="24">
-      <c r="A61" s="122" t="s">
-        <v>962</v>
+      <c r="A61" s="10" t="s">
+        <v>961</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="97">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="G61" s="17" t="s">
         <v>104</v>
@@ -7324,7 +7311,7 @@
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="26" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="L61" s="91"/>
       <c r="M61" s="66" t="s">
@@ -7340,31 +7327,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
-      <c r="A62" s="122" t="s">
-        <v>964</v>
+    <row r="62" spans="1:16" ht="24">
+      <c r="A62" s="10" t="s">
+        <v>961</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
-      <c r="F62" s="98">
-        <v>-5.4</v>
+      <c r="F62" s="97">
+        <v>-5</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="8"/>
+        <v>104</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>903</v>
+      </c>
       <c r="I62" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="26" t="s">
-        <v>905</v>
+        <v>962</v>
       </c>
       <c r="L62" s="91"/>
       <c r="M62" s="66" t="s">
@@ -7381,19 +7370,19 @@
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="122" t="s">
-        <v>964</v>
+      <c r="A63" s="10" t="s">
+        <v>963</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="98">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="G63" s="17" t="s">
         <v>15</v>
@@ -7403,7 +7392,9 @@
         <v>573</v>
       </c>
       <c r="J63" s="17"/>
-      <c r="K63" s="26"/>
+      <c r="K63" s="26" t="s">
+        <v>905</v>
+      </c>
       <c r="L63" s="91"/>
       <c r="M63" s="66" t="s">
         <v>855</v>
@@ -7419,26 +7410,24 @@
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="122" t="s">
-        <v>965</v>
-      </c>
-      <c r="B64" s="17" t="s">
+      <c r="A64" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="B64" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
-      <c r="F64" s="51">
-        <v>5</v>
+      <c r="F64" s="98">
+        <v>0</v>
       </c>
       <c r="G64" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H64" s="17" t="s">
-        <v>961</v>
-      </c>
+      <c r="H64" s="8"/>
       <c r="I64" s="17" t="s">
         <v>573</v>
       </c>
@@ -7459,25 +7448,25 @@
       </c>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" s="122" t="s">
-        <v>965</v>
+      <c r="A65" s="10" t="s">
+        <v>964</v>
       </c>
       <c r="B65" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="51">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G65" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I65" s="17" t="s">
         <v>573</v>
@@ -7498,33 +7487,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="24">
-      <c r="A66" s="122" t="s">
-        <v>966</v>
-      </c>
-      <c r="B66" s="18" t="s">
+    <row r="66" spans="1:16">
+      <c r="A66" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="B66" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="51">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>853</v>
+        <v>15</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J66" s="17" t="s">
-        <v>968</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="J66" s="17"/>
       <c r="K66" s="26"/>
       <c r="L66" s="91"/>
       <c r="M66" s="66" t="s">
@@ -7541,14 +7528,14 @@
       </c>
     </row>
     <row r="67" spans="1:16" ht="24">
-      <c r="A67" s="122" t="s">
-        <v>966</v>
+      <c r="A67" s="10" t="s">
+        <v>965</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
@@ -7559,13 +7546,13 @@
         <v>853</v>
       </c>
       <c r="H67" s="17" t="s">
+        <v>966</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J67" s="17" t="s">
         <v>967</v>
-      </c>
-      <c r="I67" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J67" s="17" t="s">
-        <v>968</v>
       </c>
       <c r="K67" s="26"/>
       <c r="L67" s="91"/>
@@ -7582,31 +7569,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="122" t="s">
-        <v>969</v>
+    <row r="68" spans="1:16" ht="24">
+      <c r="A68" s="10" t="s">
+        <v>965</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="51">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>104</v>
+        <v>853</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>908</v>
+        <v>966</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J68" s="17"/>
+        <v>49</v>
+      </c>
+      <c r="J68" s="17" t="s">
+        <v>967</v>
+      </c>
       <c r="K68" s="26"/>
       <c r="L68" s="91"/>
       <c r="M68" s="66" t="s">
@@ -7623,19 +7612,19 @@
       </c>
     </row>
     <row r="69" spans="1:16">
-      <c r="A69" s="122" t="s">
-        <v>969</v>
+      <c r="A69" s="10" t="s">
+        <v>968</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>852</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="51">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G69" s="17" t="s">
         <v>104</v>
@@ -7663,24 +7652,28 @@
       </c>
     </row>
     <row r="70" spans="1:16">
-      <c r="A70" s="122" t="s">
-        <v>970</v>
-      </c>
-      <c r="B70" s="18"/>
-      <c r="C70" s="51" t="s">
-        <v>46</v>
+      <c r="A70" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>385</v>
       </c>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
-      <c r="F70" s="51" t="s">
-        <v>971</v>
+      <c r="F70" s="51">
+        <v>1</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>972</v>
-      </c>
-      <c r="H70" s="17"/>
+        <v>104</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>908</v>
+      </c>
       <c r="I70" s="17" t="s">
-        <v>49</v>
+        <v>573</v>
       </c>
       <c r="J70" s="17"/>
       <c r="K70" s="26"/>
@@ -7698,540 +7691,534 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="24">
-      <c r="A71" s="123" t="s">
+    <row r="71" spans="1:16">
+      <c r="A71" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="51" t="s">
+        <v>970</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J71" s="17"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="91"/>
+      <c r="M71" s="66" t="s">
+        <v>855</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O71" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P71" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="24">
+      <c r="A72" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C72" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D72" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="E72" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F72" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G72" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="H71" s="29" t="s">
+      <c r="H72" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K72" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L71" s="29" t="s">
+      <c r="L72" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="M71" s="9" t="s">
+      <c r="M72" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N71" s="9" t="s">
+      <c r="N72" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="O71" s="9" t="s">
+      <c r="O72" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P71" s="9" t="s">
+      <c r="P72" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="25.5" customHeight="1">
-      <c r="A72" s="122" t="s">
-        <v>973</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="101" t="s">
-        <v>974</v>
-      </c>
-      <c r="G72" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="17" t="s">
-        <v>975</v>
-      </c>
-      <c r="I72" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J72" s="17" t="s">
-        <v>976</v>
-      </c>
-      <c r="K72" s="26" t="s">
-        <v>977</v>
-      </c>
-      <c r="L72" s="91"/>
-      <c r="M72" s="66" t="s">
-        <v>978</v>
-      </c>
-      <c r="N72" s="5" t="s">
-        <v>979</v>
-      </c>
-      <c r="O72" s="66" t="s">
-        <v>980</v>
-      </c>
-      <c r="P72" s="66">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="24">
-      <c r="A73" s="122" t="s">
-        <v>973</v>
+    <row r="73" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A73" s="10" t="s">
+        <v>972</v>
       </c>
       <c r="B73" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="101" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="G73" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J73" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="K73" s="26" t="s">
         <v>976</v>
-      </c>
-      <c r="K73" s="26" t="s">
-        <v>977</v>
       </c>
       <c r="L73" s="91"/>
       <c r="M73" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N73" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N73" s="5" t="s">
+      <c r="O73" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O73" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P73" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="24">
-      <c r="A74" s="122" t="s">
-        <v>982</v>
+      <c r="A74" s="10" t="s">
+        <v>972</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>200</v>
+        <v>852</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
-      <c r="F74" s="17" t="s">
-        <v>983</v>
-      </c>
-      <c r="G74" s="99" t="s">
-        <v>984</v>
+      <c r="F74" s="101" t="s">
+        <v>980</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J74" s="17"/>
+        <v>573</v>
+      </c>
+      <c r="J74" s="17" t="s">
+        <v>975</v>
+      </c>
       <c r="K74" s="26" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="L74" s="91"/>
       <c r="M74" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N74" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N74" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="O74" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P74" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
-      <c r="A75" s="122" t="s">
-        <v>982</v>
+    <row r="75" spans="1:16" ht="24">
+      <c r="A75" s="10" t="s">
+        <v>981</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>200</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
-      <c r="F75" s="102">
-        <v>120</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>104</v>
+      <c r="F75" s="17" t="s">
+        <v>982</v>
+      </c>
+      <c r="G75" s="99" t="s">
+        <v>983</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="I75" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="17"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="56"/>
+      <c r="K75" s="26" t="s">
+        <v>985</v>
+      </c>
+      <c r="L75" s="91"/>
       <c r="M75" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O75" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P75" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:16">
-      <c r="A76" s="122" t="s">
-        <v>988</v>
+      <c r="A76" s="10" t="s">
+        <v>981</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>200</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
-      <c r="F76" s="51" t="s">
-        <v>989</v>
+      <c r="F76" s="102">
+        <v>120</v>
       </c>
       <c r="G76" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="91"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="56"/>
       <c r="M76" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N76" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="O76" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P76" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="30" customHeight="1">
-      <c r="A77" s="122" t="s">
-        <v>988</v>
+    <row r="77" spans="1:16">
+      <c r="A77" s="10" t="s">
+        <v>987</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>200</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
-      <c r="F77" s="17" t="s">
-        <v>991</v>
-      </c>
-      <c r="G77" s="99" t="s">
-        <v>984</v>
+      <c r="F77" s="51" t="s">
+        <v>988</v>
+      </c>
+      <c r="G77" s="51" t="s">
+        <v>104</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="I77" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J77" s="17"/>
-      <c r="K77" s="26" t="s">
-        <v>992</v>
-      </c>
+      <c r="K77" s="17"/>
       <c r="L77" s="91"/>
       <c r="M77" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O77" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P77" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="24">
-      <c r="A78" s="122" t="s">
-        <v>993</v>
+    <row r="78" spans="1:16" ht="30" customHeight="1">
+      <c r="A78" s="10" t="s">
+        <v>987</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>852</v>
+        <v>200</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
-      <c r="F78" s="51">
-        <v>1028.2</v>
-      </c>
-      <c r="G78" s="17" t="s">
-        <v>15</v>
+      <c r="F78" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="G78" s="99" t="s">
+        <v>983</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J78" s="17" t="s">
-        <v>976</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J78" s="17"/>
       <c r="K78" s="26" t="s">
-        <v>994</v>
-      </c>
-      <c r="L78" s="56"/>
+        <v>991</v>
+      </c>
+      <c r="L78" s="91"/>
       <c r="M78" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N78" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O78" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O78" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P78" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="24">
-      <c r="A79" s="122" t="s">
-        <v>993</v>
+      <c r="A79" s="10" t="s">
+        <v>992</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="51">
-        <v>1025.7</v>
+        <v>1028.2</v>
       </c>
       <c r="G79" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I79" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K79" s="26" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L79" s="56"/>
       <c r="M79" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N79" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N79" s="5" t="s">
+      <c r="O79" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O79" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P79" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="24">
-      <c r="A80" s="122" t="s">
-        <v>995</v>
+      <c r="A80" s="10" t="s">
+        <v>992</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="51">
-        <v>1028.2</v>
+        <v>1025.7</v>
       </c>
       <c r="G80" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K80" s="26" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L80" s="56"/>
       <c r="M80" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N80" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="O80" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O80" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P80" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="24">
-      <c r="A81" s="122" t="s">
-        <v>995</v>
+      <c r="A81" s="10" t="s">
+        <v>994</v>
       </c>
       <c r="B81" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="51">
-        <v>1025.7</v>
+        <v>1028.2</v>
       </c>
       <c r="G81" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I81" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L81" s="56"/>
       <c r="M81" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N81" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="O81" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O81" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P81" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
-      <c r="A82" s="122" t="s">
-        <v>996</v>
-      </c>
-      <c r="B82" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="C82" s="51" t="s">
-        <v>997</v>
-      </c>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="103">
-        <v>0.03</v>
-      </c>
-      <c r="G82" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>888</v>
+    <row r="82" spans="1:16" ht="24">
+      <c r="A82" s="10" t="s">
+        <v>994</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="51">
+        <v>1025.7</v>
+      </c>
+      <c r="G82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>960</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J82" s="17"/>
-      <c r="K82" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="L82" s="104"/>
+        <v>573</v>
+      </c>
+      <c r="J82" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="K82" s="26" t="s">
+        <v>993</v>
+      </c>
+      <c r="L82" s="56"/>
       <c r="M82" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N82" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N82" s="5" t="s">
-        <v>860</v>
-      </c>
       <c r="O82" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P82" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:16">
-      <c r="A83" s="122" t="s">
+      <c r="A83" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C83" s="51" t="s">
         <v>996</v>
-      </c>
-      <c r="B83" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="C83" s="51" t="s">
-        <v>999</v>
       </c>
       <c r="D83" s="51"/>
       <c r="E83" s="51"/>
-      <c r="F83" s="5">
-        <v>3.6999999999999998E-2</v>
+      <c r="F83" s="103">
+        <v>0.03</v>
       </c>
       <c r="G83" s="51" t="s">
         <v>104</v>
@@ -8244,254 +8231,254 @@
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="5" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="L83" s="104"/>
       <c r="M83" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>860</v>
       </c>
       <c r="O83" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P83" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="24">
-      <c r="A84" s="122" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="17" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G84" s="17" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H84" s="17" t="s">
-        <v>1004</v>
+    <row r="84" spans="1:16">
+      <c r="A84" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C84" s="51" t="s">
+        <v>998</v>
+      </c>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="G84" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J84" s="17" t="s">
-        <v>976</v>
-      </c>
-      <c r="K84" s="26" t="s">
-        <v>1005</v>
-      </c>
-      <c r="L84" s="91"/>
+        <v>49</v>
+      </c>
+      <c r="J84" s="17"/>
+      <c r="K84" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="L84" s="104"/>
       <c r="M84" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N84" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="O84" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O84" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P84" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="24">
-      <c r="A85" s="122" t="s">
-        <v>1001</v>
+      <c r="A85" s="10" t="s">
+        <v>1000</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="17" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G85" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H85" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="H85" s="17" t="s">
-        <v>1004</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="L85" s="91"/>
       <c r="M85" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N85" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N85" s="5" t="s">
+      <c r="O85" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O85" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P85" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="24">
-      <c r="A86" s="122" t="s">
-        <v>1007</v>
+      <c r="A86" s="10" t="s">
+        <v>1000</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G86" s="17" t="s">
         <v>1002</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="H86" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>1004</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="L86" s="91"/>
       <c r="M86" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N86" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N86" s="5" t="s">
+      <c r="O86" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O86" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P86" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="24">
-      <c r="A87" s="122" t="s">
-        <v>1007</v>
+      <c r="A87" s="10" t="s">
+        <v>1006</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="17" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G87" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H87" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>1004</v>
       </c>
       <c r="I87" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K87" s="26" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L87" s="91"/>
       <c r="M87" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N87" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N87" s="5" t="s">
+      <c r="O87" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O87" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P87" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="24">
-      <c r="A88" s="122" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="C88" s="51" t="s">
-        <v>997</v>
-      </c>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="5">
-        <v>1.26E-2</v>
-      </c>
-      <c r="G88" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>888</v>
+      <c r="A88" s="10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H88" s="17" t="s">
+        <v>1003</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17" t="s">
-        <v>1010</v>
+        <v>573</v>
+      </c>
+      <c r="J88" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="K88" s="26" t="s">
+        <v>1007</v>
       </c>
       <c r="L88" s="91"/>
       <c r="M88" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N88" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N88" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="O88" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P88" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="24">
-      <c r="A89" s="122" t="s">
-        <v>1009</v>
+      <c r="A89" s="10" t="s">
+        <v>1008</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D89" s="51"/>
       <c r="E89" s="51"/>
       <c r="F89" s="5">
-        <v>1.5800000000000002E-2</v>
+        <v>1.26E-2</v>
       </c>
       <c r="G89" s="51" t="s">
         <v>104</v>
@@ -8504,149 +8491,151 @@
       </c>
       <c r="J89" s="17"/>
       <c r="K89" s="17" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="L89" s="91"/>
       <c r="M89" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O89" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P89" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="24">
-      <c r="A90" s="122" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B90" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D90" s="20"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="17" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G90" s="17" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H90" s="17" t="s">
-        <v>1004</v>
+      <c r="A90" s="10" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C90" s="51" t="s">
+        <v>998</v>
+      </c>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="5">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="G90" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J90" s="17" t="s">
-        <v>976</v>
-      </c>
-      <c r="K90" s="26"/>
+        <v>49</v>
+      </c>
+      <c r="J90" s="17"/>
+      <c r="K90" s="17" t="s">
+        <v>1010</v>
+      </c>
       <c r="L90" s="91"/>
       <c r="M90" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N90" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O90" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O90" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P90" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="24">
-      <c r="A91" s="122" t="s">
-        <v>1012</v>
+      <c r="A91" s="10" t="s">
+        <v>1011</v>
       </c>
       <c r="B91" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="17" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G91" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H91" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="H91" s="17" t="s">
-        <v>1004</v>
       </c>
       <c r="I91" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K91" s="26"/>
       <c r="L91" s="91"/>
       <c r="M91" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N91" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N91" s="5" t="s">
+      <c r="O91" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O91" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P91" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="36">
-      <c r="A92" s="122" t="s">
-        <v>1013</v>
+    <row r="92" spans="1:16" ht="24">
+      <c r="A92" s="10" t="s">
+        <v>1011</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="C92" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="105" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G92" s="99" t="s">
-        <v>1015</v>
+        <v>852</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>1002</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J92" s="17"/>
+        <v>573</v>
+      </c>
+      <c r="J92" s="17" t="s">
+        <v>975</v>
+      </c>
       <c r="K92" s="26"/>
       <c r="L92" s="91"/>
       <c r="M92" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N92" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N92" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="O92" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P92" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="39" customHeight="1">
-      <c r="A93" s="122" t="s">
-        <v>1017</v>
+    <row r="93" spans="1:16" ht="36">
+      <c r="A93" s="10" t="s">
+        <v>1012</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>200</v>
@@ -8656,89 +8645,87 @@
       </c>
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
-      <c r="F93" s="17" t="s">
-        <v>1018</v>
+      <c r="F93" s="105" t="s">
+        <v>1013</v>
       </c>
       <c r="G93" s="99" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="I93" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J93" s="17"/>
+      <c r="K93" s="26"/>
       <c r="L93" s="91"/>
       <c r="M93" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="O93" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P93" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="24">
-      <c r="A94" s="122" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B94" s="18" t="s">
-        <v>932</v>
+    <row r="94" spans="1:16" ht="39" customHeight="1">
+      <c r="A94" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B94" s="17" t="s">
+        <v>200</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>997</v>
+        <v>46</v>
       </c>
       <c r="D94" s="51"/>
       <c r="E94" s="51"/>
-      <c r="F94" s="5">
-        <v>1.54E-2</v>
-      </c>
-      <c r="G94" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>888</v>
+      <c r="F94" s="17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G94" s="99" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>1019</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J94" s="17"/>
-      <c r="K94" s="17" t="s">
-        <v>1010</v>
-      </c>
       <c r="L94" s="91"/>
       <c r="M94" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O94" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P94" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="24">
-      <c r="A95" s="122" t="s">
-        <v>1021</v>
+      <c r="A95" s="10" t="s">
+        <v>1020</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D95" s="51"/>
       <c r="E95" s="51"/>
       <c r="F95" s="5">
-        <v>1.9300000000000001E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="G95" s="51" t="s">
         <v>104</v>
@@ -8751,149 +8738,151 @@
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="L95" s="91"/>
       <c r="M95" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O95" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P95" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="24">
-      <c r="A96" s="122" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B96" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D96" s="20"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="17" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G96" s="17" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H96" s="17" t="s">
-        <v>1004</v>
+      <c r="A96" s="10" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C96" s="51" t="s">
+        <v>998</v>
+      </c>
+      <c r="D96" s="51"/>
+      <c r="E96" s="51"/>
+      <c r="F96" s="5">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="G96" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="J96" s="17" t="s">
-        <v>976</v>
-      </c>
-      <c r="K96" s="26"/>
+        <v>49</v>
+      </c>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17" t="s">
+        <v>1010</v>
+      </c>
       <c r="L96" s="91"/>
       <c r="M96" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N96" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O96" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O96" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P96" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="24">
-      <c r="A97" s="122" t="s">
-        <v>1022</v>
+      <c r="A97" s="10" t="s">
+        <v>1021</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>852</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="17" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G97" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H97" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="H97" s="17" t="s">
-        <v>1004</v>
       </c>
       <c r="I97" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K97" s="26"/>
       <c r="L97" s="91"/>
       <c r="M97" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N97" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N97" s="5" t="s">
+      <c r="O97" s="66" t="s">
         <v>979</v>
-      </c>
-      <c r="O97" s="66" t="s">
-        <v>980</v>
       </c>
       <c r="P97" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="36">
-      <c r="A98" s="122" t="s">
-        <v>1023</v>
+    <row r="98" spans="1:16" ht="24">
+      <c r="A98" s="10" t="s">
+        <v>1021</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="C98" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="105" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G98" s="99" t="s">
-        <v>1015</v>
+        <v>852</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D98" s="20"/>
+      <c r="E98" s="20"/>
+      <c r="F98" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>1002</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J98" s="17"/>
+        <v>573</v>
+      </c>
+      <c r="J98" s="17" t="s">
+        <v>975</v>
+      </c>
       <c r="K98" s="26"/>
       <c r="L98" s="91"/>
       <c r="M98" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N98" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="N98" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="O98" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P98" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="36.75" customHeight="1">
-      <c r="A99" s="122" t="s">
-        <v>1024</v>
+    <row r="99" spans="1:16" ht="36">
+      <c r="A99" s="10" t="s">
+        <v>1022</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>200</v>
@@ -8903,14 +8892,14 @@
       </c>
       <c r="D99" s="51"/>
       <c r="E99" s="51"/>
-      <c r="F99" s="17" t="s">
-        <v>1018</v>
+      <c r="F99" s="105" t="s">
+        <v>1013</v>
       </c>
       <c r="G99" s="99" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>49</v>
@@ -8919,105 +8908,103 @@
       <c r="K99" s="26"/>
       <c r="L99" s="91"/>
       <c r="M99" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N99" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="O99" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P99" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
-      <c r="A100" s="122" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B100" s="18" t="s">
-        <v>932</v>
+    <row r="100" spans="1:16" ht="36.75" customHeight="1">
+      <c r="A100" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>200</v>
       </c>
       <c r="C100" s="51" t="s">
-        <v>862</v>
+        <v>46</v>
       </c>
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
-      <c r="F100" s="106">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="G100" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>888</v>
+      <c r="F100" s="17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G100" s="99" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H100" s="17" t="s">
+        <v>1019</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J100" s="17"/>
-      <c r="K100" s="17" t="s">
-        <v>1026</v>
-      </c>
+      <c r="K100" s="26"/>
       <c r="L100" s="91"/>
       <c r="M100" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>860</v>
+        <v>101</v>
       </c>
       <c r="O100" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P100" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" s="122" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B101" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="17" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G101" s="99" t="s">
+      <c r="A101" s="10" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C101" s="51" t="s">
+        <v>862</v>
+      </c>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="106">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G101" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="H101" s="17" t="s">
-        <v>1029</v>
+      <c r="H101" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="I101" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J101" s="17"/>
-      <c r="K101" s="26" t="s">
-        <v>1030</v>
+      <c r="K101" s="17" t="s">
+        <v>1025</v>
       </c>
       <c r="L101" s="91"/>
       <c r="M101" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>122</v>
+        <v>860</v>
       </c>
       <c r="O101" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P101" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" s="122" t="s">
-        <v>1031</v>
+      <c r="A102" s="10" t="s">
+        <v>1026</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>200</v>
@@ -9027,123 +9014,123 @@
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
-      <c r="F102" s="51" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G102" s="51" t="s">
+      <c r="F102" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G102" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J102" s="17"/>
       <c r="K102" s="26" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L102" s="91"/>
       <c r="M102" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N102" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="O102" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P102" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" s="122" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B103" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="C103" s="51" t="s">
-        <v>862</v>
-      </c>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="94">
-        <v>1.1000000000000001E-3</v>
+      <c r="A103" s="10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="51" t="s">
+        <v>1031</v>
       </c>
       <c r="G103" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="H103" s="8" t="s">
-        <v>888</v>
+      <c r="H103" s="17" t="s">
+        <v>1028</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="17"/>
-      <c r="K103" s="17" t="s">
-        <v>1034</v>
+      <c r="K103" s="26" t="s">
+        <v>1029</v>
       </c>
       <c r="L103" s="91"/>
       <c r="M103" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>860</v>
+        <v>101</v>
       </c>
       <c r="O103" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P103" s="66">
         <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:16">
-      <c r="A104" s="122" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="C104" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="17" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G104" s="99" t="s">
+      <c r="A104" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C104" s="51" t="s">
+        <v>862</v>
+      </c>
+      <c r="D104" s="51"/>
+      <c r="E104" s="51"/>
+      <c r="F104" s="94">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="G104" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="H104" s="17" t="s">
-        <v>1029</v>
+      <c r="H104" s="8" t="s">
+        <v>888</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J104" s="17"/>
-      <c r="K104" s="26" t="s">
-        <v>1030</v>
+      <c r="K104" s="17" t="s">
+        <v>1033</v>
       </c>
       <c r="L104" s="91"/>
       <c r="M104" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>122</v>
+        <v>860</v>
       </c>
       <c r="O104" s="66" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P104" s="66">
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="14.25" customHeight="1">
-      <c r="A105" s="122" t="s">
-        <v>1036</v>
+    <row r="105" spans="1:16">
+      <c r="A105" s="10" t="s">
+        <v>1034</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>200</v>
@@ -9153,33 +9140,75 @@
       </c>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
-      <c r="F105" s="51" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G105" s="51" t="s">
+      <c r="F105" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G105" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I105" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J105" s="17"/>
       <c r="K105" s="26" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L105" s="91"/>
       <c r="M105" s="66" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N105" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="O105" s="66" t="s">
+        <v>979</v>
+      </c>
+      <c r="P105" s="66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="14.25" customHeight="1">
+      <c r="A106" s="10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C106" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="51" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G106" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H106" s="17" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J106" s="17"/>
+      <c r="K106" s="26" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L106" s="91"/>
+      <c r="M106" s="66" t="s">
+        <v>977</v>
+      </c>
+      <c r="N106" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="O105" s="66" t="s">
-        <v>980</v>
-      </c>
-      <c r="P105" s="66">
+      <c r="O106" s="66" t="s">
+        <v>979</v>
+      </c>
+      <c r="P106" s="66">
         <v>4</v>
       </c>
     </row>
@@ -9243,7 +9272,7 @@
         <v>38</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>40</v>
@@ -9260,7 +9289,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="67" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>14</v>
@@ -9274,7 +9303,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
@@ -9286,7 +9315,7 @@
         <v>200</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>71</v>
@@ -9298,7 +9327,7 @@
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="23.25" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>17</v>
@@ -9313,23 +9342,23 @@
         <v>8751.6116205773851</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K3" s="35" t="s">
         <v>1043</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>1044</v>
       </c>
       <c r="L3" s="8">
         <v>7363</v>
       </c>
       <c r="M3" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>57</v>
@@ -9341,7 +9370,7 @@
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1">
       <c r="A4" s="10" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>17</v>
@@ -9356,7 +9385,7 @@
         <v>34084.065120622952</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="14" t="s">
@@ -9364,13 +9393,13 @@
       </c>
       <c r="J4" s="87"/>
       <c r="K4" s="12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>1047</v>
-      </c>
       <c r="M4" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>57</v>
@@ -9382,7 +9411,7 @@
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1" ht="24">
       <c r="A5" s="10" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="8" t="s">
@@ -9391,26 +9420,26 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>1050</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>1051</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="109"/>
       <c r="K5" s="8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="M5" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>71</v>
@@ -9424,7 +9453,7 @@
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1">
       <c r="A6" s="10" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>17</v>
@@ -9439,21 +9468,21 @@
         <v>25271.303751033935</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
         <v>16700</v>
       </c>
       <c r="M6" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>57</v>
@@ -9465,7 +9494,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>14</v>
@@ -9479,7 +9508,7 @@
         <v>250</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H7" s="59"/>
       <c r="I7" s="14" t="s">
@@ -9491,7 +9520,7 @@
         <v>250</v>
       </c>
       <c r="M7" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>57</v>
@@ -9503,7 +9532,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="67" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="8" t="s">
@@ -9515,10 +9544,10 @@
         <v>0.85</v>
       </c>
       <c r="G8" s="111" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H8" s="111" t="s">
         <v>1057</v>
-      </c>
-      <c r="H8" s="111" t="s">
-        <v>1058</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>49</v>
@@ -9529,7 +9558,7 @@
         <v>0.85</v>
       </c>
       <c r="M8" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>51</v>
@@ -9543,10 +9572,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="120" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>46</v>
@@ -9557,7 +9586,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="111" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H9" s="111"/>
       <c r="I9" s="14" t="s">
@@ -9569,7 +9598,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>71</v>
@@ -9581,7 +9610,7 @@
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A10" s="28" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
@@ -9614,7 +9643,7 @@
         <v>38</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>40</v>
@@ -9631,7 +9660,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="67" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>14</v>
@@ -9648,7 +9677,7 @@
         <v>104</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>49</v>
@@ -9659,7 +9688,7 @@
         <v>250</v>
       </c>
       <c r="M11" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>57</v>
@@ -9673,7 +9702,7 @@
     </row>
     <row r="12" spans="1:16" s="1" customFormat="1">
       <c r="A12" s="67" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>14</v>
@@ -9690,7 +9719,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>49</v>
@@ -9701,7 +9730,7 @@
         <v>300</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>57</v>
@@ -9715,7 +9744,7 @@
     </row>
     <row r="13" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A13" s="28" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -9748,7 +9777,7 @@
         <v>38</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>40</v>
@@ -9765,10 +9794,10 @@
     </row>
     <row r="14" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A14" s="30" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>46</v>
@@ -9787,32 +9816,32 @@
         <v>273</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L14" s="5">
         <v>3140</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A15" s="30" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
@@ -9827,23 +9856,23 @@
         <v>2119.3689320388348</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I15" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L15" s="5">
         <v>3140</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>71</v>
@@ -9855,7 +9884,7 @@
     </row>
     <row r="16" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A16" s="30" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
@@ -9870,23 +9899,23 @@
         <v>266.88349514563106</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I16" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L16" s="5">
         <v>3140</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>71</v>
@@ -9898,10 +9927,10 @@
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A17" s="30" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>46</v>
@@ -9920,32 +9949,32 @@
         <v>273</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="L17" s="5">
         <v>2680</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A18" s="30" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>17</v>
@@ -9960,23 +9989,23 @@
         <v>807.69230769230774</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="L18" s="5">
         <v>2680</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>71</v>
@@ -9988,7 +10017,7 @@
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A19" s="30" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
@@ -10003,23 +10032,23 @@
         <v>2794.6153846153843</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="L19" s="5">
         <v>2680</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>71</v>
@@ -10031,10 +10060,10 @@
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A20" s="30" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>46</v>
@@ -10053,32 +10082,32 @@
         <v>273</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L20" s="5">
         <v>1020</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A21" s="30" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>17</v>
@@ -10093,23 +10122,23 @@
         <v>234.9</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I21" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L21" s="5">
         <v>1020</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>71</v>
@@ -10121,7 +10150,7 @@
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A22" s="30" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>17</v>
@@ -10136,23 +10165,23 @@
         <v>899</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L22" s="5">
         <v>1020</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>71</v>
@@ -10164,10 +10193,10 @@
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A23" s="30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>46</v>
@@ -10186,32 +10215,32 @@
         <v>273</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I23" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L23" s="5">
         <v>730</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N23" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A24" s="30" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>17</v>
@@ -10226,23 +10255,23 @@
         <v>287.63999999999993</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L24" s="5">
         <v>730</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>71</v>
@@ -10254,7 +10283,7 @@
     </row>
     <row r="25" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A25" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>17</v>
@@ -10269,23 +10298,23 @@
         <v>484.5</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L25" s="5">
         <v>730</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>71</v>
@@ -10297,10 +10326,10 @@
     </row>
     <row r="26" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A26" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>46</v>
@@ -10319,32 +10348,32 @@
         <v>273</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L26" s="5">
         <v>110</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A27" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>17</v>
@@ -10359,23 +10388,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L27" s="5">
         <v>110</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N27" s="5" t="s">
         <v>71</v>
@@ -10387,7 +10416,7 @@
     </row>
     <row r="28" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A28" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>17</v>
@@ -10402,23 +10431,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L28" s="5">
         <v>110</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N28" s="5" t="s">
         <v>71</v>
@@ -10430,10 +10459,10 @@
     </row>
     <row r="29" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A29" s="30" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>46</v>
@@ -10452,32 +10481,32 @@
         <v>273</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L29" s="5">
         <v>110</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A30" s="30" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>17</v>
@@ -10492,23 +10521,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I30" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L30" s="5">
         <v>110</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>71</v>
@@ -10520,7 +10549,7 @@
     </row>
     <row r="31" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A31" s="30" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>17</v>
@@ -10535,23 +10564,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L31" s="5">
         <v>110</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>71</v>
@@ -10563,10 +10592,10 @@
     </row>
     <row r="32" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A32" s="30" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>46</v>
@@ -10585,32 +10614,32 @@
         <v>273</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L32" s="5">
         <v>1030</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A33" s="30" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>17</v>
@@ -10625,23 +10654,23 @@
         <v>289.8</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L33" s="5">
         <v>1030</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>71</v>
@@ -10653,7 +10682,7 @@
     </row>
     <row r="34" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A34" s="30" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>17</v>
@@ -10668,23 +10697,23 @@
         <v>1031.3999999999999</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L34" s="5">
         <v>1030</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>71</v>
@@ -10696,10 +10725,10 @@
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A35" s="30" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>46</v>
@@ -10720,32 +10749,32 @@
         <v>273</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L35" s="5">
         <v>160</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O35" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A36" s="30" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>17</v>
@@ -10760,23 +10789,23 @@
         <v>100.8</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L36" s="5">
         <v>160</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>71</v>
@@ -10788,7 +10817,7 @@
     </row>
     <row r="37" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A37" s="30" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>17</v>
@@ -10803,23 +10832,23 @@
         <v>133.80000000000001</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L37" s="5">
         <v>160</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N37" s="5" t="s">
         <v>71</v>
@@ -10831,10 +10860,10 @@
     </row>
     <row r="38" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A38" s="30" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>46</v>
@@ -10855,32 +10884,32 @@
         <v>273</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L38" s="5">
         <v>160</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A39" s="30" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>17</v>
@@ -10895,23 +10924,23 @@
         <v>67.2</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L39" s="5">
         <v>160</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N39" s="5" t="s">
         <v>71</v>
@@ -10923,7 +10952,7 @@
     </row>
     <row r="40" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A40" s="30" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>17</v>
@@ -10938,23 +10967,23 @@
         <v>89.2</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L40" s="5">
         <v>160</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N40" s="5" t="s">
         <v>71</v>
@@ -10966,10 +10995,10 @@
     </row>
     <row r="41" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A41" s="30" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>46</v>
@@ -10988,32 +11017,32 @@
         <v>273</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L41" s="5">
         <v>13090</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A42" s="30" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>17</v>
@@ -11028,23 +11057,23 @@
         <v>3421.9999999999995</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I42" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L42" s="5">
         <v>13090</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>71</v>
@@ -11056,7 +11085,7 @@
     </row>
     <row r="43" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A43" s="30" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>17</v>
@@ -11071,23 +11100,23 @@
         <v>18270</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L43" s="5">
         <v>13090</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>71</v>
@@ -11099,7 +11128,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="30" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>89</v>
@@ -11110,10 +11139,10 @@
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="52" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G44" s="17" t="s">
         <v>1101</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>1102</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="26" t="s">
@@ -11123,7 +11152,7 @@
       <c r="K44" s="33"/>
       <c r="L44" s="21"/>
       <c r="M44" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>71</v>
@@ -11135,7 +11164,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="30" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>89</v>
@@ -11146,7 +11175,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="113" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G45" s="17" t="s">
         <v>548</v>
@@ -11157,11 +11186,11 @@
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="33" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>71</v>
@@ -11173,10 +11202,10 @@
     </row>
     <row r="46" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A46" s="30" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>46</v>
@@ -11195,32 +11224,32 @@
         <v>273</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L46" s="5">
         <v>190</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A47" s="30" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>17</v>
@@ -11235,23 +11264,23 @@
         <v>105.60000000000001</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L47" s="5">
         <v>190</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>71</v>
@@ -11263,7 +11292,7 @@
     </row>
     <row r="48" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A48" s="30" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>17</v>
@@ -11278,23 +11307,23 @@
         <v>150.47999999999999</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I48" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L48" s="5">
         <v>190</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>71</v>
@@ -11306,10 +11335,10 @@
     </row>
     <row r="49" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A49" s="30" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>46</v>
@@ -11328,32 +11357,32 @@
         <v>273</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I49" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L49" s="5">
         <v>1550</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A50" s="30" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>17</v>
@@ -11368,23 +11397,23 @@
         <v>1200.9303808462425</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I50" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L50" s="5">
         <v>1550</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N50" s="5" t="s">
         <v>71</v>
@@ -11396,7 +11425,7 @@
     </row>
     <row r="51" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A51" s="30" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
@@ -11411,23 +11440,23 @@
         <v>914.844871272923</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I51" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L51" s="5">
         <v>1550</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N51" s="5" t="s">
         <v>71</v>
@@ -11439,10 +11468,10 @@
     </row>
     <row r="52" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A52" s="30" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>46</v>
@@ -11461,32 +11490,32 @@
         <v>273</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I52" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L52" s="5">
         <v>100</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A53" s="30" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
@@ -11501,23 +11530,23 @@
         <v>31.049999999999997</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I53" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L53" s="5">
         <v>100</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>71</v>
@@ -11529,7 +11558,7 @@
     </row>
     <row r="54" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A54" s="30" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>17</v>
@@ -11544,23 +11573,23 @@
         <v>86.85</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="L54" s="5">
         <v>100</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>71</v>
@@ -11572,7 +11601,7 @@
     </row>
     <row r="55" spans="1:16" ht="24">
       <c r="A55" s="28" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1</v>
@@ -11622,7 +11651,7 @@
     </row>
     <row r="56" spans="1:16" ht="24.75">
       <c r="A56" s="30" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>89</v>
@@ -11633,7 +11662,7 @@
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="18" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G56" s="18" t="s">
         <v>143</v>
@@ -11644,23 +11673,23 @@
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="114" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="30" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>89</v>
@@ -11681,22 +11710,22 @@
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="35" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="30" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>89</v>
@@ -11710,10 +11739,10 @@
         <v>25</v>
       </c>
       <c r="G58" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H58" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>49</v>
@@ -11721,22 +11750,22 @@
       <c r="J58" s="17"/>
       <c r="K58" s="19"/>
       <c r="L58" s="12" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="30" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>89</v>
@@ -11750,10 +11779,10 @@
         <v>1.2</v>
       </c>
       <c r="G59" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H59" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I59" s="18" t="s">
         <v>49</v>
@@ -11761,22 +11790,22 @@
       <c r="J59" s="17"/>
       <c r="K59" s="19"/>
       <c r="L59" s="8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" ht="24">
       <c r="A60" s="30" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>89</v>
@@ -11787,7 +11816,7 @@
       <c r="D60" s="115"/>
       <c r="E60" s="115"/>
       <c r="F60" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G60" s="115"/>
       <c r="H60" s="116"/>
@@ -11796,23 +11825,23 @@
       </c>
       <c r="J60" s="116"/>
       <c r="K60" s="116" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L60" s="8"/>
       <c r="M60" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="30" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>89</v>
@@ -11826,10 +11855,10 @@
         <v>116</v>
       </c>
       <c r="G61" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H61" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>49</v>
@@ -11838,19 +11867,19 @@
       <c r="K61" s="33"/>
       <c r="L61" s="14"/>
       <c r="M61" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" ht="36.75">
       <c r="A62" s="30" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B62" s="115"/>
       <c r="C62" s="116"/>
@@ -11864,26 +11893,26 @@
       </c>
       <c r="J62" s="116"/>
       <c r="K62" s="117" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="L62" s="14"/>
       <c r="M62" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N62" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="72.75">
       <c r="A63" s="30" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B63" s="17" t="s">
         <v>1131</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>1132</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -11891,36 +11920,36 @@
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G63" s="17" t="s">
         <v>1133</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="H63" s="17" t="s">
         <v>1134</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>1135</v>
       </c>
       <c r="I63" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="114" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N63" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="30" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>89</v>
@@ -11934,10 +11963,10 @@
         <v>5.9</v>
       </c>
       <c r="G64" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H64" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I64" s="18" t="s">
         <v>49</v>
@@ -11946,19 +11975,19 @@
       <c r="K64" s="33"/>
       <c r="L64" s="21"/>
       <c r="M64" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="30" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>89</v>
@@ -11978,26 +12007,26 @@
       </c>
       <c r="J65" s="26"/>
       <c r="K65" s="33" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N65" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" ht="24.75">
       <c r="A66" s="30" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>46</v>
@@ -12005,36 +12034,36 @@
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G66" s="17" t="s">
         <v>1141</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="H66" s="26" t="s">
         <v>1142</v>
-      </c>
-      <c r="H66" s="26" t="s">
-        <v>1143</v>
       </c>
       <c r="I66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="114" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N66" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" ht="48.75">
       <c r="A67" s="30" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>89</v>
@@ -12045,36 +12074,36 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G67" s="17" t="s">
         <v>1145</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="H67" s="26" t="s">
         <v>1146</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>1147</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="33" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="30" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B68" s="115"/>
       <c r="C68" s="116"/>
@@ -12088,26 +12117,26 @@
       </c>
       <c r="J68" s="116"/>
       <c r="K68" s="115" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="30" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>46</v>
@@ -12115,13 +12144,13 @@
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="26" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H69" s="26" t="s">
         <v>1152</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>1153</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>49</v>
@@ -12130,19 +12159,19 @@
       <c r="K69" s="26"/>
       <c r="L69" s="4"/>
       <c r="M69" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" ht="24">
       <c r="A70" s="30" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>89</v>
@@ -12153,7 +12182,7 @@
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
       <c r="F70" s="8" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G70" s="17"/>
       <c r="H70" s="8"/>
@@ -12162,23 +12191,23 @@
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="116" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N70" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>89</v>
@@ -12192,10 +12221,10 @@
         <v>4.5</v>
       </c>
       <c r="G71" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>1122</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>1123</v>
       </c>
       <c r="I71" s="18" t="s">
         <v>49</v>
@@ -12204,19 +12233,19 @@
       <c r="K71" s="33"/>
       <c r="L71" s="4"/>
       <c r="M71" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="30" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>89</v>
@@ -12230,10 +12259,10 @@
         <v>145</v>
       </c>
       <c r="G72" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H72" s="26" t="s">
         <v>1122</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>1123</v>
       </c>
       <c r="I72" s="18" t="s">
         <v>49</v>
@@ -12242,19 +12271,19 @@
       <c r="K72" s="33"/>
       <c r="L72" s="4"/>
       <c r="M72" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N72" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="30" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B73" s="36" t="s">
         <v>89</v>
@@ -12272,23 +12301,23 @@
       </c>
       <c r="J73" s="118"/>
       <c r="K73" s="114" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" ht="36">
       <c r="A74" s="30" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>66</v>
@@ -12310,23 +12339,23 @@
       </c>
       <c r="J74" s="119"/>
       <c r="K74" s="47" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N74" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" ht="24.75">
       <c r="A75" s="30" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>89</v>
@@ -12337,7 +12366,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="18" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G75" s="18"/>
       <c r="H75" s="18"/>
@@ -12346,23 +12375,23 @@
       </c>
       <c r="J75" s="18"/>
       <c r="K75" s="114" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="30" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>89</v>
@@ -12382,23 +12411,23 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="35" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="30" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>89</v>
@@ -12412,10 +12441,10 @@
         <v>16</v>
       </c>
       <c r="G77" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H77" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>49</v>
@@ -12424,19 +12453,19 @@
       <c r="K77" s="19"/>
       <c r="L77" s="4"/>
       <c r="M77" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O77" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="30" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>89</v>
@@ -12450,10 +12479,10 @@
         <v>1E-4</v>
       </c>
       <c r="G78" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H78" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>49</v>
@@ -12462,19 +12491,19 @@
       <c r="K78" s="19"/>
       <c r="L78" s="4"/>
       <c r="M78" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="30" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B79" s="115" t="s">
         <v>89</v>
@@ -12485,7 +12514,7 @@
       <c r="D79" s="115"/>
       <c r="E79" s="115"/>
       <c r="F79" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G79" s="115"/>
       <c r="H79" s="116"/>
@@ -12494,23 +12523,23 @@
       </c>
       <c r="J79" s="116"/>
       <c r="K79" s="116" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N79" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="30" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>89</v>
@@ -12524,10 +12553,10 @@
         <v>20</v>
       </c>
       <c r="G80" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H80" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I80" s="18" t="s">
         <v>49</v>
@@ -12536,19 +12565,19 @@
       <c r="K80" s="33"/>
       <c r="L80" s="4"/>
       <c r="M80" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N80" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" ht="36.75">
       <c r="A81" s="30" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>89</v>
@@ -12566,26 +12595,26 @@
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="114" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N81" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" ht="72.75">
       <c r="A82" s="30" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>46</v>
@@ -12593,36 +12622,36 @@
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G82" s="17" t="s">
         <v>1133</v>
       </c>
-      <c r="G82" s="17" t="s">
+      <c r="H82" s="17" t="s">
         <v>1134</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>1135</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="114" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N82" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="30" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>89</v>
@@ -12636,10 +12665,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H83" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>49</v>
@@ -12648,19 +12677,19 @@
       <c r="K83" s="33"/>
       <c r="L83" s="21"/>
       <c r="M83" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="30" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>89</v>
@@ -12680,26 +12709,26 @@
       </c>
       <c r="J84" s="26"/>
       <c r="K84" s="33" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" ht="24.75">
       <c r="A85" s="30" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>46</v>
@@ -12707,36 +12736,36 @@
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G85" s="17" t="s">
         <v>1141</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="H85" s="26" t="s">
         <v>1142</v>
-      </c>
-      <c r="H85" s="26" t="s">
-        <v>1143</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="114" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N85" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" ht="48.75">
       <c r="A86" s="30" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>89</v>
@@ -12747,36 +12776,36 @@
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G86" s="17" t="s">
         <v>1145</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="H86" s="26" t="s">
         <v>1146</v>
-      </c>
-      <c r="H86" s="26" t="s">
-        <v>1147</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="33" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N86" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="30" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>89</v>
@@ -12796,22 +12825,22 @@
       <c r="K87" s="26"/>
       <c r="L87" s="4"/>
       <c r="M87" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N87" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="30" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>46</v>
@@ -12819,13 +12848,13 @@
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="26" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H88" s="26" t="s">
         <v>1152</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H88" s="26" t="s">
-        <v>1153</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>49</v>
@@ -12834,19 +12863,19 @@
       <c r="K88" s="26"/>
       <c r="L88" s="4"/>
       <c r="M88" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="30" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>89</v>
@@ -12857,7 +12886,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="8" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G89" s="17"/>
       <c r="H89" s="8"/>
@@ -12866,23 +12895,23 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="116" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="10" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>89</v>
@@ -12896,10 +12925,10 @@
         <v>120</v>
       </c>
       <c r="G90" s="18" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H90" s="18" t="s">
         <v>1122</v>
-      </c>
-      <c r="H90" s="18" t="s">
-        <v>1123</v>
       </c>
       <c r="I90" s="18" t="s">
         <v>49</v>
@@ -12908,19 +12937,19 @@
       <c r="K90" s="33"/>
       <c r="L90" s="4"/>
       <c r="M90" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="30" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>89</v>
@@ -12934,10 +12963,10 @@
         <v>15</v>
       </c>
       <c r="G91" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H91" s="26" t="s">
         <v>1122</v>
-      </c>
-      <c r="H91" s="26" t="s">
-        <v>1123</v>
       </c>
       <c r="I91" s="18" t="s">
         <v>49</v>
@@ -12946,19 +12975,19 @@
       <c r="K91" s="33"/>
       <c r="L91" s="4"/>
       <c r="M91" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N91" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="30" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B92" s="36" t="s">
         <v>89</v>
@@ -12976,23 +13005,23 @@
       </c>
       <c r="J92" s="114"/>
       <c r="K92" s="114" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N92" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="30" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>66</v>
@@ -13014,17 +13043,17 @@
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="33" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P93" s="14"/>
     </row>
@@ -13570,7 +13599,7 @@
     </row>
     <row r="14" spans="1:16" ht="24">
       <c r="A14" s="10" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>585</v>
@@ -13581,7 +13610,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="26" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>15</v>
@@ -13608,7 +13637,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="48" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="8"/>
@@ -20780,7 +20809,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="49"/>
       <c r="K2" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="14" t="s">
@@ -20818,7 +20847,7 @@
       </c>
       <c r="J3" s="49"/>
       <c r="K3" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>57</v>
@@ -20856,7 +20885,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="49"/>
       <c r="K4" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>71</v>
@@ -20894,7 +20923,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="49"/>
       <c r="K5" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>57</v>
@@ -20934,7 +20963,7 @@
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="14" t="s">
@@ -20968,7 +20997,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="49"/>
       <c r="K7" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>57</v>
@@ -21004,7 +21033,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="49"/>
       <c r="K8" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>71</v>
@@ -21044,7 +21073,7 @@
       </c>
       <c r="J9" s="49"/>
       <c r="K9" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>71</v>
@@ -21080,7 +21109,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="49"/>
       <c r="K10" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>71</v>
@@ -21118,7 +21147,7 @@
       </c>
       <c r="J11" s="49"/>
       <c r="K11" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>71</v>
@@ -21154,7 +21183,7 @@
       </c>
       <c r="J12" s="49"/>
       <c r="K12" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>51</v>
@@ -21191,7 +21220,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="49"/>
       <c r="K13" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>57</v>
@@ -21221,7 +21250,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="49"/>
       <c r="K14" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="14" t="s">
@@ -21255,7 +21284,7 @@
       </c>
       <c r="J15" s="49"/>
       <c r="K15" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>71</v>
@@ -21293,7 +21322,7 @@
       <c r="I16" s="17"/>
       <c r="J16" s="49"/>
       <c r="K16" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>71</v>
@@ -21333,7 +21362,7 @@
       </c>
       <c r="J17" s="49"/>
       <c r="K17" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>71</v>
@@ -21363,7 +21392,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="49"/>
       <c r="K18" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="14" t="s">
@@ -21389,7 +21418,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="49"/>
       <c r="K19" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="14" t="s">
@@ -21427,7 +21456,7 @@
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>71</v>
@@ -21465,7 +21494,7 @@
       </c>
       <c r="J21" s="49"/>
       <c r="K21" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>71</v>
@@ -21493,7 +21522,7 @@
       <c r="I22" s="8"/>
       <c r="J22" s="49"/>
       <c r="K22" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="14" t="s">
@@ -21529,7 +21558,7 @@
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>71</v>
@@ -21569,7 +21598,7 @@
       </c>
       <c r="J24" s="49"/>
       <c r="K24" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>71</v>
@@ -21603,7 +21632,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="49"/>
       <c r="K25" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>71</v>
@@ -21631,7 +21660,7 @@
       </c>
       <c r="J26" s="49"/>
       <c r="K26" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="14" t="s">
@@ -21657,7 +21686,7 @@
       </c>
       <c r="J27" s="49"/>
       <c r="K27" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="14" t="s">
@@ -21693,7 +21722,7 @@
       </c>
       <c r="J28" s="49"/>
       <c r="K28" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>71</v>
@@ -21729,7 +21758,7 @@
       <c r="I29" s="8"/>
       <c r="J29" s="49"/>
       <c r="K29" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>140</v>
@@ -21769,7 +21798,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="49"/>
       <c r="K30" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>140</v>
@@ -21811,7 +21840,7 @@
       </c>
       <c r="J31" s="49"/>
       <c r="K31" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>71</v>
@@ -21849,7 +21878,7 @@
       </c>
       <c r="J32" s="49"/>
       <c r="K32" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>71</v>
@@ -21889,7 +21918,7 @@
       </c>
       <c r="J33" s="49"/>
       <c r="K33" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>71</v>
@@ -21929,7 +21958,7 @@
       </c>
       <c r="J34" s="49"/>
       <c r="K34" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>71</v>
@@ -21965,7 +21994,7 @@
       <c r="I35" s="8"/>
       <c r="J35" s="49"/>
       <c r="K35" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>71</v>
@@ -22047,7 +22076,7 @@
       </c>
       <c r="J37" s="49"/>
       <c r="K37" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>71</v>
@@ -22081,7 +22110,7 @@
       <c r="I38" s="25"/>
       <c r="J38" s="49"/>
       <c r="K38" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>71</v>
@@ -22117,7 +22146,7 @@
       </c>
       <c r="J39" s="49"/>
       <c r="K39" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>71</v>
@@ -22151,7 +22180,7 @@
       <c r="I40" s="25"/>
       <c r="J40" s="49"/>
       <c r="K40" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>71</v>
@@ -22185,7 +22214,7 @@
       <c r="I41" s="25"/>
       <c r="J41" s="49"/>
       <c r="K41" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>71</v>
@@ -22219,7 +22248,7 @@
       <c r="I42" s="25"/>
       <c r="J42" s="49"/>
       <c r="K42" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>71</v>
@@ -22253,7 +22282,7 @@
       <c r="I43" s="25"/>
       <c r="J43" s="49"/>
       <c r="K43" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>71</v>
@@ -22287,7 +22316,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="49"/>
       <c r="K44" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>71</v>
@@ -22323,7 +22352,7 @@
       </c>
       <c r="J45" s="49"/>
       <c r="K45" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>71</v>
@@ -22357,7 +22386,7 @@
       <c r="I46" s="25"/>
       <c r="J46" s="49"/>
       <c r="K46" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>71</v>
@@ -22391,7 +22420,7 @@
       <c r="I47" s="25"/>
       <c r="J47" s="49"/>
       <c r="K47" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>71</v>
@@ -22425,7 +22454,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="49"/>
       <c r="K48" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>71</v>
@@ -22461,7 +22490,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="49"/>
       <c r="K49" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>71</v>
@@ -22497,7 +22526,7 @@
       <c r="I50" s="25"/>
       <c r="J50" s="49"/>
       <c r="K50" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>71</v>
@@ -22531,7 +22560,7 @@
       <c r="I51" s="25"/>
       <c r="J51" s="49"/>
       <c r="K51" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>71</v>
@@ -22565,7 +22594,7 @@
       <c r="I52" s="59"/>
       <c r="J52" s="49"/>
       <c r="K52" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>71</v>
@@ -22599,7 +22628,7 @@
       <c r="I53" s="25"/>
       <c r="J53" s="49"/>
       <c r="K53" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>71</v>
@@ -22633,7 +22662,7 @@
       <c r="I54" s="59"/>
       <c r="J54" s="49"/>
       <c r="K54" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>71</v>
@@ -22669,7 +22698,7 @@
       </c>
       <c r="J55" s="49"/>
       <c r="K55" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>71</v>
@@ -22705,7 +22734,7 @@
       </c>
       <c r="J56" s="49"/>
       <c r="K56" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>71</v>
@@ -22741,7 +22770,7 @@
       </c>
       <c r="J57" s="49"/>
       <c r="K57" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>71</v>
@@ -22777,7 +22806,7 @@
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>71</v>
@@ -22813,7 +22842,7 @@
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>71</v>
@@ -22849,7 +22878,7 @@
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>71</v>
@@ -22885,7 +22914,7 @@
       </c>
       <c r="J61" s="49"/>
       <c r="K61" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>71</v>
@@ -22921,7 +22950,7 @@
       </c>
       <c r="J62" s="49"/>
       <c r="K62" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>71</v>
@@ -22957,7 +22986,7 @@
       </c>
       <c r="J63" s="49"/>
       <c r="K63" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>71</v>
@@ -22991,7 +23020,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="49"/>
       <c r="K64" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>71</v>
@@ -23027,7 +23056,7 @@
       <c r="I65" s="25"/>
       <c r="J65" s="49"/>
       <c r="K65" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>71</v>
@@ -23063,7 +23092,7 @@
       <c r="I66" s="25"/>
       <c r="J66" s="49"/>
       <c r="K66" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>71</v>
@@ -23103,7 +23132,7 @@
       </c>
       <c r="J67" s="49"/>
       <c r="K67" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>71</v>
@@ -23139,7 +23168,7 @@
       <c r="I68" s="25"/>
       <c r="J68" s="49"/>
       <c r="K68" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>71</v>
@@ -23175,7 +23204,7 @@
       </c>
       <c r="J69" s="49"/>
       <c r="K69" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>71</v>
@@ -23211,7 +23240,7 @@
       </c>
       <c r="J70" s="49"/>
       <c r="K70" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>71</v>
@@ -23247,7 +23276,7 @@
       </c>
       <c r="J71" s="49"/>
       <c r="K71" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>71</v>
@@ -23283,7 +23312,7 @@
       </c>
       <c r="J72" s="49"/>
       <c r="K72" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>71</v>
@@ -23319,7 +23348,7 @@
       </c>
       <c r="J73" s="49"/>
       <c r="K73" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>71</v>
@@ -23355,7 +23384,7 @@
       </c>
       <c r="J74" s="49"/>
       <c r="K74" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>71</v>
@@ -23391,7 +23420,7 @@
       </c>
       <c r="J75" s="49"/>
       <c r="K75" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>71</v>
@@ -23427,7 +23456,7 @@
       </c>
       <c r="J76" s="49"/>
       <c r="K76" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>71</v>
@@ -23463,7 +23492,7 @@
       </c>
       <c r="J77" s="49"/>
       <c r="K77" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>71</v>
@@ -23499,7 +23528,7 @@
       </c>
       <c r="J78" s="49"/>
       <c r="K78" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>71</v>
@@ -23535,7 +23564,7 @@
       </c>
       <c r="J79" s="49"/>
       <c r="K79" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>71</v>
@@ -23571,7 +23600,7 @@
       </c>
       <c r="J80" s="49"/>
       <c r="K80" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>71</v>
@@ -23607,7 +23636,7 @@
       </c>
       <c r="J81" s="49"/>
       <c r="K81" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>71</v>
@@ -23643,7 +23672,7 @@
       <c r="I82" s="25"/>
       <c r="J82" s="49"/>
       <c r="K82" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>71</v>
@@ -23679,7 +23708,7 @@
       </c>
       <c r="J83" s="49"/>
       <c r="K83" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>71</v>
@@ -23715,7 +23744,7 @@
       <c r="I84" s="25"/>
       <c r="J84" s="49"/>
       <c r="K84" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>71</v>
@@ -23751,7 +23780,7 @@
       </c>
       <c r="J85" s="49"/>
       <c r="K85" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>71</v>
@@ -23787,7 +23816,7 @@
       <c r="I86" s="25"/>
       <c r="J86" s="49"/>
       <c r="K86" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>71</v>
@@ -23821,7 +23850,7 @@
       <c r="I87" s="59"/>
       <c r="J87" s="49"/>
       <c r="K87" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>71</v>
@@ -23859,7 +23888,7 @@
       </c>
       <c r="J88" s="49"/>
       <c r="K88" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>71</v>
@@ -23895,7 +23924,7 @@
       </c>
       <c r="J89" s="49"/>
       <c r="K89" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>71</v>
@@ -23929,7 +23958,7 @@
       <c r="I90" s="25"/>
       <c r="J90" s="49"/>
       <c r="K90" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>71</v>
@@ -23965,7 +23994,7 @@
       </c>
       <c r="J91" s="49"/>
       <c r="K91" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>71</v>
@@ -23999,7 +24028,7 @@
       <c r="I92" s="25"/>
       <c r="J92" s="49"/>
       <c r="K92" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>71</v>
@@ -24035,7 +24064,7 @@
       </c>
       <c r="J93" s="49"/>
       <c r="K93" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>71</v>
@@ -24069,7 +24098,7 @@
       <c r="I94" s="25"/>
       <c r="J94" s="49"/>
       <c r="K94" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>71</v>
@@ -24105,7 +24134,7 @@
       <c r="I95" s="25"/>
       <c r="J95" s="49"/>
       <c r="K95" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>71</v>
@@ -24141,7 +24170,7 @@
       <c r="I96" s="25"/>
       <c r="J96" s="49"/>
       <c r="K96" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>71</v>
@@ -24177,7 +24206,7 @@
       </c>
       <c r="J97" s="49"/>
       <c r="K97" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>71</v>
@@ -24211,7 +24240,7 @@
       <c r="I98" s="25"/>
       <c r="J98" s="49"/>
       <c r="K98" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>71</v>
@@ -24249,7 +24278,7 @@
       </c>
       <c r="J99" s="49"/>
       <c r="K99" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>71</v>
@@ -24287,7 +24316,7 @@
       </c>
       <c r="J100" s="49"/>
       <c r="K100" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>71</v>
@@ -24321,7 +24350,7 @@
       <c r="I101" s="25"/>
       <c r="J101" s="49"/>
       <c r="K101" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>71</v>
@@ -24359,7 +24388,7 @@
       </c>
       <c r="J102" s="49"/>
       <c r="K102" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>71</v>
@@ -24395,7 +24424,7 @@
       <c r="I103" s="59"/>
       <c r="J103" s="49"/>
       <c r="K103" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>71</v>
@@ -24431,7 +24460,7 @@
       </c>
       <c r="J104" s="49"/>
       <c r="K104" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>71</v>
@@ -24467,7 +24496,7 @@
       </c>
       <c r="J105" s="49"/>
       <c r="K105" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>71</v>
@@ -24503,7 +24532,7 @@
       </c>
       <c r="J106" s="49"/>
       <c r="K106" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>71</v>
@@ -24539,7 +24568,7 @@
       </c>
       <c r="J107" s="49"/>
       <c r="K107" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>71</v>
@@ -24575,7 +24604,7 @@
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>71</v>
@@ -24611,7 +24640,7 @@
       </c>
       <c r="J109" s="49"/>
       <c r="K109" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>71</v>
@@ -24647,7 +24676,7 @@
       </c>
       <c r="J110" s="49"/>
       <c r="K110" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>71</v>
@@ -24683,7 +24712,7 @@
       </c>
       <c r="J111" s="49"/>
       <c r="K111" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>71</v>
@@ -24719,7 +24748,7 @@
       </c>
       <c r="J112" s="49"/>
       <c r="K112" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>71</v>
@@ -24755,7 +24784,7 @@
       </c>
       <c r="J113" s="49"/>
       <c r="K113" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>71</v>
@@ -24789,7 +24818,7 @@
       <c r="I114" s="25"/>
       <c r="J114" s="49"/>
       <c r="K114" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>71</v>
@@ -24825,7 +24854,7 @@
       </c>
       <c r="J115" s="49"/>
       <c r="K115" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>71</v>
@@ -24859,7 +24888,7 @@
       <c r="I116" s="25"/>
       <c r="J116" s="49"/>
       <c r="K116" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>71</v>
@@ -24893,7 +24922,7 @@
       <c r="I117" s="25"/>
       <c r="J117" s="49"/>
       <c r="K117" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>71</v>
@@ -24929,7 +24958,7 @@
       </c>
       <c r="J118" s="49"/>
       <c r="K118" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>71</v>
@@ -24965,7 +24994,7 @@
       </c>
       <c r="J119" s="49"/>
       <c r="K119" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L119" s="5" t="s">
         <v>71</v>
@@ -24999,7 +25028,7 @@
       <c r="I120" s="59"/>
       <c r="J120" s="49"/>
       <c r="K120" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>71</v>
@@ -25035,7 +25064,7 @@
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L121" s="5" t="s">
         <v>71</v>
@@ -25071,7 +25100,7 @@
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>71</v>
@@ -25107,7 +25136,7 @@
       </c>
       <c r="J123" s="49"/>
       <c r="K123" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>71</v>
@@ -25143,7 +25172,7 @@
       </c>
       <c r="J124" s="49"/>
       <c r="K124" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>71</v>
@@ -25179,7 +25208,7 @@
       </c>
       <c r="J125" s="49"/>
       <c r="K125" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L125" s="5" t="s">
         <v>71</v>
@@ -25215,7 +25244,7 @@
       </c>
       <c r="J126" s="49"/>
       <c r="K126" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L126" s="5" t="s">
         <v>71</v>
@@ -25251,7 +25280,7 @@
       </c>
       <c r="J127" s="49"/>
       <c r="K127" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L127" s="5" t="s">
         <v>71</v>
@@ -25287,7 +25316,7 @@
       </c>
       <c r="J128" s="49"/>
       <c r="K128" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L128" s="5" t="s">
         <v>71</v>
@@ -25323,7 +25352,7 @@
       </c>
       <c r="J129" s="49"/>
       <c r="K129" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L129" s="5" t="s">
         <v>71</v>
@@ -25359,7 +25388,7 @@
       </c>
       <c r="J130" s="49"/>
       <c r="K130" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>71</v>
@@ -25395,7 +25424,7 @@
       <c r="I131" s="25"/>
       <c r="J131" s="49"/>
       <c r="K131" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L131" s="5" t="s">
         <v>71</v>
@@ -25431,7 +25460,7 @@
       </c>
       <c r="J132" s="49"/>
       <c r="K132" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L132" s="5" t="s">
         <v>71</v>
@@ -25467,7 +25496,7 @@
       <c r="I133" s="25"/>
       <c r="J133" s="49"/>
       <c r="K133" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L133" s="5" t="s">
         <v>71</v>
@@ -25503,7 +25532,7 @@
       </c>
       <c r="J134" s="49"/>
       <c r="K134" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L134" s="5" t="s">
         <v>71</v>
@@ -25539,7 +25568,7 @@
       <c r="I135" s="25"/>
       <c r="J135" s="49"/>
       <c r="K135" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>71</v>
@@ -25573,7 +25602,7 @@
       <c r="I136" s="59"/>
       <c r="J136" s="49"/>
       <c r="K136" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L136" s="5" t="s">
         <v>71</v>
@@ -25607,7 +25636,7 @@
       <c r="I137" s="25"/>
       <c r="J137" s="49"/>
       <c r="K137" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L137" s="5" t="s">
         <v>71</v>
@@ -25641,7 +25670,7 @@
       <c r="I138" s="25"/>
       <c r="J138" s="49"/>
       <c r="K138" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L138" s="5" t="s">
         <v>71</v>
@@ -25675,7 +25704,7 @@
       <c r="I139" s="25"/>
       <c r="J139" s="49"/>
       <c r="K139" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>71</v>
@@ -25709,7 +25738,7 @@
       <c r="I140" s="25"/>
       <c r="J140" s="49"/>
       <c r="K140" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L140" s="5" t="s">
         <v>71</v>
@@ -25745,7 +25774,7 @@
       </c>
       <c r="J141" s="49"/>
       <c r="K141" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L141" s="5" t="s">
         <v>71</v>
@@ -25779,7 +25808,7 @@
       <c r="I142" s="25"/>
       <c r="J142" s="49"/>
       <c r="K142" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L142" s="5" t="s">
         <v>71</v>
@@ -25813,7 +25842,7 @@
       <c r="I143" s="25"/>
       <c r="J143" s="49"/>
       <c r="K143" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L143" s="5" t="s">
         <v>71</v>
@@ -25849,7 +25878,7 @@
       </c>
       <c r="J144" s="49"/>
       <c r="K144" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L144" s="5" t="s">
         <v>71</v>
@@ -25885,7 +25914,7 @@
       </c>
       <c r="J145" s="49"/>
       <c r="K145" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>71</v>
@@ -25921,7 +25950,7 @@
       </c>
       <c r="J146" s="49"/>
       <c r="K146" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>71</v>
@@ -25957,7 +25986,7 @@
       </c>
       <c r="J147" s="49"/>
       <c r="K147" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L147" s="5" t="s">
         <v>71</v>
@@ -25993,7 +26022,7 @@
       </c>
       <c r="J148" s="49"/>
       <c r="K148" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L148" s="5" t="s">
         <v>71</v>
@@ -26029,7 +26058,7 @@
       </c>
       <c r="J149" s="49"/>
       <c r="K149" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L149" s="5" t="s">
         <v>71</v>
@@ -26065,7 +26094,7 @@
       </c>
       <c r="J150" s="49"/>
       <c r="K150" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L150" s="5" t="s">
         <v>71</v>
@@ -26101,7 +26130,7 @@
       </c>
       <c r="J151" s="49"/>
       <c r="K151" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L151" s="5" t="s">
         <v>71</v>
@@ -26137,7 +26166,7 @@
       </c>
       <c r="J152" s="49"/>
       <c r="K152" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L152" s="5" t="s">
         <v>71</v>
@@ -26173,7 +26202,7 @@
       </c>
       <c r="J153" s="49"/>
       <c r="K153" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L153" s="5" t="s">
         <v>71</v>
@@ -26207,7 +26236,7 @@
       <c r="I154" s="59"/>
       <c r="J154" s="56"/>
       <c r="K154" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L154" s="5" t="s">
         <v>71</v>
@@ -26241,7 +26270,7 @@
       <c r="I155" s="33"/>
       <c r="J155" s="56"/>
       <c r="K155" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>71</v>
@@ -26725,7 +26754,7 @@
     </row>
     <row r="10" spans="1:16" ht="24">
       <c r="A10" s="67" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>787</v>
@@ -26739,14 +26768,14 @@
         <v>347</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="59"/>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64092B70-20B1-4C38-A1F4-E6F01939C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D1EC96-9277-44A0-A590-6364D8FE849E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19425" yWindow="5955" windowWidth="35475" windowHeight="23445" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28650" yWindow="5730" windowWidth="27210" windowHeight="23445" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -2930,10 +2930,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>Derived from Tidal Volume (TV) 
-~1/2 TV</t>
-  </si>
-  <si>
     <t>ResistiveExpiratoryWorkOfBreathing*</t>
   </si>
   <si>
@@ -3767,6 +3763,9 @@
   </si>
   <si>
     <t>TotalPositiveEndExpiratoryPressure</t>
+  </si>
+  <si>
+    <t>Same as Tidal Volume</t>
   </si>
 </sst>
 </file>
@@ -5425,7 +5424,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="10" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>852</v>
@@ -5503,7 +5502,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>884</v>
@@ -5801,7 +5800,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="10" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>884</v>
@@ -6039,7 +6038,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="10" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>852</v>
@@ -6451,7 +6450,7 @@
     </row>
     <row r="39" spans="1:16" ht="96">
       <c r="A39" s="10" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>870</v>
@@ -6493,7 +6492,7 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="10" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>927</v>
@@ -6533,20 +6532,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="24">
+    <row r="41" spans="1:16">
       <c r="A41" s="10" t="s">
         <v>930</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>931</v>
+        <v>17</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>862</v>
+        <v>997</v>
       </c>
       <c r="D41" s="51"/>
       <c r="E41" s="51"/>
       <c r="F41" s="17">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G41" s="17" t="s">
         <v>104</v>
@@ -6557,9 +6556,8 @@
       <c r="I41" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="J41" s="17"/>
-      <c r="K41" s="26" t="s">
-        <v>932</v>
+      <c r="J41" s="26" t="s">
+        <v>1197</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="66" t="s">
@@ -6577,7 +6575,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="48" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>873</v>
@@ -6607,7 +6605,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="48" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>873</v>
@@ -6637,7 +6635,7 @@
     </row>
     <row r="44" spans="1:16" ht="36">
       <c r="A44" s="10" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>292</v>
@@ -6648,13 +6646,13 @@
       <c r="D44" s="51"/>
       <c r="E44" s="51"/>
       <c r="F44" s="18" t="s">
+        <v>935</v>
+      </c>
+      <c r="G44" s="99" t="s">
         <v>936</v>
       </c>
-      <c r="G44" s="99" t="s">
+      <c r="H44" s="8" t="s">
         <v>937</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>938</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>49</v>
@@ -6677,7 +6675,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="48" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="51" t="s">
@@ -6689,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
@@ -6711,7 +6709,7 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="48" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="51"/>
@@ -6739,7 +6737,7 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="10" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="51" t="s">
@@ -6758,7 +6756,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="K47" s="51"/>
       <c r="L47" s="51"/>
@@ -6777,7 +6775,7 @@
     </row>
     <row r="48" spans="1:16" ht="24">
       <c r="A48" s="10" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="51" t="s">
@@ -6799,7 +6797,7 @@
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="26" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L48" s="92"/>
       <c r="M48" s="66" t="s">
@@ -6817,7 +6815,7 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="10" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>17</v>
@@ -6857,10 +6855,10 @@
     </row>
     <row r="50" spans="1:16" ht="24">
       <c r="A50" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="B50" s="17" t="s">
         <v>947</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>948</v>
       </c>
       <c r="C50" s="51" t="s">
         <v>862</v>
@@ -6881,7 +6879,7 @@
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="26" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="L50" s="91"/>
       <c r="M50" s="66" t="s">
@@ -6899,10 +6897,10 @@
     </row>
     <row r="51" spans="1:16" ht="24">
       <c r="A51" s="10" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C51" s="51" t="s">
         <v>862</v>
@@ -6924,7 +6922,7 @@
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="26" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="L51" s="56"/>
       <c r="M51" s="66" t="s">
@@ -6942,7 +6940,7 @@
     </row>
     <row r="52" spans="1:16" ht="36">
       <c r="A52" s="10" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B52" s="18" t="s">
         <v>931</v>
@@ -6966,7 +6964,7 @@
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="26" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="L52" s="56"/>
       <c r="M52" s="66" t="s">
@@ -6984,7 +6982,7 @@
     </row>
     <row r="53" spans="1:16" ht="108">
       <c r="A53" s="10" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>852</v>
@@ -7024,7 +7022,7 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="48" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>894</v>
@@ -7054,10 +7052,10 @@
     </row>
     <row r="55" spans="1:16" ht="45.75" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C55" s="51" t="s">
         <v>862</v>
@@ -7079,7 +7077,7 @@
       </c>
       <c r="J55" s="17"/>
       <c r="K55" s="26" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="L55" s="91"/>
       <c r="M55" s="66" t="s">
@@ -7097,7 +7095,7 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="48" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>873</v>
@@ -7127,7 +7125,7 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>852</v>
@@ -7167,7 +7165,7 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>852</v>
@@ -7207,7 +7205,7 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B59" s="17" t="s">
         <v>852</v>
@@ -7224,7 +7222,7 @@
         <v>15</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>573</v>
@@ -7247,7 +7245,7 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B60" s="17" t="s">
         <v>852</v>
@@ -7264,7 +7262,7 @@
         <v>15</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>573</v>
@@ -7287,7 +7285,7 @@
     </row>
     <row r="61" spans="1:16" ht="24">
       <c r="A61" s="10" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>852</v>
@@ -7311,7 +7309,7 @@
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="26" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L61" s="91"/>
       <c r="M61" s="66" t="s">
@@ -7329,7 +7327,7 @@
     </row>
     <row r="62" spans="1:16" ht="24">
       <c r="A62" s="10" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>852</v>
@@ -7353,7 +7351,7 @@
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="26" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L62" s="91"/>
       <c r="M62" s="66" t="s">
@@ -7371,7 +7369,7 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>852</v>
@@ -7411,7 +7409,7 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>852</v>
@@ -7449,7 +7447,7 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="10" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B65" s="17" t="s">
         <v>852</v>
@@ -7466,7 +7464,7 @@
         <v>15</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I65" s="17" t="s">
         <v>573</v>
@@ -7489,7 +7487,7 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="10" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B66" s="17" t="s">
         <v>852</v>
@@ -7506,7 +7504,7 @@
         <v>15</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I66" s="17" t="s">
         <v>573</v>
@@ -7529,7 +7527,7 @@
     </row>
     <row r="67" spans="1:16" ht="24">
       <c r="A67" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>852</v>
@@ -7546,13 +7544,13 @@
         <v>853</v>
       </c>
       <c r="H67" s="17" t="s">
+        <v>965</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J67" s="17" t="s">
         <v>966</v>
-      </c>
-      <c r="I67" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J67" s="17" t="s">
-        <v>967</v>
       </c>
       <c r="K67" s="26"/>
       <c r="L67" s="91"/>
@@ -7571,7 +7569,7 @@
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>852</v>
@@ -7588,13 +7586,13 @@
         <v>853</v>
       </c>
       <c r="H68" s="17" t="s">
+        <v>965</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J68" s="17" t="s">
         <v>966</v>
-      </c>
-      <c r="I68" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J68" s="17" t="s">
-        <v>967</v>
       </c>
       <c r="K68" s="26"/>
       <c r="L68" s="91"/>
@@ -7613,7 +7611,7 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>852</v>
@@ -7653,7 +7651,7 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>852</v>
@@ -7693,7 +7691,7 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="51" t="s">
@@ -7702,10 +7700,10 @@
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="51" t="s">
+        <v>969</v>
+      </c>
+      <c r="G71" s="17" t="s">
         <v>970</v>
-      </c>
-      <c r="G71" s="17" t="s">
-        <v>971</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17" t="s">
@@ -7779,7 +7777,7 @@
     </row>
     <row r="73" spans="1:16" ht="25.5" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B73" s="17" t="s">
         <v>852</v>
@@ -7790,32 +7788,32 @@
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="101" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G73" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J73" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="K73" s="26" t="s">
         <v>975</v>
-      </c>
-      <c r="K73" s="26" t="s">
-        <v>976</v>
       </c>
       <c r="L73" s="91"/>
       <c r="M73" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N73" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N73" s="5" t="s">
+      <c r="O73" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O73" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P73" s="66">
         <v>4</v>
@@ -7823,7 +7821,7 @@
     </row>
     <row r="74" spans="1:16" ht="24">
       <c r="A74" s="10" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>852</v>
@@ -7834,32 +7832,32 @@
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="101" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G74" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="I74" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J74" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="K74" s="26" t="s">
         <v>975</v>
-      </c>
-      <c r="K74" s="26" t="s">
-        <v>976</v>
       </c>
       <c r="L74" s="91"/>
       <c r="M74" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N74" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N74" s="5" t="s">
+      <c r="O74" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O74" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P74" s="66">
         <v>4</v>
@@ -7867,7 +7865,7 @@
     </row>
     <row r="75" spans="1:16" ht="24">
       <c r="A75" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>200</v>
@@ -7878,30 +7876,30 @@
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="17" t="s">
+        <v>981</v>
+      </c>
+      <c r="G75" s="99" t="s">
         <v>982</v>
       </c>
-      <c r="G75" s="99" t="s">
+      <c r="H75" s="17" t="s">
         <v>983</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>984</v>
       </c>
       <c r="I75" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="17"/>
       <c r="K75" s="26" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="L75" s="91"/>
       <c r="M75" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O75" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P75" s="66">
         <v>4</v>
@@ -7909,7 +7907,7 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>200</v>
@@ -7926,7 +7924,7 @@
         <v>104</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>49</v>
@@ -7935,13 +7933,13 @@
       <c r="K76" s="5"/>
       <c r="L76" s="56"/>
       <c r="M76" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O76" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P76" s="66">
         <v>4</v>
@@ -7949,7 +7947,7 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="10" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>200</v>
@@ -7960,13 +7958,13 @@
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="51" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G77" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="I77" s="17" t="s">
         <v>49</v>
@@ -7975,13 +7973,13 @@
       <c r="K77" s="17"/>
       <c r="L77" s="91"/>
       <c r="M77" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O77" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P77" s="66">
         <v>4</v>
@@ -7989,7 +7987,7 @@
     </row>
     <row r="78" spans="1:16" ht="30" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B78" s="17" t="s">
         <v>200</v>
@@ -8000,30 +7998,30 @@
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="17" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G78" s="99" t="s">
+        <v>982</v>
+      </c>
+      <c r="H78" s="17" t="s">
         <v>983</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>984</v>
       </c>
       <c r="I78" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J78" s="17"/>
       <c r="K78" s="26" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="L78" s="91"/>
       <c r="M78" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P78" s="66">
         <v>4</v>
@@ -8031,7 +8029,7 @@
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="10" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>852</v>
@@ -8048,26 +8046,26 @@
         <v>15</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I79" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K79" s="26" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L79" s="56"/>
       <c r="M79" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N79" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N79" s="5" t="s">
+      <c r="O79" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O79" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P79" s="66">
         <v>4</v>
@@ -8075,7 +8073,7 @@
     </row>
     <row r="80" spans="1:16" ht="24">
       <c r="A80" s="10" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>852</v>
@@ -8092,26 +8090,26 @@
         <v>15</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K80" s="26" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L80" s="56"/>
       <c r="M80" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N80" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="O80" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O80" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P80" s="66">
         <v>4</v>
@@ -8119,7 +8117,7 @@
     </row>
     <row r="81" spans="1:16" ht="24">
       <c r="A81" s="10" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B81" s="17" t="s">
         <v>852</v>
@@ -8136,26 +8134,26 @@
         <v>15</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I81" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L81" s="56"/>
       <c r="M81" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N81" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="O81" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O81" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P81" s="66">
         <v>4</v>
@@ -8163,7 +8161,7 @@
     </row>
     <row r="82" spans="1:16" ht="24">
       <c r="A82" s="10" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B82" s="17" t="s">
         <v>852</v>
@@ -8180,26 +8178,26 @@
         <v>15</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I82" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L82" s="56"/>
       <c r="M82" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N82" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N82" s="5" t="s">
+      <c r="O82" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O82" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P82" s="66">
         <v>4</v>
@@ -8207,13 +8205,13 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D83" s="51"/>
       <c r="E83" s="51"/>
@@ -8231,17 +8229,17 @@
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L83" s="104"/>
       <c r="M83" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>860</v>
       </c>
       <c r="O83" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P83" s="66">
         <v>4</v>
@@ -8249,13 +8247,13 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D84" s="51"/>
       <c r="E84" s="51"/>
@@ -8273,17 +8271,17 @@
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L84" s="104"/>
       <c r="M84" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>860</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P84" s="66">
         <v>4</v>
@@ -8291,7 +8289,7 @@
     </row>
     <row r="85" spans="1:16" ht="24">
       <c r="A85" s="10" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>852</v>
@@ -8302,32 +8300,32 @@
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G85" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="H85" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H85" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="L85" s="91"/>
       <c r="M85" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N85" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N85" s="5" t="s">
+      <c r="O85" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O85" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P85" s="66">
         <v>4</v>
@@ -8335,7 +8333,7 @@
     </row>
     <row r="86" spans="1:16" ht="24">
       <c r="A86" s="10" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>852</v>
@@ -8346,32 +8344,32 @@
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G86" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H86" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="L86" s="91"/>
       <c r="M86" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N86" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N86" s="5" t="s">
+      <c r="O86" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O86" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P86" s="66">
         <v>4</v>
@@ -8379,7 +8377,7 @@
     </row>
     <row r="87" spans="1:16" ht="24">
       <c r="A87" s="10" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>852</v>
@@ -8390,32 +8388,32 @@
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G87" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="G87" s="17" t="s">
+      <c r="H87" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I87" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K87" s="26" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="L87" s="91"/>
       <c r="M87" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N87" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N87" s="5" t="s">
+      <c r="O87" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O87" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P87" s="66">
         <v>4</v>
@@ -8423,7 +8421,7 @@
     </row>
     <row r="88" spans="1:16" ht="24">
       <c r="A88" s="10" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>852</v>
@@ -8434,32 +8432,32 @@
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G88" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H88" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I88" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K88" s="26" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="L88" s="91"/>
       <c r="M88" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N88" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N88" s="5" t="s">
+      <c r="O88" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O88" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P88" s="66">
         <v>4</v>
@@ -8467,13 +8465,13 @@
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="10" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D89" s="51"/>
       <c r="E89" s="51"/>
@@ -8491,17 +8489,17 @@
       </c>
       <c r="J89" s="17"/>
       <c r="K89" s="17" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L89" s="91"/>
       <c r="M89" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O89" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P89" s="66">
         <v>4</v>
@@ -8509,13 +8507,13 @@
     </row>
     <row r="90" spans="1:16" ht="24">
       <c r="A90" s="10" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D90" s="51"/>
       <c r="E90" s="51"/>
@@ -8533,17 +8531,17 @@
       </c>
       <c r="J90" s="17"/>
       <c r="K90" s="17" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L90" s="91"/>
       <c r="M90" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O90" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P90" s="66">
         <v>4</v>
@@ -8551,7 +8549,7 @@
     </row>
     <row r="91" spans="1:16" ht="24">
       <c r="A91" s="10" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B91" s="17" t="s">
         <v>852</v>
@@ -8562,30 +8560,30 @@
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G91" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="G91" s="17" t="s">
+      <c r="H91" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H91" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I91" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K91" s="26"/>
       <c r="L91" s="91"/>
       <c r="M91" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N91" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N91" s="5" t="s">
+      <c r="O91" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O91" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P91" s="66">
         <v>4</v>
@@ -8593,7 +8591,7 @@
     </row>
     <row r="92" spans="1:16" ht="24">
       <c r="A92" s="10" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B92" s="17" t="s">
         <v>852</v>
@@ -8604,30 +8602,30 @@
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G92" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H92" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H92" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I92" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K92" s="26"/>
       <c r="L92" s="91"/>
       <c r="M92" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N92" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N92" s="5" t="s">
+      <c r="O92" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O92" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P92" s="66">
         <v>4</v>
@@ -8635,7 +8633,7 @@
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="10" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>200</v>
@@ -8646,13 +8644,13 @@
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
       <c r="F93" s="105" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G93" s="99" t="s">
         <v>1013</v>
       </c>
-      <c r="G93" s="99" t="s">
+      <c r="H93" s="17" t="s">
         <v>1014</v>
-      </c>
-      <c r="H93" s="17" t="s">
-        <v>1015</v>
       </c>
       <c r="I93" s="17" t="s">
         <v>49</v>
@@ -8661,13 +8659,13 @@
       <c r="K93" s="26"/>
       <c r="L93" s="91"/>
       <c r="M93" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O93" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P93" s="66">
         <v>4</v>
@@ -8675,7 +8673,7 @@
     </row>
     <row r="94" spans="1:16" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>200</v>
@@ -8686,13 +8684,13 @@
       <c r="D94" s="51"/>
       <c r="E94" s="51"/>
       <c r="F94" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G94" s="99" t="s">
         <v>1017</v>
       </c>
-      <c r="G94" s="99" t="s">
+      <c r="H94" s="17" t="s">
         <v>1018</v>
-      </c>
-      <c r="H94" s="17" t="s">
-        <v>1019</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>49</v>
@@ -8700,13 +8698,13 @@
       <c r="J94" s="17"/>
       <c r="L94" s="91"/>
       <c r="M94" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O94" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P94" s="66">
         <v>4</v>
@@ -8714,13 +8712,13 @@
     </row>
     <row r="95" spans="1:16" ht="24">
       <c r="A95" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B95" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D95" s="51"/>
       <c r="E95" s="51"/>
@@ -8738,17 +8736,17 @@
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L95" s="91"/>
       <c r="M95" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O95" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P95" s="66">
         <v>4</v>
@@ -8756,13 +8754,13 @@
     </row>
     <row r="96" spans="1:16" ht="24">
       <c r="A96" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B96" s="18" t="s">
         <v>931</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D96" s="51"/>
       <c r="E96" s="51"/>
@@ -8780,17 +8778,17 @@
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="17" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L96" s="91"/>
       <c r="M96" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N96" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O96" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P96" s="66">
         <v>4</v>
@@ -8798,7 +8796,7 @@
     </row>
     <row r="97" spans="1:16" ht="24">
       <c r="A97" s="10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>852</v>
@@ -8809,30 +8807,30 @@
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="17" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G97" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="G97" s="17" t="s">
+      <c r="H97" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H97" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I97" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K97" s="26"/>
       <c r="L97" s="91"/>
       <c r="M97" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N97" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N97" s="5" t="s">
+      <c r="O97" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O97" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P97" s="66">
         <v>4</v>
@@ -8840,7 +8838,7 @@
     </row>
     <row r="98" spans="1:16" ht="24">
       <c r="A98" s="10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>852</v>
@@ -8851,30 +8849,30 @@
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G98" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H98" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="H98" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="I98" s="17" t="s">
         <v>573</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="K98" s="26"/>
       <c r="L98" s="91"/>
       <c r="M98" s="66" t="s">
+        <v>976</v>
+      </c>
+      <c r="N98" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="N98" s="5" t="s">
+      <c r="O98" s="66" t="s">
         <v>978</v>
-      </c>
-      <c r="O98" s="66" t="s">
-        <v>979</v>
       </c>
       <c r="P98" s="66">
         <v>4</v>
@@ -8882,7 +8880,7 @@
     </row>
     <row r="99" spans="1:16" ht="36">
       <c r="A99" s="10" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>200</v>
@@ -8893,13 +8891,13 @@
       <c r="D99" s="51"/>
       <c r="E99" s="51"/>
       <c r="F99" s="105" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G99" s="99" t="s">
         <v>1013</v>
       </c>
-      <c r="G99" s="99" t="s">
+      <c r="H99" s="17" t="s">
         <v>1014</v>
-      </c>
-      <c r="H99" s="17" t="s">
-        <v>1015</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>49</v>
@@ -8908,13 +8906,13 @@
       <c r="K99" s="26"/>
       <c r="L99" s="91"/>
       <c r="M99" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N99" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O99" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P99" s="66">
         <v>4</v>
@@ -8922,7 +8920,7 @@
     </row>
     <row r="100" spans="1:16" ht="36.75" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>200</v>
@@ -8933,13 +8931,13 @@
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
       <c r="F100" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G100" s="99" t="s">
         <v>1017</v>
       </c>
-      <c r="G100" s="99" t="s">
+      <c r="H100" s="17" t="s">
         <v>1018</v>
-      </c>
-      <c r="H100" s="17" t="s">
-        <v>1019</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>49</v>
@@ -8948,13 +8946,13 @@
       <c r="K100" s="26"/>
       <c r="L100" s="91"/>
       <c r="M100" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N100" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O100" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P100" s="66">
         <v>4</v>
@@ -8962,7 +8960,7 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="10" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B101" s="18" t="s">
         <v>931</v>
@@ -8986,17 +8984,17 @@
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L101" s="91"/>
       <c r="M101" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N101" s="5" t="s">
         <v>860</v>
       </c>
       <c r="O101" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P101" s="66">
         <v>4</v>
@@ -9004,7 +9002,7 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="10" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>200</v>
@@ -9015,30 +9013,30 @@
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="17" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G102" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J102" s="17"/>
       <c r="K102" s="26" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L102" s="91"/>
       <c r="M102" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N102" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O102" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P102" s="66">
         <v>4</v>
@@ -9046,7 +9044,7 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="10" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B103" s="17" t="s">
         <v>200</v>
@@ -9057,30 +9055,30 @@
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="51" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G103" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="17"/>
       <c r="K103" s="26" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L103" s="91"/>
       <c r="M103" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N103" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O103" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P103" s="66">
         <v>4</v>
@@ -9088,7 +9086,7 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="10" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>931</v>
@@ -9112,17 +9110,17 @@
       </c>
       <c r="J104" s="17"/>
       <c r="K104" s="17" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="L104" s="91"/>
       <c r="M104" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N104" s="5" t="s">
         <v>860</v>
       </c>
       <c r="O104" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P104" s="66">
         <v>4</v>
@@ -9130,7 +9128,7 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="10" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>200</v>
@@ -9141,30 +9139,30 @@
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="17" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G105" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="I105" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J105" s="17"/>
       <c r="K105" s="26" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L105" s="91"/>
       <c r="M105" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N105" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O105" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P105" s="66">
         <v>4</v>
@@ -9172,7 +9170,7 @@
     </row>
     <row r="106" spans="1:16" ht="14.25" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>200</v>
@@ -9183,30 +9181,30 @@
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="51" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G106" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="I106" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="26" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L106" s="91"/>
       <c r="M106" s="66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="N106" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O106" s="66" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P106" s="66">
         <v>4</v>
@@ -9272,7 +9270,7 @@
         <v>38</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>40</v>
@@ -9289,7 +9287,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="67" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>14</v>
@@ -9303,7 +9301,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
@@ -9315,7 +9313,7 @@
         <v>200</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>71</v>
@@ -9327,7 +9325,7 @@
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="23.25" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>17</v>
@@ -9342,23 +9340,23 @@
         <v>8751.6116205773851</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K3" s="35" t="s">
         <v>1042</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>1043</v>
       </c>
       <c r="L3" s="8">
         <v>7363</v>
       </c>
       <c r="M3" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>57</v>
@@ -9370,7 +9368,7 @@
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1">
       <c r="A4" s="10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>17</v>
@@ -9385,7 +9383,7 @@
         <v>34084.065120622952</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="14" t="s">
@@ -9393,13 +9391,13 @@
       </c>
       <c r="J4" s="87"/>
       <c r="K4" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>1046</v>
-      </c>
       <c r="M4" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>57</v>
@@ -9411,7 +9409,7 @@
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1" ht="24">
       <c r="A5" s="10" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="8" t="s">
@@ -9420,26 +9418,26 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>1049</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>1050</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="109"/>
       <c r="K5" s="8" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="M5" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>71</v>
@@ -9453,7 +9451,7 @@
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1">
       <c r="A6" s="10" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>17</v>
@@ -9468,21 +9466,21 @@
         <v>25271.303751033935</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
         <v>16700</v>
       </c>
       <c r="M6" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>57</v>
@@ -9494,7 +9492,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="67" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>14</v>
@@ -9508,7 +9506,7 @@
         <v>250</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H7" s="59"/>
       <c r="I7" s="14" t="s">
@@ -9520,7 +9518,7 @@
         <v>250</v>
       </c>
       <c r="M7" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>57</v>
@@ -9532,7 +9530,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="8" t="s">
@@ -9544,10 +9542,10 @@
         <v>0.85</v>
       </c>
       <c r="G8" s="111" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H8" s="111" t="s">
         <v>1056</v>
-      </c>
-      <c r="H8" s="111" t="s">
-        <v>1057</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>49</v>
@@ -9558,7 +9556,7 @@
         <v>0.85</v>
       </c>
       <c r="M8" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>51</v>
@@ -9572,7 +9570,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="120" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>931</v>
@@ -9586,7 +9584,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="111" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H9" s="111"/>
       <c r="I9" s="14" t="s">
@@ -9598,7 +9596,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>71</v>
@@ -9610,7 +9608,7 @@
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A10" s="28" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
@@ -9643,7 +9641,7 @@
         <v>38</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>40</v>
@@ -9660,7 +9658,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>14</v>
@@ -9677,7 +9675,7 @@
         <v>104</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>49</v>
@@ -9688,7 +9686,7 @@
         <v>250</v>
       </c>
       <c r="M11" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>57</v>
@@ -9702,7 +9700,7 @@
     </row>
     <row r="12" spans="1:16" s="1" customFormat="1">
       <c r="A12" s="67" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>14</v>
@@ -9719,7 +9717,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>49</v>
@@ -9730,7 +9728,7 @@
         <v>300</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>57</v>
@@ -9744,7 +9742,7 @@
     </row>
     <row r="13" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A13" s="28" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -9777,7 +9775,7 @@
         <v>38</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>40</v>
@@ -9794,7 +9792,7 @@
     </row>
     <row r="14" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A14" s="30" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>931</v>
@@ -9816,32 +9814,32 @@
         <v>273</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="33" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L14" s="5">
         <v>3140</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A15" s="30" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
@@ -9856,23 +9854,23 @@
         <v>2119.3689320388348</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I15" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="33" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L15" s="5">
         <v>3140</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>71</v>
@@ -9884,7 +9882,7 @@
     </row>
     <row r="16" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A16" s="30" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
@@ -9899,23 +9897,23 @@
         <v>266.88349514563106</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I16" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="33" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L16" s="5">
         <v>3140</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>71</v>
@@ -9927,7 +9925,7 @@
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A17" s="30" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>931</v>
@@ -9949,32 +9947,32 @@
         <v>273</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="33" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L17" s="5">
         <v>2680</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A18" s="30" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>17</v>
@@ -9989,23 +9987,23 @@
         <v>807.69230769230774</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="33" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L18" s="5">
         <v>2680</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>71</v>
@@ -10017,7 +10015,7 @@
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A19" s="30" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
@@ -10032,23 +10030,23 @@
         <v>2794.6153846153843</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="33" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L19" s="5">
         <v>2680</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>71</v>
@@ -10060,7 +10058,7 @@
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A20" s="30" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>931</v>
@@ -10082,32 +10080,32 @@
         <v>273</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L20" s="5">
         <v>1020</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A21" s="30" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>17</v>
@@ -10122,23 +10120,23 @@
         <v>234.9</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I21" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L21" s="5">
         <v>1020</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>71</v>
@@ -10150,7 +10148,7 @@
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A22" s="30" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>17</v>
@@ -10165,23 +10163,23 @@
         <v>899</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L22" s="5">
         <v>1020</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>71</v>
@@ -10193,7 +10191,7 @@
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A23" s="30" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>931</v>
@@ -10215,32 +10213,32 @@
         <v>273</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I23" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L23" s="5">
         <v>730</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N23" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A24" s="30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>17</v>
@@ -10255,23 +10253,23 @@
         <v>287.63999999999993</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L24" s="5">
         <v>730</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>71</v>
@@ -10283,7 +10281,7 @@
     </row>
     <row r="25" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A25" s="30" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>17</v>
@@ -10298,23 +10296,23 @@
         <v>484.5</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L25" s="5">
         <v>730</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>71</v>
@@ -10326,7 +10324,7 @@
     </row>
     <row r="26" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A26" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>931</v>
@@ -10348,32 +10346,32 @@
         <v>273</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L26" s="5">
         <v>110</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A27" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>17</v>
@@ -10388,23 +10386,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L27" s="5">
         <v>110</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N27" s="5" t="s">
         <v>71</v>
@@ -10416,7 +10414,7 @@
     </row>
     <row r="28" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A28" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>17</v>
@@ -10431,23 +10429,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L28" s="5">
         <v>110</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N28" s="5" t="s">
         <v>71</v>
@@ -10459,7 +10457,7 @@
     </row>
     <row r="29" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A29" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>931</v>
@@ -10481,32 +10479,32 @@
         <v>273</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L29" s="5">
         <v>110</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A30" s="30" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>17</v>
@@ -10521,23 +10519,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I30" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L30" s="5">
         <v>110</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>71</v>
@@ -10549,7 +10547,7 @@
     </row>
     <row r="31" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A31" s="30" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>17</v>
@@ -10564,23 +10562,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L31" s="5">
         <v>110</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>71</v>
@@ -10592,7 +10590,7 @@
     </row>
     <row r="32" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A32" s="30" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>931</v>
@@ -10614,32 +10612,32 @@
         <v>273</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L32" s="5">
         <v>1030</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A33" s="30" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>17</v>
@@ -10654,23 +10652,23 @@
         <v>289.8</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L33" s="5">
         <v>1030</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>71</v>
@@ -10682,7 +10680,7 @@
     </row>
     <row r="34" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A34" s="30" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>17</v>
@@ -10697,23 +10695,23 @@
         <v>1031.3999999999999</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L34" s="5">
         <v>1030</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>71</v>
@@ -10725,7 +10723,7 @@
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A35" s="30" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>931</v>
@@ -10749,32 +10747,32 @@
         <v>273</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L35" s="5">
         <v>160</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O35" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A36" s="30" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>17</v>
@@ -10789,23 +10787,23 @@
         <v>100.8</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L36" s="5">
         <v>160</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>71</v>
@@ -10817,7 +10815,7 @@
     </row>
     <row r="37" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A37" s="30" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>17</v>
@@ -10832,23 +10830,23 @@
         <v>133.80000000000001</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L37" s="5">
         <v>160</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N37" s="5" t="s">
         <v>71</v>
@@ -10860,7 +10858,7 @@
     </row>
     <row r="38" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A38" s="30" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>931</v>
@@ -10884,32 +10882,32 @@
         <v>273</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L38" s="5">
         <v>160</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A39" s="30" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>17</v>
@@ -10924,23 +10922,23 @@
         <v>67.2</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L39" s="5">
         <v>160</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N39" s="5" t="s">
         <v>71</v>
@@ -10952,7 +10950,7 @@
     </row>
     <row r="40" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A40" s="30" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>17</v>
@@ -10967,23 +10965,23 @@
         <v>89.2</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L40" s="5">
         <v>160</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N40" s="5" t="s">
         <v>71</v>
@@ -10995,7 +10993,7 @@
     </row>
     <row r="41" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A41" s="30" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>931</v>
@@ -11017,32 +11015,32 @@
         <v>273</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L41" s="5">
         <v>13090</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A42" s="30" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>17</v>
@@ -11057,23 +11055,23 @@
         <v>3421.9999999999995</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I42" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L42" s="5">
         <v>13090</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>71</v>
@@ -11085,7 +11083,7 @@
     </row>
     <row r="43" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A43" s="30" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>17</v>
@@ -11100,23 +11098,23 @@
         <v>18270</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L43" s="5">
         <v>13090</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>71</v>
@@ -11128,7 +11126,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="30" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>89</v>
@@ -11139,10 +11137,10 @@
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="52" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G44" s="17" t="s">
         <v>1100</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>1101</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="26" t="s">
@@ -11152,7 +11150,7 @@
       <c r="K44" s="33"/>
       <c r="L44" s="21"/>
       <c r="M44" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>71</v>
@@ -11164,7 +11162,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="30" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>89</v>
@@ -11175,7 +11173,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="113" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G45" s="17" t="s">
         <v>548</v>
@@ -11186,11 +11184,11 @@
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="33" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>71</v>
@@ -11202,7 +11200,7 @@
     </row>
     <row r="46" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A46" s="30" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>931</v>
@@ -11224,32 +11222,32 @@
         <v>273</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L46" s="5">
         <v>190</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A47" s="30" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>17</v>
@@ -11264,23 +11262,23 @@
         <v>105.60000000000001</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L47" s="5">
         <v>190</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>71</v>
@@ -11292,7 +11290,7 @@
     </row>
     <row r="48" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A48" s="30" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>17</v>
@@ -11307,23 +11305,23 @@
         <v>150.47999999999999</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I48" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L48" s="5">
         <v>190</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>71</v>
@@ -11335,7 +11333,7 @@
     </row>
     <row r="49" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A49" s="30" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>931</v>
@@ -11357,32 +11355,32 @@
         <v>273</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I49" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L49" s="5">
         <v>1550</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A50" s="30" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>17</v>
@@ -11397,23 +11395,23 @@
         <v>1200.9303808462425</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I50" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L50" s="5">
         <v>1550</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N50" s="5" t="s">
         <v>71</v>
@@ -11425,7 +11423,7 @@
     </row>
     <row r="51" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A51" s="30" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
@@ -11440,23 +11438,23 @@
         <v>914.844871272923</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I51" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L51" s="5">
         <v>1550</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N51" s="5" t="s">
         <v>71</v>
@@ -11468,7 +11466,7 @@
     </row>
     <row r="52" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A52" s="30" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>931</v>
@@ -11490,32 +11488,32 @@
         <v>273</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I52" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L52" s="5">
         <v>100</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A53" s="30" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
@@ -11530,23 +11528,23 @@
         <v>31.049999999999997</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I53" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L53" s="5">
         <v>100</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>71</v>
@@ -11558,7 +11556,7 @@
     </row>
     <row r="54" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A54" s="30" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>17</v>
@@ -11573,23 +11571,23 @@
         <v>86.85</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L54" s="5">
         <v>100</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>71</v>
@@ -11601,7 +11599,7 @@
     </row>
     <row r="55" spans="1:16" ht="24">
       <c r="A55" s="28" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1</v>
@@ -11651,7 +11649,7 @@
     </row>
     <row r="56" spans="1:16" ht="24.75">
       <c r="A56" s="30" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>89</v>
@@ -11662,7 +11660,7 @@
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="18" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G56" s="18" t="s">
         <v>143</v>
@@ -11673,23 +11671,23 @@
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="114" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="30" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>89</v>
@@ -11710,22 +11708,22 @@
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="35" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="30" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>89</v>
@@ -11739,10 +11737,10 @@
         <v>25</v>
       </c>
       <c r="G58" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H58" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>49</v>
@@ -11750,22 +11748,22 @@
       <c r="J58" s="17"/>
       <c r="K58" s="19"/>
       <c r="L58" s="12" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="30" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>89</v>
@@ -11779,10 +11777,10 @@
         <v>1.2</v>
       </c>
       <c r="G59" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H59" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I59" s="18" t="s">
         <v>49</v>
@@ -11790,22 +11788,22 @@
       <c r="J59" s="17"/>
       <c r="K59" s="19"/>
       <c r="L59" s="8" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" ht="24">
       <c r="A60" s="30" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>89</v>
@@ -11816,7 +11814,7 @@
       <c r="D60" s="115"/>
       <c r="E60" s="115"/>
       <c r="F60" s="116" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G60" s="115"/>
       <c r="H60" s="116"/>
@@ -11825,23 +11823,23 @@
       </c>
       <c r="J60" s="116"/>
       <c r="K60" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L60" s="8"/>
       <c r="M60" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="30" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>89</v>
@@ -11855,10 +11853,10 @@
         <v>116</v>
       </c>
       <c r="G61" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H61" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>49</v>
@@ -11867,19 +11865,19 @@
       <c r="K61" s="33"/>
       <c r="L61" s="14"/>
       <c r="M61" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" ht="36.75">
       <c r="A62" s="30" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B62" s="115"/>
       <c r="C62" s="116"/>
@@ -11893,26 +11891,26 @@
       </c>
       <c r="J62" s="116"/>
       <c r="K62" s="117" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L62" s="14"/>
       <c r="M62" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N62" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="72.75">
       <c r="A63" s="30" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B63" s="17" t="s">
         <v>1130</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>1131</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -11920,36 +11918,36 @@
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G63" s="17" t="s">
         <v>1132</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="H63" s="17" t="s">
         <v>1133</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>1134</v>
       </c>
       <c r="I63" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="114" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N63" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="30" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>89</v>
@@ -11963,10 +11961,10 @@
         <v>5.9</v>
       </c>
       <c r="G64" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H64" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I64" s="18" t="s">
         <v>49</v>
@@ -11975,19 +11973,19 @@
       <c r="K64" s="33"/>
       <c r="L64" s="21"/>
       <c r="M64" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="30" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>89</v>
@@ -12007,26 +12005,26 @@
       </c>
       <c r="J65" s="26"/>
       <c r="K65" s="33" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N65" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" ht="24.75">
       <c r="A66" s="30" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>46</v>
@@ -12034,36 +12032,36 @@
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="26" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G66" s="17" t="s">
         <v>1140</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="H66" s="26" t="s">
         <v>1141</v>
-      </c>
-      <c r="H66" s="26" t="s">
-        <v>1142</v>
       </c>
       <c r="I66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="114" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N66" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" ht="48.75">
       <c r="A67" s="30" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>89</v>
@@ -12074,36 +12072,36 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="26" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G67" s="17" t="s">
         <v>1144</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="H67" s="26" t="s">
         <v>1145</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>1146</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="33" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="30" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B68" s="115"/>
       <c r="C68" s="116"/>
@@ -12117,26 +12115,26 @@
       </c>
       <c r="J68" s="116"/>
       <c r="K68" s="115" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="30" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>46</v>
@@ -12144,13 +12142,13 @@
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="26" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H69" s="26" t="s">
         <v>1151</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>1152</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>49</v>
@@ -12159,19 +12157,19 @@
       <c r="K69" s="26"/>
       <c r="L69" s="4"/>
       <c r="M69" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" ht="24">
       <c r="A70" s="30" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>89</v>
@@ -12182,7 +12180,7 @@
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
       <c r="F70" s="8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G70" s="17"/>
       <c r="H70" s="8"/>
@@ -12191,23 +12189,23 @@
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N70" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>89</v>
@@ -12221,10 +12219,10 @@
         <v>4.5</v>
       </c>
       <c r="G71" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>1121</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>1122</v>
       </c>
       <c r="I71" s="18" t="s">
         <v>49</v>
@@ -12233,19 +12231,19 @@
       <c r="K71" s="33"/>
       <c r="L71" s="4"/>
       <c r="M71" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="30" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>89</v>
@@ -12259,10 +12257,10 @@
         <v>145</v>
       </c>
       <c r="G72" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H72" s="26" t="s">
         <v>1121</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>1122</v>
       </c>
       <c r="I72" s="18" t="s">
         <v>49</v>
@@ -12271,19 +12269,19 @@
       <c r="K72" s="33"/>
       <c r="L72" s="4"/>
       <c r="M72" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N72" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="30" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B73" s="36" t="s">
         <v>89</v>
@@ -12301,23 +12299,23 @@
       </c>
       <c r="J73" s="118"/>
       <c r="K73" s="114" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" ht="36">
       <c r="A74" s="30" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>66</v>
@@ -12339,23 +12337,23 @@
       </c>
       <c r="J74" s="119"/>
       <c r="K74" s="47" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N74" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" ht="24.75">
       <c r="A75" s="30" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>89</v>
@@ -12366,7 +12364,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="18" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G75" s="18"/>
       <c r="H75" s="18"/>
@@ -12375,23 +12373,23 @@
       </c>
       <c r="J75" s="18"/>
       <c r="K75" s="114" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="30" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>89</v>
@@ -12411,23 +12409,23 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="35" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="30" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>89</v>
@@ -12441,10 +12439,10 @@
         <v>16</v>
       </c>
       <c r="G77" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H77" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>49</v>
@@ -12453,19 +12451,19 @@
       <c r="K77" s="19"/>
       <c r="L77" s="4"/>
       <c r="M77" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O77" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="30" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>89</v>
@@ -12479,10 +12477,10 @@
         <v>1E-4</v>
       </c>
       <c r="G78" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H78" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>49</v>
@@ -12491,19 +12489,19 @@
       <c r="K78" s="19"/>
       <c r="L78" s="4"/>
       <c r="M78" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="30" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B79" s="115" t="s">
         <v>89</v>
@@ -12514,7 +12512,7 @@
       <c r="D79" s="115"/>
       <c r="E79" s="115"/>
       <c r="F79" s="116" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G79" s="115"/>
       <c r="H79" s="116"/>
@@ -12523,23 +12521,23 @@
       </c>
       <c r="J79" s="116"/>
       <c r="K79" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N79" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="30" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>89</v>
@@ -12553,10 +12551,10 @@
         <v>20</v>
       </c>
       <c r="G80" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H80" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I80" s="18" t="s">
         <v>49</v>
@@ -12565,19 +12563,19 @@
       <c r="K80" s="33"/>
       <c r="L80" s="4"/>
       <c r="M80" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N80" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" ht="36.75">
       <c r="A81" s="30" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>89</v>
@@ -12595,26 +12593,26 @@
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="114" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N81" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" ht="72.75">
       <c r="A82" s="30" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>46</v>
@@ -12622,36 +12620,36 @@
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G82" s="17" t="s">
         <v>1132</v>
       </c>
-      <c r="G82" s="17" t="s">
+      <c r="H82" s="17" t="s">
         <v>1133</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>1134</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="114" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N82" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="30" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>89</v>
@@ -12665,10 +12663,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H83" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>49</v>
@@ -12677,19 +12675,19 @@
       <c r="K83" s="33"/>
       <c r="L83" s="21"/>
       <c r="M83" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="30" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>89</v>
@@ -12709,26 +12707,26 @@
       </c>
       <c r="J84" s="26"/>
       <c r="K84" s="33" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" ht="24.75">
       <c r="A85" s="30" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>46</v>
@@ -12736,36 +12734,36 @@
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="26" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G85" s="17" t="s">
         <v>1140</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="H85" s="26" t="s">
         <v>1141</v>
-      </c>
-      <c r="H85" s="26" t="s">
-        <v>1142</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="114" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N85" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" ht="48.75">
       <c r="A86" s="30" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>89</v>
@@ -12776,36 +12774,36 @@
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="26" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G86" s="17" t="s">
         <v>1144</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="H86" s="26" t="s">
         <v>1145</v>
-      </c>
-      <c r="H86" s="26" t="s">
-        <v>1146</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="33" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N86" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="30" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>89</v>
@@ -12825,22 +12823,22 @@
       <c r="K87" s="26"/>
       <c r="L87" s="4"/>
       <c r="M87" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N87" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="30" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>46</v>
@@ -12848,13 +12846,13 @@
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="26" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H88" s="26" t="s">
         <v>1151</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H88" s="26" t="s">
-        <v>1152</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>49</v>
@@ -12863,19 +12861,19 @@
       <c r="K88" s="26"/>
       <c r="L88" s="4"/>
       <c r="M88" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="30" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>89</v>
@@ -12886,7 +12884,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G89" s="17"/>
       <c r="H89" s="8"/>
@@ -12895,23 +12893,23 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="116" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="10" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>89</v>
@@ -12925,10 +12923,10 @@
         <v>120</v>
       </c>
       <c r="G90" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H90" s="18" t="s">
         <v>1121</v>
-      </c>
-      <c r="H90" s="18" t="s">
-        <v>1122</v>
       </c>
       <c r="I90" s="18" t="s">
         <v>49</v>
@@ -12937,19 +12935,19 @@
       <c r="K90" s="33"/>
       <c r="L90" s="4"/>
       <c r="M90" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="30" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>89</v>
@@ -12963,10 +12961,10 @@
         <v>15</v>
       </c>
       <c r="G91" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H91" s="26" t="s">
         <v>1121</v>
-      </c>
-      <c r="H91" s="26" t="s">
-        <v>1122</v>
       </c>
       <c r="I91" s="18" t="s">
         <v>49</v>
@@ -12975,19 +12973,19 @@
       <c r="K91" s="33"/>
       <c r="L91" s="4"/>
       <c r="M91" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N91" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="30" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B92" s="36" t="s">
         <v>89</v>
@@ -13005,23 +13003,23 @@
       </c>
       <c r="J92" s="114"/>
       <c r="K92" s="114" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N92" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="30" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>66</v>
@@ -13043,17 +13041,17 @@
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="33" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P93" s="14"/>
     </row>
@@ -13599,7 +13597,7 @@
     </row>
     <row r="14" spans="1:16" ht="24">
       <c r="A14" s="10" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>585</v>
@@ -13610,7 +13608,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="26" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>15</v>
@@ -13637,7 +13635,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="48" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="8"/>
@@ -20809,7 +20807,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="49"/>
       <c r="K2" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="14" t="s">
@@ -20847,7 +20845,7 @@
       </c>
       <c r="J3" s="49"/>
       <c r="K3" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>57</v>
@@ -20885,7 +20883,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="49"/>
       <c r="K4" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>71</v>
@@ -20923,7 +20921,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="49"/>
       <c r="K5" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>57</v>
@@ -20963,7 +20961,7 @@
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="14" t="s">
@@ -20997,7 +20995,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="49"/>
       <c r="K7" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>57</v>
@@ -21033,7 +21031,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="49"/>
       <c r="K8" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>71</v>
@@ -21073,7 +21071,7 @@
       </c>
       <c r="J9" s="49"/>
       <c r="K9" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>71</v>
@@ -21109,7 +21107,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="49"/>
       <c r="K10" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>71</v>
@@ -21147,7 +21145,7 @@
       </c>
       <c r="J11" s="49"/>
       <c r="K11" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>71</v>
@@ -21183,7 +21181,7 @@
       </c>
       <c r="J12" s="49"/>
       <c r="K12" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>51</v>
@@ -21220,7 +21218,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="49"/>
       <c r="K13" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>57</v>
@@ -21250,7 +21248,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="49"/>
       <c r="K14" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="14" t="s">
@@ -21284,7 +21282,7 @@
       </c>
       <c r="J15" s="49"/>
       <c r="K15" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>71</v>
@@ -21322,7 +21320,7 @@
       <c r="I16" s="17"/>
       <c r="J16" s="49"/>
       <c r="K16" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>71</v>
@@ -21362,7 +21360,7 @@
       </c>
       <c r="J17" s="49"/>
       <c r="K17" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>71</v>
@@ -21392,7 +21390,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="49"/>
       <c r="K18" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="14" t="s">
@@ -21418,7 +21416,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="49"/>
       <c r="K19" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="14" t="s">
@@ -21456,7 +21454,7 @@
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>71</v>
@@ -21494,7 +21492,7 @@
       </c>
       <c r="J21" s="49"/>
       <c r="K21" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>71</v>
@@ -21522,7 +21520,7 @@
       <c r="I22" s="8"/>
       <c r="J22" s="49"/>
       <c r="K22" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="14" t="s">
@@ -21558,7 +21556,7 @@
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>71</v>
@@ -21598,7 +21596,7 @@
       </c>
       <c r="J24" s="49"/>
       <c r="K24" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>71</v>
@@ -21632,7 +21630,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="49"/>
       <c r="K25" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>71</v>
@@ -21660,7 +21658,7 @@
       </c>
       <c r="J26" s="49"/>
       <c r="K26" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="14" t="s">
@@ -21686,7 +21684,7 @@
       </c>
       <c r="J27" s="49"/>
       <c r="K27" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="14" t="s">
@@ -21722,7 +21720,7 @@
       </c>
       <c r="J28" s="49"/>
       <c r="K28" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>71</v>
@@ -21758,7 +21756,7 @@
       <c r="I29" s="8"/>
       <c r="J29" s="49"/>
       <c r="K29" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>140</v>
@@ -21798,7 +21796,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="49"/>
       <c r="K30" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>140</v>
@@ -21840,7 +21838,7 @@
       </c>
       <c r="J31" s="49"/>
       <c r="K31" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>71</v>
@@ -21878,7 +21876,7 @@
       </c>
       <c r="J32" s="49"/>
       <c r="K32" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>71</v>
@@ -21918,7 +21916,7 @@
       </c>
       <c r="J33" s="49"/>
       <c r="K33" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>71</v>
@@ -21958,7 +21956,7 @@
       </c>
       <c r="J34" s="49"/>
       <c r="K34" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>71</v>
@@ -21994,7 +21992,7 @@
       <c r="I35" s="8"/>
       <c r="J35" s="49"/>
       <c r="K35" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>71</v>
@@ -22076,7 +22074,7 @@
       </c>
       <c r="J37" s="49"/>
       <c r="K37" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>71</v>
@@ -22110,7 +22108,7 @@
       <c r="I38" s="25"/>
       <c r="J38" s="49"/>
       <c r="K38" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>71</v>
@@ -22146,7 +22144,7 @@
       </c>
       <c r="J39" s="49"/>
       <c r="K39" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>71</v>
@@ -22180,7 +22178,7 @@
       <c r="I40" s="25"/>
       <c r="J40" s="49"/>
       <c r="K40" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>71</v>
@@ -22214,7 +22212,7 @@
       <c r="I41" s="25"/>
       <c r="J41" s="49"/>
       <c r="K41" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>71</v>
@@ -22248,7 +22246,7 @@
       <c r="I42" s="25"/>
       <c r="J42" s="49"/>
       <c r="K42" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>71</v>
@@ -22282,7 +22280,7 @@
       <c r="I43" s="25"/>
       <c r="J43" s="49"/>
       <c r="K43" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>71</v>
@@ -22316,7 +22314,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="49"/>
       <c r="K44" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>71</v>
@@ -22352,7 +22350,7 @@
       </c>
       <c r="J45" s="49"/>
       <c r="K45" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>71</v>
@@ -22386,7 +22384,7 @@
       <c r="I46" s="25"/>
       <c r="J46" s="49"/>
       <c r="K46" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>71</v>
@@ -22420,7 +22418,7 @@
       <c r="I47" s="25"/>
       <c r="J47" s="49"/>
       <c r="K47" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>71</v>
@@ -22454,7 +22452,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="49"/>
       <c r="K48" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>71</v>
@@ -22490,7 +22488,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="49"/>
       <c r="K49" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>71</v>
@@ -22526,7 +22524,7 @@
       <c r="I50" s="25"/>
       <c r="J50" s="49"/>
       <c r="K50" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>71</v>
@@ -22560,7 +22558,7 @@
       <c r="I51" s="25"/>
       <c r="J51" s="49"/>
       <c r="K51" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>71</v>
@@ -22594,7 +22592,7 @@
       <c r="I52" s="59"/>
       <c r="J52" s="49"/>
       <c r="K52" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>71</v>
@@ -22628,7 +22626,7 @@
       <c r="I53" s="25"/>
       <c r="J53" s="49"/>
       <c r="K53" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>71</v>
@@ -22662,7 +22660,7 @@
       <c r="I54" s="59"/>
       <c r="J54" s="49"/>
       <c r="K54" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>71</v>
@@ -22698,7 +22696,7 @@
       </c>
       <c r="J55" s="49"/>
       <c r="K55" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>71</v>
@@ -22734,7 +22732,7 @@
       </c>
       <c r="J56" s="49"/>
       <c r="K56" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>71</v>
@@ -22770,7 +22768,7 @@
       </c>
       <c r="J57" s="49"/>
       <c r="K57" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>71</v>
@@ -22806,7 +22804,7 @@
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>71</v>
@@ -22842,7 +22840,7 @@
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>71</v>
@@ -22878,7 +22876,7 @@
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>71</v>
@@ -22914,7 +22912,7 @@
       </c>
       <c r="J61" s="49"/>
       <c r="K61" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>71</v>
@@ -22950,7 +22948,7 @@
       </c>
       <c r="J62" s="49"/>
       <c r="K62" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>71</v>
@@ -22986,7 +22984,7 @@
       </c>
       <c r="J63" s="49"/>
       <c r="K63" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>71</v>
@@ -23020,7 +23018,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="49"/>
       <c r="K64" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>71</v>
@@ -23056,7 +23054,7 @@
       <c r="I65" s="25"/>
       <c r="J65" s="49"/>
       <c r="K65" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>71</v>
@@ -23092,7 +23090,7 @@
       <c r="I66" s="25"/>
       <c r="J66" s="49"/>
       <c r="K66" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>71</v>
@@ -23132,7 +23130,7 @@
       </c>
       <c r="J67" s="49"/>
       <c r="K67" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>71</v>
@@ -23168,7 +23166,7 @@
       <c r="I68" s="25"/>
       <c r="J68" s="49"/>
       <c r="K68" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>71</v>
@@ -23204,7 +23202,7 @@
       </c>
       <c r="J69" s="49"/>
       <c r="K69" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>71</v>
@@ -23240,7 +23238,7 @@
       </c>
       <c r="J70" s="49"/>
       <c r="K70" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>71</v>
@@ -23276,7 +23274,7 @@
       </c>
       <c r="J71" s="49"/>
       <c r="K71" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>71</v>
@@ -23312,7 +23310,7 @@
       </c>
       <c r="J72" s="49"/>
       <c r="K72" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>71</v>
@@ -23348,7 +23346,7 @@
       </c>
       <c r="J73" s="49"/>
       <c r="K73" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>71</v>
@@ -23384,7 +23382,7 @@
       </c>
       <c r="J74" s="49"/>
       <c r="K74" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>71</v>
@@ -23420,7 +23418,7 @@
       </c>
       <c r="J75" s="49"/>
       <c r="K75" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>71</v>
@@ -23456,7 +23454,7 @@
       </c>
       <c r="J76" s="49"/>
       <c r="K76" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>71</v>
@@ -23492,7 +23490,7 @@
       </c>
       <c r="J77" s="49"/>
       <c r="K77" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>71</v>
@@ -23528,7 +23526,7 @@
       </c>
       <c r="J78" s="49"/>
       <c r="K78" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>71</v>
@@ -23564,7 +23562,7 @@
       </c>
       <c r="J79" s="49"/>
       <c r="K79" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>71</v>
@@ -23600,7 +23598,7 @@
       </c>
       <c r="J80" s="49"/>
       <c r="K80" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>71</v>
@@ -23636,7 +23634,7 @@
       </c>
       <c r="J81" s="49"/>
       <c r="K81" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>71</v>
@@ -23672,7 +23670,7 @@
       <c r="I82" s="25"/>
       <c r="J82" s="49"/>
       <c r="K82" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>71</v>
@@ -23708,7 +23706,7 @@
       </c>
       <c r="J83" s="49"/>
       <c r="K83" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>71</v>
@@ -23744,7 +23742,7 @@
       <c r="I84" s="25"/>
       <c r="J84" s="49"/>
       <c r="K84" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>71</v>
@@ -23780,7 +23778,7 @@
       </c>
       <c r="J85" s="49"/>
       <c r="K85" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>71</v>
@@ -23816,7 +23814,7 @@
       <c r="I86" s="25"/>
       <c r="J86" s="49"/>
       <c r="K86" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>71</v>
@@ -23850,7 +23848,7 @@
       <c r="I87" s="59"/>
       <c r="J87" s="49"/>
       <c r="K87" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>71</v>
@@ -23888,7 +23886,7 @@
       </c>
       <c r="J88" s="49"/>
       <c r="K88" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>71</v>
@@ -23924,7 +23922,7 @@
       </c>
       <c r="J89" s="49"/>
       <c r="K89" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>71</v>
@@ -23958,7 +23956,7 @@
       <c r="I90" s="25"/>
       <c r="J90" s="49"/>
       <c r="K90" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>71</v>
@@ -23994,7 +23992,7 @@
       </c>
       <c r="J91" s="49"/>
       <c r="K91" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>71</v>
@@ -24028,7 +24026,7 @@
       <c r="I92" s="25"/>
       <c r="J92" s="49"/>
       <c r="K92" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>71</v>
@@ -24064,7 +24062,7 @@
       </c>
       <c r="J93" s="49"/>
       <c r="K93" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>71</v>
@@ -24098,7 +24096,7 @@
       <c r="I94" s="25"/>
       <c r="J94" s="49"/>
       <c r="K94" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>71</v>
@@ -24134,7 +24132,7 @@
       <c r="I95" s="25"/>
       <c r="J95" s="49"/>
       <c r="K95" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>71</v>
@@ -24170,7 +24168,7 @@
       <c r="I96" s="25"/>
       <c r="J96" s="49"/>
       <c r="K96" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>71</v>
@@ -24206,7 +24204,7 @@
       </c>
       <c r="J97" s="49"/>
       <c r="K97" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>71</v>
@@ -24240,7 +24238,7 @@
       <c r="I98" s="25"/>
       <c r="J98" s="49"/>
       <c r="K98" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>71</v>
@@ -24278,7 +24276,7 @@
       </c>
       <c r="J99" s="49"/>
       <c r="K99" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>71</v>
@@ -24316,7 +24314,7 @@
       </c>
       <c r="J100" s="49"/>
       <c r="K100" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>71</v>
@@ -24350,7 +24348,7 @@
       <c r="I101" s="25"/>
       <c r="J101" s="49"/>
       <c r="K101" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>71</v>
@@ -24388,7 +24386,7 @@
       </c>
       <c r="J102" s="49"/>
       <c r="K102" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>71</v>
@@ -24424,7 +24422,7 @@
       <c r="I103" s="59"/>
       <c r="J103" s="49"/>
       <c r="K103" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>71</v>
@@ -24460,7 +24458,7 @@
       </c>
       <c r="J104" s="49"/>
       <c r="K104" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>71</v>
@@ -24496,7 +24494,7 @@
       </c>
       <c r="J105" s="49"/>
       <c r="K105" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>71</v>
@@ -24532,7 +24530,7 @@
       </c>
       <c r="J106" s="49"/>
       <c r="K106" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>71</v>
@@ -24568,7 +24566,7 @@
       </c>
       <c r="J107" s="49"/>
       <c r="K107" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>71</v>
@@ -24604,7 +24602,7 @@
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>71</v>
@@ -24640,7 +24638,7 @@
       </c>
       <c r="J109" s="49"/>
       <c r="K109" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>71</v>
@@ -24676,7 +24674,7 @@
       </c>
       <c r="J110" s="49"/>
       <c r="K110" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>71</v>
@@ -24712,7 +24710,7 @@
       </c>
       <c r="J111" s="49"/>
       <c r="K111" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>71</v>
@@ -24748,7 +24746,7 @@
       </c>
       <c r="J112" s="49"/>
       <c r="K112" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>71</v>
@@ -24784,7 +24782,7 @@
       </c>
       <c r="J113" s="49"/>
       <c r="K113" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>71</v>
@@ -24818,7 +24816,7 @@
       <c r="I114" s="25"/>
       <c r="J114" s="49"/>
       <c r="K114" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>71</v>
@@ -24854,7 +24852,7 @@
       </c>
       <c r="J115" s="49"/>
       <c r="K115" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>71</v>
@@ -24888,7 +24886,7 @@
       <c r="I116" s="25"/>
       <c r="J116" s="49"/>
       <c r="K116" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>71</v>
@@ -24922,7 +24920,7 @@
       <c r="I117" s="25"/>
       <c r="J117" s="49"/>
       <c r="K117" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>71</v>
@@ -24958,7 +24956,7 @@
       </c>
       <c r="J118" s="49"/>
       <c r="K118" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>71</v>
@@ -24994,7 +24992,7 @@
       </c>
       <c r="J119" s="49"/>
       <c r="K119" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L119" s="5" t="s">
         <v>71</v>
@@ -25028,7 +25026,7 @@
       <c r="I120" s="59"/>
       <c r="J120" s="49"/>
       <c r="K120" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>71</v>
@@ -25064,7 +25062,7 @@
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L121" s="5" t="s">
         <v>71</v>
@@ -25100,7 +25098,7 @@
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>71</v>
@@ -25136,7 +25134,7 @@
       </c>
       <c r="J123" s="49"/>
       <c r="K123" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>71</v>
@@ -25172,7 +25170,7 @@
       </c>
       <c r="J124" s="49"/>
       <c r="K124" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>71</v>
@@ -25208,7 +25206,7 @@
       </c>
       <c r="J125" s="49"/>
       <c r="K125" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L125" s="5" t="s">
         <v>71</v>
@@ -25244,7 +25242,7 @@
       </c>
       <c r="J126" s="49"/>
       <c r="K126" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L126" s="5" t="s">
         <v>71</v>
@@ -25280,7 +25278,7 @@
       </c>
       <c r="J127" s="49"/>
       <c r="K127" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L127" s="5" t="s">
         <v>71</v>
@@ -25316,7 +25314,7 @@
       </c>
       <c r="J128" s="49"/>
       <c r="K128" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L128" s="5" t="s">
         <v>71</v>
@@ -25352,7 +25350,7 @@
       </c>
       <c r="J129" s="49"/>
       <c r="K129" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L129" s="5" t="s">
         <v>71</v>
@@ -25388,7 +25386,7 @@
       </c>
       <c r="J130" s="49"/>
       <c r="K130" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>71</v>
@@ -25424,7 +25422,7 @@
       <c r="I131" s="25"/>
       <c r="J131" s="49"/>
       <c r="K131" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L131" s="5" t="s">
         <v>71</v>
@@ -25460,7 +25458,7 @@
       </c>
       <c r="J132" s="49"/>
       <c r="K132" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L132" s="5" t="s">
         <v>71</v>
@@ -25496,7 +25494,7 @@
       <c r="I133" s="25"/>
       <c r="J133" s="49"/>
       <c r="K133" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L133" s="5" t="s">
         <v>71</v>
@@ -25532,7 +25530,7 @@
       </c>
       <c r="J134" s="49"/>
       <c r="K134" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L134" s="5" t="s">
         <v>71</v>
@@ -25568,7 +25566,7 @@
       <c r="I135" s="25"/>
       <c r="J135" s="49"/>
       <c r="K135" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>71</v>
@@ -25602,7 +25600,7 @@
       <c r="I136" s="59"/>
       <c r="J136" s="49"/>
       <c r="K136" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L136" s="5" t="s">
         <v>71</v>
@@ -25636,7 +25634,7 @@
       <c r="I137" s="25"/>
       <c r="J137" s="49"/>
       <c r="K137" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L137" s="5" t="s">
         <v>71</v>
@@ -25670,7 +25668,7 @@
       <c r="I138" s="25"/>
       <c r="J138" s="49"/>
       <c r="K138" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L138" s="5" t="s">
         <v>71</v>
@@ -25704,7 +25702,7 @@
       <c r="I139" s="25"/>
       <c r="J139" s="49"/>
       <c r="K139" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>71</v>
@@ -25738,7 +25736,7 @@
       <c r="I140" s="25"/>
       <c r="J140" s="49"/>
       <c r="K140" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L140" s="5" t="s">
         <v>71</v>
@@ -25774,7 +25772,7 @@
       </c>
       <c r="J141" s="49"/>
       <c r="K141" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L141" s="5" t="s">
         <v>71</v>
@@ -25808,7 +25806,7 @@
       <c r="I142" s="25"/>
       <c r="J142" s="49"/>
       <c r="K142" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L142" s="5" t="s">
         <v>71</v>
@@ -25842,7 +25840,7 @@
       <c r="I143" s="25"/>
       <c r="J143" s="49"/>
       <c r="K143" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L143" s="5" t="s">
         <v>71</v>
@@ -25878,7 +25876,7 @@
       </c>
       <c r="J144" s="49"/>
       <c r="K144" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L144" s="5" t="s">
         <v>71</v>
@@ -25914,7 +25912,7 @@
       </c>
       <c r="J145" s="49"/>
       <c r="K145" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>71</v>
@@ -25950,7 +25948,7 @@
       </c>
       <c r="J146" s="49"/>
       <c r="K146" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>71</v>
@@ -25986,7 +25984,7 @@
       </c>
       <c r="J147" s="49"/>
       <c r="K147" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L147" s="5" t="s">
         <v>71</v>
@@ -26022,7 +26020,7 @@
       </c>
       <c r="J148" s="49"/>
       <c r="K148" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L148" s="5" t="s">
         <v>71</v>
@@ -26058,7 +26056,7 @@
       </c>
       <c r="J149" s="49"/>
       <c r="K149" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L149" s="5" t="s">
         <v>71</v>
@@ -26094,7 +26092,7 @@
       </c>
       <c r="J150" s="49"/>
       <c r="K150" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L150" s="5" t="s">
         <v>71</v>
@@ -26130,7 +26128,7 @@
       </c>
       <c r="J151" s="49"/>
       <c r="K151" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L151" s="5" t="s">
         <v>71</v>
@@ -26166,7 +26164,7 @@
       </c>
       <c r="J152" s="49"/>
       <c r="K152" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L152" s="5" t="s">
         <v>71</v>
@@ -26202,7 +26200,7 @@
       </c>
       <c r="J153" s="49"/>
       <c r="K153" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L153" s="5" t="s">
         <v>71</v>
@@ -26236,7 +26234,7 @@
       <c r="I154" s="59"/>
       <c r="J154" s="56"/>
       <c r="K154" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L154" s="5" t="s">
         <v>71</v>
@@ -26270,7 +26268,7 @@
       <c r="I155" s="33"/>
       <c r="J155" s="56"/>
       <c r="K155" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>71</v>
@@ -26754,7 +26752,7 @@
     </row>
     <row r="10" spans="1:16" ht="24">
       <c r="A10" s="67" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>787</v>
@@ -26768,14 +26766,14 @@
         <v>347</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="59"/>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD91FF9-D35E-4770-8A0B-544E7A81E593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EB14ED-C40F-47BF-B9AC-E54B52784344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16620" yWindow="4695" windowWidth="28095" windowHeight="24255" tabRatio="500" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27825" yWindow="7020" windowWidth="24735" windowHeight="19980" tabRatio="500" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="1193">
   <si>
     <t>Patient Inputs</t>
   </si>
@@ -3289,9 +3289,6 @@
  7.0</t>
   </si>
   <si>
-    <t>guyton2006medical,         Rodgers2005physiologically</t>
-  </si>
-  <si>
     <t>p384</t>
   </si>
   <si>
@@ -3748,6 +3745,12 @@
   </si>
   <si>
     <t>TotalKidneySmallVasculature = TotalKidney/2 &lt;br&gt; SmallVasculature = TotalKidneySmallVasculature/5</t>
+  </si>
+  <si>
+    <t>[6.0,7.4]</t>
+  </si>
+  <si>
+    <t>guyton2006medical, rodgers2005physiologically</t>
   </si>
 </sst>
 </file>
@@ -5406,7 +5409,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="10" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>844</v>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="10" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>876</v>
@@ -5782,7 +5785,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="10" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>876</v>
@@ -6020,7 +6023,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="10" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>844</v>
@@ -6432,7 +6435,7 @@
     </row>
     <row r="39" spans="1:16" ht="96">
       <c r="A39" s="10" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>862</v>
@@ -6474,7 +6477,7 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="10" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>919</v>
@@ -6539,7 +6542,7 @@
         <v>49</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="66" t="s">
@@ -6964,7 +6967,7 @@
     </row>
     <row r="53" spans="1:16" ht="108">
       <c r="A53" s="10" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>844</v>
@@ -9400,20 +9403,20 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="8" t="s">
-        <v>1039</v>
+        <v>1191</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>1040</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>1041</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="109"/>
       <c r="K5" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>1039</v>
@@ -9433,7 +9436,7 @@
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1">
       <c r="A6" s="10" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>17</v>
@@ -9455,7 +9458,7 @@
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
@@ -9474,7 +9477,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="67" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>14</v>
@@ -9512,7 +9515,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="67" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="8" t="s">
@@ -9524,10 +9527,10 @@
         <v>0.85</v>
       </c>
       <c r="G8" s="111" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H8" s="111" t="s">
         <v>1047</v>
-      </c>
-      <c r="H8" s="111" t="s">
-        <v>1048</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>49</v>
@@ -9552,7 +9555,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="120" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>923</v>
@@ -9590,7 +9593,7 @@
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A10" s="28" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
@@ -9640,7 +9643,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="67" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>14</v>
@@ -9657,7 +9660,7 @@
         <v>104</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>49</v>
@@ -9682,7 +9685,7 @@
     </row>
     <row r="12" spans="1:16" s="1" customFormat="1">
       <c r="A12" s="67" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>14</v>
@@ -9699,7 +9702,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>49</v>
@@ -9724,7 +9727,7 @@
     </row>
     <row r="13" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A13" s="28" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -9774,7 +9777,7 @@
     </row>
     <row r="14" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A14" s="30" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>923</v>
@@ -9796,32 +9799,32 @@
         <v>273</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="33" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L14" s="5">
         <v>3140</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A15" s="30" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
@@ -9839,20 +9842,20 @@
         <v>1032</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I15" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="33" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L15" s="5">
         <v>3140</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>71</v>
@@ -9864,7 +9867,7 @@
     </row>
     <row r="16" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A16" s="30" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
@@ -9882,20 +9885,20 @@
         <v>1032</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I16" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="33" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L16" s="5">
         <v>3140</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>71</v>
@@ -9907,7 +9910,7 @@
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A17" s="30" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>923</v>
@@ -9929,32 +9932,32 @@
         <v>273</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="33" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L17" s="5">
         <v>2680</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A18" s="30" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>17</v>
@@ -9972,20 +9975,20 @@
         <v>1032</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="33" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L18" s="5">
         <v>2680</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>71</v>
@@ -9997,7 +10000,7 @@
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A19" s="30" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
@@ -10015,20 +10018,20 @@
         <v>1032</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="33" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="L19" s="5">
         <v>2680</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>71</v>
@@ -10040,7 +10043,7 @@
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A20" s="30" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>923</v>
@@ -10062,32 +10065,32 @@
         <v>273</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L20" s="5">
         <v>1020</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A21" s="30" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>17</v>
@@ -10105,20 +10108,20 @@
         <v>1032</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I21" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L21" s="5">
         <v>1020</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>71</v>
@@ -10130,7 +10133,7 @@
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A22" s="30" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>17</v>
@@ -10148,20 +10151,20 @@
         <v>1032</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L22" s="5">
         <v>1020</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>71</v>
@@ -10173,7 +10176,7 @@
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A23" s="30" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>923</v>
@@ -10195,32 +10198,32 @@
         <v>273</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I23" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L23" s="5">
         <v>730</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N23" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A24" s="30" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>17</v>
@@ -10238,20 +10241,20 @@
         <v>1032</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L24" s="5">
         <v>730</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>71</v>
@@ -10263,7 +10266,7 @@
     </row>
     <row r="25" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A25" s="30" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>17</v>
@@ -10281,20 +10284,20 @@
         <v>1032</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L25" s="5">
         <v>730</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>71</v>
@@ -10306,7 +10309,7 @@
     </row>
     <row r="26" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A26" s="30" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>923</v>
@@ -10328,32 +10331,32 @@
         <v>273</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L26" s="5">
         <v>110</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A27" s="30" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>17</v>
@@ -10371,20 +10374,20 @@
         <v>1032</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L27" s="5">
         <v>110</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N27" s="5" t="s">
         <v>71</v>
@@ -10396,7 +10399,7 @@
     </row>
     <row r="28" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A28" s="30" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>17</v>
@@ -10414,20 +10417,20 @@
         <v>1032</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L28" s="5">
         <v>110</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N28" s="5" t="s">
         <v>71</v>
@@ -10439,7 +10442,7 @@
     </row>
     <row r="29" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A29" s="30" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>923</v>
@@ -10461,32 +10464,32 @@
         <v>273</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L29" s="5">
         <v>110</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A30" s="30" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>17</v>
@@ -10504,20 +10507,20 @@
         <v>1032</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I30" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L30" s="5">
         <v>110</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>71</v>
@@ -10529,7 +10532,7 @@
     </row>
     <row r="31" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A31" s="30" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>17</v>
@@ -10547,20 +10550,20 @@
         <v>1032</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L31" s="5">
         <v>110</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>71</v>
@@ -10572,7 +10575,7 @@
     </row>
     <row r="32" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A32" s="30" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>923</v>
@@ -10594,32 +10597,32 @@
         <v>273</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L32" s="5">
         <v>1030</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A33" s="30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>17</v>
@@ -10637,20 +10640,20 @@
         <v>1032</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L33" s="5">
         <v>1030</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>71</v>
@@ -10662,7 +10665,7 @@
     </row>
     <row r="34" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A34" s="30" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>17</v>
@@ -10680,20 +10683,20 @@
         <v>1032</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L34" s="5">
         <v>1030</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>71</v>
@@ -10705,7 +10708,7 @@
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A35" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>923</v>
@@ -10729,32 +10732,32 @@
         <v>273</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L35" s="5">
         <v>160</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O35" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A36" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>17</v>
@@ -10772,20 +10775,20 @@
         <v>1032</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L36" s="5">
         <v>160</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>71</v>
@@ -10797,7 +10800,7 @@
     </row>
     <row r="37" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A37" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>17</v>
@@ -10815,20 +10818,20 @@
         <v>1032</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L37" s="5">
         <v>160</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N37" s="5" t="s">
         <v>71</v>
@@ -10840,7 +10843,7 @@
     </row>
     <row r="38" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A38" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>923</v>
@@ -10864,32 +10867,32 @@
         <v>273</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L38" s="5">
         <v>160</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A39" s="30" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>17</v>
@@ -10907,20 +10910,20 @@
         <v>1032</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L39" s="5">
         <v>160</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N39" s="5" t="s">
         <v>71</v>
@@ -10932,7 +10935,7 @@
     </row>
     <row r="40" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A40" s="30" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>17</v>
@@ -10950,20 +10953,20 @@
         <v>1032</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L40" s="5">
         <v>160</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N40" s="5" t="s">
         <v>71</v>
@@ -10975,7 +10978,7 @@
     </row>
     <row r="41" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A41" s="30" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>923</v>
@@ -10997,32 +11000,32 @@
         <v>273</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L41" s="5">
         <v>13090</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A42" s="30" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>17</v>
@@ -11040,20 +11043,20 @@
         <v>1032</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I42" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L42" s="5">
         <v>13090</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>71</v>
@@ -11065,7 +11068,7 @@
     </row>
     <row r="43" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A43" s="30" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>17</v>
@@ -11083,20 +11086,20 @@
         <v>1032</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L43" s="5">
         <v>13090</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>71</v>
@@ -11108,7 +11111,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="30" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>89</v>
@@ -11119,10 +11122,10 @@
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="52" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G44" s="17" t="s">
         <v>1091</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>1092</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="26" t="s">
@@ -11132,7 +11135,7 @@
       <c r="K44" s="33"/>
       <c r="L44" s="21"/>
       <c r="M44" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>71</v>
@@ -11144,7 +11147,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="30" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>89</v>
@@ -11155,7 +11158,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="113" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G45" s="17" t="s">
         <v>547</v>
@@ -11166,11 +11169,11 @@
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="33" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>71</v>
@@ -11182,7 +11185,7 @@
     </row>
     <row r="46" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A46" s="30" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>923</v>
@@ -11204,32 +11207,32 @@
         <v>273</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L46" s="5">
         <v>190</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A47" s="30" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>17</v>
@@ -11247,20 +11250,20 @@
         <v>1032</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L47" s="5">
         <v>190</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>71</v>
@@ -11272,7 +11275,7 @@
     </row>
     <row r="48" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A48" s="30" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>17</v>
@@ -11290,20 +11293,20 @@
         <v>1032</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I48" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L48" s="5">
         <v>190</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>71</v>
@@ -11315,7 +11318,7 @@
     </row>
     <row r="49" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A49" s="30" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>923</v>
@@ -11337,32 +11340,32 @@
         <v>273</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I49" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L49" s="5">
         <v>1550</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A50" s="30" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>17</v>
@@ -11380,20 +11383,20 @@
         <v>1032</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I50" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L50" s="5">
         <v>1550</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N50" s="5" t="s">
         <v>71</v>
@@ -11405,7 +11408,7 @@
     </row>
     <row r="51" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A51" s="30" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
@@ -11423,20 +11426,20 @@
         <v>1032</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I51" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L51" s="5">
         <v>1550</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N51" s="5" t="s">
         <v>71</v>
@@ -11448,7 +11451,7 @@
     </row>
     <row r="52" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A52" s="30" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>923</v>
@@ -11470,32 +11473,32 @@
         <v>273</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I52" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L52" s="5">
         <v>100</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A53" s="30" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
@@ -11513,20 +11516,20 @@
         <v>1032</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I53" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L53" s="5">
         <v>100</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>71</v>
@@ -11538,7 +11541,7 @@
     </row>
     <row r="54" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A54" s="30" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>17</v>
@@ -11556,20 +11559,20 @@
         <v>1032</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L54" s="5">
         <v>100</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>71</v>
@@ -11581,7 +11584,7 @@
     </row>
     <row r="55" spans="1:16" ht="24">
       <c r="A55" s="28" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1</v>
@@ -11631,7 +11634,7 @@
     </row>
     <row r="56" spans="1:16" ht="24.75">
       <c r="A56" s="30" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>89</v>
@@ -11642,7 +11645,7 @@
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="18" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G56" s="18" t="s">
         <v>143</v>
@@ -11653,23 +11656,23 @@
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="114" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="30" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>89</v>
@@ -11693,19 +11696,19 @@
         <v>1034</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="30" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>89</v>
@@ -11719,10 +11722,10 @@
         <v>25</v>
       </c>
       <c r="G58" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H58" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>49</v>
@@ -11733,19 +11736,19 @@
         <v>1036</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="30" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>89</v>
@@ -11759,10 +11762,10 @@
         <v>1.2</v>
       </c>
       <c r="G59" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H59" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I59" s="18" t="s">
         <v>49</v>
@@ -11770,22 +11773,22 @@
       <c r="J59" s="17"/>
       <c r="K59" s="19"/>
       <c r="L59" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" ht="24">
       <c r="A60" s="30" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>89</v>
@@ -11796,7 +11799,7 @@
       <c r="D60" s="115"/>
       <c r="E60" s="115"/>
       <c r="F60" s="116" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G60" s="115"/>
       <c r="H60" s="116"/>
@@ -11805,23 +11808,23 @@
       </c>
       <c r="J60" s="116"/>
       <c r="K60" s="116" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L60" s="8"/>
       <c r="M60" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="30" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>89</v>
@@ -11835,10 +11838,10 @@
         <v>116</v>
       </c>
       <c r="G61" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H61" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>49</v>
@@ -11847,19 +11850,19 @@
       <c r="K61" s="33"/>
       <c r="L61" s="14"/>
       <c r="M61" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" ht="36.75">
       <c r="A62" s="30" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B62" s="115"/>
       <c r="C62" s="116"/>
@@ -11873,26 +11876,26 @@
       </c>
       <c r="J62" s="116"/>
       <c r="K62" s="117" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L62" s="14"/>
       <c r="M62" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N62" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="72.75">
       <c r="A63" s="30" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B63" s="17" t="s">
         <v>1121</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>1122</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -11900,36 +11903,36 @@
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G63" s="17" t="s">
         <v>1123</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="H63" s="17" t="s">
         <v>1124</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>1125</v>
       </c>
       <c r="I63" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="114" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N63" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="30" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>89</v>
@@ -11943,10 +11946,10 @@
         <v>5.9</v>
       </c>
       <c r="G64" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H64" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I64" s="18" t="s">
         <v>49</v>
@@ -11955,19 +11958,19 @@
       <c r="K64" s="33"/>
       <c r="L64" s="21"/>
       <c r="M64" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="30" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>89</v>
@@ -11987,26 +11990,26 @@
       </c>
       <c r="J65" s="26"/>
       <c r="K65" s="33" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N65" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" ht="24.75">
       <c r="A66" s="30" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>46</v>
@@ -12014,36 +12017,36 @@
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="26" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G66" s="17" t="s">
         <v>1131</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="H66" s="26" t="s">
         <v>1132</v>
-      </c>
-      <c r="H66" s="26" t="s">
-        <v>1133</v>
       </c>
       <c r="I66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="114" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N66" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" ht="48.75">
       <c r="A67" s="30" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>89</v>
@@ -12054,36 +12057,36 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G67" s="17" t="s">
         <v>1135</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="H67" s="26" t="s">
         <v>1136</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>1137</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="33" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="30" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B68" s="115"/>
       <c r="C68" s="116"/>
@@ -12097,26 +12100,26 @@
       </c>
       <c r="J68" s="116"/>
       <c r="K68" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="30" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>46</v>
@@ -12124,13 +12127,13 @@
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="26" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H69" s="26" t="s">
         <v>1142</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>1143</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>49</v>
@@ -12139,19 +12142,19 @@
       <c r="K69" s="26"/>
       <c r="L69" s="4"/>
       <c r="M69" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" ht="24">
       <c r="A70" s="30" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>89</v>
@@ -12162,7 +12165,7 @@
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
       <c r="F70" s="8" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G70" s="17"/>
       <c r="H70" s="8"/>
@@ -12171,23 +12174,23 @@
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="116" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N70" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>89</v>
@@ -12201,10 +12204,10 @@
         <v>4.5</v>
       </c>
       <c r="G71" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>1112</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>1113</v>
       </c>
       <c r="I71" s="18" t="s">
         <v>49</v>
@@ -12213,19 +12216,19 @@
       <c r="K71" s="33"/>
       <c r="L71" s="4"/>
       <c r="M71" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="30" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>89</v>
@@ -12239,10 +12242,10 @@
         <v>145</v>
       </c>
       <c r="G72" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H72" s="26" t="s">
         <v>1112</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>1113</v>
       </c>
       <c r="I72" s="18" t="s">
         <v>49</v>
@@ -12251,19 +12254,19 @@
       <c r="K72" s="33"/>
       <c r="L72" s="4"/>
       <c r="M72" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N72" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="30" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B73" s="36" t="s">
         <v>89</v>
@@ -12281,23 +12284,23 @@
       </c>
       <c r="J73" s="118"/>
       <c r="K73" s="114" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" ht="36">
       <c r="A74" s="30" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>66</v>
@@ -12319,23 +12322,23 @@
       </c>
       <c r="J74" s="119"/>
       <c r="K74" s="47" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N74" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" ht="24.75">
       <c r="A75" s="30" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>89</v>
@@ -12346,7 +12349,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="18" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G75" s="18"/>
       <c r="H75" s="18"/>
@@ -12355,23 +12358,23 @@
       </c>
       <c r="J75" s="18"/>
       <c r="K75" s="114" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="30" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>89</v>
@@ -12391,23 +12394,23 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="35" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="30" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>89</v>
@@ -12421,10 +12424,10 @@
         <v>16</v>
       </c>
       <c r="G77" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H77" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>49</v>
@@ -12433,19 +12436,19 @@
       <c r="K77" s="19"/>
       <c r="L77" s="4"/>
       <c r="M77" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O77" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="30" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>89</v>
@@ -12459,10 +12462,10 @@
         <v>1E-4</v>
       </c>
       <c r="G78" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H78" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>49</v>
@@ -12471,19 +12474,19 @@
       <c r="K78" s="19"/>
       <c r="L78" s="4"/>
       <c r="M78" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="30" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B79" s="115" t="s">
         <v>89</v>
@@ -12494,7 +12497,7 @@
       <c r="D79" s="115"/>
       <c r="E79" s="115"/>
       <c r="F79" s="116" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G79" s="115"/>
       <c r="H79" s="116"/>
@@ -12503,23 +12506,23 @@
       </c>
       <c r="J79" s="116"/>
       <c r="K79" s="116" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N79" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="30" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>89</v>
@@ -12533,10 +12536,10 @@
         <v>20</v>
       </c>
       <c r="G80" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H80" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I80" s="18" t="s">
         <v>49</v>
@@ -12545,19 +12548,19 @@
       <c r="K80" s="33"/>
       <c r="L80" s="4"/>
       <c r="M80" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N80" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" ht="36.75">
       <c r="A81" s="30" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>89</v>
@@ -12575,26 +12578,26 @@
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="114" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N81" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" ht="72.75">
       <c r="A82" s="30" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>46</v>
@@ -12602,36 +12605,36 @@
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G82" s="17" t="s">
         <v>1123</v>
       </c>
-      <c r="G82" s="17" t="s">
+      <c r="H82" s="17" t="s">
         <v>1124</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>1125</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="114" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N82" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="30" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>89</v>
@@ -12645,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H83" s="17" t="s">
         <v>1112</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>1113</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>49</v>
@@ -12657,19 +12660,19 @@
       <c r="K83" s="33"/>
       <c r="L83" s="21"/>
       <c r="M83" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="30" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>89</v>
@@ -12689,26 +12692,26 @@
       </c>
       <c r="J84" s="26"/>
       <c r="K84" s="33" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" ht="24.75">
       <c r="A85" s="30" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>46</v>
@@ -12716,36 +12719,36 @@
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="26" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G85" s="17" t="s">
         <v>1131</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="H85" s="26" t="s">
         <v>1132</v>
-      </c>
-      <c r="H85" s="26" t="s">
-        <v>1133</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="114" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N85" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" ht="48.75">
       <c r="A86" s="30" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>89</v>
@@ -12756,36 +12759,36 @@
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G86" s="17" t="s">
         <v>1135</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="H86" s="26" t="s">
         <v>1136</v>
-      </c>
-      <c r="H86" s="26" t="s">
-        <v>1137</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="33" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N86" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="30" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>89</v>
@@ -12805,22 +12808,22 @@
       <c r="K87" s="26"/>
       <c r="L87" s="4"/>
       <c r="M87" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N87" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="30" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>46</v>
@@ -12828,13 +12831,13 @@
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="26" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H88" s="26" t="s">
         <v>1142</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H88" s="26" t="s">
-        <v>1143</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>49</v>
@@ -12843,19 +12846,19 @@
       <c r="K88" s="26"/>
       <c r="L88" s="4"/>
       <c r="M88" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="30" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>89</v>
@@ -12866,7 +12869,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="8" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G89" s="17"/>
       <c r="H89" s="8"/>
@@ -12875,23 +12878,23 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="116" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="10" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>89</v>
@@ -12905,10 +12908,10 @@
         <v>120</v>
       </c>
       <c r="G90" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H90" s="18" t="s">
         <v>1112</v>
-      </c>
-      <c r="H90" s="18" t="s">
-        <v>1113</v>
       </c>
       <c r="I90" s="18" t="s">
         <v>49</v>
@@ -12917,19 +12920,19 @@
       <c r="K90" s="33"/>
       <c r="L90" s="4"/>
       <c r="M90" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="30" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>89</v>
@@ -12943,10 +12946,10 @@
         <v>15</v>
       </c>
       <c r="G91" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H91" s="26" t="s">
         <v>1112</v>
-      </c>
-      <c r="H91" s="26" t="s">
-        <v>1113</v>
       </c>
       <c r="I91" s="18" t="s">
         <v>49</v>
@@ -12955,19 +12958,19 @@
       <c r="K91" s="33"/>
       <c r="L91" s="4"/>
       <c r="M91" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N91" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="30" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B92" s="36" t="s">
         <v>89</v>
@@ -12985,23 +12988,23 @@
       </c>
       <c r="J92" s="114"/>
       <c r="K92" s="114" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N92" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="30" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>66</v>
@@ -13023,17 +13026,17 @@
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="33" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P93" s="14"/>
     </row>
@@ -13579,7 +13582,7 @@
     </row>
     <row r="14" spans="1:16" ht="24">
       <c r="A14" s="10" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>584</v>
@@ -13590,7 +13593,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="26" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>15</v>
@@ -13617,7 +13620,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="48" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="8"/>
@@ -20789,7 +20792,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="49"/>
       <c r="K2" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="14" t="s">
@@ -20827,7 +20830,7 @@
       </c>
       <c r="J3" s="49"/>
       <c r="K3" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>57</v>
@@ -20865,7 +20868,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="49"/>
       <c r="K4" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>71</v>
@@ -20903,7 +20906,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="49"/>
       <c r="K5" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>57</v>
@@ -20943,7 +20946,7 @@
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="14" t="s">
@@ -20977,7 +20980,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="49"/>
       <c r="K7" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>57</v>
@@ -21013,7 +21016,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="49"/>
       <c r="K8" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>71</v>
@@ -21053,7 +21056,7 @@
       </c>
       <c r="J9" s="49"/>
       <c r="K9" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>71</v>
@@ -21089,7 +21092,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="49"/>
       <c r="K10" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>71</v>
@@ -21127,7 +21130,7 @@
       </c>
       <c r="J11" s="49"/>
       <c r="K11" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>71</v>
@@ -21163,7 +21166,7 @@
       </c>
       <c r="J12" s="49"/>
       <c r="K12" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>51</v>
@@ -21200,7 +21203,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="49"/>
       <c r="K13" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>57</v>
@@ -21230,7 +21233,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="49"/>
       <c r="K14" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="14" t="s">
@@ -21264,7 +21267,7 @@
       </c>
       <c r="J15" s="49"/>
       <c r="K15" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>71</v>
@@ -21302,7 +21305,7 @@
       <c r="I16" s="17"/>
       <c r="J16" s="49"/>
       <c r="K16" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>71</v>
@@ -21342,7 +21345,7 @@
       </c>
       <c r="J17" s="49"/>
       <c r="K17" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>71</v>
@@ -21372,7 +21375,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="49"/>
       <c r="K18" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="14" t="s">
@@ -21398,7 +21401,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="49"/>
       <c r="K19" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="14" t="s">
@@ -21436,7 +21439,7 @@
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>71</v>
@@ -21474,7 +21477,7 @@
       </c>
       <c r="J21" s="49"/>
       <c r="K21" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>71</v>
@@ -21502,7 +21505,7 @@
       <c r="I22" s="8"/>
       <c r="J22" s="49"/>
       <c r="K22" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="14" t="s">
@@ -21538,7 +21541,7 @@
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>71</v>
@@ -21578,7 +21581,7 @@
       </c>
       <c r="J24" s="49"/>
       <c r="K24" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>71</v>
@@ -21612,7 +21615,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="49"/>
       <c r="K25" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>71</v>
@@ -21640,7 +21643,7 @@
       </c>
       <c r="J26" s="49"/>
       <c r="K26" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="14" t="s">
@@ -21666,7 +21669,7 @@
       </c>
       <c r="J27" s="49"/>
       <c r="K27" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="14" t="s">
@@ -21702,7 +21705,7 @@
       </c>
       <c r="J28" s="49"/>
       <c r="K28" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>71</v>
@@ -21738,7 +21741,7 @@
       <c r="I29" s="8"/>
       <c r="J29" s="49"/>
       <c r="K29" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>140</v>
@@ -21778,7 +21781,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="49"/>
       <c r="K30" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>140</v>
@@ -21820,7 +21823,7 @@
       </c>
       <c r="J31" s="49"/>
       <c r="K31" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>71</v>
@@ -21858,7 +21861,7 @@
       </c>
       <c r="J32" s="49"/>
       <c r="K32" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>71</v>
@@ -21898,7 +21901,7 @@
       </c>
       <c r="J33" s="49"/>
       <c r="K33" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>71</v>
@@ -21938,7 +21941,7 @@
       </c>
       <c r="J34" s="49"/>
       <c r="K34" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>71</v>
@@ -21974,7 +21977,7 @@
       <c r="I35" s="8"/>
       <c r="J35" s="49"/>
       <c r="K35" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>71</v>
@@ -22056,7 +22059,7 @@
       </c>
       <c r="J37" s="49"/>
       <c r="K37" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>71</v>
@@ -22090,7 +22093,7 @@
       <c r="I38" s="25"/>
       <c r="J38" s="49"/>
       <c r="K38" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>71</v>
@@ -22126,7 +22129,7 @@
       </c>
       <c r="J39" s="49"/>
       <c r="K39" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>71</v>
@@ -22160,7 +22163,7 @@
       <c r="I40" s="25"/>
       <c r="J40" s="49"/>
       <c r="K40" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>71</v>
@@ -22194,7 +22197,7 @@
       <c r="I41" s="25"/>
       <c r="J41" s="49"/>
       <c r="K41" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>71</v>
@@ -22228,7 +22231,7 @@
       <c r="I42" s="25"/>
       <c r="J42" s="49"/>
       <c r="K42" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>71</v>
@@ -22262,7 +22265,7 @@
       <c r="I43" s="25"/>
       <c r="J43" s="49"/>
       <c r="K43" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>71</v>
@@ -22296,7 +22299,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="49"/>
       <c r="K44" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>71</v>
@@ -22332,7 +22335,7 @@
       </c>
       <c r="J45" s="49"/>
       <c r="K45" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>71</v>
@@ -22366,7 +22369,7 @@
       <c r="I46" s="25"/>
       <c r="J46" s="49"/>
       <c r="K46" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>71</v>
@@ -22400,7 +22403,7 @@
       <c r="I47" s="25"/>
       <c r="J47" s="49"/>
       <c r="K47" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>71</v>
@@ -22434,7 +22437,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="49"/>
       <c r="K48" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>71</v>
@@ -22470,7 +22473,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="49"/>
       <c r="K49" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>71</v>
@@ -22506,7 +22509,7 @@
       <c r="I50" s="25"/>
       <c r="J50" s="49"/>
       <c r="K50" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>71</v>
@@ -22540,7 +22543,7 @@
       <c r="I51" s="25"/>
       <c r="J51" s="49"/>
       <c r="K51" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>71</v>
@@ -22574,7 +22577,7 @@
       <c r="I52" s="59"/>
       <c r="J52" s="49"/>
       <c r="K52" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>71</v>
@@ -22608,7 +22611,7 @@
       <c r="I53" s="25"/>
       <c r="J53" s="49"/>
       <c r="K53" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>71</v>
@@ -22642,7 +22645,7 @@
       <c r="I54" s="59"/>
       <c r="J54" s="49"/>
       <c r="K54" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>71</v>
@@ -22678,7 +22681,7 @@
       </c>
       <c r="J55" s="49"/>
       <c r="K55" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>71</v>
@@ -22714,7 +22717,7 @@
       </c>
       <c r="J56" s="49"/>
       <c r="K56" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>71</v>
@@ -22750,7 +22753,7 @@
       </c>
       <c r="J57" s="49"/>
       <c r="K57" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>71</v>
@@ -22786,7 +22789,7 @@
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>71</v>
@@ -22822,7 +22825,7 @@
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>71</v>
@@ -22858,7 +22861,7 @@
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>71</v>
@@ -22894,7 +22897,7 @@
       </c>
       <c r="J61" s="49"/>
       <c r="K61" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>71</v>
@@ -22930,7 +22933,7 @@
       </c>
       <c r="J62" s="49"/>
       <c r="K62" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>71</v>
@@ -22966,7 +22969,7 @@
       </c>
       <c r="J63" s="49"/>
       <c r="K63" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>71</v>
@@ -23000,7 +23003,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="49"/>
       <c r="K64" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>71</v>
@@ -23036,7 +23039,7 @@
       <c r="I65" s="25"/>
       <c r="J65" s="49"/>
       <c r="K65" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>71</v>
@@ -23072,7 +23075,7 @@
       <c r="I66" s="25"/>
       <c r="J66" s="49"/>
       <c r="K66" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>71</v>
@@ -23112,7 +23115,7 @@
       </c>
       <c r="J67" s="49"/>
       <c r="K67" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>71</v>
@@ -23148,7 +23151,7 @@
       <c r="I68" s="25"/>
       <c r="J68" s="49"/>
       <c r="K68" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>71</v>
@@ -23184,7 +23187,7 @@
       </c>
       <c r="J69" s="49"/>
       <c r="K69" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>71</v>
@@ -23220,7 +23223,7 @@
       </c>
       <c r="J70" s="49"/>
       <c r="K70" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>71</v>
@@ -23256,7 +23259,7 @@
       </c>
       <c r="J71" s="49"/>
       <c r="K71" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>71</v>
@@ -23292,7 +23295,7 @@
       </c>
       <c r="J72" s="49"/>
       <c r="K72" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>71</v>
@@ -23328,7 +23331,7 @@
       </c>
       <c r="J73" s="49"/>
       <c r="K73" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>71</v>
@@ -23364,7 +23367,7 @@
       </c>
       <c r="J74" s="49"/>
       <c r="K74" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>71</v>
@@ -23400,7 +23403,7 @@
       </c>
       <c r="J75" s="49"/>
       <c r="K75" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>71</v>
@@ -23436,7 +23439,7 @@
       </c>
       <c r="J76" s="49"/>
       <c r="K76" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>71</v>
@@ -23472,7 +23475,7 @@
       </c>
       <c r="J77" s="49"/>
       <c r="K77" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>71</v>
@@ -23508,7 +23511,7 @@
       </c>
       <c r="J78" s="49"/>
       <c r="K78" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>71</v>
@@ -23544,7 +23547,7 @@
       </c>
       <c r="J79" s="49"/>
       <c r="K79" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>71</v>
@@ -23580,7 +23583,7 @@
       </c>
       <c r="J80" s="49"/>
       <c r="K80" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>71</v>
@@ -23616,7 +23619,7 @@
       </c>
       <c r="J81" s="49"/>
       <c r="K81" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>71</v>
@@ -23652,7 +23655,7 @@
       <c r="I82" s="25"/>
       <c r="J82" s="49"/>
       <c r="K82" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>71</v>
@@ -23688,7 +23691,7 @@
       </c>
       <c r="J83" s="49"/>
       <c r="K83" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>71</v>
@@ -23724,7 +23727,7 @@
       <c r="I84" s="25"/>
       <c r="J84" s="49"/>
       <c r="K84" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>71</v>
@@ -23760,7 +23763,7 @@
       </c>
       <c r="J85" s="49"/>
       <c r="K85" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>71</v>
@@ -23796,7 +23799,7 @@
       <c r="I86" s="25"/>
       <c r="J86" s="49"/>
       <c r="K86" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>71</v>
@@ -23830,7 +23833,7 @@
       <c r="I87" s="59"/>
       <c r="J87" s="49"/>
       <c r="K87" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>71</v>
@@ -23868,7 +23871,7 @@
       </c>
       <c r="J88" s="49"/>
       <c r="K88" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>71</v>
@@ -23904,7 +23907,7 @@
       </c>
       <c r="J89" s="49"/>
       <c r="K89" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>71</v>
@@ -23938,7 +23941,7 @@
       <c r="I90" s="25"/>
       <c r="J90" s="49"/>
       <c r="K90" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>71</v>
@@ -23974,7 +23977,7 @@
       </c>
       <c r="J91" s="49"/>
       <c r="K91" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>71</v>
@@ -24008,7 +24011,7 @@
       <c r="I92" s="25"/>
       <c r="J92" s="49"/>
       <c r="K92" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>71</v>
@@ -24044,7 +24047,7 @@
       </c>
       <c r="J93" s="49"/>
       <c r="K93" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>71</v>
@@ -24078,7 +24081,7 @@
       <c r="I94" s="25"/>
       <c r="J94" s="49"/>
       <c r="K94" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>71</v>
@@ -24114,7 +24117,7 @@
       <c r="I95" s="25"/>
       <c r="J95" s="49"/>
       <c r="K95" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>71</v>
@@ -24150,7 +24153,7 @@
       <c r="I96" s="25"/>
       <c r="J96" s="49"/>
       <c r="K96" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>71</v>
@@ -24186,7 +24189,7 @@
       </c>
       <c r="J97" s="49"/>
       <c r="K97" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>71</v>
@@ -24220,7 +24223,7 @@
       <c r="I98" s="25"/>
       <c r="J98" s="49"/>
       <c r="K98" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>71</v>
@@ -24258,7 +24261,7 @@
       </c>
       <c r="J99" s="49"/>
       <c r="K99" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>71</v>
@@ -24296,7 +24299,7 @@
       </c>
       <c r="J100" s="49"/>
       <c r="K100" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>71</v>
@@ -24330,7 +24333,7 @@
       <c r="I101" s="25"/>
       <c r="J101" s="49"/>
       <c r="K101" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>71</v>
@@ -24368,7 +24371,7 @@
       </c>
       <c r="J102" s="49"/>
       <c r="K102" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>71</v>
@@ -24404,7 +24407,7 @@
       <c r="I103" s="59"/>
       <c r="J103" s="49"/>
       <c r="K103" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>71</v>
@@ -24440,7 +24443,7 @@
       </c>
       <c r="J104" s="49"/>
       <c r="K104" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>71</v>
@@ -24476,7 +24479,7 @@
       </c>
       <c r="J105" s="49"/>
       <c r="K105" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>71</v>
@@ -24512,7 +24515,7 @@
       </c>
       <c r="J106" s="49"/>
       <c r="K106" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>71</v>
@@ -24548,7 +24551,7 @@
       </c>
       <c r="J107" s="49"/>
       <c r="K107" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>71</v>
@@ -24584,7 +24587,7 @@
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>71</v>
@@ -24620,7 +24623,7 @@
       </c>
       <c r="J109" s="49"/>
       <c r="K109" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>71</v>
@@ -24656,7 +24659,7 @@
       </c>
       <c r="J110" s="49"/>
       <c r="K110" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>71</v>
@@ -24692,7 +24695,7 @@
       </c>
       <c r="J111" s="49"/>
       <c r="K111" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>71</v>
@@ -24728,7 +24731,7 @@
       </c>
       <c r="J112" s="49"/>
       <c r="K112" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>71</v>
@@ -24764,7 +24767,7 @@
       </c>
       <c r="J113" s="49"/>
       <c r="K113" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>71</v>
@@ -24798,7 +24801,7 @@
       <c r="I114" s="25"/>
       <c r="J114" s="49"/>
       <c r="K114" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>71</v>
@@ -24834,7 +24837,7 @@
       </c>
       <c r="J115" s="49"/>
       <c r="K115" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>71</v>
@@ -24868,7 +24871,7 @@
       <c r="I116" s="25"/>
       <c r="J116" s="49"/>
       <c r="K116" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>71</v>
@@ -24902,7 +24905,7 @@
       <c r="I117" s="25"/>
       <c r="J117" s="49"/>
       <c r="K117" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>71</v>
@@ -24938,7 +24941,7 @@
       </c>
       <c r="J118" s="49"/>
       <c r="K118" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>71</v>
@@ -24974,7 +24977,7 @@
       </c>
       <c r="J119" s="49"/>
       <c r="K119" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L119" s="5" t="s">
         <v>71</v>
@@ -25008,7 +25011,7 @@
       <c r="I120" s="59"/>
       <c r="J120" s="49"/>
       <c r="K120" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>71</v>
@@ -25044,7 +25047,7 @@
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L121" s="5" t="s">
         <v>71</v>
@@ -25080,7 +25083,7 @@
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>71</v>
@@ -25116,7 +25119,7 @@
       </c>
       <c r="J123" s="49"/>
       <c r="K123" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>71</v>
@@ -25152,7 +25155,7 @@
       </c>
       <c r="J124" s="49"/>
       <c r="K124" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>71</v>
@@ -25188,7 +25191,7 @@
       </c>
       <c r="J125" s="49"/>
       <c r="K125" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L125" s="5" t="s">
         <v>71</v>
@@ -25224,7 +25227,7 @@
       </c>
       <c r="J126" s="49"/>
       <c r="K126" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L126" s="5" t="s">
         <v>71</v>
@@ -25260,7 +25263,7 @@
       </c>
       <c r="J127" s="49"/>
       <c r="K127" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L127" s="5" t="s">
         <v>71</v>
@@ -25296,7 +25299,7 @@
       </c>
       <c r="J128" s="49"/>
       <c r="K128" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L128" s="5" t="s">
         <v>71</v>
@@ -25332,7 +25335,7 @@
       </c>
       <c r="J129" s="49"/>
       <c r="K129" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L129" s="5" t="s">
         <v>71</v>
@@ -25368,7 +25371,7 @@
       </c>
       <c r="J130" s="49"/>
       <c r="K130" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>71</v>
@@ -25404,7 +25407,7 @@
       <c r="I131" s="25"/>
       <c r="J131" s="49"/>
       <c r="K131" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L131" s="5" t="s">
         <v>71</v>
@@ -25440,7 +25443,7 @@
       </c>
       <c r="J132" s="49"/>
       <c r="K132" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L132" s="5" t="s">
         <v>71</v>
@@ -25476,7 +25479,7 @@
       <c r="I133" s="25"/>
       <c r="J133" s="49"/>
       <c r="K133" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L133" s="5" t="s">
         <v>71</v>
@@ -25512,7 +25515,7 @@
       </c>
       <c r="J134" s="49"/>
       <c r="K134" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L134" s="5" t="s">
         <v>71</v>
@@ -25548,7 +25551,7 @@
       <c r="I135" s="25"/>
       <c r="J135" s="49"/>
       <c r="K135" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>71</v>
@@ -25582,7 +25585,7 @@
       <c r="I136" s="59"/>
       <c r="J136" s="49"/>
       <c r="K136" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L136" s="5" t="s">
         <v>71</v>
@@ -25616,7 +25619,7 @@
       <c r="I137" s="25"/>
       <c r="J137" s="49"/>
       <c r="K137" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L137" s="5" t="s">
         <v>71</v>
@@ -25650,7 +25653,7 @@
       <c r="I138" s="25"/>
       <c r="J138" s="49"/>
       <c r="K138" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L138" s="5" t="s">
         <v>71</v>
@@ -25684,7 +25687,7 @@
       <c r="I139" s="25"/>
       <c r="J139" s="49"/>
       <c r="K139" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>71</v>
@@ -25718,7 +25721,7 @@
       <c r="I140" s="25"/>
       <c r="J140" s="49"/>
       <c r="K140" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L140" s="5" t="s">
         <v>71</v>
@@ -25754,7 +25757,7 @@
       </c>
       <c r="J141" s="49"/>
       <c r="K141" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L141" s="5" t="s">
         <v>71</v>
@@ -25788,7 +25791,7 @@
       <c r="I142" s="25"/>
       <c r="J142" s="49"/>
       <c r="K142" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L142" s="5" t="s">
         <v>71</v>
@@ -25822,7 +25825,7 @@
       <c r="I143" s="25"/>
       <c r="J143" s="49"/>
       <c r="K143" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L143" s="5" t="s">
         <v>71</v>
@@ -25858,7 +25861,7 @@
       </c>
       <c r="J144" s="49"/>
       <c r="K144" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L144" s="5" t="s">
         <v>71</v>
@@ -25894,7 +25897,7 @@
       </c>
       <c r="J145" s="49"/>
       <c r="K145" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>71</v>
@@ -25930,7 +25933,7 @@
       </c>
       <c r="J146" s="49"/>
       <c r="K146" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>71</v>
@@ -25966,7 +25969,7 @@
       </c>
       <c r="J147" s="49"/>
       <c r="K147" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L147" s="5" t="s">
         <v>71</v>
@@ -26002,7 +26005,7 @@
       </c>
       <c r="J148" s="49"/>
       <c r="K148" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L148" s="5" t="s">
         <v>71</v>
@@ -26038,7 +26041,7 @@
       </c>
       <c r="J149" s="49"/>
       <c r="K149" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L149" s="5" t="s">
         <v>71</v>
@@ -26074,7 +26077,7 @@
       </c>
       <c r="J150" s="49"/>
       <c r="K150" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L150" s="5" t="s">
         <v>71</v>
@@ -26110,7 +26113,7 @@
       </c>
       <c r="J151" s="49"/>
       <c r="K151" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L151" s="5" t="s">
         <v>71</v>
@@ -26146,7 +26149,7 @@
       </c>
       <c r="J152" s="49"/>
       <c r="K152" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L152" s="5" t="s">
         <v>71</v>
@@ -26182,7 +26185,7 @@
       </c>
       <c r="J153" s="49"/>
       <c r="K153" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L153" s="5" t="s">
         <v>71</v>
@@ -26216,7 +26219,7 @@
       <c r="I154" s="59"/>
       <c r="J154" s="56"/>
       <c r="K154" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L154" s="5" t="s">
         <v>71</v>
@@ -26250,7 +26253,7 @@
       <c r="I155" s="33"/>
       <c r="J155" s="56"/>
       <c r="K155" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>71</v>
@@ -26734,7 +26737,7 @@
     </row>
     <row r="10" spans="1:16" ht="24">
       <c r="A10" s="67" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>779</v>
@@ -26748,14 +26751,14 @@
         <v>347</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="59"/>
@@ -27830,7 +27833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="24">
+    <row r="17" spans="1:16">
       <c r="A17" s="85" t="s">
         <v>602</v>
       </c>
@@ -28644,7 +28647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="24">
+    <row r="38" spans="1:16">
       <c r="A38" s="85" t="s">
         <v>638</v>
       </c>
@@ -29451,7 +29454,7 @@
         <v>49</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -29492,7 +29495,7 @@
         <v>49</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
@@ -29533,7 +29536,7 @@
         <v>49</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
@@ -29574,7 +29577,7 @@
         <v>49</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
@@ -29615,7 +29618,7 @@
         <v>49</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
@@ -29656,7 +29659,7 @@
         <v>49</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -29697,7 +29700,7 @@
         <v>49</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -29738,7 +29741,7 @@
         <v>49</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -29862,7 +29865,7 @@
         <v>49</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -29903,7 +29906,7 @@
         <v>49</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
@@ -29944,7 +29947,7 @@
         <v>49</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
@@ -29985,7 +29988,7 @@
         <v>49</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -30026,7 +30029,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
@@ -30067,7 +30070,7 @@
         <v>49</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -30108,7 +30111,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
@@ -30149,7 +30152,7 @@
         <v>49</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4A4C4-C66E-43F7-85C2-75573A554285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA06D4F-522B-4ED2-8DF9-D096181116FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28725" yWindow="4710" windowWidth="28530" windowHeight="23445" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -2575,15 +2575,9 @@
     <t>walker1990clinical</t>
   </si>
   <si>
-    <t>Determined by concentration &gt; 100mg/dL</t>
-  </si>
-  <si>
     <t>Ketone</t>
   </si>
   <si>
-    <t>Determined by concentration &gt; 5 mg/dL</t>
-  </si>
-  <si>
     <t>Bilirubin*</t>
   </si>
   <si>
@@ -2593,16 +2587,10 @@
     <t>Blood</t>
   </si>
   <si>
-    <t>Determined by concentration &gt; 0.15 mg/dL</t>
-  </si>
-  <si>
     <t>pH*</t>
   </si>
   <si>
     <t>Protein</t>
-  </si>
-  <si>
-    <t>Determined by concentration &gt; 25 mg/dL</t>
   </si>
   <si>
     <t>Urobilinogen*</t>
@@ -3754,6 +3742,18 @@
   </si>
   <si>
     <t>Any changes should be done to system row above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determined by glucose concentration &gt; 100mg/dL </t>
+  </si>
+  <si>
+    <t>Determined by glucose concentration &gt; 5 mg/dL</t>
+  </si>
+  <si>
+    <t>Determined by trace amount of Hb</t>
+  </si>
+  <si>
+    <t>Determined by albumin concentration &gt; 0.2 mg/mL</t>
   </si>
 </sst>
 </file>
@@ -5054,10 +5054,10 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="10" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>46</v>
@@ -5068,17 +5068,17 @@
         <v>1033.23</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
       <c r="J2" s="17" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="K2" s="26"/>
       <c r="L2" s="91"/>
       <c r="M2" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>101</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="3" spans="1:16" ht="36">
       <c r="A3" s="10" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>200</v>
@@ -5103,10 +5103,10 @@
       <c r="D3" s="51"/>
       <c r="E3" s="51"/>
       <c r="F3" s="51" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17" t="s">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="26" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="L3" s="92"/>
       <c r="M3" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>52</v>
@@ -5132,13 +5132,13 @@
     </row>
     <row r="4" spans="1:16" ht="36">
       <c r="A4" s="10" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D4" s="51"/>
       <c r="E4" s="51"/>
@@ -5149,20 +5149,20 @@
         <v>104</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="L4" s="92"/>
       <c r="M4" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>101</v>
@@ -5176,13 +5176,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="10" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
@@ -5193,18 +5193,18 @@
         <v>104</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="92"/>
       <c r="M5" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>101</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="10" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C6" s="51" t="s">
         <v>46</v>
@@ -5235,7 +5235,7 @@
         <v>104</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>49</v>
@@ -5244,7 +5244,7 @@
       <c r="K6" s="26"/>
       <c r="L6" s="91"/>
       <c r="M6" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>101</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="48" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
@@ -5274,7 +5274,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="91"/>
       <c r="M7" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>101</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="48" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="20"/>
@@ -5302,10 +5302,10 @@
       <c r="K8" s="26"/>
       <c r="L8" s="92"/>
       <c r="M8" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O8" s="14" t="s">
         <v>52</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="10" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>200</v>
@@ -5327,13 +5327,13 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="51" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>49</v>
@@ -5342,7 +5342,7 @@
       <c r="K9" s="26"/>
       <c r="L9" s="92"/>
       <c r="M9" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>101</v>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="48" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="51"/>
@@ -5370,7 +5370,7 @@
       <c r="K10" s="26"/>
       <c r="L10" s="92"/>
       <c r="M10" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>101</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="48" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="51"/>
@@ -5398,7 +5398,7 @@
       <c r="K11" s="26"/>
       <c r="L11" s="92"/>
       <c r="M11" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>101</v>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="10" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>379</v>
@@ -5436,7 +5436,7 @@
       <c r="K12" s="26"/>
       <c r="L12" s="91"/>
       <c r="M12" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>101</v>
@@ -5450,10 +5450,10 @@
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>382</v>
@@ -5464,10 +5464,10 @@
         <v>0.44</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>49</v>
@@ -5476,7 +5476,7 @@
       <c r="K13" s="26"/>
       <c r="L13" s="91"/>
       <c r="M13" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>101</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="10" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C14" s="51" t="s">
         <v>46</v>
@@ -5501,13 +5501,13 @@
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
       <c r="F14" s="51" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>49</v>
@@ -5516,7 +5516,7 @@
       <c r="K14" s="26"/>
       <c r="L14" s="95"/>
       <c r="M14" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>101</v>
@@ -5530,13 +5530,13 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="10" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -5547,7 +5547,7 @@
         <v>104</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>49</v>
@@ -5556,10 +5556,10 @@
       <c r="K15" s="26"/>
       <c r="L15" s="91"/>
       <c r="M15" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>52</v>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="10" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="51" t="s">
@@ -5592,7 +5592,7 @@
       <c r="K16" s="26"/>
       <c r="L16" s="95"/>
       <c r="M16" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>101</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="10" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>200</v>
@@ -5623,18 +5623,18 @@
         <v>15</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="K17" s="26"/>
       <c r="L17" s="92"/>
       <c r="M17" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>101</v>
@@ -5648,10 +5648,10 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="48" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
@@ -5664,7 +5664,7 @@
       <c r="K18" s="26"/>
       <c r="L18" s="91"/>
       <c r="M18" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>101</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="48" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
@@ -5694,7 +5694,7 @@
       <c r="K19" s="26"/>
       <c r="L19" s="91"/>
       <c r="M19" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>101</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="10" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="51" t="s">
@@ -5717,24 +5717,24 @@
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="51" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="26" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="L20" s="95"/>
       <c r="M20" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>101</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="10" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>382</v>
@@ -5762,10 +5762,10 @@
         <v>0.4</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>569</v>
@@ -5774,7 +5774,7 @@
       <c r="K21" s="26"/>
       <c r="L21" s="91"/>
       <c r="M21" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>101</v>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="10" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C22" s="51" t="s">
         <v>46</v>
@@ -5799,13 +5799,13 @@
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>49</v>
@@ -5814,7 +5814,7 @@
       <c r="K22" s="26"/>
       <c r="L22" s="95"/>
       <c r="M22" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>101</v>
@@ -5828,13 +5828,13 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="10" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
@@ -5845,7 +5845,7 @@
         <v>104</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I23" s="17" t="s">
         <v>49</v>
@@ -5854,10 +5854,10 @@
       <c r="K23" s="26"/>
       <c r="L23" s="91"/>
       <c r="M23" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>52</v>
@@ -5868,10 +5868,10 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>379</v>
@@ -5885,7 +5885,7 @@
         <v>104</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>569</v>
@@ -5894,7 +5894,7 @@
       <c r="K24" s="26"/>
       <c r="L24" s="91"/>
       <c r="M24" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>101</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>382</v>
@@ -5925,7 +5925,7 @@
         <v>104</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>569</v>
@@ -5934,7 +5934,7 @@
       <c r="K25" s="26"/>
       <c r="L25" s="91"/>
       <c r="M25" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>101</v>
@@ -5948,10 +5948,10 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="10" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>382</v>
@@ -5970,11 +5970,11 @@
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="26" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="L26" s="91"/>
       <c r="M26" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>101</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="10" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>379</v>
@@ -6012,7 +6012,7 @@
       <c r="K27" s="26"/>
       <c r="L27" s="91"/>
       <c r="M27" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N27" s="5" t="s">
         <v>101</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="10" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>379</v>
@@ -6050,7 +6050,7 @@
       <c r="K28" s="26"/>
       <c r="L28" s="91"/>
       <c r="M28" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N28" s="5" t="s">
         <v>101</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="10" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C29" s="51" t="s">
         <v>46</v>
@@ -6081,7 +6081,7 @@
         <v>104</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>49</v>
@@ -6090,7 +6090,7 @@
       <c r="K29" s="26"/>
       <c r="L29" s="91"/>
       <c r="M29" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>101</v>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="30" spans="1:16" ht="60">
       <c r="A30" s="10" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C30" s="51" t="s">
         <v>46</v>
@@ -6121,18 +6121,18 @@
         <v>104</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="26" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="L30" s="91"/>
       <c r="M30" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>101</v>
@@ -6146,10 +6146,10 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="10" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C31" s="51" t="s">
         <v>46</v>
@@ -6160,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="17" t="s">
@@ -6170,7 +6170,7 @@
       <c r="K31" s="26"/>
       <c r="L31" s="91"/>
       <c r="M31" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>101</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="10" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B32" s="26"/>
       <c r="C32" s="51" t="s">
@@ -6196,19 +6196,19 @@
         <v>0</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="K32" s="26"/>
       <c r="L32" s="91"/>
       <c r="M32" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>101</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="10" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>200</v>
@@ -6236,19 +6236,19 @@
         <v>0</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="K33" s="26"/>
       <c r="L33" s="91"/>
       <c r="M33" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>101</v>
@@ -6262,10 +6262,10 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="48" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
@@ -6278,7 +6278,7 @@
       <c r="K34" s="26"/>
       <c r="L34" s="91"/>
       <c r="M34" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>101</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="48" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C35" s="51"/>
       <c r="D35" s="51"/>
@@ -6308,7 +6308,7 @@
       <c r="K35" s="26"/>
       <c r="L35" s="91"/>
       <c r="M35" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N35" s="5" t="s">
         <v>101</v>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="36" spans="1:16" ht="24">
       <c r="A36" s="10" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C36" s="51" t="s">
         <v>46</v>
@@ -6344,11 +6344,11 @@
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="26" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="L36" s="91"/>
       <c r="M36" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>101</v>
@@ -6362,13 +6362,13 @@
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D37" s="51"/>
       <c r="E37" s="51"/>
@@ -6379,7 +6379,7 @@
         <v>104</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>49</v>
@@ -6388,7 +6388,7 @@
       <c r="K37" s="26"/>
       <c r="L37" s="91"/>
       <c r="M37" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N37" s="5" t="s">
         <v>101</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="10" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="51" t="s">
@@ -6411,10 +6411,10 @@
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
       <c r="F38" s="51" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="H38" s="17"/>
       <c r="I38" s="17" t="s">
@@ -6424,7 +6424,7 @@
       <c r="K38" s="26"/>
       <c r="L38" s="91"/>
       <c r="M38" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>101</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="39" spans="1:16" ht="96">
       <c r="A39" s="10" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>46</v>
@@ -6449,24 +6449,24 @@
       <c r="D39" s="51"/>
       <c r="E39" s="51"/>
       <c r="F39" s="17" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="26" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="L39" s="95"/>
       <c r="M39" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N39" s="5" t="s">
         <v>101</v>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="10" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C40" s="51" t="s">
         <v>46</v>
@@ -6491,24 +6491,24 @@
       <c r="D40" s="51"/>
       <c r="E40" s="51"/>
       <c r="F40" s="17" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G40" s="17" t="s">
         <v>104</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="26" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="L40" s="95"/>
       <c r="M40" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N40" s="5" t="s">
         <v>101</v>
@@ -6522,13 +6522,13 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="10" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D41" s="51"/>
       <c r="E41" s="51"/>
@@ -6539,17 +6539,17 @@
         <v>104</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>101</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="48" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C42" s="51"/>
       <c r="D42" s="51"/>
@@ -6579,7 +6579,7 @@
       <c r="K42" s="26"/>
       <c r="L42" s="91"/>
       <c r="M42" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>101</v>
@@ -6593,10 +6593,10 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="48" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="51"/>
@@ -6609,7 +6609,7 @@
       <c r="K43" s="26"/>
       <c r="L43" s="91"/>
       <c r="M43" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>101</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="44" spans="1:16" ht="36">
       <c r="A44" s="10" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>289</v>
@@ -6634,13 +6634,13 @@
       <c r="D44" s="51"/>
       <c r="E44" s="51"/>
       <c r="F44" s="18" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="G44" s="99" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>49</v>
@@ -6649,7 +6649,7 @@
       <c r="K44" s="26"/>
       <c r="L44" s="100"/>
       <c r="M44" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>101</v>
@@ -6663,7 +6663,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="48" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="51" t="s">
@@ -6675,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
@@ -6683,7 +6683,7 @@
       <c r="K45" s="26"/>
       <c r="L45" s="91"/>
       <c r="M45" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>101</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="48" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="51"/>
@@ -6711,7 +6711,7 @@
       <c r="K46" s="51"/>
       <c r="L46" s="51"/>
       <c r="M46" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>101</v>
@@ -6725,7 +6725,7 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="10" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="51" t="s">
@@ -6744,12 +6744,12 @@
         <v>49</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="K47" s="51"/>
       <c r="L47" s="51"/>
       <c r="M47" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>101</v>
@@ -6763,7 +6763,7 @@
     </row>
     <row r="48" spans="1:16" ht="24">
       <c r="A48" s="10" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="51" t="s">
@@ -6778,18 +6778,18 @@
         <v>104</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I48" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="26" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="L48" s="92"/>
       <c r="M48" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>101</v>
@@ -6803,13 +6803,13 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="10" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D49" s="51"/>
       <c r="E49" s="51"/>
@@ -6820,7 +6820,7 @@
         <v>104</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I49" s="17" t="s">
         <v>49</v>
@@ -6829,10 +6829,10 @@
       <c r="K49" s="26"/>
       <c r="L49" s="91"/>
       <c r="M49" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>52</v>
@@ -6843,13 +6843,13 @@
     </row>
     <row r="50" spans="1:16" ht="24">
       <c r="A50" s="10" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D50" s="51"/>
       <c r="E50" s="51"/>
@@ -6860,18 +6860,18 @@
         <v>104</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="26" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="L50" s="91"/>
       <c r="M50" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N50" s="5" t="s">
         <v>101</v>
@@ -6885,13 +6885,13 @@
     </row>
     <row r="51" spans="1:16" ht="24">
       <c r="A51" s="10" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D51" s="51"/>
       <c r="E51" s="51"/>
@@ -6903,18 +6903,18 @@
         <v>104</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I51" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="26" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="L51" s="56"/>
       <c r="M51" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N51" s="5" t="s">
         <v>101</v>
@@ -6928,13 +6928,13 @@
     </row>
     <row r="52" spans="1:16" ht="36">
       <c r="A52" s="10" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D52" s="51"/>
       <c r="E52" s="51"/>
@@ -6945,18 +6945,18 @@
         <v>104</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="26" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="L52" s="56"/>
       <c r="M52" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>101</v>
@@ -6970,10 +6970,10 @@
     </row>
     <row r="53" spans="1:16" ht="108">
       <c r="A53" s="10" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C53" s="51" t="s">
         <v>46</v>
@@ -6992,11 +6992,11 @@
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="26" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="L53" s="91"/>
       <c r="M53" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>101</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="48" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C54" s="51"/>
       <c r="D54" s="51"/>
@@ -7026,7 +7026,7 @@
       <c r="K54" s="26"/>
       <c r="L54" s="91"/>
       <c r="M54" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>101</v>
@@ -7040,13 +7040,13 @@
     </row>
     <row r="55" spans="1:16" ht="45.75" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D55" s="51"/>
       <c r="E55" s="51"/>
@@ -7058,18 +7058,18 @@
         <v>104</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I55" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J55" s="17"/>
       <c r="K55" s="26" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="L55" s="91"/>
       <c r="M55" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N55" s="5" t="s">
         <v>101</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="48" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C56" s="51"/>
       <c r="D56" s="51"/>
@@ -7099,7 +7099,7 @@
       <c r="K56" s="26"/>
       <c r="L56" s="91"/>
       <c r="M56" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>101</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="10" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>379</v>
@@ -7130,7 +7130,7 @@
         <v>104</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I57" s="17" t="s">
         <v>569</v>
@@ -7139,7 +7139,7 @@
       <c r="K57" s="26"/>
       <c r="L57" s="91"/>
       <c r="M57" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>101</v>
@@ -7153,10 +7153,10 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="10" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>382</v>
@@ -7170,7 +7170,7 @@
         <v>104</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>569</v>
@@ -7179,7 +7179,7 @@
       <c r="K58" s="26"/>
       <c r="L58" s="91"/>
       <c r="M58" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>101</v>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="10" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C59" s="20" t="s">
         <v>379</v>
@@ -7210,7 +7210,7 @@
         <v>15</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>569</v>
@@ -7219,7 +7219,7 @@
       <c r="K59" s="26"/>
       <c r="L59" s="91"/>
       <c r="M59" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>101</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="10" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>382</v>
@@ -7250,7 +7250,7 @@
         <v>15</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>569</v>
@@ -7259,7 +7259,7 @@
       <c r="K60" s="26"/>
       <c r="L60" s="91"/>
       <c r="M60" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>101</v>
@@ -7273,10 +7273,10 @@
     </row>
     <row r="61" spans="1:16" ht="24">
       <c r="A61" s="10" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>379</v>
@@ -7290,18 +7290,18 @@
         <v>104</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I61" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="26" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="L61" s="91"/>
       <c r="M61" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>101</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="62" spans="1:16" ht="24">
       <c r="A62" s="10" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>382</v>
@@ -7332,18 +7332,18 @@
         <v>104</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I62" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="26" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="L62" s="91"/>
       <c r="M62" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N62" s="5" t="s">
         <v>101</v>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="10" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>379</v>
@@ -7379,11 +7379,11 @@
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="26" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="L63" s="91"/>
       <c r="M63" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N63" s="5" t="s">
         <v>101</v>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="10" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>382</v>
@@ -7421,7 +7421,7 @@
       <c r="K64" s="26"/>
       <c r="L64" s="91"/>
       <c r="M64" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N64" s="5" t="s">
         <v>101</v>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="10" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C65" s="20" t="s">
         <v>379</v>
@@ -7452,7 +7452,7 @@
         <v>15</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I65" s="17" t="s">
         <v>569</v>
@@ -7461,7 +7461,7 @@
       <c r="K65" s="26"/>
       <c r="L65" s="91"/>
       <c r="M65" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N65" s="5" t="s">
         <v>101</v>
@@ -7475,10 +7475,10 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="10" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>382</v>
@@ -7492,7 +7492,7 @@
         <v>15</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I66" s="17" t="s">
         <v>569</v>
@@ -7501,7 +7501,7 @@
       <c r="K66" s="26"/>
       <c r="L66" s="91"/>
       <c r="M66" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N66" s="5" t="s">
         <v>101</v>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="67" spans="1:16" ht="24">
       <c r="A67" s="10" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C67" s="20" t="s">
         <v>379</v>
@@ -7529,21 +7529,21 @@
         <v>0</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="I67" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="K67" s="26"/>
       <c r="L67" s="91"/>
       <c r="M67" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>101</v>
@@ -7557,10 +7557,10 @@
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="10" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C68" s="20" t="s">
         <v>382</v>
@@ -7571,21 +7571,21 @@
         <v>0</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="I68" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="K68" s="26"/>
       <c r="L68" s="91"/>
       <c r="M68" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>101</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="10" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C69" s="20" t="s">
         <v>379</v>
@@ -7616,7 +7616,7 @@
         <v>104</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I69" s="17" t="s">
         <v>569</v>
@@ -7625,7 +7625,7 @@
       <c r="K69" s="26"/>
       <c r="L69" s="91"/>
       <c r="M69" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>101</v>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="10" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C70" s="20" t="s">
         <v>382</v>
@@ -7656,7 +7656,7 @@
         <v>104</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I70" s="17" t="s">
         <v>569</v>
@@ -7665,7 +7665,7 @@
       <c r="K70" s="26"/>
       <c r="L70" s="91"/>
       <c r="M70" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N70" s="5" t="s">
         <v>101</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="51" t="s">
@@ -7688,10 +7688,10 @@
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="51" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17" t="s">
@@ -7701,7 +7701,7 @@
       <c r="K71" s="26"/>
       <c r="L71" s="91"/>
       <c r="M71" s="66" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>101</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="73" spans="1:16" ht="25.5" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C73" s="20" t="s">
         <v>382</v>
@@ -7776,32 +7776,32 @@
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="101" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="G73" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J73" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K73" s="26" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="L73" s="91"/>
       <c r="M73" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N73" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O73" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P73" s="66">
         <v>4</v>
@@ -7809,10 +7809,10 @@
     </row>
     <row r="74" spans="1:16" ht="24">
       <c r="A74" s="10" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C74" s="20" t="s">
         <v>379</v>
@@ -7820,32 +7820,32 @@
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="101" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="G74" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="I74" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K74" s="26" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="L74" s="91"/>
       <c r="M74" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N74" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O74" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P74" s="66">
         <v>4</v>
@@ -7853,7 +7853,7 @@
     </row>
     <row r="75" spans="1:16" ht="24">
       <c r="A75" s="10" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>200</v>
@@ -7864,30 +7864,30 @@
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="17" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G75" s="99" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="I75" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="17"/>
       <c r="K75" s="26" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="L75" s="91"/>
       <c r="M75" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O75" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P75" s="66">
         <v>4</v>
@@ -7895,7 +7895,7 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="10" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>200</v>
@@ -7912,7 +7912,7 @@
         <v>104</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>49</v>
@@ -7921,13 +7921,13 @@
       <c r="K76" s="5"/>
       <c r="L76" s="56"/>
       <c r="M76" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O76" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P76" s="66">
         <v>4</v>
@@ -7935,7 +7935,7 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="10" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>200</v>
@@ -7946,13 +7946,13 @@
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="51" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="G77" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="I77" s="17" t="s">
         <v>49</v>
@@ -7961,13 +7961,13 @@
       <c r="K77" s="17"/>
       <c r="L77" s="91"/>
       <c r="M77" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O77" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P77" s="66">
         <v>4</v>
@@ -7975,7 +7975,7 @@
     </row>
     <row r="78" spans="1:16" ht="30" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B78" s="17" t="s">
         <v>200</v>
@@ -7986,30 +7986,30 @@
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="17" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="G78" s="99" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="I78" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J78" s="17"/>
       <c r="K78" s="26" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="L78" s="91"/>
       <c r="M78" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P78" s="66">
         <v>4</v>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="10" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>382</v>
@@ -8034,26 +8034,26 @@
         <v>15</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I79" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K79" s="26" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="L79" s="56"/>
       <c r="M79" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O79" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P79" s="66">
         <v>4</v>
@@ -8061,10 +8061,10 @@
     </row>
     <row r="80" spans="1:16" ht="24">
       <c r="A80" s="10" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>379</v>
@@ -8078,26 +8078,26 @@
         <v>15</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K80" s="26" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="L80" s="56"/>
       <c r="M80" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P80" s="66">
         <v>4</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="81" spans="1:16" ht="24">
       <c r="A81" s="10" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>382</v>
@@ -8122,26 +8122,26 @@
         <v>15</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I81" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="L81" s="56"/>
       <c r="M81" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O81" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P81" s="66">
         <v>4</v>
@@ -8149,10 +8149,10 @@
     </row>
     <row r="82" spans="1:16" ht="24">
       <c r="A82" s="10" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>379</v>
@@ -8166,26 +8166,26 @@
         <v>15</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="I82" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="L82" s="56"/>
       <c r="M82" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O82" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P82" s="66">
         <v>4</v>
@@ -8193,13 +8193,13 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="10" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D83" s="51"/>
       <c r="E83" s="51"/>
@@ -8210,24 +8210,24 @@
         <v>104</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I83" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="5" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="L83" s="104"/>
       <c r="M83" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O83" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P83" s="66">
         <v>4</v>
@@ -8235,13 +8235,13 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="10" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D84" s="51"/>
       <c r="E84" s="51"/>
@@ -8252,24 +8252,24 @@
         <v>104</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I84" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="5" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="L84" s="104"/>
       <c r="M84" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P84" s="66">
         <v>4</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="85" spans="1:16" ht="24">
       <c r="A85" s="10" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>382</v>
@@ -8288,32 +8288,32 @@
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="17" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="L85" s="91"/>
       <c r="M85" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N85" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O85" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P85" s="66">
         <v>4</v>
@@ -8321,10 +8321,10 @@
     </row>
     <row r="86" spans="1:16" ht="24">
       <c r="A86" s="10" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>379</v>
@@ -8332,32 +8332,32 @@
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="17" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="L86" s="91"/>
       <c r="M86" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P86" s="66">
         <v>4</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="87" spans="1:16" ht="24">
       <c r="A87" s="10" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C87" s="20" t="s">
         <v>382</v>
@@ -8376,32 +8376,32 @@
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="17" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I87" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K87" s="26" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="L87" s="91"/>
       <c r="M87" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O87" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P87" s="66">
         <v>4</v>
@@ -8409,10 +8409,10 @@
     </row>
     <row r="88" spans="1:16" ht="24">
       <c r="A88" s="10" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C88" s="20" t="s">
         <v>379</v>
@@ -8420,32 +8420,32 @@
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="17" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I88" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K88" s="26" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="L88" s="91"/>
       <c r="M88" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P88" s="66">
         <v>4</v>
@@ -8453,13 +8453,13 @@
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="10" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D89" s="51"/>
       <c r="E89" s="51"/>
@@ -8470,24 +8470,24 @@
         <v>104</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I89" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J89" s="17"/>
       <c r="K89" s="17" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="L89" s="91"/>
       <c r="M89" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O89" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P89" s="66">
         <v>4</v>
@@ -8495,13 +8495,13 @@
     </row>
     <row r="90" spans="1:16" ht="24">
       <c r="A90" s="10" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D90" s="51"/>
       <c r="E90" s="51"/>
@@ -8512,24 +8512,24 @@
         <v>104</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I90" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J90" s="17"/>
       <c r="K90" s="17" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="L90" s="91"/>
       <c r="M90" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O90" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P90" s="66">
         <v>4</v>
@@ -8537,10 +8537,10 @@
     </row>
     <row r="91" spans="1:16" ht="24">
       <c r="A91" s="10" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C91" s="20" t="s">
         <v>382</v>
@@ -8548,30 +8548,30 @@
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="17" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I91" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K91" s="26"/>
       <c r="L91" s="91"/>
       <c r="M91" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O91" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P91" s="66">
         <v>4</v>
@@ -8579,10 +8579,10 @@
     </row>
     <row r="92" spans="1:16" ht="24">
       <c r="A92" s="10" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C92" s="20" t="s">
         <v>379</v>
@@ -8590,30 +8590,30 @@
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="17" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I92" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K92" s="26"/>
       <c r="L92" s="91"/>
       <c r="M92" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O92" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P92" s="66">
         <v>4</v>
@@ -8621,7 +8621,7 @@
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="10" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>200</v>
@@ -8632,13 +8632,13 @@
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
       <c r="F93" s="105" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G93" s="99" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="I93" s="17" t="s">
         <v>49</v>
@@ -8647,13 +8647,13 @@
       <c r="K93" s="26"/>
       <c r="L93" s="91"/>
       <c r="M93" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O93" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P93" s="66">
         <v>4</v>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="94" spans="1:16" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>200</v>
@@ -8672,13 +8672,13 @@
       <c r="D94" s="51"/>
       <c r="E94" s="51"/>
       <c r="F94" s="17" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="G94" s="99" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>49</v>
@@ -8686,13 +8686,13 @@
       <c r="J94" s="17"/>
       <c r="L94" s="91"/>
       <c r="M94" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O94" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P94" s="66">
         <v>4</v>
@@ -8700,13 +8700,13 @@
     </row>
     <row r="95" spans="1:16" ht="24">
       <c r="A95" s="10" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D95" s="51"/>
       <c r="E95" s="51"/>
@@ -8717,24 +8717,24 @@
         <v>104</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I95" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="L95" s="91"/>
       <c r="M95" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O95" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P95" s="66">
         <v>4</v>
@@ -8742,13 +8742,13 @@
     </row>
     <row r="96" spans="1:16" ht="24">
       <c r="A96" s="10" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D96" s="51"/>
       <c r="E96" s="51"/>
@@ -8759,24 +8759,24 @@
         <v>104</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I96" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="17" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="L96" s="91"/>
       <c r="M96" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N96" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O96" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P96" s="66">
         <v>4</v>
@@ -8784,10 +8784,10 @@
     </row>
     <row r="97" spans="1:16" ht="24">
       <c r="A97" s="10" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C97" s="20" t="s">
         <v>382</v>
@@ -8795,30 +8795,30 @@
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="17" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I97" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K97" s="26"/>
       <c r="L97" s="91"/>
       <c r="M97" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O97" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P97" s="66">
         <v>4</v>
@@ -8826,10 +8826,10 @@
     </row>
     <row r="98" spans="1:16" ht="24">
       <c r="A98" s="10" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C98" s="20" t="s">
         <v>379</v>
@@ -8837,30 +8837,30 @@
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="17" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="I98" s="17" t="s">
         <v>569</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K98" s="26"/>
       <c r="L98" s="91"/>
       <c r="M98" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="O98" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P98" s="66">
         <v>4</v>
@@ -8868,7 +8868,7 @@
     </row>
     <row r="99" spans="1:16" ht="36">
       <c r="A99" s="10" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>200</v>
@@ -8879,13 +8879,13 @@
       <c r="D99" s="51"/>
       <c r="E99" s="51"/>
       <c r="F99" s="105" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G99" s="99" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>49</v>
@@ -8894,13 +8894,13 @@
       <c r="K99" s="26"/>
       <c r="L99" s="91"/>
       <c r="M99" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N99" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O99" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P99" s="66">
         <v>4</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="100" spans="1:16" ht="36.75" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>200</v>
@@ -8919,13 +8919,13 @@
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
       <c r="F100" s="17" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="G100" s="99" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>49</v>
@@ -8934,13 +8934,13 @@
       <c r="K100" s="26"/>
       <c r="L100" s="91"/>
       <c r="M100" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N100" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O100" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P100" s="66">
         <v>4</v>
@@ -8948,13 +8948,13 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="10" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C101" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D101" s="51"/>
       <c r="E101" s="51"/>
@@ -8965,24 +8965,24 @@
         <v>104</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I101" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="L101" s="91"/>
       <c r="M101" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O101" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P101" s="66">
         <v>4</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="10" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>200</v>
@@ -9001,30 +9001,30 @@
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="17" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G102" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J102" s="17"/>
       <c r="K102" s="26" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="L102" s="91"/>
       <c r="M102" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N102" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O102" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P102" s="66">
         <v>4</v>
@@ -9032,7 +9032,7 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="10" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B103" s="17" t="s">
         <v>200</v>
@@ -9043,30 +9043,30 @@
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="51" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G103" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="17"/>
       <c r="K103" s="26" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="L103" s="91"/>
       <c r="M103" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N103" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O103" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P103" s="66">
         <v>4</v>
@@ -9074,13 +9074,13 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="10" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D104" s="51"/>
       <c r="E104" s="51"/>
@@ -9091,24 +9091,24 @@
         <v>104</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J104" s="17"/>
       <c r="K104" s="17" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="L104" s="91"/>
       <c r="M104" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="O104" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P104" s="66">
         <v>4</v>
@@ -9116,7 +9116,7 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="10" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>200</v>
@@ -9127,30 +9127,30 @@
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="17" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G105" s="99" t="s">
         <v>104</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="I105" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J105" s="17"/>
       <c r="K105" s="26" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="L105" s="91"/>
       <c r="M105" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N105" s="5" t="s">
         <v>122</v>
       </c>
       <c r="O105" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P105" s="66">
         <v>4</v>
@@ -9158,7 +9158,7 @@
     </row>
     <row r="106" spans="1:16" ht="14.25" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>200</v>
@@ -9169,30 +9169,30 @@
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="51" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G106" s="51" t="s">
         <v>104</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="I106" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="26" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="L106" s="91"/>
       <c r="M106" s="66" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="N106" s="5" t="s">
         <v>101</v>
       </c>
       <c r="O106" s="66" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="P106" s="66">
         <v>4</v>
@@ -9258,7 +9258,7 @@
         <v>38</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>40</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="67" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>14</v>
@@ -9289,7 +9289,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
@@ -9301,7 +9301,7 @@
         <v>200</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>71</v>
@@ -9313,7 +9313,7 @@
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="23.25" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>17</v>
@@ -9328,23 +9328,23 @@
         <v>8751.6116205773851</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="L3" s="8">
         <v>7363</v>
       </c>
       <c r="M3" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>57</v>
@@ -9356,7 +9356,7 @@
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1">
       <c r="A4" s="10" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>17</v>
@@ -9371,7 +9371,7 @@
         <v>34084.065120622952</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="14" t="s">
@@ -9379,13 +9379,13 @@
       </c>
       <c r="J4" s="87"/>
       <c r="K4" s="12" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>57</v>
@@ -9397,7 +9397,7 @@
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1" ht="24">
       <c r="A5" s="10" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="8" t="s">
@@ -9406,26 +9406,26 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="8" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="109"/>
       <c r="K5" s="8" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="M5" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>71</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1">
       <c r="A6" s="10" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>17</v>
@@ -9454,21 +9454,21 @@
         <v>25271.303751033935</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
         <v>16700</v>
       </c>
       <c r="M6" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>57</v>
@@ -9480,7 +9480,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="67" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>14</v>
@@ -9494,7 +9494,7 @@
         <v>250</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H7" s="59"/>
       <c r="I7" s="14" t="s">
@@ -9506,7 +9506,7 @@
         <v>250</v>
       </c>
       <c r="M7" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>57</v>
@@ -9518,7 +9518,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="67" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="8" t="s">
@@ -9530,10 +9530,10 @@
         <v>0.85</v>
       </c>
       <c r="G8" s="111" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="H8" s="111" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>49</v>
@@ -9544,7 +9544,7 @@
         <v>0.85</v>
       </c>
       <c r="M8" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>51</v>
@@ -9558,10 +9558,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="120" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>46</v>
@@ -9572,7 +9572,7 @@
         <v>42</v>
       </c>
       <c r="G9" s="111" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H9" s="111"/>
       <c r="I9" s="14" t="s">
@@ -9584,7 +9584,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>71</v>
@@ -9596,7 +9596,7 @@
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A10" s="28" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
@@ -9629,7 +9629,7 @@
         <v>38</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>40</v>
@@ -9646,7 +9646,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="67" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>14</v>
@@ -9663,7 +9663,7 @@
         <v>104</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>49</v>
@@ -9674,7 +9674,7 @@
         <v>250</v>
       </c>
       <c r="M11" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>57</v>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="12" spans="1:16" s="1" customFormat="1">
       <c r="A12" s="67" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>14</v>
@@ -9705,7 +9705,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>49</v>
@@ -9716,7 +9716,7 @@
         <v>300</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>57</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="13" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A13" s="28" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -9763,7 +9763,7 @@
         <v>38</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>40</v>
@@ -9780,10 +9780,10 @@
     </row>
     <row r="14" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A14" s="30" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>46</v>
@@ -9802,32 +9802,32 @@
         <v>270</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="33" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="L14" s="5">
         <v>3140</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A15" s="30" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
@@ -9842,23 +9842,23 @@
         <v>2119.3689320388348</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I15" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="33" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="L15" s="5">
         <v>3140</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>71</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="16" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A16" s="30" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
@@ -9885,23 +9885,23 @@
         <v>266.88349514563106</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I16" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="33" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="L16" s="5">
         <v>3140</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>71</v>
@@ -9913,10 +9913,10 @@
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A17" s="30" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>46</v>
@@ -9935,32 +9935,32 @@
         <v>270</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="33" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="L17" s="5">
         <v>2680</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A18" s="30" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>17</v>
@@ -9975,23 +9975,23 @@
         <v>807.69230769230774</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="33" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="L18" s="5">
         <v>2680</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>71</v>
@@ -10003,7 +10003,7 @@
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A19" s="30" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
@@ -10018,23 +10018,23 @@
         <v>2794.6153846153843</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="33" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="L19" s="5">
         <v>2680</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>71</v>
@@ -10046,10 +10046,10 @@
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A20" s="30" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>46</v>
@@ -10068,32 +10068,32 @@
         <v>270</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L20" s="5">
         <v>1020</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A21" s="30" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>17</v>
@@ -10108,23 +10108,23 @@
         <v>234.9</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I21" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L21" s="5">
         <v>1020</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>71</v>
@@ -10136,7 +10136,7 @@
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A22" s="30" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>17</v>
@@ -10151,23 +10151,23 @@
         <v>899</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L22" s="5">
         <v>1020</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>71</v>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A23" s="30" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>46</v>
@@ -10201,32 +10201,32 @@
         <v>270</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I23" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L23" s="5">
         <v>730</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N23" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A24" s="30" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>17</v>
@@ -10241,23 +10241,23 @@
         <v>287.63999999999993</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L24" s="5">
         <v>730</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>71</v>
@@ -10269,7 +10269,7 @@
     </row>
     <row r="25" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A25" s="30" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>17</v>
@@ -10284,23 +10284,23 @@
         <v>484.5</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L25" s="5">
         <v>730</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>71</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="26" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A26" s="30" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>46</v>
@@ -10334,32 +10334,32 @@
         <v>270</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L26" s="5">
         <v>110</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A27" s="30" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>17</v>
@@ -10374,23 +10374,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L27" s="5">
         <v>110</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N27" s="5" t="s">
         <v>71</v>
@@ -10402,7 +10402,7 @@
     </row>
     <row r="28" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A28" s="30" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>17</v>
@@ -10417,23 +10417,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L28" s="5">
         <v>110</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N28" s="5" t="s">
         <v>71</v>
@@ -10445,10 +10445,10 @@
     </row>
     <row r="29" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A29" s="30" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>46</v>
@@ -10467,32 +10467,32 @@
         <v>270</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L29" s="5">
         <v>110</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A30" s="30" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>17</v>
@@ -10507,23 +10507,23 @@
         <v>42.315000000000005</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I30" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L30" s="5">
         <v>110</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>71</v>
@@ -10535,7 +10535,7 @@
     </row>
     <row r="31" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A31" s="30" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>17</v>
@@ -10550,23 +10550,23 @@
         <v>74.864999999999995</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L31" s="5">
         <v>110</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N31" s="5" t="s">
         <v>71</v>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="32" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A32" s="30" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>46</v>
@@ -10600,32 +10600,32 @@
         <v>270</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L32" s="5">
         <v>1030</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A33" s="30" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>17</v>
@@ -10640,23 +10640,23 @@
         <v>289.8</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L33" s="5">
         <v>1030</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>71</v>
@@ -10668,7 +10668,7 @@
     </row>
     <row r="34" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A34" s="30" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>17</v>
@@ -10683,23 +10683,23 @@
         <v>1031.3999999999999</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L34" s="5">
         <v>1030</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>71</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A35" s="30" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>46</v>
@@ -10735,32 +10735,32 @@
         <v>270</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L35" s="5">
         <v>160</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O35" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A36" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>17</v>
@@ -10775,23 +10775,23 @@
         <v>100.8</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L36" s="5">
         <v>160</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N36" s="5" t="s">
         <v>71</v>
@@ -10803,7 +10803,7 @@
     </row>
     <row r="37" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A37" s="30" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>17</v>
@@ -10818,23 +10818,23 @@
         <v>133.80000000000001</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L37" s="5">
         <v>160</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N37" s="5" t="s">
         <v>71</v>
@@ -10846,10 +10846,10 @@
     </row>
     <row r="38" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A38" s="30" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>46</v>
@@ -10870,32 +10870,32 @@
         <v>270</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L38" s="5">
         <v>160</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A39" s="30" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>17</v>
@@ -10910,23 +10910,23 @@
         <v>67.2</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L39" s="5">
         <v>160</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N39" s="5" t="s">
         <v>71</v>
@@ -10938,7 +10938,7 @@
     </row>
     <row r="40" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A40" s="30" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>17</v>
@@ -10953,23 +10953,23 @@
         <v>89.2</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L40" s="5">
         <v>160</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N40" s="5" t="s">
         <v>71</v>
@@ -10981,10 +10981,10 @@
     </row>
     <row r="41" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A41" s="30" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>46</v>
@@ -11003,32 +11003,32 @@
         <v>270</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L41" s="5">
         <v>13090</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A42" s="30" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>17</v>
@@ -11043,23 +11043,23 @@
         <v>3421.9999999999995</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I42" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L42" s="5">
         <v>13090</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>71</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="43" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A43" s="30" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>17</v>
@@ -11086,23 +11086,23 @@
         <v>18270</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L43" s="5">
         <v>13090</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>71</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="30" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>89</v>
@@ -11125,10 +11125,10 @@
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="52" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="26" t="s">
@@ -11138,7 +11138,7 @@
       <c r="K44" s="33"/>
       <c r="L44" s="21"/>
       <c r="M44" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>71</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="30" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>89</v>
@@ -11161,7 +11161,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="113" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="G45" s="17" t="s">
         <v>544</v>
@@ -11172,11 +11172,11 @@
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="33" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>71</v>
@@ -11188,10 +11188,10 @@
     </row>
     <row r="46" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A46" s="30" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>46</v>
@@ -11210,32 +11210,32 @@
         <v>270</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L46" s="5">
         <v>190</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A47" s="30" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>17</v>
@@ -11250,23 +11250,23 @@
         <v>105.60000000000001</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L47" s="5">
         <v>190</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>71</v>
@@ -11278,7 +11278,7 @@
     </row>
     <row r="48" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A48" s="30" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>17</v>
@@ -11293,23 +11293,23 @@
         <v>150.47999999999999</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I48" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="17"/>
       <c r="K48" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L48" s="5">
         <v>190</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>71</v>
@@ -11321,10 +11321,10 @@
     </row>
     <row r="49" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A49" s="30" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>46</v>
@@ -11343,32 +11343,32 @@
         <v>270</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I49" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L49" s="5">
         <v>1550</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A50" s="30" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>17</v>
@@ -11383,23 +11383,23 @@
         <v>1200.9303808462425</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I50" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L50" s="5">
         <v>1550</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N50" s="5" t="s">
         <v>71</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="51" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A51" s="30" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
@@ -11426,23 +11426,23 @@
         <v>914.844871272923</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I51" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="17"/>
       <c r="K51" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L51" s="5">
         <v>1550</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N51" s="5" t="s">
         <v>71</v>
@@ -11454,10 +11454,10 @@
     </row>
     <row r="52" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A52" s="30" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>46</v>
@@ -11476,32 +11476,32 @@
         <v>270</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I52" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L52" s="5">
         <v>100</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A53" s="30" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
@@ -11516,23 +11516,23 @@
         <v>31.049999999999997</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I53" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L53" s="5">
         <v>100</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>71</v>
@@ -11544,7 +11544,7 @@
     </row>
     <row r="54" spans="1:16" s="1" customFormat="1" ht="12">
       <c r="A54" s="30" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>17</v>
@@ -11559,23 +11559,23 @@
         <v>86.85</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>49</v>
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L54" s="5">
         <v>100</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>71</v>
@@ -11587,7 +11587,7 @@
     </row>
     <row r="55" spans="1:16" ht="24">
       <c r="A55" s="28" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1</v>
@@ -11637,7 +11637,7 @@
     </row>
     <row r="56" spans="1:16" ht="24.75">
       <c r="A56" s="30" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>89</v>
@@ -11648,7 +11648,7 @@
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="18" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="G56" s="18" t="s">
         <v>143</v>
@@ -11659,23 +11659,23 @@
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="114" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="30" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>89</v>
@@ -11696,22 +11696,22 @@
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="35" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="30" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>89</v>
@@ -11725,10 +11725,10 @@
         <v>25</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>49</v>
@@ -11736,22 +11736,22 @@
       <c r="J58" s="17"/>
       <c r="K58" s="19"/>
       <c r="L58" s="12" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="30" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>89</v>
@@ -11765,10 +11765,10 @@
         <v>1.2</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I59" s="18" t="s">
         <v>49</v>
@@ -11776,22 +11776,22 @@
       <c r="J59" s="17"/>
       <c r="K59" s="19"/>
       <c r="L59" s="8" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O59" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" ht="24">
       <c r="A60" s="30" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="B60" s="115" t="s">
         <v>89</v>
@@ -11802,7 +11802,7 @@
       <c r="D60" s="115"/>
       <c r="E60" s="115"/>
       <c r="F60" s="116" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="G60" s="115"/>
       <c r="H60" s="116"/>
@@ -11811,23 +11811,23 @@
       </c>
       <c r="J60" s="116"/>
       <c r="K60" s="116" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L60" s="8"/>
       <c r="M60" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="30" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>89</v>
@@ -11841,10 +11841,10 @@
         <v>116</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>49</v>
@@ -11853,19 +11853,19 @@
       <c r="K61" s="33"/>
       <c r="L61" s="14"/>
       <c r="M61" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O61" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" ht="36.75">
       <c r="A62" s="30" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="B62" s="115"/>
       <c r="C62" s="116"/>
@@ -11879,26 +11879,26 @@
       </c>
       <c r="J62" s="116"/>
       <c r="K62" s="117" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="L62" s="14"/>
       <c r="M62" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N62" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="72.75">
       <c r="A63" s="30" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -11906,36 +11906,36 @@
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="8" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="I63" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="114" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N63" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="30" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>89</v>
@@ -11949,10 +11949,10 @@
         <v>5.9</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I64" s="18" t="s">
         <v>49</v>
@@ -11961,19 +11961,19 @@
       <c r="K64" s="33"/>
       <c r="L64" s="21"/>
       <c r="M64" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="30" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>89</v>
@@ -11993,26 +11993,26 @@
       </c>
       <c r="J65" s="26"/>
       <c r="K65" s="33" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N65" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" ht="24.75">
       <c r="A66" s="30" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>46</v>
@@ -12020,36 +12020,36 @@
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="26" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="I66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="114" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N66" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O66" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" ht="48.75">
       <c r="A67" s="30" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>89</v>
@@ -12060,36 +12060,36 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="26" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="33" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O67" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" ht="24">
       <c r="A68" s="30" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B68" s="115"/>
       <c r="C68" s="116"/>
@@ -12103,26 +12103,26 @@
       </c>
       <c r="J68" s="116"/>
       <c r="K68" s="115" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="30" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>46</v>
@@ -12130,13 +12130,13 @@
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="26" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>49</v>
@@ -12145,19 +12145,19 @@
       <c r="K69" s="26"/>
       <c r="L69" s="4"/>
       <c r="M69" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" ht="24">
       <c r="A70" s="30" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>89</v>
@@ -12168,7 +12168,7 @@
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
       <c r="F70" s="8" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="G70" s="17"/>
       <c r="H70" s="8"/>
@@ -12177,23 +12177,23 @@
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="116" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N70" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="10" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>89</v>
@@ -12207,10 +12207,10 @@
         <v>4.5</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I71" s="18" t="s">
         <v>49</v>
@@ -12219,19 +12219,19 @@
       <c r="K71" s="33"/>
       <c r="L71" s="4"/>
       <c r="M71" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="30" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>89</v>
@@ -12245,10 +12245,10 @@
         <v>145</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I72" s="18" t="s">
         <v>49</v>
@@ -12257,19 +12257,19 @@
       <c r="K72" s="33"/>
       <c r="L72" s="4"/>
       <c r="M72" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N72" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O72" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="30" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B73" s="36" t="s">
         <v>89</v>
@@ -12287,23 +12287,23 @@
       </c>
       <c r="J73" s="118"/>
       <c r="K73" s="114" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O73" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" ht="36">
       <c r="A74" s="30" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>66</v>
@@ -12325,23 +12325,23 @@
       </c>
       <c r="J74" s="119"/>
       <c r="K74" s="47" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N74" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" ht="24.75">
       <c r="A75" s="30" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>89</v>
@@ -12352,7 +12352,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="18" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="G75" s="18"/>
       <c r="H75" s="18"/>
@@ -12361,23 +12361,23 @@
       </c>
       <c r="J75" s="18"/>
       <c r="K75" s="114" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N75" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O75" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="30" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>89</v>
@@ -12397,23 +12397,23 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="35" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N76" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O76" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="30" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>89</v>
@@ -12427,10 +12427,10 @@
         <v>16</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>49</v>
@@ -12439,19 +12439,19 @@
       <c r="K77" s="19"/>
       <c r="L77" s="4"/>
       <c r="M77" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O77" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="30" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>89</v>
@@ -12465,10 +12465,10 @@
         <v>1E-4</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>49</v>
@@ -12477,19 +12477,19 @@
       <c r="K78" s="19"/>
       <c r="L78" s="4"/>
       <c r="M78" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O78" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" ht="24">
       <c r="A79" s="30" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="B79" s="115" t="s">
         <v>89</v>
@@ -12500,7 +12500,7 @@
       <c r="D79" s="115"/>
       <c r="E79" s="115"/>
       <c r="F79" s="116" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="G79" s="115"/>
       <c r="H79" s="116"/>
@@ -12509,23 +12509,23 @@
       </c>
       <c r="J79" s="116"/>
       <c r="K79" s="116" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N79" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="30" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>89</v>
@@ -12539,10 +12539,10 @@
         <v>20</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I80" s="18" t="s">
         <v>49</v>
@@ -12551,19 +12551,19 @@
       <c r="K80" s="33"/>
       <c r="L80" s="4"/>
       <c r="M80" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N80" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" ht="36.75">
       <c r="A81" s="30" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>89</v>
@@ -12581,26 +12581,26 @@
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="114" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N81" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" ht="72.75">
       <c r="A82" s="30" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>46</v>
@@ -12608,36 +12608,36 @@
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="8" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="114" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N82" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="30" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>89</v>
@@ -12651,10 +12651,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>49</v>
@@ -12663,19 +12663,19 @@
       <c r="K83" s="33"/>
       <c r="L83" s="21"/>
       <c r="M83" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N83" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="30" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>89</v>
@@ -12695,26 +12695,26 @@
       </c>
       <c r="J84" s="26"/>
       <c r="K84" s="33" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" ht="24.75">
       <c r="A85" s="30" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>46</v>
@@ -12722,36 +12722,36 @@
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="26" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="114" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N85" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" ht="48.75">
       <c r="A86" s="30" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>89</v>
@@ -12762,36 +12762,36 @@
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="26" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="33" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N86" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O86" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="30" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>89</v>
@@ -12811,22 +12811,22 @@
       <c r="K87" s="26"/>
       <c r="L87" s="4"/>
       <c r="M87" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N87" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="30" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>46</v>
@@ -12834,13 +12834,13 @@
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="26" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>49</v>
@@ -12849,19 +12849,19 @@
       <c r="K88" s="26"/>
       <c r="L88" s="4"/>
       <c r="M88" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O88" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" ht="24">
       <c r="A89" s="30" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>89</v>
@@ -12872,7 +12872,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="8" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="G89" s="17"/>
       <c r="H89" s="8"/>
@@ -12881,23 +12881,23 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="116" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="10" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>89</v>
@@ -12911,10 +12911,10 @@
         <v>120</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I90" s="18" t="s">
         <v>49</v>
@@ -12923,19 +12923,19 @@
       <c r="K90" s="33"/>
       <c r="L90" s="4"/>
       <c r="M90" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="30" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>89</v>
@@ -12949,10 +12949,10 @@
         <v>15</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H91" s="26" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I91" s="18" t="s">
         <v>49</v>
@@ -12961,19 +12961,19 @@
       <c r="K91" s="33"/>
       <c r="L91" s="4"/>
       <c r="M91" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N91" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="30" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="B92" s="36" t="s">
         <v>89</v>
@@ -12991,23 +12991,23 @@
       </c>
       <c r="J92" s="114"/>
       <c r="K92" s="114" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N92" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O92" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" ht="36">
       <c r="A93" s="30" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>66</v>
@@ -13029,17 +13029,17 @@
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="33" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="5" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="N93" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O93" s="14" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="P93" s="14"/>
     </row>
@@ -13585,7 +13585,7 @@
     </row>
     <row r="14" spans="1:16" ht="24">
       <c r="A14" s="10" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>581</v>
@@ -13596,7 +13596,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="26" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>15</v>
@@ -13623,7 +13623,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="48" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="8"/>
@@ -15134,7 +15134,7 @@
         <v>213</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="5" t="s">
@@ -15144,7 +15144,7 @@
         <v>71</v>
       </c>
       <c r="O52" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="P52" s="14"/>
     </row>
@@ -15184,7 +15184,7 @@
         <v>71</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="P53" s="14"/>
     </row>
@@ -15224,7 +15224,7 @@
         <v>71</v>
       </c>
       <c r="O54" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="P54" s="14"/>
     </row>
@@ -15264,7 +15264,7 @@
         <v>71</v>
       </c>
       <c r="O55" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="P55" s="14"/>
     </row>
@@ -15302,7 +15302,7 @@
         <v>71</v>
       </c>
       <c r="O56" s="5" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="P56" s="14"/>
     </row>
@@ -15386,7 +15386,7 @@
         <v>71</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P58" s="14"/>
     </row>
@@ -15428,7 +15428,7 @@
         <v>71</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P59" s="14"/>
     </row>
@@ -15466,7 +15466,7 @@
         <v>71</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P60" s="14"/>
     </row>
@@ -15502,7 +15502,7 @@
         <v>71</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P61" s="14"/>
     </row>
@@ -15540,7 +15540,7 @@
         <v>101</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P62" s="14"/>
     </row>
@@ -15578,7 +15578,7 @@
         <v>101</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P63" s="14"/>
     </row>
@@ -15617,7 +15617,7 @@
         <v>101</v>
       </c>
       <c r="O64" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P64" s="14"/>
     </row>
@@ -15656,7 +15656,7 @@
         <v>71</v>
       </c>
       <c r="O65" s="5" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="P65" s="14"/>
     </row>
@@ -15744,7 +15744,7 @@
         <v>71</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P67" s="14"/>
     </row>
@@ -15774,7 +15774,7 @@
         <v>71</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P68" s="14"/>
     </row>
@@ -15804,7 +15804,7 @@
         <v>71</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P69" s="14"/>
     </row>
@@ -15834,7 +15834,7 @@
         <v>71</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P70" s="14"/>
     </row>
@@ -15874,7 +15874,7 @@
         <v>71</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P71" s="14"/>
     </row>
@@ -15912,7 +15912,7 @@
         <v>71</v>
       </c>
       <c r="O72" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P72" s="14"/>
     </row>
@@ -15942,7 +15942,7 @@
         <v>71</v>
       </c>
       <c r="O73" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P73" s="14"/>
     </row>
@@ -15979,7 +15979,7 @@
         <v>71</v>
       </c>
       <c r="O74" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P74" s="14"/>
     </row>
@@ -16017,7 +16017,7 @@
         <v>71</v>
       </c>
       <c r="O75" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P75" s="14"/>
     </row>
@@ -16053,7 +16053,7 @@
         <v>71</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P76" s="14"/>
     </row>
@@ -16083,7 +16083,7 @@
         <v>71</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P77" s="14"/>
     </row>
@@ -16121,7 +16121,7 @@
         <v>71</v>
       </c>
       <c r="O78" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P78" s="14"/>
     </row>
@@ -16151,7 +16151,7 @@
         <v>71</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P79" s="14"/>
     </row>
@@ -16189,7 +16189,7 @@
         <v>71</v>
       </c>
       <c r="O80" s="5" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="P80" s="14"/>
     </row>
@@ -20811,7 +20811,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="49"/>
       <c r="K2" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="14" t="s">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="J3" s="49"/>
       <c r="K3" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>57</v>
@@ -20887,7 +20887,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="49"/>
       <c r="K4" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>71</v>
@@ -20925,7 +20925,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="49"/>
       <c r="K5" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>57</v>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="14" t="s">
@@ -20999,7 +20999,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="49"/>
       <c r="K7" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>57</v>
@@ -21035,7 +21035,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="49"/>
       <c r="K8" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>71</v>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="J9" s="49"/>
       <c r="K9" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>71</v>
@@ -21111,7 +21111,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="49"/>
       <c r="K10" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>71</v>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="J11" s="49"/>
       <c r="K11" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>71</v>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="J12" s="49"/>
       <c r="K12" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>51</v>
@@ -21222,7 +21222,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="49"/>
       <c r="K13" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>57</v>
@@ -21252,7 +21252,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="49"/>
       <c r="K14" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="14" t="s">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="J15" s="49"/>
       <c r="K15" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>71</v>
@@ -21324,7 +21324,7 @@
       <c r="I16" s="17"/>
       <c r="J16" s="49"/>
       <c r="K16" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>71</v>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="J17" s="49"/>
       <c r="K17" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>71</v>
@@ -21394,7 +21394,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="49"/>
       <c r="K18" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="14" t="s">
@@ -21420,7 +21420,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="49"/>
       <c r="K19" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="14" t="s">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>71</v>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="J21" s="49"/>
       <c r="K21" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>71</v>
@@ -21524,7 +21524,7 @@
       <c r="I22" s="8"/>
       <c r="J22" s="49"/>
       <c r="K22" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="14" t="s">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>71</v>
@@ -21600,7 +21600,7 @@
       </c>
       <c r="J24" s="49"/>
       <c r="K24" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>71</v>
@@ -21634,7 +21634,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="49"/>
       <c r="K25" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>71</v>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="J26" s="49"/>
       <c r="K26" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="14" t="s">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="J27" s="49"/>
       <c r="K27" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="14" t="s">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="J28" s="49"/>
       <c r="K28" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>71</v>
@@ -21760,7 +21760,7 @@
       <c r="I29" s="8"/>
       <c r="J29" s="49"/>
       <c r="K29" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>140</v>
@@ -21800,7 +21800,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="49"/>
       <c r="K30" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>140</v>
@@ -21842,7 +21842,7 @@
       </c>
       <c r="J31" s="49"/>
       <c r="K31" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>71</v>
@@ -21880,7 +21880,7 @@
       </c>
       <c r="J32" s="49"/>
       <c r="K32" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>71</v>
@@ -21920,7 +21920,7 @@
       </c>
       <c r="J33" s="49"/>
       <c r="K33" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>71</v>
@@ -21960,7 +21960,7 @@
       </c>
       <c r="J34" s="49"/>
       <c r="K34" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>71</v>
@@ -21996,7 +21996,7 @@
       <c r="I35" s="8"/>
       <c r="J35" s="49"/>
       <c r="K35" s="5" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>71</v>
@@ -22078,7 +22078,7 @@
       </c>
       <c r="J37" s="49"/>
       <c r="K37" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>71</v>
@@ -22112,7 +22112,7 @@
       <c r="I38" s="25"/>
       <c r="J38" s="49"/>
       <c r="K38" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>71</v>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="J39" s="49"/>
       <c r="K39" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>71</v>
@@ -22182,7 +22182,7 @@
       <c r="I40" s="25"/>
       <c r="J40" s="49"/>
       <c r="K40" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>71</v>
@@ -22216,7 +22216,7 @@
       <c r="I41" s="25"/>
       <c r="J41" s="49"/>
       <c r="K41" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>71</v>
@@ -22250,7 +22250,7 @@
       <c r="I42" s="25"/>
       <c r="J42" s="49"/>
       <c r="K42" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>71</v>
@@ -22284,7 +22284,7 @@
       <c r="I43" s="25"/>
       <c r="J43" s="49"/>
       <c r="K43" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>71</v>
@@ -22318,7 +22318,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="49"/>
       <c r="K44" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>71</v>
@@ -22354,7 +22354,7 @@
       </c>
       <c r="J45" s="49"/>
       <c r="K45" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>71</v>
@@ -22388,7 +22388,7 @@
       <c r="I46" s="25"/>
       <c r="J46" s="49"/>
       <c r="K46" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>71</v>
@@ -22422,7 +22422,7 @@
       <c r="I47" s="25"/>
       <c r="J47" s="49"/>
       <c r="K47" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>71</v>
@@ -22456,7 +22456,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="49"/>
       <c r="K48" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>71</v>
@@ -22492,7 +22492,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="49"/>
       <c r="K49" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>71</v>
@@ -22528,7 +22528,7 @@
       <c r="I50" s="25"/>
       <c r="J50" s="49"/>
       <c r="K50" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>71</v>
@@ -22562,7 +22562,7 @@
       <c r="I51" s="25"/>
       <c r="J51" s="49"/>
       <c r="K51" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>71</v>
@@ -22596,7 +22596,7 @@
       <c r="I52" s="59"/>
       <c r="J52" s="49"/>
       <c r="K52" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>71</v>
@@ -22630,7 +22630,7 @@
       <c r="I53" s="25"/>
       <c r="J53" s="49"/>
       <c r="K53" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>71</v>
@@ -22664,7 +22664,7 @@
       <c r="I54" s="59"/>
       <c r="J54" s="49"/>
       <c r="K54" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>71</v>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="J55" s="49"/>
       <c r="K55" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>71</v>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="J56" s="49"/>
       <c r="K56" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>71</v>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="J57" s="49"/>
       <c r="K57" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>71</v>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>71</v>
@@ -22844,7 +22844,7 @@
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>71</v>
@@ -22880,7 +22880,7 @@
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>71</v>
@@ -22916,7 +22916,7 @@
       </c>
       <c r="J61" s="49"/>
       <c r="K61" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>71</v>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="J62" s="49"/>
       <c r="K62" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>71</v>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="J63" s="49"/>
       <c r="K63" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>71</v>
@@ -23022,7 +23022,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="49"/>
       <c r="K64" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>71</v>
@@ -23058,7 +23058,7 @@
       <c r="I65" s="25"/>
       <c r="J65" s="49"/>
       <c r="K65" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>71</v>
@@ -23094,7 +23094,7 @@
       <c r="I66" s="25"/>
       <c r="J66" s="49"/>
       <c r="K66" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>71</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="J67" s="49"/>
       <c r="K67" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>71</v>
@@ -23170,7 +23170,7 @@
       <c r="I68" s="25"/>
       <c r="J68" s="49"/>
       <c r="K68" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>71</v>
@@ -23206,7 +23206,7 @@
       </c>
       <c r="J69" s="49"/>
       <c r="K69" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>71</v>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="J70" s="49"/>
       <c r="K70" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>71</v>
@@ -23278,7 +23278,7 @@
       </c>
       <c r="J71" s="49"/>
       <c r="K71" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>71</v>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="J72" s="49"/>
       <c r="K72" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>71</v>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="J73" s="49"/>
       <c r="K73" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>71</v>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="J74" s="49"/>
       <c r="K74" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>71</v>
@@ -23422,7 +23422,7 @@
       </c>
       <c r="J75" s="49"/>
       <c r="K75" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>71</v>
@@ -23458,7 +23458,7 @@
       </c>
       <c r="J76" s="49"/>
       <c r="K76" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>71</v>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="J77" s="49"/>
       <c r="K77" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>71</v>
@@ -23530,7 +23530,7 @@
       </c>
       <c r="J78" s="49"/>
       <c r="K78" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>71</v>
@@ -23566,7 +23566,7 @@
       </c>
       <c r="J79" s="49"/>
       <c r="K79" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>71</v>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="J80" s="49"/>
       <c r="K80" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>71</v>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="J81" s="49"/>
       <c r="K81" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>71</v>
@@ -23674,7 +23674,7 @@
       <c r="I82" s="25"/>
       <c r="J82" s="49"/>
       <c r="K82" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>71</v>
@@ -23710,7 +23710,7 @@
       </c>
       <c r="J83" s="49"/>
       <c r="K83" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>71</v>
@@ -23746,7 +23746,7 @@
       <c r="I84" s="25"/>
       <c r="J84" s="49"/>
       <c r="K84" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>71</v>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="J85" s="49"/>
       <c r="K85" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>71</v>
@@ -23818,7 +23818,7 @@
       <c r="I86" s="25"/>
       <c r="J86" s="49"/>
       <c r="K86" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>71</v>
@@ -23852,7 +23852,7 @@
       <c r="I87" s="59"/>
       <c r="J87" s="49"/>
       <c r="K87" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>71</v>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="J88" s="49"/>
       <c r="K88" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>71</v>
@@ -23926,7 +23926,7 @@
       </c>
       <c r="J89" s="49"/>
       <c r="K89" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>71</v>
@@ -23960,7 +23960,7 @@
       <c r="I90" s="25"/>
       <c r="J90" s="49"/>
       <c r="K90" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>71</v>
@@ -23996,7 +23996,7 @@
       </c>
       <c r="J91" s="49"/>
       <c r="K91" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>71</v>
@@ -24030,7 +24030,7 @@
       <c r="I92" s="25"/>
       <c r="J92" s="49"/>
       <c r="K92" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>71</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="J93" s="49"/>
       <c r="K93" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>71</v>
@@ -24100,7 +24100,7 @@
       <c r="I94" s="25"/>
       <c r="J94" s="49"/>
       <c r="K94" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>71</v>
@@ -24136,7 +24136,7 @@
       <c r="I95" s="25"/>
       <c r="J95" s="49"/>
       <c r="K95" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>71</v>
@@ -24172,7 +24172,7 @@
       <c r="I96" s="25"/>
       <c r="J96" s="49"/>
       <c r="K96" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>71</v>
@@ -24208,7 +24208,7 @@
       </c>
       <c r="J97" s="49"/>
       <c r="K97" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>71</v>
@@ -24242,7 +24242,7 @@
       <c r="I98" s="25"/>
       <c r="J98" s="49"/>
       <c r="K98" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>71</v>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="J99" s="49"/>
       <c r="K99" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>71</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="J100" s="49"/>
       <c r="K100" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>71</v>
@@ -24352,7 +24352,7 @@
       <c r="I101" s="25"/>
       <c r="J101" s="49"/>
       <c r="K101" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>71</v>
@@ -24390,7 +24390,7 @@
       </c>
       <c r="J102" s="49"/>
       <c r="K102" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>71</v>
@@ -24426,7 +24426,7 @@
       <c r="I103" s="59"/>
       <c r="J103" s="49"/>
       <c r="K103" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>71</v>
@@ -24462,7 +24462,7 @@
       </c>
       <c r="J104" s="49"/>
       <c r="K104" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>71</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="J105" s="49"/>
       <c r="K105" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>71</v>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="J106" s="49"/>
       <c r="K106" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>71</v>
@@ -24570,7 +24570,7 @@
       </c>
       <c r="J107" s="49"/>
       <c r="K107" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>71</v>
@@ -24606,7 +24606,7 @@
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>71</v>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="J109" s="49"/>
       <c r="K109" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>71</v>
@@ -24678,7 +24678,7 @@
       </c>
       <c r="J110" s="49"/>
       <c r="K110" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>71</v>
@@ -24714,7 +24714,7 @@
       </c>
       <c r="J111" s="49"/>
       <c r="K111" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>71</v>
@@ -24750,7 +24750,7 @@
       </c>
       <c r="J112" s="49"/>
       <c r="K112" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>71</v>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="J113" s="49"/>
       <c r="K113" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>71</v>
@@ -24820,7 +24820,7 @@
       <c r="I114" s="25"/>
       <c r="J114" s="49"/>
       <c r="K114" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>71</v>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="J115" s="49"/>
       <c r="K115" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>71</v>
@@ -24890,7 +24890,7 @@
       <c r="I116" s="25"/>
       <c r="J116" s="49"/>
       <c r="K116" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>71</v>
@@ -24924,7 +24924,7 @@
       <c r="I117" s="25"/>
       <c r="J117" s="49"/>
       <c r="K117" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>71</v>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="J118" s="49"/>
       <c r="K118" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>71</v>
@@ -24996,7 +24996,7 @@
       </c>
       <c r="J119" s="49"/>
       <c r="K119" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L119" s="5" t="s">
         <v>71</v>
@@ -25030,7 +25030,7 @@
       <c r="I120" s="59"/>
       <c r="J120" s="49"/>
       <c r="K120" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>71</v>
@@ -25066,7 +25066,7 @@
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L121" s="5" t="s">
         <v>71</v>
@@ -25102,7 +25102,7 @@
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>71</v>
@@ -25138,7 +25138,7 @@
       </c>
       <c r="J123" s="49"/>
       <c r="K123" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>71</v>
@@ -25174,7 +25174,7 @@
       </c>
       <c r="J124" s="49"/>
       <c r="K124" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>71</v>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="J125" s="49"/>
       <c r="K125" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L125" s="5" t="s">
         <v>71</v>
@@ -25246,7 +25246,7 @@
       </c>
       <c r="J126" s="49"/>
       <c r="K126" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L126" s="5" t="s">
         <v>71</v>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="J127" s="49"/>
       <c r="K127" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L127" s="5" t="s">
         <v>71</v>
@@ -25318,7 +25318,7 @@
       </c>
       <c r="J128" s="49"/>
       <c r="K128" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L128" s="5" t="s">
         <v>71</v>
@@ -25354,7 +25354,7 @@
       </c>
       <c r="J129" s="49"/>
       <c r="K129" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L129" s="5" t="s">
         <v>71</v>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="J130" s="49"/>
       <c r="K130" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>71</v>
@@ -25426,7 +25426,7 @@
       <c r="I131" s="25"/>
       <c r="J131" s="49"/>
       <c r="K131" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L131" s="5" t="s">
         <v>71</v>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="J132" s="49"/>
       <c r="K132" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L132" s="5" t="s">
         <v>71</v>
@@ -25498,7 +25498,7 @@
       <c r="I133" s="25"/>
       <c r="J133" s="49"/>
       <c r="K133" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L133" s="5" t="s">
         <v>71</v>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="J134" s="49"/>
       <c r="K134" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L134" s="5" t="s">
         <v>71</v>
@@ -25570,7 +25570,7 @@
       <c r="I135" s="25"/>
       <c r="J135" s="49"/>
       <c r="K135" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>71</v>
@@ -25604,7 +25604,7 @@
       <c r="I136" s="59"/>
       <c r="J136" s="49"/>
       <c r="K136" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L136" s="5" t="s">
         <v>71</v>
@@ -25638,7 +25638,7 @@
       <c r="I137" s="25"/>
       <c r="J137" s="49"/>
       <c r="K137" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L137" s="5" t="s">
         <v>71</v>
@@ -25672,7 +25672,7 @@
       <c r="I138" s="25"/>
       <c r="J138" s="49"/>
       <c r="K138" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L138" s="5" t="s">
         <v>71</v>
@@ -25706,7 +25706,7 @@
       <c r="I139" s="25"/>
       <c r="J139" s="49"/>
       <c r="K139" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>71</v>
@@ -25740,7 +25740,7 @@
       <c r="I140" s="25"/>
       <c r="J140" s="49"/>
       <c r="K140" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L140" s="5" t="s">
         <v>71</v>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="J141" s="49"/>
       <c r="K141" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L141" s="5" t="s">
         <v>71</v>
@@ -25810,7 +25810,7 @@
       <c r="I142" s="25"/>
       <c r="J142" s="49"/>
       <c r="K142" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L142" s="5" t="s">
         <v>71</v>
@@ -25844,7 +25844,7 @@
       <c r="I143" s="25"/>
       <c r="J143" s="49"/>
       <c r="K143" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L143" s="5" t="s">
         <v>71</v>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="J144" s="49"/>
       <c r="K144" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L144" s="5" t="s">
         <v>71</v>
@@ -25916,7 +25916,7 @@
       </c>
       <c r="J145" s="49"/>
       <c r="K145" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>71</v>
@@ -25952,7 +25952,7 @@
       </c>
       <c r="J146" s="49"/>
       <c r="K146" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>71</v>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="J147" s="49"/>
       <c r="K147" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L147" s="5" t="s">
         <v>71</v>
@@ -26024,7 +26024,7 @@
       </c>
       <c r="J148" s="49"/>
       <c r="K148" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L148" s="5" t="s">
         <v>71</v>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="J149" s="49"/>
       <c r="K149" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L149" s="5" t="s">
         <v>71</v>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="J150" s="49"/>
       <c r="K150" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L150" s="5" t="s">
         <v>71</v>
@@ -26132,7 +26132,7 @@
       </c>
       <c r="J151" s="49"/>
       <c r="K151" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L151" s="5" t="s">
         <v>71</v>
@@ -26168,7 +26168,7 @@
       </c>
       <c r="J152" s="49"/>
       <c r="K152" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L152" s="5" t="s">
         <v>71</v>
@@ -26204,7 +26204,7 @@
       </c>
       <c r="J153" s="49"/>
       <c r="K153" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L153" s="5" t="s">
         <v>71</v>
@@ -26238,7 +26238,7 @@
       <c r="I154" s="59"/>
       <c r="J154" s="56"/>
       <c r="K154" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L154" s="5" t="s">
         <v>71</v>
@@ -26272,7 +26272,7 @@
       <c r="I155" s="33"/>
       <c r="J155" s="56"/>
       <c r="K155" s="5" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>71</v>
@@ -26756,7 +26756,7 @@
     </row>
     <row r="10" spans="1:16" ht="24">
       <c r="A10" s="67" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>776</v>
@@ -26770,14 +26770,14 @@
         <v>347</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="59"/>
@@ -29473,7 +29473,7 @@
         <v>49</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -29514,7 +29514,7 @@
         <v>49</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
@@ -29555,7 +29555,7 @@
         <v>49</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
@@ -29596,7 +29596,7 @@
         <v>49</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
@@ -29637,7 +29637,7 @@
         <v>49</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
@@ -29678,7 +29678,7 @@
         <v>49</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
@@ -29719,7 +29719,7 @@
         <v>49</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -29760,7 +29760,7 @@
         <v>49</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -29884,7 +29884,7 @@
         <v>49</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -29925,7 +29925,7 @@
         <v>49</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
@@ -29966,7 +29966,7 @@
         <v>49</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
@@ -30007,7 +30007,7 @@
         <v>49</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -30048,7 +30048,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
@@ -30089,7 +30089,7 @@
         <v>49</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -30130,7 +30130,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
@@ -30171,7 +30171,7 @@
         <v>49</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
@@ -31606,7 +31606,7 @@
         <v>2.41E-5</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>748</v>
+        <v>710</v>
       </c>
       <c r="H110" s="18" t="s">
         <v>748</v>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="51" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
@@ -33112,7 +33112,7 @@
       </c>
       <c r="N146" s="5"/>
       <c r="O146" s="2" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P146" s="14"/>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="N147" s="5"/>
       <c r="O147" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P147" s="14"/>
     </row>
@@ -33148,7 +33148,7 @@
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="51" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
@@ -33163,7 +33163,7 @@
         <v>49</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>825</v>
+        <v>1190</v>
       </c>
       <c r="K148" s="90"/>
       <c r="L148" s="59"/>
@@ -33172,17 +33172,17 @@
       </c>
       <c r="N148" s="5"/>
       <c r="O148" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P148" s="14"/>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="40" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="51" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
@@ -33197,7 +33197,7 @@
         <v>49</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>827</v>
+        <v>1191</v>
       </c>
       <c r="K149" s="90"/>
       <c r="L149" s="59"/>
@@ -33206,13 +33206,13 @@
       </c>
       <c r="N149" s="5"/>
       <c r="O149" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P149" s="14"/>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="40" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="51"/>
@@ -33232,13 +33232,13 @@
       </c>
       <c r="N150" s="5"/>
       <c r="O150" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P150" s="14"/>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="40" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="str">
@@ -33272,17 +33272,17 @@
       </c>
       <c r="N151" s="5"/>
       <c r="O151" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P151" s="14"/>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="40" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="51" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
@@ -33297,7 +33297,7 @@
         <v>49</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>831</v>
+        <v>1192</v>
       </c>
       <c r="K152" s="90"/>
       <c r="L152" s="59"/>
@@ -33306,13 +33306,13 @@
       </c>
       <c r="N152" s="5"/>
       <c r="O152" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P152" s="14"/>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="40" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="51"/>
@@ -33332,17 +33332,17 @@
       </c>
       <c r="N153" s="5"/>
       <c r="O153" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P153" s="14"/>
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="40" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="51" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
@@ -33357,7 +33357,7 @@
         <v>49</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>834</v>
+        <v>1193</v>
       </c>
       <c r="K154" s="90"/>
       <c r="L154" s="59"/>
@@ -33366,13 +33366,13 @@
       </c>
       <c r="N154" s="5"/>
       <c r="O154" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P154" s="14"/>
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="40" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="51"/>
@@ -33392,13 +33392,13 @@
       </c>
       <c r="N155" s="5"/>
       <c r="O155" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P155" s="14"/>
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="40" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="51"/>
@@ -33418,13 +33418,13 @@
       </c>
       <c r="N156" s="5"/>
       <c r="O156" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P156" s="14"/>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="40" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="51"/>
@@ -33444,7 +33444,7 @@
       </c>
       <c r="N157" s="5"/>
       <c r="O157" s="5" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="P157" s="14"/>
     </row>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA06D4F-522B-4ED2-8DF9-D096181116FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271B74B7-C4C6-4E33-8098-20A5AB5D62BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28725" yWindow="4710" windowWidth="28530" windowHeight="23445" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="17250" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6593" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6617" uniqueCount="1195">
   <si>
     <t>Patient Inputs</t>
   </si>
@@ -3754,6 +3754,9 @@
   </si>
   <si>
     <t>Determined by albumin concentration &gt; 0.2 mg/mL</t>
+  </si>
+  <si>
+    <t>Thresholds</t>
   </si>
 </sst>
 </file>
@@ -4983,7 +4986,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -4999,10 +5002,10 @@
     <col min="13" max="13" width="24.7109375" style="64" customWidth="1"/>
     <col min="14" max="14" width="12.5703125" style="1" customWidth="1"/>
     <col min="15" max="15" width="18.5703125" style="64" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="64"/>
+    <col min="16" max="17" width="9.140625" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -5051,8 +5054,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
         <v>834</v>
       </c>
@@ -5089,8 +5095,9 @@
       <c r="P2" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="36">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" ht="36">
       <c r="A3" s="10" t="s">
         <v>839</v>
       </c>
@@ -5129,8 +5136,9 @@
       <c r="P3" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="36">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" ht="36">
       <c r="A4" s="10" t="s">
         <v>844</v>
       </c>
@@ -5173,8 +5181,9 @@
       <c r="P4" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
         <v>849</v>
       </c>
@@ -5215,8 +5224,9 @@
       <c r="P5" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="10" t="s">
         <v>852</v>
       </c>
@@ -5255,8 +5265,9 @@
       <c r="P6" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="48" t="s">
         <v>855</v>
       </c>
@@ -5285,8 +5296,9 @@
       <c r="P7" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="48" t="s">
         <v>857</v>
       </c>
@@ -5313,8 +5325,9 @@
       <c r="P8" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
         <v>858</v>
       </c>
@@ -5353,8 +5366,9 @@
       <c r="P9" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="48" t="s">
         <v>861</v>
       </c>
@@ -5381,8 +5395,9 @@
       <c r="P10" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="48" t="s">
         <v>862</v>
       </c>
@@ -5409,8 +5424,9 @@
       <c r="P11" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="10" t="s">
         <v>1177</v>
       </c>
@@ -5447,8 +5463,9 @@
       <c r="P12" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>863</v>
       </c>
@@ -5487,8 +5504,9 @@
       <c r="P13" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="10" t="s">
         <v>1172</v>
       </c>
@@ -5527,8 +5545,9 @@
       <c r="P14" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="10" t="s">
         <v>870</v>
       </c>
@@ -5567,8 +5586,9 @@
       <c r="P15" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="10" t="s">
         <v>872</v>
       </c>
@@ -5603,8 +5623,9 @@
       <c r="P16" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="10" t="s">
         <v>873</v>
       </c>
@@ -5645,8 +5666,9 @@
       <c r="P17" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="48" t="s">
         <v>876</v>
       </c>
@@ -5675,8 +5697,9 @@
       <c r="P18" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="48" t="s">
         <v>878</v>
       </c>
@@ -5705,8 +5728,9 @@
       <c r="P19" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="10" t="s">
         <v>879</v>
       </c>
@@ -5745,8 +5769,9 @@
       <c r="P20" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="10" t="s">
         <v>883</v>
       </c>
@@ -5785,8 +5810,9 @@
       <c r="P21" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="10" t="s">
         <v>1173</v>
       </c>
@@ -5825,8 +5851,9 @@
       <c r="P22" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="10" t="s">
         <v>884</v>
       </c>
@@ -5865,8 +5892,9 @@
       <c r="P23" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="10" t="s">
         <v>885</v>
       </c>
@@ -5905,8 +5933,9 @@
       <c r="P24" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="10" t="s">
         <v>885</v>
       </c>
@@ -5945,8 +5974,9 @@
       <c r="P25" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="10" t="s">
         <v>887</v>
       </c>
@@ -5985,8 +6015,9 @@
       <c r="P26" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="10" t="s">
         <v>887</v>
       </c>
@@ -6023,8 +6054,9 @@
       <c r="P27" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27" s="14"/>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="10" t="s">
         <v>1174</v>
       </c>
@@ -6061,8 +6093,9 @@
       <c r="P28" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="14"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="10" t="s">
         <v>889</v>
       </c>
@@ -6101,8 +6134,9 @@
       <c r="P29" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="60">
+      <c r="Q29" s="14"/>
+    </row>
+    <row r="30" spans="1:17" ht="60">
       <c r="A30" s="10" t="s">
         <v>890</v>
       </c>
@@ -6143,8 +6177,9 @@
       <c r="P30" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30" s="14"/>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="10" t="s">
         <v>893</v>
       </c>
@@ -6181,8 +6216,9 @@
       <c r="P31" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="10" t="s">
         <v>894</v>
       </c>
@@ -6219,8 +6255,9 @@
       <c r="P32" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="10" t="s">
         <v>896</v>
       </c>
@@ -6259,8 +6296,9 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="48" t="s">
         <v>898</v>
       </c>
@@ -6289,8 +6327,9 @@
       <c r="P34" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="48" t="s">
         <v>899</v>
       </c>
@@ -6319,8 +6358,9 @@
       <c r="P35" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="24">
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17" ht="24">
       <c r="A36" s="10" t="s">
         <v>900</v>
       </c>
@@ -6359,8 +6399,9 @@
       <c r="P36" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1">
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>902</v>
       </c>
@@ -6399,8 +6440,9 @@
       <c r="P37" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="10" t="s">
         <v>903</v>
       </c>
@@ -6435,8 +6477,9 @@
       <c r="P38" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="96">
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17" ht="96">
       <c r="A39" s="10" t="s">
         <v>1175</v>
       </c>
@@ -6477,8 +6520,9 @@
       <c r="P39" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39" s="14"/>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="10" t="s">
         <v>1176</v>
       </c>
@@ -6519,8 +6563,9 @@
       <c r="P40" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" s="10" t="s">
         <v>913</v>
       </c>
@@ -6560,8 +6605,9 @@
       <c r="P41" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" s="48" t="s">
         <v>915</v>
       </c>
@@ -6590,8 +6636,9 @@
       <c r="P42" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="48" t="s">
         <v>916</v>
       </c>
@@ -6620,8 +6667,9 @@
       <c r="P43" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="36">
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17" ht="36">
       <c r="A44" s="10" t="s">
         <v>917</v>
       </c>
@@ -6660,8 +6708,9 @@
       <c r="P44" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="48" t="s">
         <v>921</v>
       </c>
@@ -6694,8 +6743,9 @@
       <c r="P45" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="48" t="s">
         <v>923</v>
       </c>
@@ -6722,8 +6772,9 @@
       <c r="P46" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="10" t="s">
         <v>924</v>
       </c>
@@ -6760,8 +6811,9 @@
       <c r="P47" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="24">
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17" ht="24">
       <c r="A48" s="10" t="s">
         <v>926</v>
       </c>
@@ -6800,8 +6852,9 @@
       <c r="P48" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" s="10" t="s">
         <v>928</v>
       </c>
@@ -6840,8 +6893,9 @@
       <c r="P49" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="24">
+      <c r="Q49" s="14"/>
+    </row>
+    <row r="50" spans="1:17" ht="24">
       <c r="A50" s="10" t="s">
         <v>929</v>
       </c>
@@ -6882,8 +6936,9 @@
       <c r="P50" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="24">
+      <c r="Q50" s="14"/>
+    </row>
+    <row r="51" spans="1:17" ht="24">
       <c r="A51" s="10" t="s">
         <v>932</v>
       </c>
@@ -6925,8 +6980,9 @@
       <c r="P51" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="36">
+      <c r="Q51" s="14"/>
+    </row>
+    <row r="52" spans="1:17" ht="36">
       <c r="A52" s="10" t="s">
         <v>934</v>
       </c>
@@ -6967,8 +7023,9 @@
       <c r="P52" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="108">
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="1:17" ht="108">
       <c r="A53" s="10" t="s">
         <v>1178</v>
       </c>
@@ -7007,8 +7064,9 @@
       <c r="P53" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="14"/>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54" s="48" t="s">
         <v>936</v>
       </c>
@@ -7037,8 +7095,9 @@
       <c r="P54" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="45.75" customHeight="1">
+      <c r="Q54" s="14"/>
+    </row>
+    <row r="55" spans="1:17" ht="45.75" customHeight="1">
       <c r="A55" s="10" t="s">
         <v>937</v>
       </c>
@@ -7080,8 +7139,9 @@
       <c r="P55" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:16">
+      <c r="Q55" s="14"/>
+    </row>
+    <row r="56" spans="1:17">
       <c r="A56" s="48" t="s">
         <v>939</v>
       </c>
@@ -7110,8 +7170,9 @@
       <c r="P56" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56" s="14"/>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57" s="10" t="s">
         <v>940</v>
       </c>
@@ -7150,8 +7211,9 @@
       <c r="P57" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57" s="14"/>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58" s="10" t="s">
         <v>940</v>
       </c>
@@ -7190,8 +7252,9 @@
       <c r="P58" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="14"/>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="10" t="s">
         <v>941</v>
       </c>
@@ -7230,8 +7293,9 @@
       <c r="P59" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="Q59" s="14"/>
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60" s="10" t="s">
         <v>941</v>
       </c>
@@ -7270,8 +7334,9 @@
       <c r="P60" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="24">
+      <c r="Q60" s="14"/>
+    </row>
+    <row r="61" spans="1:17" ht="24">
       <c r="A61" s="10" t="s">
         <v>943</v>
       </c>
@@ -7312,8 +7377,9 @@
       <c r="P61" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="24">
+      <c r="Q61" s="14"/>
+    </row>
+    <row r="62" spans="1:17" ht="24">
       <c r="A62" s="10" t="s">
         <v>943</v>
       </c>
@@ -7354,8 +7420,9 @@
       <c r="P62" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62" s="14"/>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" s="10" t="s">
         <v>945</v>
       </c>
@@ -7394,8 +7461,9 @@
       <c r="P63" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63" s="14"/>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" s="10" t="s">
         <v>945</v>
       </c>
@@ -7432,8 +7500,9 @@
       <c r="P64" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64" s="14"/>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="10" t="s">
         <v>946</v>
       </c>
@@ -7472,8 +7541,9 @@
       <c r="P65" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="Q65" s="14"/>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66" s="10" t="s">
         <v>946</v>
       </c>
@@ -7512,8 +7582,9 @@
       <c r="P66" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="24">
+      <c r="Q66" s="14"/>
+    </row>
+    <row r="67" spans="1:17" ht="24">
       <c r="A67" s="10" t="s">
         <v>947</v>
       </c>
@@ -7554,8 +7625,9 @@
       <c r="P67" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="24">
+      <c r="Q67" s="14"/>
+    </row>
+    <row r="68" spans="1:17" ht="24">
       <c r="A68" s="10" t="s">
         <v>947</v>
       </c>
@@ -7596,8 +7668,9 @@
       <c r="P68" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68" s="14"/>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="10" t="s">
         <v>950</v>
       </c>
@@ -7636,8 +7709,9 @@
       <c r="P69" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="Q69" s="14"/>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" s="10" t="s">
         <v>950</v>
       </c>
@@ -7676,8 +7750,9 @@
       <c r="P70" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="10" t="s">
         <v>951</v>
       </c>
@@ -7712,8 +7787,9 @@
       <c r="P71" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="24">
+      <c r="Q71" s="14"/>
+    </row>
+    <row r="72" spans="1:17" ht="24">
       <c r="A72" s="28" t="s">
         <v>353</v>
       </c>
@@ -7762,8 +7838,11 @@
       <c r="P72" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="25.5" customHeight="1">
+      <c r="Q72" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="25.5" customHeight="1">
       <c r="A73" s="10" t="s">
         <v>954</v>
       </c>
@@ -7806,8 +7885,9 @@
       <c r="P73" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="24">
+      <c r="Q73" s="66"/>
+    </row>
+    <row r="74" spans="1:17" ht="24">
       <c r="A74" s="10" t="s">
         <v>954</v>
       </c>
@@ -7850,8 +7930,9 @@
       <c r="P74" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="24">
+      <c r="Q74" s="66"/>
+    </row>
+    <row r="75" spans="1:17" ht="24">
       <c r="A75" s="10" t="s">
         <v>963</v>
       </c>
@@ -7892,8 +7973,9 @@
       <c r="P75" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75" s="66"/>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" s="10" t="s">
         <v>963</v>
       </c>
@@ -7932,8 +8014,9 @@
       <c r="P76" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="66"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="10" t="s">
         <v>969</v>
       </c>
@@ -7972,8 +8055,9 @@
       <c r="P77" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="30" customHeight="1">
+      <c r="Q77" s="66"/>
+    </row>
+    <row r="78" spans="1:17" ht="30" customHeight="1">
       <c r="A78" s="10" t="s">
         <v>969</v>
       </c>
@@ -8014,8 +8098,9 @@
       <c r="P78" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" ht="24">
+      <c r="Q78" s="66"/>
+    </row>
+    <row r="79" spans="1:17" ht="24">
       <c r="A79" s="10" t="s">
         <v>974</v>
       </c>
@@ -8058,8 +8143,9 @@
       <c r="P79" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" ht="24">
+      <c r="Q79" s="66"/>
+    </row>
+    <row r="80" spans="1:17" ht="24">
       <c r="A80" s="10" t="s">
         <v>974</v>
       </c>
@@ -8102,8 +8188,9 @@
       <c r="P80" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" ht="24">
+      <c r="Q80" s="66"/>
+    </row>
+    <row r="81" spans="1:17" ht="24">
       <c r="A81" s="10" t="s">
         <v>976</v>
       </c>
@@ -8146,8 +8233,9 @@
       <c r="P81" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" ht="24">
+      <c r="Q81" s="66"/>
+    </row>
+    <row r="82" spans="1:17" ht="24">
       <c r="A82" s="10" t="s">
         <v>976</v>
       </c>
@@ -8190,8 +8278,9 @@
       <c r="P82" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82" s="66"/>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83" s="10" t="s">
         <v>977</v>
       </c>
@@ -8232,8 +8321,9 @@
       <c r="P83" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83" s="66"/>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" s="10" t="s">
         <v>977</v>
       </c>
@@ -8274,8 +8364,9 @@
       <c r="P84" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="24">
+      <c r="Q84" s="66"/>
+    </row>
+    <row r="85" spans="1:17" ht="24">
       <c r="A85" s="10" t="s">
         <v>982</v>
       </c>
@@ -8318,8 +8409,9 @@
       <c r="P85" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="24">
+      <c r="Q85" s="66"/>
+    </row>
+    <row r="86" spans="1:17" ht="24">
       <c r="A86" s="10" t="s">
         <v>982</v>
       </c>
@@ -8362,8 +8454,9 @@
       <c r="P86" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="24">
+      <c r="Q86" s="66"/>
+    </row>
+    <row r="87" spans="1:17" ht="24">
       <c r="A87" s="10" t="s">
         <v>988</v>
       </c>
@@ -8406,8 +8499,9 @@
       <c r="P87" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="24">
+      <c r="Q87" s="66"/>
+    </row>
+    <row r="88" spans="1:17" ht="24">
       <c r="A88" s="10" t="s">
         <v>988</v>
       </c>
@@ -8450,8 +8544,9 @@
       <c r="P88" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" ht="24">
+      <c r="Q88" s="66"/>
+    </row>
+    <row r="89" spans="1:17" ht="24">
       <c r="A89" s="10" t="s">
         <v>990</v>
       </c>
@@ -8492,8 +8587,9 @@
       <c r="P89" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" ht="24">
+      <c r="Q89" s="66"/>
+    </row>
+    <row r="90" spans="1:17" ht="24">
       <c r="A90" s="10" t="s">
         <v>990</v>
       </c>
@@ -8534,8 +8630,9 @@
       <c r="P90" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" ht="24">
+      <c r="Q90" s="66"/>
+    </row>
+    <row r="91" spans="1:17" ht="24">
       <c r="A91" s="10" t="s">
         <v>993</v>
       </c>
@@ -8576,8 +8673,9 @@
       <c r="P91" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" ht="24">
+      <c r="Q91" s="66"/>
+    </row>
+    <row r="92" spans="1:17" ht="24">
       <c r="A92" s="10" t="s">
         <v>993</v>
       </c>
@@ -8618,8 +8716,9 @@
       <c r="P92" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" ht="36">
+      <c r="Q92" s="66"/>
+    </row>
+    <row r="93" spans="1:17" ht="36">
       <c r="A93" s="10" t="s">
         <v>994</v>
       </c>
@@ -8658,8 +8757,9 @@
       <c r="P93" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" ht="39" customHeight="1">
+      <c r="Q93" s="66"/>
+    </row>
+    <row r="94" spans="1:17" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
         <v>998</v>
       </c>
@@ -8697,8 +8797,9 @@
       <c r="P94" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" ht="24">
+      <c r="Q94" s="66"/>
+    </row>
+    <row r="95" spans="1:17" ht="24">
       <c r="A95" s="10" t="s">
         <v>1002</v>
       </c>
@@ -8739,8 +8840,9 @@
       <c r="P95" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" ht="24">
+      <c r="Q95" s="66"/>
+    </row>
+    <row r="96" spans="1:17" ht="24">
       <c r="A96" s="10" t="s">
         <v>1002</v>
       </c>
@@ -8781,8 +8883,9 @@
       <c r="P96" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" ht="24">
+      <c r="Q96" s="66"/>
+    </row>
+    <row r="97" spans="1:17" ht="24">
       <c r="A97" s="10" t="s">
         <v>1003</v>
       </c>
@@ -8823,8 +8926,9 @@
       <c r="P97" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" ht="24">
+      <c r="Q97" s="66"/>
+    </row>
+    <row r="98" spans="1:17" ht="24">
       <c r="A98" s="10" t="s">
         <v>1003</v>
       </c>
@@ -8865,8 +8969,9 @@
       <c r="P98" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" ht="36">
+      <c r="Q98" s="66"/>
+    </row>
+    <row r="99" spans="1:17" ht="36">
       <c r="A99" s="10" t="s">
         <v>1004</v>
       </c>
@@ -8905,8 +9010,9 @@
       <c r="P99" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" ht="36.75" customHeight="1">
+      <c r="Q99" s="66"/>
+    </row>
+    <row r="100" spans="1:17" ht="36.75" customHeight="1">
       <c r="A100" s="10" t="s">
         <v>1005</v>
       </c>
@@ -8945,8 +9051,9 @@
       <c r="P100" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:16">
+      <c r="Q100" s="66"/>
+    </row>
+    <row r="101" spans="1:17">
       <c r="A101" s="10" t="s">
         <v>1006</v>
       </c>
@@ -8987,8 +9094,9 @@
       <c r="P101" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="1:16">
+      <c r="Q101" s="66"/>
+    </row>
+    <row r="102" spans="1:17">
       <c r="A102" s="10" t="s">
         <v>1008</v>
       </c>
@@ -9029,8 +9137,9 @@
       <c r="P102" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="103" spans="1:16">
+      <c r="Q102" s="66"/>
+    </row>
+    <row r="103" spans="1:17">
       <c r="A103" s="10" t="s">
         <v>1012</v>
       </c>
@@ -9071,8 +9180,9 @@
       <c r="P103" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="1:16">
+      <c r="Q103" s="66"/>
+    </row>
+    <row r="104" spans="1:17">
       <c r="A104" s="10" t="s">
         <v>1014</v>
       </c>
@@ -9113,8 +9223,9 @@
       <c r="P104" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="Q104" s="66"/>
+    </row>
+    <row r="105" spans="1:17">
       <c r="A105" s="10" t="s">
         <v>1016</v>
       </c>
@@ -9155,8 +9266,9 @@
       <c r="P105" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" ht="14.25" customHeight="1">
+      <c r="Q105" s="66"/>
+    </row>
+    <row r="106" spans="1:17" ht="14.25" customHeight="1">
       <c r="A106" s="10" t="s">
         <v>1017</v>
       </c>
@@ -9197,6 +9309,7 @@
       <c r="P106" s="66">
         <v>4</v>
       </c>
+      <c r="Q106" s="66"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -9206,7 +9319,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -9223,7 +9336,7 @@
     <col min="15" max="15" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -9272,8 +9385,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="67" t="s">
         <v>1019</v>
       </c>
@@ -9310,8 +9426,9 @@
         <v>52</v>
       </c>
       <c r="P2" s="14"/>
-    </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="23.25" customHeight="1">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="23.25" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>1022</v>
       </c>
@@ -9353,8 +9470,9 @@
         <v>52</v>
       </c>
       <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16" s="1" customFormat="1">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" s="1" customFormat="1">
       <c r="A4" s="10" t="s">
         <v>1026</v>
       </c>
@@ -9394,8 +9512,9 @@
         <v>52</v>
       </c>
       <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" ht="24">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="24">
       <c r="A5" s="10" t="s">
         <v>1029</v>
       </c>
@@ -9436,8 +9555,9 @@
       <c r="P5" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" s="1" customFormat="1">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1">
       <c r="A6" s="10" t="s">
         <v>1033</v>
       </c>
@@ -9477,8 +9597,9 @@
         <v>52</v>
       </c>
       <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="67" t="s">
         <v>1035</v>
       </c>
@@ -9515,8 +9636,9 @@
         <v>52</v>
       </c>
       <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="67" t="s">
         <v>1036</v>
       </c>
@@ -9555,8 +9677,9 @@
       <c r="P8" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="120" t="s">
         <v>1168</v>
       </c>
@@ -9593,8 +9716,9 @@
         <v>52</v>
       </c>
       <c r="P9" s="69"/>
-    </row>
-    <row r="10" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
+      <c r="Q9" s="69"/>
+    </row>
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A10" s="28" t="s">
         <v>1039</v>
       </c>
@@ -9643,8 +9767,11 @@
       <c r="P10" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="67" t="s">
         <v>1040</v>
       </c>
@@ -9685,8 +9812,9 @@
       <c r="P11" s="66">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" s="1" customFormat="1">
+      <c r="Q11" s="66"/>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1">
       <c r="A12" s="67" t="s">
         <v>1042</v>
       </c>
@@ -9727,8 +9855,9 @@
       <c r="P12" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" s="1" customFormat="1" ht="26.25" customHeight="1">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="26.25" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>1043</v>
       </c>
@@ -9777,8 +9906,11 @@
       <c r="P13" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q13" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A14" s="30" t="s">
         <v>1044</v>
       </c>
@@ -9824,8 +9956,9 @@
         <v>1048</v>
       </c>
       <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A15" s="30" t="s">
         <v>1049</v>
       </c>
@@ -9867,8 +10000,9 @@
         <v>357</v>
       </c>
       <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A16" s="30" t="s">
         <v>1050</v>
       </c>
@@ -9910,8 +10044,9 @@
         <v>357</v>
       </c>
       <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A17" s="30" t="s">
         <v>1051</v>
       </c>
@@ -9957,8 +10092,9 @@
         <v>1048</v>
       </c>
       <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A18" s="30" t="s">
         <v>1053</v>
       </c>
@@ -10000,8 +10136,9 @@
         <v>357</v>
       </c>
       <c r="P18" s="14"/>
-    </row>
-    <row r="19" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A19" s="30" t="s">
         <v>1054</v>
       </c>
@@ -10043,8 +10180,9 @@
         <v>357</v>
       </c>
       <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A20" s="30" t="s">
         <v>1055</v>
       </c>
@@ -10090,8 +10228,9 @@
         <v>1048</v>
       </c>
       <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A21" s="30" t="s">
         <v>1057</v>
       </c>
@@ -10133,8 +10272,9 @@
         <v>357</v>
       </c>
       <c r="P21" s="14"/>
-    </row>
-    <row r="22" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A22" s="30" t="s">
         <v>1058</v>
       </c>
@@ -10176,8 +10316,9 @@
         <v>357</v>
       </c>
       <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A23" s="30" t="s">
         <v>1059</v>
       </c>
@@ -10223,8 +10364,9 @@
         <v>1048</v>
       </c>
       <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A24" s="30" t="s">
         <v>1060</v>
       </c>
@@ -10266,8 +10408,9 @@
         <v>357</v>
       </c>
       <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A25" s="30" t="s">
         <v>1061</v>
       </c>
@@ -10309,8 +10452,9 @@
         <v>357</v>
       </c>
       <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A26" s="30" t="s">
         <v>1062</v>
       </c>
@@ -10356,8 +10500,9 @@
         <v>1048</v>
       </c>
       <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A27" s="30" t="s">
         <v>1063</v>
       </c>
@@ -10399,8 +10544,9 @@
         <v>357</v>
       </c>
       <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q27" s="14"/>
+    </row>
+    <row r="28" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A28" s="30" t="s">
         <v>1064</v>
       </c>
@@ -10442,8 +10588,9 @@
         <v>357</v>
       </c>
       <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q28" s="14"/>
+    </row>
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A29" s="30" t="s">
         <v>1065</v>
       </c>
@@ -10489,8 +10636,9 @@
         <v>1048</v>
       </c>
       <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q29" s="14"/>
+    </row>
+    <row r="30" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A30" s="30" t="s">
         <v>1066</v>
       </c>
@@ -10532,8 +10680,9 @@
         <v>357</v>
       </c>
       <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q30" s="14"/>
+    </row>
+    <row r="31" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A31" s="30" t="s">
         <v>1067</v>
       </c>
@@ -10575,8 +10724,9 @@
         <v>357</v>
       </c>
       <c r="P31" s="14"/>
-    </row>
-    <row r="32" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A32" s="30" t="s">
         <v>1068</v>
       </c>
@@ -10622,8 +10772,9 @@
         <v>1048</v>
       </c>
       <c r="P32" s="14"/>
-    </row>
-    <row r="33" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A33" s="30" t="s">
         <v>1069</v>
       </c>
@@ -10665,8 +10816,9 @@
         <v>357</v>
       </c>
       <c r="P33" s="14"/>
-    </row>
-    <row r="34" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A34" s="30" t="s">
         <v>1070</v>
       </c>
@@ -10708,8 +10860,9 @@
         <v>357</v>
       </c>
       <c r="P34" s="14"/>
-    </row>
-    <row r="35" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A35" s="30" t="s">
         <v>1071</v>
       </c>
@@ -10757,8 +10910,9 @@
         <v>1048</v>
       </c>
       <c r="P35" s="14"/>
-    </row>
-    <row r="36" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A36" s="30" t="s">
         <v>1072</v>
       </c>
@@ -10800,8 +10954,9 @@
         <v>357</v>
       </c>
       <c r="P36" s="14"/>
-    </row>
-    <row r="37" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A37" s="30" t="s">
         <v>1073</v>
       </c>
@@ -10843,8 +10998,9 @@
         <v>357</v>
       </c>
       <c r="P37" s="14"/>
-    </row>
-    <row r="38" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A38" s="30" t="s">
         <v>1074</v>
       </c>
@@ -10892,8 +11048,9 @@
         <v>1048</v>
       </c>
       <c r="P38" s="14"/>
-    </row>
-    <row r="39" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A39" s="30" t="s">
         <v>1075</v>
       </c>
@@ -10935,8 +11092,9 @@
         <v>357</v>
       </c>
       <c r="P39" s="14"/>
-    </row>
-    <row r="40" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q39" s="14"/>
+    </row>
+    <row r="40" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A40" s="30" t="s">
         <v>1076</v>
       </c>
@@ -10978,8 +11136,9 @@
         <v>357</v>
       </c>
       <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A41" s="30" t="s">
         <v>1077</v>
       </c>
@@ -11025,8 +11184,9 @@
         <v>1048</v>
       </c>
       <c r="P41" s="14"/>
-    </row>
-    <row r="42" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A42" s="30" t="s">
         <v>1078</v>
       </c>
@@ -11068,8 +11228,9 @@
         <v>357</v>
       </c>
       <c r="P42" s="14"/>
-    </row>
-    <row r="43" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A43" s="30" t="s">
         <v>1079</v>
       </c>
@@ -11111,8 +11272,9 @@
         <v>357</v>
       </c>
       <c r="P43" s="14"/>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44" s="30" t="s">
         <v>1080</v>
       </c>
@@ -11147,8 +11309,9 @@
         <v>357</v>
       </c>
       <c r="P44" s="14"/>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="30" t="s">
         <v>1083</v>
       </c>
@@ -11185,8 +11348,9 @@
         <v>357</v>
       </c>
       <c r="P45" s="14"/>
-    </row>
-    <row r="46" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A46" s="30" t="s">
         <v>1086</v>
       </c>
@@ -11232,8 +11396,9 @@
         <v>1048</v>
       </c>
       <c r="P46" s="14"/>
-    </row>
-    <row r="47" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A47" s="30" t="s">
         <v>1087</v>
       </c>
@@ -11275,8 +11440,9 @@
         <v>357</v>
       </c>
       <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A48" s="30" t="s">
         <v>1088</v>
       </c>
@@ -11318,8 +11484,9 @@
         <v>357</v>
       </c>
       <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A49" s="30" t="s">
         <v>1089</v>
       </c>
@@ -11365,8 +11532,9 @@
         <v>1048</v>
       </c>
       <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q49" s="14"/>
+    </row>
+    <row r="50" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A50" s="30" t="s">
         <v>1090</v>
       </c>
@@ -11408,8 +11576,9 @@
         <v>357</v>
       </c>
       <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q50" s="14"/>
+    </row>
+    <row r="51" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A51" s="30" t="s">
         <v>1091</v>
       </c>
@@ -11451,8 +11620,9 @@
         <v>357</v>
       </c>
       <c r="P51" s="14"/>
-    </row>
-    <row r="52" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q51" s="14"/>
+    </row>
+    <row r="52" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A52" s="30" t="s">
         <v>1092</v>
       </c>
@@ -11498,8 +11668,9 @@
         <v>1048</v>
       </c>
       <c r="P52" s="14"/>
-    </row>
-    <row r="53" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A53" s="30" t="s">
         <v>1093</v>
       </c>
@@ -11541,8 +11712,9 @@
         <v>357</v>
       </c>
       <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q53" s="14"/>
+    </row>
+    <row r="54" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A54" s="30" t="s">
         <v>1094</v>
       </c>
@@ -11584,8 +11756,9 @@
         <v>357</v>
       </c>
       <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="1:16" ht="24">
+      <c r="Q54" s="14"/>
+    </row>
+    <row r="55" spans="1:17" ht="24">
       <c r="A55" s="28" t="s">
         <v>1095</v>
       </c>
@@ -11634,8 +11807,11 @@
       <c r="P55" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="24.75">
+      <c r="Q55" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="24.75">
       <c r="A56" s="30" t="s">
         <v>1096</v>
       </c>
@@ -11672,8 +11848,9 @@
         <v>1048</v>
       </c>
       <c r="P56" s="14"/>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56" s="14"/>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57" s="30" t="s">
         <v>1100</v>
       </c>
@@ -11708,8 +11885,9 @@
         <v>1048</v>
       </c>
       <c r="P57" s="14"/>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57" s="14"/>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58" s="30" t="s">
         <v>1101</v>
       </c>
@@ -11748,8 +11926,9 @@
         <v>1048</v>
       </c>
       <c r="P58" s="14"/>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="14"/>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="30" t="s">
         <v>1104</v>
       </c>
@@ -11788,8 +11967,9 @@
         <v>1048</v>
       </c>
       <c r="P59" s="14"/>
-    </row>
-    <row r="60" spans="1:16" ht="24">
+      <c r="Q59" s="14"/>
+    </row>
+    <row r="60" spans="1:17" ht="24">
       <c r="A60" s="30" t="s">
         <v>1105</v>
       </c>
@@ -11824,8 +12004,9 @@
         <v>1048</v>
       </c>
       <c r="P60" s="14"/>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="Q60" s="14"/>
+    </row>
+    <row r="61" spans="1:17">
       <c r="A61" s="30" t="s">
         <v>1108</v>
       </c>
@@ -11862,8 +12043,9 @@
         <v>1048</v>
       </c>
       <c r="P61" s="14"/>
-    </row>
-    <row r="62" spans="1:16" ht="36.75">
+      <c r="Q61" s="14"/>
+    </row>
+    <row r="62" spans="1:17" ht="36.75">
       <c r="A62" s="30" t="s">
         <v>1109</v>
       </c>
@@ -11892,8 +12074,9 @@
         <v>1048</v>
       </c>
       <c r="P62" s="14"/>
-    </row>
-    <row r="63" spans="1:16" ht="72.75">
+      <c r="Q62" s="14"/>
+    </row>
+    <row r="63" spans="1:17" ht="72.75">
       <c r="A63" s="30" t="s">
         <v>1111</v>
       </c>
@@ -11932,8 +12115,9 @@
         <v>1048</v>
       </c>
       <c r="P63" s="14"/>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63" s="14"/>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" s="30" t="s">
         <v>1117</v>
       </c>
@@ -11970,8 +12154,9 @@
         <v>1048</v>
       </c>
       <c r="P64" s="14"/>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64" s="14"/>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="30" t="s">
         <v>1118</v>
       </c>
@@ -12006,8 +12191,9 @@
         <v>1048</v>
       </c>
       <c r="P65" s="14"/>
-    </row>
-    <row r="66" spans="1:16" ht="24.75">
+      <c r="Q65" s="14"/>
+    </row>
+    <row r="66" spans="1:17" ht="24.75">
       <c r="A66" s="30" t="s">
         <v>1120</v>
       </c>
@@ -12046,8 +12232,9 @@
         <v>1048</v>
       </c>
       <c r="P66" s="14"/>
-    </row>
-    <row r="67" spans="1:16" ht="48.75">
+      <c r="Q66" s="14"/>
+    </row>
+    <row r="67" spans="1:17" ht="48.75">
       <c r="A67" s="30" t="s">
         <v>1124</v>
       </c>
@@ -12086,8 +12273,9 @@
         <v>1048</v>
       </c>
       <c r="P67" s="14"/>
-    </row>
-    <row r="68" spans="1:16" ht="24">
+      <c r="Q67" s="14"/>
+    </row>
+    <row r="68" spans="1:17" ht="24">
       <c r="A68" s="30" t="s">
         <v>1129</v>
       </c>
@@ -12116,8 +12304,9 @@
         <v>1048</v>
       </c>
       <c r="P68" s="14"/>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68" s="14"/>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="30" t="s">
         <v>1131</v>
       </c>
@@ -12154,8 +12343,9 @@
         <v>1048</v>
       </c>
       <c r="P69" s="14"/>
-    </row>
-    <row r="70" spans="1:16" ht="24">
+      <c r="Q69" s="14"/>
+    </row>
+    <row r="70" spans="1:17" ht="24">
       <c r="A70" s="30" t="s">
         <v>1134</v>
       </c>
@@ -12190,8 +12380,9 @@
         <v>1048</v>
       </c>
       <c r="P70" s="14"/>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="10" t="s">
         <v>1136</v>
       </c>
@@ -12228,8 +12419,9 @@
         <v>1048</v>
       </c>
       <c r="P71" s="14"/>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71" s="14"/>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" s="30" t="s">
         <v>1137</v>
       </c>
@@ -12266,8 +12458,9 @@
         <v>1048</v>
       </c>
       <c r="P72" s="14"/>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72" s="14"/>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73" s="30" t="s">
         <v>1138</v>
       </c>
@@ -12300,8 +12493,9 @@
         <v>1048</v>
       </c>
       <c r="P73" s="14"/>
-    </row>
-    <row r="74" spans="1:16" ht="36">
+      <c r="Q73" s="14"/>
+    </row>
+    <row r="74" spans="1:17" ht="36">
       <c r="A74" s="30" t="s">
         <v>1140</v>
       </c>
@@ -12338,8 +12532,9 @@
         <v>1048</v>
       </c>
       <c r="P74" s="14"/>
-    </row>
-    <row r="75" spans="1:16" ht="24.75">
+      <c r="Q74" s="14"/>
+    </row>
+    <row r="75" spans="1:17" ht="24.75">
       <c r="A75" s="30" t="s">
         <v>1142</v>
       </c>
@@ -12374,8 +12569,9 @@
         <v>1048</v>
       </c>
       <c r="P75" s="14"/>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75" s="14"/>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" s="30" t="s">
         <v>1143</v>
       </c>
@@ -12410,8 +12606,9 @@
         <v>1048</v>
       </c>
       <c r="P76" s="14"/>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="14"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="30" t="s">
         <v>1145</v>
       </c>
@@ -12448,8 +12645,9 @@
         <v>1048</v>
       </c>
       <c r="P77" s="14"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77" s="14"/>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="30" t="s">
         <v>1146</v>
       </c>
@@ -12486,8 +12684,9 @@
         <v>1048</v>
       </c>
       <c r="P78" s="14"/>
-    </row>
-    <row r="79" spans="1:16" ht="24">
+      <c r="Q78" s="14"/>
+    </row>
+    <row r="79" spans="1:17" ht="24">
       <c r="A79" s="30" t="s">
         <v>1147</v>
       </c>
@@ -12522,8 +12721,9 @@
         <v>1048</v>
       </c>
       <c r="P79" s="14"/>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79" s="14"/>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" s="30" t="s">
         <v>1148</v>
       </c>
@@ -12560,8 +12760,9 @@
         <v>1048</v>
       </c>
       <c r="P80" s="14"/>
-    </row>
-    <row r="81" spans="1:16" ht="36.75">
+      <c r="Q80" s="14"/>
+    </row>
+    <row r="81" spans="1:17" ht="36.75">
       <c r="A81" s="30" t="s">
         <v>1149</v>
       </c>
@@ -12594,8 +12795,9 @@
         <v>1048</v>
       </c>
       <c r="P81" s="14"/>
-    </row>
-    <row r="82" spans="1:16" ht="72.75">
+      <c r="Q81" s="14"/>
+    </row>
+    <row r="82" spans="1:17" ht="72.75">
       <c r="A82" s="30" t="s">
         <v>1151</v>
       </c>
@@ -12634,8 +12836,9 @@
         <v>1048</v>
       </c>
       <c r="P82" s="14"/>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82" s="14"/>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83" s="30" t="s">
         <v>1152</v>
       </c>
@@ -12672,8 +12875,9 @@
         <v>1048</v>
       </c>
       <c r="P83" s="14"/>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83" s="14"/>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" s="30" t="s">
         <v>1153</v>
       </c>
@@ -12708,8 +12912,9 @@
         <v>1048</v>
       </c>
       <c r="P84" s="14"/>
-    </row>
-    <row r="85" spans="1:16" ht="24.75">
+      <c r="Q84" s="14"/>
+    </row>
+    <row r="85" spans="1:17" ht="24.75">
       <c r="A85" s="30" t="s">
         <v>1154</v>
       </c>
@@ -12748,8 +12953,9 @@
         <v>1048</v>
       </c>
       <c r="P85" s="14"/>
-    </row>
-    <row r="86" spans="1:16" ht="48.75">
+      <c r="Q85" s="14"/>
+    </row>
+    <row r="86" spans="1:17" ht="48.75">
       <c r="A86" s="30" t="s">
         <v>1155</v>
       </c>
@@ -12788,8 +12994,9 @@
         <v>1048</v>
       </c>
       <c r="P86" s="14"/>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86" s="14"/>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" s="30" t="s">
         <v>1156</v>
       </c>
@@ -12820,8 +13027,9 @@
         <v>1048</v>
       </c>
       <c r="P87" s="14"/>
-    </row>
-    <row r="88" spans="1:16">
+      <c r="Q87" s="14"/>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88" s="30" t="s">
         <v>1157</v>
       </c>
@@ -12858,8 +13066,9 @@
         <v>1048</v>
       </c>
       <c r="P88" s="14"/>
-    </row>
-    <row r="89" spans="1:16" ht="24">
+      <c r="Q88" s="14"/>
+    </row>
+    <row r="89" spans="1:17" ht="24">
       <c r="A89" s="30" t="s">
         <v>1158</v>
       </c>
@@ -12894,8 +13103,9 @@
         <v>1048</v>
       </c>
       <c r="P89" s="14"/>
-    </row>
-    <row r="90" spans="1:16">
+      <c r="Q89" s="14"/>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90" s="10" t="s">
         <v>1159</v>
       </c>
@@ -12932,8 +13142,9 @@
         <v>1048</v>
       </c>
       <c r="P90" s="14"/>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90" s="14"/>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91" s="30" t="s">
         <v>1160</v>
       </c>
@@ -12970,8 +13181,9 @@
         <v>1048</v>
       </c>
       <c r="P91" s="14"/>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91" s="14"/>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92" s="30" t="s">
         <v>1161</v>
       </c>
@@ -13004,8 +13216,9 @@
         <v>1048</v>
       </c>
       <c r="P92" s="14"/>
-    </row>
-    <row r="93" spans="1:16" ht="36">
+      <c r="Q92" s="14"/>
+    </row>
+    <row r="93" spans="1:17" ht="36">
       <c r="A93" s="30" t="s">
         <v>1162</v>
       </c>
@@ -13042,6 +13255,7 @@
         <v>1048</v>
       </c>
       <c r="P93" s="14"/>
+      <c r="Q93" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -13067,10 +13281,12 @@
     <col min="13" max="13" width="28.85546875" style="2" customWidth="1"/>
     <col min="14" max="14" width="30.42578125" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.28515625" style="1" customWidth="1"/>
-    <col min="16" max="1022" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="15" style="1" customWidth="1"/>
+    <col min="18" max="1022" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1">
+    <row r="1" spans="1:17" ht="26.25" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -13119,8 +13335,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
@@ -13157,8 +13376,9 @@
       <c r="P2" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="10" t="s">
         <v>53</v>
       </c>
@@ -13195,8 +13415,9 @@
         <v>52</v>
       </c>
       <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16" ht="24">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" ht="24">
       <c r="A4" s="10" t="s">
         <v>58</v>
       </c>
@@ -13233,8 +13454,9 @@
       <c r="P4" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
         <v>62</v>
       </c>
@@ -13269,8 +13491,9 @@
         <v>52</v>
       </c>
       <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" ht="24">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" ht="24">
       <c r="A6" s="10" t="s">
         <v>65</v>
       </c>
@@ -13311,8 +13534,9 @@
       <c r="P6" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="10" t="s">
         <v>72</v>
       </c>
@@ -13347,8 +13571,9 @@
       <c r="P7" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="10" t="s">
         <v>74</v>
       </c>
@@ -13381,8 +13606,9 @@
       <c r="P8" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="24">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17" ht="24">
       <c r="A9" s="10" t="s">
         <v>76</v>
       </c>
@@ -13421,8 +13647,9 @@
       <c r="P9" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A10" s="10" t="s">
         <v>81</v>
       </c>
@@ -13461,8 +13688,9 @@
       <c r="P10" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="24">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" ht="24">
       <c r="A11" s="10" t="s">
         <v>85</v>
       </c>
@@ -13499,8 +13727,9 @@
       <c r="P11" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17" ht="27.75" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>88</v>
       </c>
@@ -13537,8 +13766,9 @@
       <c r="P12" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="27.75" customHeight="1">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" ht="27.75" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>92</v>
       </c>
@@ -13582,8 +13812,9 @@
         <v>52</v>
       </c>
       <c r="P13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" ht="24">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17" ht="24">
       <c r="A14" s="10" t="s">
         <v>1169</v>
       </c>
@@ -13620,8 +13851,9 @@
       <c r="P14" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="48" t="s">
         <v>1171</v>
       </c>
@@ -13640,8 +13872,9 @@
       <c r="N15" s="5"/>
       <c r="O15" s="14"/>
       <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" ht="24">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" ht="24">
       <c r="A16" s="10" t="s">
         <v>97</v>
       </c>
@@ -13678,8 +13911,9 @@
       <c r="P16" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="24">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17" ht="24">
       <c r="A17" s="10" t="s">
         <v>98</v>
       </c>
@@ -13719,8 +13953,9 @@
         <v>52</v>
       </c>
       <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="10" t="s">
         <v>102</v>
       </c>
@@ -13757,8 +13992,9 @@
       <c r="P18" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="10" t="s">
         <v>106</v>
       </c>
@@ -13795,8 +14031,9 @@
       <c r="P19" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="10" t="s">
         <v>109</v>
       </c>
@@ -13833,8 +14070,9 @@
         <v>52</v>
       </c>
       <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="10" t="s">
         <v>114</v>
       </c>
@@ -13869,8 +14107,9 @@
       <c r="P21" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="10" t="s">
         <v>117</v>
       </c>
@@ -13905,8 +14144,9 @@
       <c r="P22" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="10" t="s">
         <v>118</v>
       </c>
@@ -13945,8 +14185,9 @@
         <v>52</v>
       </c>
       <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" ht="24">
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" ht="24">
       <c r="A24" s="28" t="s">
         <v>123</v>
       </c>
@@ -13995,8 +14236,11 @@
       <c r="P24" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="56.25">
+      <c r="Q24" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="56.25">
       <c r="A25" s="30" t="s">
         <v>127</v>
       </c>
@@ -14035,8 +14279,9 @@
       <c r="P25" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="22.5">
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.5">
       <c r="A26" s="30" t="s">
         <v>133</v>
       </c>
@@ -14077,8 +14322,9 @@
       <c r="P26" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="10" t="s">
         <v>136</v>
       </c>
@@ -14119,8 +14365,9 @@
       <c r="P27" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27" s="14"/>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="10" t="s">
         <v>141</v>
       </c>
@@ -14161,8 +14408,9 @@
       <c r="P28" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="36">
+      <c r="Q28" s="14"/>
+    </row>
+    <row r="29" spans="1:17" ht="36">
       <c r="A29" s="10" t="s">
         <v>145</v>
       </c>
@@ -14203,8 +14451,9 @@
       <c r="P29" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="24">
+      <c r="Q29" s="14"/>
+    </row>
+    <row r="30" spans="1:17" ht="24">
       <c r="A30" s="10" t="s">
         <v>151</v>
       </c>
@@ -14243,8 +14492,9 @@
       <c r="P30" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="60">
+      <c r="Q30" s="14"/>
+    </row>
+    <row r="31" spans="1:17" ht="60">
       <c r="A31" s="10" t="s">
         <v>154</v>
       </c>
@@ -14281,8 +14531,9 @@
       <c r="P31" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="10" t="s">
         <v>158</v>
       </c>
@@ -14321,8 +14572,9 @@
       <c r="P32" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="10" t="s">
         <v>160</v>
       </c>
@@ -14361,8 +14613,9 @@
       <c r="P33" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="36.75">
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17" ht="36.75">
       <c r="A34" s="10" t="s">
         <v>164</v>
       </c>
@@ -14410,8 +14663,9 @@
       <c r="P34" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="10" t="s">
         <v>170</v>
       </c>
@@ -14450,8 +14704,9 @@
       <c r="P35" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="24">
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17" ht="24">
       <c r="A36" s="10" t="s">
         <v>172</v>
       </c>
@@ -14492,8 +14747,9 @@
       <c r="P36" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="10" t="s">
         <v>177</v>
       </c>
@@ -14530,8 +14786,9 @@
       <c r="P37" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="24">
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17" ht="24">
       <c r="A38" s="10" t="s">
         <v>180</v>
       </c>
@@ -14572,8 +14829,9 @@
       <c r="P38" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="24">
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17" ht="24">
       <c r="A39" s="10" t="s">
         <v>185</v>
       </c>
@@ -14614,8 +14872,9 @@
       <c r="P39" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39" s="14"/>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="10" t="s">
         <v>189</v>
       </c>
@@ -14654,8 +14913,9 @@
         <v>132</v>
       </c>
       <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="1:16" ht="36">
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17" ht="36">
       <c r="A41" s="10" t="s">
         <v>192</v>
       </c>
@@ -14698,8 +14958,9 @@
       <c r="P41" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="24">
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17" ht="24">
       <c r="A42" s="28" t="s">
         <v>198</v>
       </c>
@@ -14748,8 +15009,11 @@
       <c r="P42" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="10" t="s">
         <v>199</v>
       </c>
@@ -14786,8 +15050,9 @@
         <v>52</v>
       </c>
       <c r="P43" s="14"/>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44" s="10" t="s">
         <v>202</v>
       </c>
@@ -14824,8 +15089,9 @@
         <v>52</v>
       </c>
       <c r="P44" s="14"/>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="10" t="s">
         <v>204</v>
       </c>
@@ -14862,8 +15128,9 @@
         <v>52</v>
       </c>
       <c r="P45" s="14"/>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="10" t="s">
         <v>205</v>
       </c>
@@ -14900,8 +15167,9 @@
         <v>52</v>
       </c>
       <c r="P46" s="14"/>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="10" t="s">
         <v>207</v>
       </c>
@@ -14938,8 +15206,9 @@
         <v>52</v>
       </c>
       <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="10" t="s">
         <v>209</v>
       </c>
@@ -14976,8 +15245,9 @@
         <v>52</v>
       </c>
       <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" s="10" t="s">
         <v>210</v>
       </c>
@@ -15014,8 +15284,9 @@
         <v>52</v>
       </c>
       <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49" s="14"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50" s="10" t="s">
         <v>211</v>
       </c>
@@ -15052,8 +15323,9 @@
         <v>52</v>
       </c>
       <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="1:16" ht="24">
+      <c r="Q50" s="14"/>
+    </row>
+    <row r="51" spans="1:17" ht="24">
       <c r="A51" s="3" t="s">
         <v>212</v>
       </c>
@@ -15102,8 +15374,11 @@
       <c r="P51" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="24">
+      <c r="Q51" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="24">
       <c r="A52" s="40" t="s">
         <v>58</v>
       </c>
@@ -15147,8 +15422,9 @@
         <v>1185</v>
       </c>
       <c r="P52" s="14"/>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="1:17">
       <c r="A53" s="40" t="s">
         <v>215</v>
       </c>
@@ -15187,8 +15463,9 @@
         <v>1185</v>
       </c>
       <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="14"/>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54" s="40" t="s">
         <v>218</v>
       </c>
@@ -15227,8 +15504,9 @@
         <v>1185</v>
       </c>
       <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54" s="14"/>
+    </row>
+    <row r="55" spans="1:17">
       <c r="A55" s="40" t="s">
         <v>219</v>
       </c>
@@ -15267,8 +15545,9 @@
         <v>1185</v>
       </c>
       <c r="P55" s="14"/>
-    </row>
-    <row r="56" spans="1:16" ht="24">
+      <c r="Q55" s="14"/>
+    </row>
+    <row r="56" spans="1:17" ht="24">
       <c r="A56" s="40" t="s">
         <v>85</v>
       </c>
@@ -15305,8 +15584,9 @@
         <v>1185</v>
       </c>
       <c r="P56" s="14"/>
-    </row>
-    <row r="57" spans="1:16" ht="24">
+      <c r="Q56" s="14"/>
+    </row>
+    <row r="57" spans="1:17" ht="24">
       <c r="A57" s="3" t="s">
         <v>220</v>
       </c>
@@ -15351,8 +15631,11 @@
       <c r="P57" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58" s="40" t="s">
         <v>76</v>
       </c>
@@ -15389,8 +15672,9 @@
         <v>1186</v>
       </c>
       <c r="P58" s="14"/>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="14"/>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="40" t="s">
         <v>222</v>
       </c>
@@ -15431,8 +15715,9 @@
         <v>1186</v>
       </c>
       <c r="P59" s="14"/>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="Q59" s="14"/>
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60" s="40" t="s">
         <v>223</v>
       </c>
@@ -15469,8 +15754,9 @@
         <v>1186</v>
       </c>
       <c r="P60" s="14"/>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="Q60" s="14"/>
+    </row>
+    <row r="61" spans="1:17">
       <c r="A61" s="40" t="s">
         <v>228</v>
       </c>
@@ -15505,8 +15791,9 @@
         <v>1186</v>
       </c>
       <c r="P61" s="14"/>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="Q61" s="14"/>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62" s="40" t="s">
         <v>231</v>
       </c>
@@ -15543,8 +15830,9 @@
         <v>1186</v>
       </c>
       <c r="P62" s="14"/>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62" s="14"/>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" s="40" t="s">
         <v>234</v>
       </c>
@@ -15581,8 +15869,9 @@
         <v>1186</v>
       </c>
       <c r="P63" s="14"/>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63" s="14"/>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" s="40" t="s">
         <v>98</v>
       </c>
@@ -15620,8 +15909,9 @@
         <v>1186</v>
       </c>
       <c r="P64" s="14"/>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64" s="14"/>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="40" t="s">
         <v>118</v>
       </c>
@@ -15659,8 +15949,9 @@
         <v>1186</v>
       </c>
       <c r="P65" s="14"/>
-    </row>
-    <row r="66" spans="1:16" ht="24">
+      <c r="Q65" s="14"/>
+    </row>
+    <row r="66" spans="1:17" ht="24">
       <c r="A66" s="3" t="s">
         <v>238</v>
       </c>
@@ -15709,8 +16000,11 @@
       <c r="P66" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" s="40" t="s">
         <v>239</v>
       </c>
@@ -15747,8 +16041,9 @@
         <v>1187</v>
       </c>
       <c r="P67" s="14"/>
-    </row>
-    <row r="68" spans="1:16">
+      <c r="Q67" s="14"/>
+    </row>
+    <row r="68" spans="1:17">
       <c r="A68" s="40" t="s">
         <v>241</v>
       </c>
@@ -15777,8 +16072,9 @@
         <v>1187</v>
       </c>
       <c r="P68" s="14"/>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68" s="14"/>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="40" t="s">
         <v>242</v>
       </c>
@@ -15807,8 +16103,9 @@
         <v>1187</v>
       </c>
       <c r="P69" s="14"/>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="Q69" s="14"/>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" s="40" t="s">
         <v>243</v>
       </c>
@@ -15837,8 +16134,9 @@
         <v>1187</v>
       </c>
       <c r="P70" s="14"/>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="40" t="s">
         <v>244</v>
       </c>
@@ -15877,8 +16175,9 @@
         <v>1187</v>
       </c>
       <c r="P71" s="14"/>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71" s="14"/>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" s="40" t="s">
         <v>245</v>
       </c>
@@ -15915,8 +16214,9 @@
         <v>1187</v>
       </c>
       <c r="P72" s="14"/>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72" s="14"/>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73" s="40" t="s">
         <v>246</v>
       </c>
@@ -15945,8 +16245,9 @@
         <v>1187</v>
       </c>
       <c r="P73" s="14"/>
-    </row>
-    <row r="74" spans="1:16">
+      <c r="Q73" s="14"/>
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74" s="40" t="s">
         <v>247</v>
       </c>
@@ -15982,8 +16283,9 @@
         <v>1187</v>
       </c>
       <c r="P74" s="14"/>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="Q74" s="14"/>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75" s="40" t="s">
         <v>249</v>
       </c>
@@ -16020,8 +16322,9 @@
         <v>1187</v>
       </c>
       <c r="P75" s="14"/>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75" s="14"/>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" s="40" t="s">
         <v>250</v>
       </c>
@@ -16056,8 +16359,9 @@
         <v>1187</v>
       </c>
       <c r="P76" s="14"/>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="14"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="40" t="s">
         <v>252</v>
       </c>
@@ -16086,8 +16390,9 @@
         <v>1187</v>
       </c>
       <c r="P77" s="14"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77" s="14"/>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="40" t="s">
         <v>253</v>
       </c>
@@ -16124,8 +16429,9 @@
         <v>1187</v>
       </c>
       <c r="P78" s="14"/>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78" s="14"/>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79" s="40" t="s">
         <v>255</v>
       </c>
@@ -16154,8 +16460,9 @@
         <v>1187</v>
       </c>
       <c r="P79" s="14"/>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79" s="14"/>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" s="40" t="s">
         <v>256</v>
       </c>
@@ -16192,6 +16499,7 @@
         <v>1187</v>
       </c>
       <c r="P80" s="14"/>
+      <c r="Q80" s="14"/>
     </row>
     <row r="81" spans="15:15">
       <c r="O81" s="45"/>
@@ -16235,11 +16543,11 @@
     <col min="13" max="13" width="27.5703125" style="2" customWidth="1"/>
     <col min="14" max="14" width="13.7109375" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" style="1" customWidth="1"/>
-    <col min="17" max="1022" width="9.140625" style="1"/>
+    <col min="16" max="17" width="10.5703125" style="1" customWidth="1"/>
+    <col min="18" max="1022" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -16288,8 +16596,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="24">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="24">
       <c r="A2" s="48" t="s">
         <v>257</v>
       </c>
@@ -16316,8 +16627,9 @@
       <c r="P2" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="36.75" customHeight="1">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" ht="36.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
@@ -16357,8 +16669,9 @@
         <v>52</v>
       </c>
       <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16" ht="36.75" customHeight="1">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" ht="36.75" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
@@ -16400,8 +16713,9 @@
       <c r="P4" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="45.75" customHeight="1">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" ht="45.75" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
@@ -16439,8 +16753,9 @@
         <v>52</v>
       </c>
       <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" ht="60">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" ht="60">
       <c r="A6" s="48" t="s">
         <v>265</v>
       </c>
@@ -16479,8 +16794,9 @@
       <c r="P6" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="10" t="s">
         <v>269</v>
       </c>
@@ -16518,8 +16834,9 @@
       <c r="P7" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="10" t="s">
         <v>271</v>
       </c>
@@ -16556,8 +16873,9 @@
       <c r="P8" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
         <v>274</v>
       </c>
@@ -16592,8 +16910,9 @@
       <c r="P9" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="45.75" customHeight="1">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" ht="45.75" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>277</v>
       </c>
@@ -16634,8 +16953,9 @@
       <c r="P10" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="45.75" customHeight="1">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" ht="45.75" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>280</v>
       </c>
@@ -16672,8 +16992,9 @@
       <c r="P11" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="45.75" customHeight="1">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17" ht="45.75" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>283</v>
       </c>
@@ -16712,8 +17033,9 @@
       <c r="P12" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="27.75" customHeight="1">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" ht="27.75" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>286</v>
       </c>
@@ -16750,8 +17072,9 @@
       <c r="P13" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="74.25" customHeight="1">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17" ht="74.25" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>288</v>
       </c>
@@ -16787,8 +17110,9 @@
       <c r="P14" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="48" t="s">
         <v>292</v>
       </c>
@@ -16811,8 +17135,9 @@
       <c r="N15" s="5"/>
       <c r="O15" s="14"/>
       <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" ht="65.25" customHeight="1">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" ht="65.25" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>294</v>
       </c>
@@ -16851,8 +17176,9 @@
       <c r="P16" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="10" t="s">
         <v>298</v>
       </c>
@@ -16891,8 +17217,9 @@
       <c r="P17" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="40.5" customHeight="1">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17" ht="40.5" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>302</v>
       </c>
@@ -16933,8 +17260,9 @@
       <c r="P18" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="48" t="s">
         <v>304</v>
       </c>
@@ -16959,8 +17287,9 @@
         <v>52</v>
       </c>
       <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="48" t="s">
         <v>306</v>
       </c>
@@ -16987,8 +17316,9 @@
       <c r="P20" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="60">
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17" ht="60">
       <c r="A21" s="10" t="s">
         <v>307</v>
       </c>
@@ -17029,8 +17359,9 @@
       <c r="P21" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" s="1" customFormat="1" ht="24">
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17" s="1" customFormat="1" ht="24">
       <c r="A22" s="10" t="s">
         <v>308</v>
       </c>
@@ -17067,8 +17398,9 @@
         <v>52</v>
       </c>
       <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" s="1" customFormat="1" ht="12">
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A23" s="10" t="s">
         <v>311</v>
       </c>
@@ -17103,8 +17435,9 @@
       <c r="P23" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="24">
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" ht="24">
       <c r="A24" s="48" t="s">
         <v>314</v>
       </c>
@@ -17129,8 +17462,9 @@
         <v>52</v>
       </c>
       <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" ht="41.25" customHeight="1">
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17" ht="41.25" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
@@ -17171,8 +17505,9 @@
       <c r="P25" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="24">
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17" ht="24">
       <c r="A26" s="10" t="s">
         <v>317</v>
       </c>
@@ -17211,8 +17546,9 @@
         <v>52</v>
       </c>
       <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="10" t="s">
         <v>321</v>
       </c>
@@ -17247,8 +17583,9 @@
         <v>52</v>
       </c>
       <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27" s="14"/>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="48" t="s">
         <v>323</v>
       </c>
@@ -17273,8 +17610,9 @@
         <v>52</v>
       </c>
       <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="14"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="48" t="s">
         <v>325</v>
       </c>
@@ -17299,8 +17637,9 @@
         <v>52</v>
       </c>
       <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29" s="14"/>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="10" t="s">
         <v>326</v>
       </c>
@@ -17339,8 +17678,9 @@
         <v>52</v>
       </c>
       <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16" ht="24">
+      <c r="Q30" s="14"/>
+    </row>
+    <row r="31" spans="1:17" ht="24">
       <c r="A31" s="10" t="s">
         <v>328</v>
       </c>
@@ -17379,8 +17719,9 @@
       <c r="P31" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" s="1" customFormat="1" ht="36">
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17" s="1" customFormat="1" ht="36">
       <c r="A32" s="10" t="s">
         <v>331</v>
       </c>
@@ -17420,8 +17761,9 @@
       <c r="P32" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="24">
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17" ht="24">
       <c r="A33" s="10" t="s">
         <v>335</v>
       </c>
@@ -17460,8 +17802,9 @@
         <v>52</v>
       </c>
       <c r="P33" s="14"/>
-    </row>
-    <row r="34" spans="1:16" ht="24" customHeight="1">
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17" ht="24" customHeight="1">
       <c r="A34" s="10" t="s">
         <v>340</v>
       </c>
@@ -17502,8 +17845,9 @@
       <c r="P34" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="44.25" customHeight="1">
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17" ht="44.25" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>343</v>
       </c>
@@ -17544,8 +17888,9 @@
       <c r="P35" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="44.25" customHeight="1">
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17" ht="44.25" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>345</v>
       </c>
@@ -17586,8 +17931,9 @@
       <c r="P36" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="44.25" customHeight="1">
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17" ht="44.25" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>349</v>
       </c>
@@ -17624,8 +17970,9 @@
       <c r="P37" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="44.25" customHeight="1">
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17" ht="44.25" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>350</v>
       </c>
@@ -17662,8 +18009,9 @@
         <v>52</v>
       </c>
       <c r="P38" s="14"/>
-    </row>
-    <row r="39" spans="1:16" ht="24">
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17" ht="24">
       <c r="A39" s="28" t="s">
         <v>353</v>
       </c>
@@ -17712,8 +18060,11 @@
       <c r="P39" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="24.75">
+      <c r="Q39" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="24.75">
       <c r="A40" s="10" t="s">
         <v>354</v>
       </c>
@@ -17755,8 +18106,9 @@
         <v>357</v>
       </c>
       <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="1:16" ht="36.75">
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17" ht="36.75">
       <c r="A41" s="10" t="s">
         <v>358</v>
       </c>
@@ -17798,8 +18150,9 @@
         <v>357</v>
       </c>
       <c r="P41" s="14"/>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" s="10" t="s">
         <v>360</v>
       </c>
@@ -17839,8 +18192,9 @@
         <v>357</v>
       </c>
       <c r="P42" s="14"/>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="10" t="s">
         <v>361</v>
       </c>
@@ -17880,8 +18234,9 @@
         <v>357</v>
       </c>
       <c r="P43" s="14"/>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44" s="10" t="s">
         <v>362</v>
       </c>
@@ -17920,8 +18275,9 @@
       <c r="P44" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="10" t="s">
         <v>364</v>
       </c>
@@ -17963,8 +18319,9 @@
         <v>357</v>
       </c>
       <c r="P45" s="14"/>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="10" t="s">
         <v>366</v>
       </c>
@@ -18004,8 +18361,9 @@
         <v>357</v>
       </c>
       <c r="P46" s="14"/>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="10" t="s">
         <v>367</v>
       </c>
@@ -18045,8 +18403,9 @@
         <v>357</v>
       </c>
       <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="10" t="s">
         <v>368</v>
       </c>
@@ -18086,8 +18445,9 @@
         <v>357</v>
       </c>
       <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" s="10" t="s">
         <v>369</v>
       </c>
@@ -18127,8 +18487,9 @@
         <v>357</v>
       </c>
       <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49" s="14"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50" s="10" t="s">
         <v>370</v>
       </c>
@@ -18168,8 +18529,9 @@
         <v>357</v>
       </c>
       <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="1:16" ht="24.75">
+      <c r="Q50" s="14"/>
+    </row>
+    <row r="51" spans="1:17" ht="24.75">
       <c r="A51" s="10" t="s">
         <v>371</v>
       </c>
@@ -18211,8 +18573,9 @@
         <v>357</v>
       </c>
       <c r="P51" s="14"/>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="Q51" s="14"/>
+    </row>
+    <row r="52" spans="1:17">
       <c r="A52" s="10" t="s">
         <v>373</v>
       </c>
@@ -18252,8 +18615,9 @@
         <v>357</v>
       </c>
       <c r="P52" s="14"/>
-    </row>
-    <row r="53" spans="1:16" ht="36.75">
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="1:17" ht="36.75">
       <c r="A53" s="10" t="s">
         <v>374</v>
       </c>
@@ -18295,8 +18659,9 @@
         <v>357</v>
       </c>
       <c r="P53" s="14"/>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="14"/>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54" s="10" t="s">
         <v>376</v>
       </c>
@@ -18336,8 +18701,9 @@
         <v>357</v>
       </c>
       <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54" s="14"/>
+    </row>
+    <row r="55" spans="1:17">
       <c r="A55" s="10" t="s">
         <v>378</v>
       </c>
@@ -18374,8 +18740,9 @@
       <c r="P55" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="1:16">
+      <c r="Q55" s="14"/>
+    </row>
+    <row r="56" spans="1:17">
       <c r="A56" s="10" t="s">
         <v>378</v>
       </c>
@@ -18412,8 +18779,9 @@
       <c r="P56" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56" s="14"/>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57" s="10" t="s">
         <v>384</v>
       </c>
@@ -18450,8 +18818,9 @@
       <c r="P57" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="48.75">
+      <c r="Q57" s="14"/>
+    </row>
+    <row r="58" spans="1:17" ht="48.75">
       <c r="A58" s="10" t="s">
         <v>384</v>
       </c>
@@ -18492,8 +18861,9 @@
       <c r="P58" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="14"/>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="10" t="s">
         <v>385</v>
       </c>
@@ -18532,8 +18902,9 @@
         <v>357</v>
       </c>
       <c r="P59" s="14"/>
-    </row>
-    <row r="60" spans="1:16" ht="24.75">
+      <c r="Q59" s="14"/>
+    </row>
+    <row r="60" spans="1:17" ht="24.75">
       <c r="A60" s="10" t="s">
         <v>386</v>
       </c>
@@ -18571,8 +18942,9 @@
         <v>357</v>
       </c>
       <c r="P60" s="14"/>
-    </row>
-    <row r="61" spans="1:16" ht="24.75">
+      <c r="Q60" s="14"/>
+    </row>
+    <row r="61" spans="1:17" ht="24.75">
       <c r="A61" s="10" t="s">
         <v>388</v>
       </c>
@@ -18610,8 +18982,9 @@
         <v>357</v>
       </c>
       <c r="P61" s="14"/>
-    </row>
-    <row r="62" spans="1:16" ht="36.75">
+      <c r="Q61" s="14"/>
+    </row>
+    <row r="62" spans="1:17" ht="36.75">
       <c r="A62" s="10" t="s">
         <v>390</v>
       </c>
@@ -18653,8 +19026,9 @@
         <v>357</v>
       </c>
       <c r="P62" s="14"/>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62" s="14"/>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" s="10" t="s">
         <v>391</v>
       </c>
@@ -18694,8 +19068,9 @@
         <v>357</v>
       </c>
       <c r="P63" s="14"/>
-    </row>
-    <row r="64" spans="1:16" ht="24.75">
+      <c r="Q63" s="14"/>
+    </row>
+    <row r="64" spans="1:17" ht="24.75">
       <c r="A64" s="10" t="s">
         <v>394</v>
       </c>
@@ -18739,8 +19114,9 @@
       <c r="P64" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64" s="14"/>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="10" t="s">
         <v>396</v>
       </c>
@@ -18780,8 +19156,9 @@
         <v>357</v>
       </c>
       <c r="P65" s="14"/>
-    </row>
-    <row r="66" spans="1:16" ht="24.75">
+      <c r="Q65" s="14"/>
+    </row>
+    <row r="66" spans="1:17" ht="24.75">
       <c r="A66" s="10" t="s">
         <v>397</v>
       </c>
@@ -18825,8 +19202,9 @@
       <c r="P66" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66" s="14"/>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" s="10" t="s">
         <v>398</v>
       </c>
@@ -18866,8 +19244,9 @@
         <v>357</v>
       </c>
       <c r="P67" s="14"/>
-    </row>
-    <row r="68" spans="1:16" ht="24.75">
+      <c r="Q67" s="14"/>
+    </row>
+    <row r="68" spans="1:17" ht="24.75">
       <c r="A68" s="10" t="s">
         <v>399</v>
       </c>
@@ -18911,8 +19290,9 @@
       <c r="P68" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68" s="14"/>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="10" t="s">
         <v>400</v>
       </c>
@@ -18952,8 +19332,9 @@
         <v>357</v>
       </c>
       <c r="P69" s="14"/>
-    </row>
-    <row r="70" spans="1:16" ht="24.75">
+      <c r="Q69" s="14"/>
+    </row>
+    <row r="70" spans="1:17" ht="24.75">
       <c r="A70" s="10" t="s">
         <v>401</v>
       </c>
@@ -18995,8 +19376,9 @@
         <v>357</v>
       </c>
       <c r="P70" s="14"/>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="10" t="s">
         <v>403</v>
       </c>
@@ -19040,8 +19422,9 @@
         <v>357</v>
       </c>
       <c r="P71" s="14"/>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71" s="14"/>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" s="10" t="s">
         <v>406</v>
       </c>
@@ -19083,8 +19466,9 @@
         <v>357</v>
       </c>
       <c r="P72" s="14"/>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72" s="14"/>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73" s="10" t="s">
         <v>408</v>
       </c>
@@ -19124,8 +19508,9 @@
         <v>357</v>
       </c>
       <c r="P73" s="14"/>
-    </row>
-    <row r="74" spans="1:16">
+      <c r="Q73" s="14"/>
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74" s="10" t="s">
         <v>409</v>
       </c>
@@ -19167,8 +19552,9 @@
         <v>357</v>
       </c>
       <c r="P74" s="14"/>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="Q74" s="14"/>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75" s="10" t="s">
         <v>411</v>
       </c>
@@ -19208,8 +19594,9 @@
         <v>357</v>
       </c>
       <c r="P75" s="14"/>
-    </row>
-    <row r="76" spans="1:16" ht="24.75">
+      <c r="Q75" s="14"/>
+    </row>
+    <row r="76" spans="1:17" ht="24.75">
       <c r="A76" s="10" t="s">
         <v>412</v>
       </c>
@@ -19251,8 +19638,9 @@
         <v>357</v>
       </c>
       <c r="P76" s="14"/>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="14"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="10" t="s">
         <v>413</v>
       </c>
@@ -19292,8 +19680,9 @@
         <v>357</v>
       </c>
       <c r="P77" s="14"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77" s="14"/>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="10" t="s">
         <v>414</v>
       </c>
@@ -19330,8 +19719,9 @@
         <v>357</v>
       </c>
       <c r="P78" s="14"/>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78" s="14"/>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79" s="10" t="s">
         <v>414</v>
       </c>
@@ -19368,8 +19758,9 @@
         <v>357</v>
       </c>
       <c r="P79" s="14"/>
-    </row>
-    <row r="80" spans="1:16" ht="24.75">
+      <c r="Q79" s="14"/>
+    </row>
+    <row r="80" spans="1:17" ht="24.75">
       <c r="A80" s="10" t="s">
         <v>415</v>
       </c>
@@ -19411,8 +19802,9 @@
         <v>357</v>
       </c>
       <c r="P80" s="14"/>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="Q80" s="14"/>
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81" s="10" t="s">
         <v>416</v>
       </c>
@@ -19452,8 +19844,9 @@
         <v>357</v>
       </c>
       <c r="P81" s="14"/>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="Q81" s="14"/>
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82" s="10" t="s">
         <v>417</v>
       </c>
@@ -19494,8 +19887,9 @@
       <c r="P82" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" ht="24.75">
+      <c r="Q82" s="14"/>
+    </row>
+    <row r="83" spans="1:17" ht="24.75">
       <c r="A83" s="10" t="s">
         <v>419</v>
       </c>
@@ -19537,8 +19931,9 @@
         <v>357</v>
       </c>
       <c r="P83" s="14"/>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83" s="14"/>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" s="10" t="s">
         <v>420</v>
       </c>
@@ -19578,8 +19973,9 @@
         <v>357</v>
       </c>
       <c r="P84" s="14"/>
-    </row>
-    <row r="85" spans="1:16" ht="36.75">
+      <c r="Q84" s="14"/>
+    </row>
+    <row r="85" spans="1:17" ht="36.75">
       <c r="A85" s="10" t="s">
         <v>421</v>
       </c>
@@ -19620,8 +20016,9 @@
       <c r="P85" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="36.75">
+      <c r="Q85" s="14"/>
+    </row>
+    <row r="86" spans="1:17" ht="36.75">
       <c r="A86" s="10" t="s">
         <v>423</v>
       </c>
@@ -19663,8 +20060,9 @@
         <v>357</v>
       </c>
       <c r="P86" s="14"/>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86" s="14"/>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" s="10" t="s">
         <v>424</v>
       </c>
@@ -19704,8 +20102,9 @@
         <v>357</v>
       </c>
       <c r="P87" s="14"/>
-    </row>
-    <row r="88" spans="1:16" ht="60.75">
+      <c r="Q87" s="14"/>
+    </row>
+    <row r="88" spans="1:17" ht="60.75">
       <c r="A88" s="10" t="s">
         <v>426</v>
       </c>
@@ -19742,8 +20141,9 @@
         <v>357</v>
       </c>
       <c r="P88" s="14"/>
-    </row>
-    <row r="89" spans="1:16" ht="24">
+      <c r="Q88" s="14"/>
+    </row>
+    <row r="89" spans="1:17" ht="24">
       <c r="A89" s="10" t="s">
         <v>426</v>
       </c>
@@ -19778,8 +20178,9 @@
         <v>357</v>
       </c>
       <c r="P89" s="14"/>
-    </row>
-    <row r="90" spans="1:16" ht="36.75">
+      <c r="Q89" s="14"/>
+    </row>
+    <row r="90" spans="1:17" ht="36.75">
       <c r="A90" s="10" t="s">
         <v>431</v>
       </c>
@@ -19816,8 +20217,9 @@
         <v>357</v>
       </c>
       <c r="P90" s="14"/>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90" s="14"/>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91" s="10" t="s">
         <v>431</v>
       </c>
@@ -19852,8 +20254,9 @@
         <v>357</v>
       </c>
       <c r="P91" s="14"/>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91" s="14"/>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92" s="10" t="s">
         <v>432</v>
       </c>
@@ -19888,8 +20291,9 @@
         <v>357</v>
       </c>
       <c r="P92" s="14"/>
-    </row>
-    <row r="93" spans="1:16" ht="24.75">
+      <c r="Q92" s="14"/>
+    </row>
+    <row r="93" spans="1:17" ht="24.75">
       <c r="A93" s="10" t="s">
         <v>433</v>
       </c>
@@ -19927,8 +20331,9 @@
         <v>357</v>
       </c>
       <c r="P93" s="14"/>
-    </row>
-    <row r="94" spans="1:16" ht="24.75">
+      <c r="Q93" s="14"/>
+    </row>
+    <row r="94" spans="1:17" ht="24.75">
       <c r="A94" s="10" t="s">
         <v>434</v>
       </c>
@@ -19966,8 +20371,9 @@
         <v>357</v>
       </c>
       <c r="P94" s="14"/>
-    </row>
-    <row r="95" spans="1:16" ht="36.75">
+      <c r="Q94" s="14"/>
+    </row>
+    <row r="95" spans="1:17" ht="36.75">
       <c r="A95" s="10" t="s">
         <v>435</v>
       </c>
@@ -20009,8 +20415,9 @@
         <v>357</v>
       </c>
       <c r="P95" s="14"/>
-    </row>
-    <row r="96" spans="1:16">
+      <c r="Q95" s="14"/>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96" s="10" t="s">
         <v>436</v>
       </c>
@@ -20050,8 +20457,9 @@
         <v>357</v>
       </c>
       <c r="P96" s="14"/>
-    </row>
-    <row r="97" spans="1:16" ht="24.75">
+      <c r="Q96" s="14"/>
+    </row>
+    <row r="97" spans="1:17" ht="24.75">
       <c r="A97" s="10" t="s">
         <v>437</v>
       </c>
@@ -20095,8 +20503,9 @@
       <c r="P97" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:16">
+      <c r="Q97" s="14"/>
+    </row>
+    <row r="98" spans="1:17">
       <c r="A98" s="10" t="s">
         <v>438</v>
       </c>
@@ -20136,8 +20545,9 @@
         <v>357</v>
       </c>
       <c r="P98" s="14"/>
-    </row>
-    <row r="99" spans="1:16" ht="24.75">
+      <c r="Q98" s="14"/>
+    </row>
+    <row r="99" spans="1:17" ht="24.75">
       <c r="A99" s="10" t="s">
         <v>439</v>
       </c>
@@ -20181,8 +20591,9 @@
       <c r="P99" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:16">
+      <c r="Q99" s="14"/>
+    </row>
+    <row r="100" spans="1:17">
       <c r="A100" s="10" t="s">
         <v>440</v>
       </c>
@@ -20222,8 +20633,9 @@
         <v>357</v>
       </c>
       <c r="P100" s="14"/>
-    </row>
-    <row r="101" spans="1:16" ht="24.75">
+      <c r="Q100" s="14"/>
+    </row>
+    <row r="101" spans="1:17" ht="24.75">
       <c r="A101" s="10" t="s">
         <v>441</v>
       </c>
@@ -20267,8 +20679,9 @@
       <c r="P101" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:16">
+      <c r="Q101" s="14"/>
+    </row>
+    <row r="102" spans="1:17">
       <c r="A102" s="10" t="s">
         <v>442</v>
       </c>
@@ -20308,8 +20721,9 @@
         <v>357</v>
       </c>
       <c r="P102" s="14"/>
-    </row>
-    <row r="103" spans="1:16" ht="24.75">
+      <c r="Q102" s="14"/>
+    </row>
+    <row r="103" spans="1:17" ht="24.75">
       <c r="A103" s="10" t="s">
         <v>443</v>
       </c>
@@ -20351,8 +20765,9 @@
         <v>357</v>
       </c>
       <c r="P103" s="14"/>
-    </row>
-    <row r="104" spans="1:16">
+      <c r="Q103" s="14"/>
+    </row>
+    <row r="104" spans="1:17">
       <c r="A104" s="10" t="s">
         <v>444</v>
       </c>
@@ -20392,8 +20807,9 @@
         <v>357</v>
       </c>
       <c r="P104" s="14"/>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="Q104" s="14"/>
+    </row>
+    <row r="105" spans="1:17">
       <c r="A105" s="10" t="s">
         <v>445</v>
       </c>
@@ -20433,8 +20849,9 @@
         <v>357</v>
       </c>
       <c r="P105" s="14"/>
-    </row>
-    <row r="106" spans="1:16">
+      <c r="Q105" s="14"/>
+    </row>
+    <row r="106" spans="1:17">
       <c r="A106" s="10" t="s">
         <v>446</v>
       </c>
@@ -20474,8 +20891,9 @@
         <v>357</v>
       </c>
       <c r="P106" s="14"/>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="Q106" s="14"/>
+    </row>
+    <row r="107" spans="1:17">
       <c r="A107" s="10" t="s">
         <v>447</v>
       </c>
@@ -20515,8 +20933,9 @@
         <v>357</v>
       </c>
       <c r="P107" s="14"/>
-    </row>
-    <row r="108" spans="1:16">
+      <c r="Q107" s="14"/>
+    </row>
+    <row r="108" spans="1:17">
       <c r="A108" s="10" t="s">
         <v>448</v>
       </c>
@@ -20558,8 +20977,9 @@
         <v>357</v>
       </c>
       <c r="P108" s="14"/>
-    </row>
-    <row r="109" spans="1:16">
+      <c r="Q108" s="14"/>
+    </row>
+    <row r="109" spans="1:17">
       <c r="A109" s="10" t="s">
         <v>450</v>
       </c>
@@ -20599,8 +21019,9 @@
         <v>357</v>
       </c>
       <c r="P109" s="14"/>
-    </row>
-    <row r="110" spans="1:16">
+      <c r="Q109" s="14"/>
+    </row>
+    <row r="110" spans="1:17">
       <c r="A110" s="10" t="s">
         <v>451</v>
       </c>
@@ -20640,8 +21061,9 @@
         <v>357</v>
       </c>
       <c r="P110" s="14"/>
-    </row>
-    <row r="111" spans="1:16" ht="24.75">
+      <c r="Q110" s="14"/>
+    </row>
+    <row r="111" spans="1:17" ht="24.75">
       <c r="A111" s="10" t="s">
         <v>452</v>
       </c>
@@ -20683,8 +21105,9 @@
         <v>357</v>
       </c>
       <c r="P111" s="14"/>
-    </row>
-    <row r="112" spans="1:16">
+      <c r="Q111" s="14"/>
+    </row>
+    <row r="112" spans="1:17">
       <c r="A112" s="10" t="s">
         <v>453</v>
       </c>
@@ -20724,6 +21147,7 @@
         <v>357</v>
       </c>
       <c r="P112" s="14"/>
+      <c r="Q112" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -20733,7 +21157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:O159"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
@@ -20749,7 +21173,7 @@
     <col min="13" max="13" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24">
+    <row r="1" spans="1:15" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -20792,8 +21216,11 @@
       <c r="N1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="24">
+      <c r="O1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="24">
       <c r="A2" s="48" t="s">
         <v>257</v>
       </c>
@@ -20820,8 +21247,9 @@
       <c r="N2" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="24">
+      <c r="O2" s="14"/>
+    </row>
+    <row r="3" spans="1:15" ht="24">
       <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
@@ -20858,8 +21286,9 @@
         <v>52</v>
       </c>
       <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="36">
+      <c r="O3" s="14"/>
+    </row>
+    <row r="4" spans="1:15" ht="36">
       <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
@@ -20898,8 +21327,9 @@
       <c r="N4" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="14"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
@@ -20934,8 +21364,9 @@
         <v>52</v>
       </c>
       <c r="N5" s="14"/>
-    </row>
-    <row r="6" spans="1:14" ht="48">
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" spans="1:15" ht="48">
       <c r="A6" s="48" t="s">
         <v>265</v>
       </c>
@@ -20974,8 +21405,9 @@
       <c r="N6" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="14"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="10" t="s">
         <v>269</v>
       </c>
@@ -21010,8 +21442,9 @@
       <c r="N7" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="14"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="10" t="s">
         <v>271</v>
       </c>
@@ -21046,8 +21479,9 @@
       <c r="N8" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" s="14"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="10" t="s">
         <v>277</v>
       </c>
@@ -21086,8 +21520,9 @@
       <c r="N9" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" s="14"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="10" t="s">
         <v>280</v>
       </c>
@@ -21122,8 +21557,9 @@
       <c r="N10" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="24.75">
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="1:15" ht="24.75">
       <c r="A11" s="10" t="s">
         <v>283</v>
       </c>
@@ -21160,8 +21596,9 @@
       <c r="N11" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="10" t="s">
         <v>286</v>
       </c>
@@ -21196,8 +21633,9 @@
       <c r="N12" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="10" t="s">
         <v>288</v>
       </c>
@@ -21233,8 +21671,9 @@
       <c r="N13" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" s="14"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="48" t="s">
         <v>292</v>
       </c>
@@ -21259,8 +21698,9 @@
         <v>52</v>
       </c>
       <c r="N14" s="14"/>
-    </row>
-    <row r="15" spans="1:14" ht="24">
+      <c r="O14" s="14"/>
+    </row>
+    <row r="15" spans="1:15" ht="24">
       <c r="A15" s="10" t="s">
         <v>294</v>
       </c>
@@ -21297,8 +21737,9 @@
       <c r="N15" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" s="14"/>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="10" t="s">
         <v>298</v>
       </c>
@@ -21335,8 +21776,9 @@
       <c r="N16" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" s="14"/>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="10" t="s">
         <v>302</v>
       </c>
@@ -21375,8 +21817,9 @@
       <c r="N17" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" s="14"/>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="48" t="s">
         <v>304</v>
       </c>
@@ -21401,8 +21844,9 @@
         <v>52</v>
       </c>
       <c r="N18" s="14"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="14"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="48" t="s">
         <v>306</v>
       </c>
@@ -21429,8 +21873,9 @@
       <c r="N19" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="48">
+      <c r="O19" s="14"/>
+    </row>
+    <row r="20" spans="1:15" ht="48">
       <c r="A20" s="10" t="s">
         <v>307</v>
       </c>
@@ -21469,8 +21914,9 @@
       <c r="N20" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" s="14"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="10" t="s">
         <v>308</v>
       </c>
@@ -21505,8 +21951,9 @@
         <v>52</v>
       </c>
       <c r="N21" s="14"/>
-    </row>
-    <row r="22" spans="1:14" ht="24">
+      <c r="O21" s="14"/>
+    </row>
+    <row r="22" spans="1:15" ht="24">
       <c r="A22" s="48" t="s">
         <v>314</v>
       </c>
@@ -21531,8 +21978,9 @@
         <v>52</v>
       </c>
       <c r="N22" s="14"/>
-    </row>
-    <row r="23" spans="1:14" ht="36">
+      <c r="O22" s="14"/>
+    </row>
+    <row r="23" spans="1:15" ht="36">
       <c r="A23" s="10" t="s">
         <v>315</v>
       </c>
@@ -21571,8 +22019,9 @@
       <c r="N23" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="24">
+      <c r="O23" s="14"/>
+    </row>
+    <row r="24" spans="1:15" ht="24">
       <c r="A24" s="10" t="s">
         <v>317</v>
       </c>
@@ -21609,8 +22058,9 @@
         <v>52</v>
       </c>
       <c r="N24" s="14"/>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="10" t="s">
         <v>321</v>
       </c>
@@ -21643,8 +22093,9 @@
         <v>52</v>
       </c>
       <c r="N25" s="14"/>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" s="14"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="48" t="s">
         <v>323</v>
       </c>
@@ -21669,8 +22120,9 @@
         <v>52</v>
       </c>
       <c r="N26" s="14"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" s="14"/>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="48" t="s">
         <v>325</v>
       </c>
@@ -21695,8 +22147,9 @@
         <v>52</v>
       </c>
       <c r="N27" s="14"/>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" s="14"/>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="10" t="s">
         <v>326</v>
       </c>
@@ -21733,8 +22186,9 @@
         <v>52</v>
       </c>
       <c r="N28" s="14"/>
-    </row>
-    <row r="29" spans="1:14" ht="24">
+      <c r="O28" s="14"/>
+    </row>
+    <row r="29" spans="1:15" ht="24">
       <c r="A29" s="10" t="s">
         <v>328</v>
       </c>
@@ -21771,8 +22225,9 @@
       <c r="N29" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="36">
+      <c r="O29" s="14"/>
+    </row>
+    <row r="30" spans="1:15" ht="36">
       <c r="A30" s="10" t="s">
         <v>331</v>
       </c>
@@ -21811,8 +22266,9 @@
       <c r="N30" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="36">
+      <c r="O30" s="14"/>
+    </row>
+    <row r="31" spans="1:15" ht="36">
       <c r="A31" s="10" t="s">
         <v>335</v>
       </c>
@@ -21851,8 +22307,9 @@
         <v>52</v>
       </c>
       <c r="N31" s="14"/>
-    </row>
-    <row r="32" spans="1:14" ht="24">
+      <c r="O31" s="14"/>
+    </row>
+    <row r="32" spans="1:15" ht="24">
       <c r="A32" s="10" t="s">
         <v>340</v>
       </c>
@@ -21891,8 +22348,9 @@
       <c r="N32" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" s="14"/>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="10" t="s">
         <v>343</v>
       </c>
@@ -21931,8 +22389,9 @@
       <c r="N33" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="36.75">
+      <c r="O33" s="14"/>
+    </row>
+    <row r="34" spans="1:15" ht="36.75">
       <c r="A34" s="10" t="s">
         <v>345</v>
       </c>
@@ -21971,8 +22430,9 @@
       <c r="N34" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" s="14"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="10" t="s">
         <v>349</v>
       </c>
@@ -22007,8 +22467,9 @@
       <c r="N35" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="24">
+      <c r="O35" s="14"/>
+    </row>
+    <row r="36" spans="1:15" ht="24">
       <c r="A36" s="28" t="s">
         <v>353</v>
       </c>
@@ -22051,8 +22512,11 @@
       <c r="N36" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="24.75">
+      <c r="O36" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="24.75">
       <c r="A37" s="10" t="s">
         <v>354</v>
       </c>
@@ -22087,8 +22551,9 @@
         <v>357</v>
       </c>
       <c r="N37" s="14"/>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" s="14"/>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="10" t="s">
         <v>358</v>
       </c>
@@ -22121,8 +22586,9 @@
         <v>357</v>
       </c>
       <c r="N38" s="14"/>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" s="14"/>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="10" t="s">
         <v>458</v>
       </c>
@@ -22157,8 +22623,9 @@
         <v>357</v>
       </c>
       <c r="N39" s="14"/>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" s="14"/>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="10" t="s">
         <v>459</v>
       </c>
@@ -22191,8 +22658,9 @@
         <v>357</v>
       </c>
       <c r="N40" s="14"/>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" s="14"/>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="10" t="s">
         <v>364</v>
       </c>
@@ -22225,8 +22693,9 @@
         <v>357</v>
       </c>
       <c r="N41" s="14"/>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" s="14"/>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="10" t="s">
         <v>366</v>
       </c>
@@ -22259,8 +22728,9 @@
         <v>357</v>
       </c>
       <c r="N42" s="14"/>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" s="14"/>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="10" t="s">
         <v>367</v>
       </c>
@@ -22293,8 +22763,9 @@
         <v>357</v>
       </c>
       <c r="N43" s="14"/>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" s="14"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="10" t="s">
         <v>368</v>
       </c>
@@ -22327,8 +22798,9 @@
         <v>357</v>
       </c>
       <c r="N44" s="14"/>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" s="14"/>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="10" t="s">
         <v>461</v>
       </c>
@@ -22363,8 +22835,9 @@
         <v>357</v>
       </c>
       <c r="N45" s="14"/>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" s="14"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="10" t="s">
         <v>463</v>
       </c>
@@ -22397,8 +22870,9 @@
         <v>357</v>
       </c>
       <c r="N46" s="14"/>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" s="14"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="10" t="s">
         <v>464</v>
       </c>
@@ -22431,8 +22905,9 @@
         <v>357</v>
       </c>
       <c r="N47" s="14"/>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" s="14"/>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="10" t="s">
         <v>465</v>
       </c>
@@ -22465,8 +22940,9 @@
         <v>357</v>
       </c>
       <c r="N48" s="14"/>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" s="14"/>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="10" t="s">
         <v>466</v>
       </c>
@@ -22503,8 +22979,9 @@
       <c r="N49" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" s="14"/>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="10" t="s">
         <v>369</v>
       </c>
@@ -22537,8 +23014,9 @@
         <v>357</v>
       </c>
       <c r="N50" s="14"/>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" s="14"/>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="10" t="s">
         <v>370</v>
       </c>
@@ -22571,8 +23049,9 @@
         <v>357</v>
       </c>
       <c r="N51" s="14"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" s="14"/>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="10" t="s">
         <v>371</v>
       </c>
@@ -22605,8 +23084,9 @@
         <v>357</v>
       </c>
       <c r="N52" s="14"/>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" s="14"/>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="10" t="s">
         <v>373</v>
       </c>
@@ -22639,8 +23119,9 @@
         <v>357</v>
       </c>
       <c r="N53" s="14"/>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" s="14"/>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="10" t="s">
         <v>374</v>
       </c>
@@ -22673,8 +23154,9 @@
         <v>357</v>
       </c>
       <c r="N54" s="14"/>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" s="14"/>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="10" t="s">
         <v>376</v>
       </c>
@@ -22709,8 +23191,9 @@
         <v>357</v>
       </c>
       <c r="N55" s="14"/>
-    </row>
-    <row r="56" spans="1:14" ht="24.75">
+      <c r="O55" s="14"/>
+    </row>
+    <row r="56" spans="1:15" ht="24.75">
       <c r="A56" s="10" t="s">
         <v>468</v>
       </c>
@@ -22745,8 +23228,9 @@
         <v>357</v>
       </c>
       <c r="N56" s="14"/>
-    </row>
-    <row r="57" spans="1:14" ht="24.75">
+      <c r="O56" s="14"/>
+    </row>
+    <row r="57" spans="1:15" ht="24.75">
       <c r="A57" s="10" t="s">
         <v>470</v>
       </c>
@@ -22781,8 +23265,9 @@
         <v>357</v>
       </c>
       <c r="N57" s="14"/>
-    </row>
-    <row r="58" spans="1:14" ht="24.75">
+      <c r="O57" s="14"/>
+    </row>
+    <row r="58" spans="1:15" ht="24.75">
       <c r="A58" s="10" t="s">
         <v>471</v>
       </c>
@@ -22817,8 +23302,9 @@
         <v>357</v>
       </c>
       <c r="N58" s="14"/>
-    </row>
-    <row r="59" spans="1:14" ht="24.75">
+      <c r="O58" s="14"/>
+    </row>
+    <row r="59" spans="1:15" ht="24.75">
       <c r="A59" s="10" t="s">
         <v>472</v>
       </c>
@@ -22853,8 +23339,9 @@
         <v>357</v>
       </c>
       <c r="N59" s="14"/>
-    </row>
-    <row r="60" spans="1:14" ht="24.75">
+      <c r="O59" s="14"/>
+    </row>
+    <row r="60" spans="1:15" ht="24.75">
       <c r="A60" s="10" t="s">
         <v>473</v>
       </c>
@@ -22889,8 +23376,9 @@
         <v>357</v>
       </c>
       <c r="N60" s="14"/>
-    </row>
-    <row r="61" spans="1:14" ht="24.75">
+      <c r="O60" s="14"/>
+    </row>
+    <row r="61" spans="1:15" ht="24.75">
       <c r="A61" s="10" t="s">
         <v>474</v>
       </c>
@@ -22925,8 +23413,9 @@
         <v>357</v>
       </c>
       <c r="N61" s="14"/>
-    </row>
-    <row r="62" spans="1:14" ht="24.75">
+      <c r="O61" s="14"/>
+    </row>
+    <row r="62" spans="1:15" ht="24.75">
       <c r="A62" s="10" t="s">
         <v>475</v>
       </c>
@@ -22961,8 +23450,9 @@
         <v>357</v>
       </c>
       <c r="N62" s="14"/>
-    </row>
-    <row r="63" spans="1:14" ht="24.75">
+      <c r="O62" s="14"/>
+    </row>
+    <row r="63" spans="1:15" ht="24.75">
       <c r="A63" s="10" t="s">
         <v>476</v>
       </c>
@@ -22997,8 +23487,9 @@
         <v>357</v>
       </c>
       <c r="N63" s="14"/>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63" s="14"/>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="10" t="s">
         <v>378</v>
       </c>
@@ -23033,8 +23524,9 @@
       <c r="N64" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64" s="14"/>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="10" t="s">
         <v>378</v>
       </c>
@@ -23069,8 +23561,9 @@
       <c r="N65" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65" s="14"/>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="10" t="s">
         <v>384</v>
       </c>
@@ -23105,8 +23598,9 @@
       <c r="N66" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="36.75">
+      <c r="O66" s="14"/>
+    </row>
+    <row r="67" spans="1:15" ht="36.75">
       <c r="A67" s="10" t="s">
         <v>384</v>
       </c>
@@ -23145,8 +23639,9 @@
       <c r="N67" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67" s="14"/>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="10" t="s">
         <v>385</v>
       </c>
@@ -23179,8 +23674,9 @@
         <v>357</v>
       </c>
       <c r="N68" s="14"/>
-    </row>
-    <row r="69" spans="1:14" ht="36">
+      <c r="O68" s="14"/>
+    </row>
+    <row r="69" spans="1:15" ht="36">
       <c r="A69" s="10" t="s">
         <v>386</v>
       </c>
@@ -23215,8 +23711,9 @@
         <v>357</v>
       </c>
       <c r="N69" s="14"/>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69" s="14"/>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="10" t="s">
         <v>388</v>
       </c>
@@ -23251,8 +23748,9 @@
         <v>357</v>
       </c>
       <c r="N70" s="14"/>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" s="14"/>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="10" t="s">
         <v>390</v>
       </c>
@@ -23287,8 +23785,9 @@
         <v>357</v>
       </c>
       <c r="N71" s="14"/>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71" s="14"/>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="10" t="s">
         <v>391</v>
       </c>
@@ -23323,8 +23822,9 @@
         <v>357</v>
       </c>
       <c r="N72" s="14"/>
-    </row>
-    <row r="73" spans="1:14" ht="24.75">
+      <c r="O72" s="14"/>
+    </row>
+    <row r="73" spans="1:15" ht="24.75">
       <c r="A73" s="10" t="s">
         <v>484</v>
       </c>
@@ -23359,8 +23859,9 @@
         <v>357</v>
       </c>
       <c r="N73" s="14"/>
-    </row>
-    <row r="74" spans="1:14" ht="24.75">
+      <c r="O73" s="14"/>
+    </row>
+    <row r="74" spans="1:15" ht="24.75">
       <c r="A74" s="10" t="s">
         <v>485</v>
       </c>
@@ -23395,8 +23896,9 @@
         <v>357</v>
       </c>
       <c r="N74" s="14"/>
-    </row>
-    <row r="75" spans="1:14" ht="24.75">
+      <c r="O74" s="14"/>
+    </row>
+    <row r="75" spans="1:15" ht="24.75">
       <c r="A75" s="10" t="s">
         <v>486</v>
       </c>
@@ -23431,8 +23933,9 @@
         <v>357</v>
       </c>
       <c r="N75" s="14"/>
-    </row>
-    <row r="76" spans="1:14" ht="24.75">
+      <c r="O75" s="14"/>
+    </row>
+    <row r="76" spans="1:15" ht="24.75">
       <c r="A76" s="10" t="s">
         <v>487</v>
       </c>
@@ -23467,8 +23970,9 @@
         <v>357</v>
       </c>
       <c r="N76" s="14"/>
-    </row>
-    <row r="77" spans="1:14" ht="24.75">
+      <c r="O76" s="14"/>
+    </row>
+    <row r="77" spans="1:15" ht="24.75">
       <c r="A77" s="10" t="s">
         <v>488</v>
       </c>
@@ -23503,8 +24007,9 @@
         <v>357</v>
       </c>
       <c r="N77" s="14"/>
-    </row>
-    <row r="78" spans="1:14" ht="24.75">
+      <c r="O77" s="14"/>
+    </row>
+    <row r="78" spans="1:15" ht="24.75">
       <c r="A78" s="10" t="s">
         <v>489</v>
       </c>
@@ -23539,8 +24044,9 @@
         <v>357</v>
       </c>
       <c r="N78" s="14"/>
-    </row>
-    <row r="79" spans="1:14" ht="24.75">
+      <c r="O78" s="14"/>
+    </row>
+    <row r="79" spans="1:15" ht="24.75">
       <c r="A79" s="10" t="s">
         <v>490</v>
       </c>
@@ -23575,8 +24081,9 @@
         <v>357</v>
       </c>
       <c r="N79" s="14"/>
-    </row>
-    <row r="80" spans="1:14" ht="24.75">
+      <c r="O79" s="14"/>
+    </row>
+    <row r="80" spans="1:15" ht="24.75">
       <c r="A80" s="10" t="s">
         <v>491</v>
       </c>
@@ -23611,8 +24118,9 @@
         <v>357</v>
       </c>
       <c r="N80" s="14"/>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80" s="14"/>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" s="10" t="s">
         <v>394</v>
       </c>
@@ -23649,8 +24157,9 @@
       <c r="N81" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="O81" s="14"/>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" s="10" t="s">
         <v>396</v>
       </c>
@@ -23683,8 +24192,9 @@
         <v>357</v>
       </c>
       <c r="N82" s="14"/>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82" s="14"/>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" s="10" t="s">
         <v>397</v>
       </c>
@@ -23721,8 +24231,9 @@
       <c r="N83" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83" s="14"/>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="10" t="s">
         <v>398</v>
       </c>
@@ -23755,8 +24266,9 @@
         <v>357</v>
       </c>
       <c r="N84" s="14"/>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="O84" s="14"/>
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="10" t="s">
         <v>399</v>
       </c>
@@ -23793,8 +24305,9 @@
       <c r="N85" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85" s="14"/>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86" s="10" t="s">
         <v>400</v>
       </c>
@@ -23827,8 +24340,9 @@
         <v>357</v>
       </c>
       <c r="N86" s="14"/>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86" s="14"/>
+    </row>
+    <row r="87" spans="1:15">
       <c r="A87" s="10" t="s">
         <v>401</v>
       </c>
@@ -23861,8 +24375,9 @@
         <v>357</v>
       </c>
       <c r="N87" s="14"/>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87" s="14"/>
+    </row>
+    <row r="88" spans="1:15">
       <c r="A88" s="10" t="s">
         <v>403</v>
       </c>
@@ -23899,8 +24414,9 @@
         <v>357</v>
       </c>
       <c r="N88" s="14"/>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88" s="14"/>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89" s="10" t="s">
         <v>406</v>
       </c>
@@ -23935,8 +24451,9 @@
         <v>357</v>
       </c>
       <c r="N89" s="14"/>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89" s="14"/>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90" s="10" t="s">
         <v>408</v>
       </c>
@@ -23969,8 +24486,9 @@
         <v>357</v>
       </c>
       <c r="N90" s="14"/>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90" s="14"/>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91" s="10" t="s">
         <v>409</v>
       </c>
@@ -24005,8 +24523,9 @@
         <v>357</v>
       </c>
       <c r="N91" s="14"/>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91" s="14"/>
+    </row>
+    <row r="92" spans="1:15">
       <c r="A92" s="10" t="s">
         <v>411</v>
       </c>
@@ -24039,8 +24558,9 @@
         <v>357</v>
       </c>
       <c r="N92" s="14"/>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92" s="14"/>
+    </row>
+    <row r="93" spans="1:15">
       <c r="A93" s="10" t="s">
         <v>412</v>
       </c>
@@ -24075,8 +24595,9 @@
         <v>357</v>
       </c>
       <c r="N93" s="14"/>
-    </row>
-    <row r="94" spans="1:14">
+      <c r="O93" s="14"/>
+    </row>
+    <row r="94" spans="1:15">
       <c r="A94" s="10" t="s">
         <v>413</v>
       </c>
@@ -24109,8 +24630,9 @@
         <v>357</v>
       </c>
       <c r="N94" s="14"/>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94" s="14"/>
+    </row>
+    <row r="95" spans="1:15">
       <c r="A95" s="10" t="s">
         <v>414</v>
       </c>
@@ -24145,8 +24667,9 @@
         <v>357</v>
       </c>
       <c r="N95" s="14"/>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95" s="14"/>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" s="10" t="s">
         <v>414</v>
       </c>
@@ -24181,8 +24704,9 @@
         <v>357</v>
       </c>
       <c r="N96" s="14"/>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96" s="14"/>
+    </row>
+    <row r="97" spans="1:15">
       <c r="A97" s="10" t="s">
         <v>415</v>
       </c>
@@ -24217,8 +24741,9 @@
         <v>357</v>
       </c>
       <c r="N97" s="14"/>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97" s="14"/>
+    </row>
+    <row r="98" spans="1:15">
       <c r="A98" s="10" t="s">
         <v>416</v>
       </c>
@@ -24251,8 +24776,9 @@
         <v>357</v>
       </c>
       <c r="N98" s="14"/>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98" s="14"/>
+    </row>
+    <row r="99" spans="1:15">
       <c r="A99" s="10" t="s">
         <v>417</v>
       </c>
@@ -24291,8 +24817,9 @@
       <c r="N99" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99" s="14"/>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" s="10" t="s">
         <v>419</v>
       </c>
@@ -24327,8 +24854,9 @@
         <v>357</v>
       </c>
       <c r="N100" s="14"/>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100" s="14"/>
+    </row>
+    <row r="101" spans="1:15">
       <c r="A101" s="10" t="s">
         <v>420</v>
       </c>
@@ -24361,8 +24889,9 @@
         <v>357</v>
       </c>
       <c r="N101" s="14"/>
-    </row>
-    <row r="102" spans="1:14" ht="24.75">
+      <c r="O101" s="14"/>
+    </row>
+    <row r="102" spans="1:15" ht="24.75">
       <c r="A102" s="10" t="s">
         <v>421</v>
       </c>
@@ -24401,8 +24930,9 @@
       <c r="N102" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102" s="14"/>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" s="10" t="s">
         <v>423</v>
       </c>
@@ -24435,8 +24965,9 @@
         <v>357</v>
       </c>
       <c r="N103" s="14"/>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103" s="14"/>
+    </row>
+    <row r="104" spans="1:15">
       <c r="A104" s="10" t="s">
         <v>424</v>
       </c>
@@ -24471,8 +25002,9 @@
         <v>357</v>
       </c>
       <c r="N104" s="14"/>
-    </row>
-    <row r="105" spans="1:14" ht="24.75">
+      <c r="O104" s="14"/>
+    </row>
+    <row r="105" spans="1:15" ht="24.75">
       <c r="A105" s="10" t="s">
         <v>492</v>
       </c>
@@ -24507,8 +25039,9 @@
         <v>357</v>
       </c>
       <c r="N105" s="14"/>
-    </row>
-    <row r="106" spans="1:14" ht="24.75">
+      <c r="O105" s="14"/>
+    </row>
+    <row r="106" spans="1:15" ht="24.75">
       <c r="A106" s="10" t="s">
         <v>493</v>
       </c>
@@ -24543,8 +25076,9 @@
         <v>357</v>
       </c>
       <c r="N106" s="14"/>
-    </row>
-    <row r="107" spans="1:14" ht="24.75">
+      <c r="O106" s="14"/>
+    </row>
+    <row r="107" spans="1:15" ht="24.75">
       <c r="A107" s="10" t="s">
         <v>494</v>
       </c>
@@ -24579,8 +25113,9 @@
         <v>357</v>
       </c>
       <c r="N107" s="14"/>
-    </row>
-    <row r="108" spans="1:14" ht="24.75">
+      <c r="O107" s="14"/>
+    </row>
+    <row r="108" spans="1:15" ht="24.75">
       <c r="A108" s="10" t="s">
         <v>495</v>
       </c>
@@ -24615,8 +25150,9 @@
         <v>357</v>
       </c>
       <c r="N108" s="14"/>
-    </row>
-    <row r="109" spans="1:14" ht="24.75">
+      <c r="O108" s="14"/>
+    </row>
+    <row r="109" spans="1:15" ht="24.75">
       <c r="A109" s="10" t="s">
         <v>496</v>
       </c>
@@ -24651,8 +25187,9 @@
         <v>357</v>
       </c>
       <c r="N109" s="14"/>
-    </row>
-    <row r="110" spans="1:14" ht="24.75">
+      <c r="O109" s="14"/>
+    </row>
+    <row r="110" spans="1:15" ht="24.75">
       <c r="A110" s="10" t="s">
         <v>497</v>
       </c>
@@ -24687,8 +25224,9 @@
         <v>357</v>
       </c>
       <c r="N110" s="14"/>
-    </row>
-    <row r="111" spans="1:14" ht="24.75">
+      <c r="O110" s="14"/>
+    </row>
+    <row r="111" spans="1:15" ht="24.75">
       <c r="A111" s="10" t="s">
         <v>498</v>
       </c>
@@ -24723,8 +25261,9 @@
         <v>357</v>
       </c>
       <c r="N111" s="14"/>
-    </row>
-    <row r="112" spans="1:14" ht="24.75">
+      <c r="O111" s="14"/>
+    </row>
+    <row r="112" spans="1:15" ht="24.75">
       <c r="A112" s="10" t="s">
         <v>499</v>
       </c>
@@ -24759,8 +25298,9 @@
         <v>357</v>
       </c>
       <c r="N112" s="14"/>
-    </row>
-    <row r="113" spans="1:14" ht="48.75">
+      <c r="O112" s="14"/>
+    </row>
+    <row r="113" spans="1:15" ht="48.75">
       <c r="A113" s="10" t="s">
         <v>426</v>
       </c>
@@ -24795,8 +25335,9 @@
         <v>357</v>
       </c>
       <c r="N113" s="14"/>
-    </row>
-    <row r="114" spans="1:14" ht="24">
+      <c r="O113" s="14"/>
+    </row>
+    <row r="114" spans="1:15" ht="24">
       <c r="A114" s="10" t="s">
         <v>426</v>
       </c>
@@ -24829,8 +25370,9 @@
         <v>357</v>
       </c>
       <c r="N114" s="14"/>
-    </row>
-    <row r="115" spans="1:14" ht="24.75">
+      <c r="O114" s="14"/>
+    </row>
+    <row r="115" spans="1:15" ht="24.75">
       <c r="A115" s="10" t="s">
         <v>431</v>
       </c>
@@ -24865,8 +25407,9 @@
         <v>357</v>
       </c>
       <c r="N115" s="14"/>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115" s="14"/>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="10" t="s">
         <v>431</v>
       </c>
@@ -24899,8 +25442,9 @@
         <v>357</v>
       </c>
       <c r="N116" s="14"/>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116" s="14"/>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="10" t="s">
         <v>432</v>
       </c>
@@ -24933,8 +25477,9 @@
         <v>357</v>
       </c>
       <c r="N117" s="14"/>
-    </row>
-    <row r="118" spans="1:14" ht="36">
+      <c r="O117" s="14"/>
+    </row>
+    <row r="118" spans="1:15" ht="36">
       <c r="A118" s="10" t="s">
         <v>433</v>
       </c>
@@ -24969,8 +25514,9 @@
         <v>357</v>
       </c>
       <c r="N118" s="14"/>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118" s="14"/>
+    </row>
+    <row r="119" spans="1:15">
       <c r="A119" s="10" t="s">
         <v>434</v>
       </c>
@@ -25005,8 +25551,9 @@
         <v>357</v>
       </c>
       <c r="N119" s="14"/>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119" s="14"/>
+    </row>
+    <row r="120" spans="1:15">
       <c r="A120" s="10" t="s">
         <v>435</v>
       </c>
@@ -25039,8 +25586,9 @@
         <v>357</v>
       </c>
       <c r="N120" s="14"/>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120" s="14"/>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" s="10" t="s">
         <v>500</v>
       </c>
@@ -25075,8 +25623,9 @@
         <v>357</v>
       </c>
       <c r="N121" s="14"/>
-    </row>
-    <row r="122" spans="1:14" ht="24.75">
+      <c r="O121" s="14"/>
+    </row>
+    <row r="122" spans="1:15" ht="24.75">
       <c r="A122" s="10" t="s">
         <v>501</v>
       </c>
@@ -25111,8 +25660,9 @@
         <v>357</v>
       </c>
       <c r="N122" s="14"/>
-    </row>
-    <row r="123" spans="1:14" ht="24.75">
+      <c r="O122" s="14"/>
+    </row>
+    <row r="123" spans="1:15" ht="24.75">
       <c r="A123" s="10" t="s">
         <v>502</v>
       </c>
@@ -25147,8 +25697,9 @@
         <v>357</v>
       </c>
       <c r="N123" s="14"/>
-    </row>
-    <row r="124" spans="1:14" ht="24.75">
+      <c r="O123" s="14"/>
+    </row>
+    <row r="124" spans="1:15" ht="24.75">
       <c r="A124" s="10" t="s">
         <v>503</v>
       </c>
@@ -25183,8 +25734,9 @@
         <v>357</v>
       </c>
       <c r="N124" s="14"/>
-    </row>
-    <row r="125" spans="1:14" ht="24.75">
+      <c r="O124" s="14"/>
+    </row>
+    <row r="125" spans="1:15" ht="24.75">
       <c r="A125" s="10" t="s">
         <v>504</v>
       </c>
@@ -25219,8 +25771,9 @@
         <v>357</v>
       </c>
       <c r="N125" s="14"/>
-    </row>
-    <row r="126" spans="1:14" ht="24.75">
+      <c r="O125" s="14"/>
+    </row>
+    <row r="126" spans="1:15" ht="24.75">
       <c r="A126" s="10" t="s">
         <v>505</v>
       </c>
@@ -25255,8 +25808,9 @@
         <v>357</v>
       </c>
       <c r="N126" s="14"/>
-    </row>
-    <row r="127" spans="1:14" ht="24.75">
+      <c r="O126" s="14"/>
+    </row>
+    <row r="127" spans="1:15" ht="24.75">
       <c r="A127" s="10" t="s">
         <v>506</v>
       </c>
@@ -25291,8 +25845,9 @@
         <v>357</v>
       </c>
       <c r="N127" s="14"/>
-    </row>
-    <row r="128" spans="1:14" ht="24.75">
+      <c r="O127" s="14"/>
+    </row>
+    <row r="128" spans="1:15" ht="24.75">
       <c r="A128" s="10" t="s">
         <v>507</v>
       </c>
@@ -25327,8 +25882,9 @@
         <v>357</v>
       </c>
       <c r="N128" s="14"/>
-    </row>
-    <row r="129" spans="1:14" ht="24.75">
+      <c r="O128" s="14"/>
+    </row>
+    <row r="129" spans="1:15" ht="24.75">
       <c r="A129" s="10" t="s">
         <v>508</v>
       </c>
@@ -25363,8 +25919,9 @@
         <v>357</v>
       </c>
       <c r="N129" s="14"/>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129" s="14"/>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" s="10" t="s">
         <v>437</v>
       </c>
@@ -25401,8 +25958,9 @@
       <c r="N130" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130" s="14"/>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" s="10" t="s">
         <v>438</v>
       </c>
@@ -25435,8 +25993,9 @@
         <v>357</v>
       </c>
       <c r="N131" s="14"/>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131" s="14"/>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" s="10" t="s">
         <v>439</v>
       </c>
@@ -25473,8 +26032,9 @@
       <c r="N132" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132" s="14"/>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" s="10" t="s">
         <v>440</v>
       </c>
@@ -25507,8 +26067,9 @@
         <v>357</v>
       </c>
       <c r="N133" s="14"/>
-    </row>
-    <row r="134" spans="1:14">
+      <c r="O133" s="14"/>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="10" t="s">
         <v>441</v>
       </c>
@@ -25545,8 +26106,9 @@
       <c r="N134" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:14">
+      <c r="O134" s="14"/>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="10" t="s">
         <v>442</v>
       </c>
@@ -25579,8 +26141,9 @@
         <v>357</v>
       </c>
       <c r="N135" s="14"/>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135" s="14"/>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" s="10" t="s">
         <v>443</v>
       </c>
@@ -25613,8 +26176,9 @@
         <v>357</v>
       </c>
       <c r="N136" s="14"/>
-    </row>
-    <row r="137" spans="1:14">
+      <c r="O136" s="14"/>
+    </row>
+    <row r="137" spans="1:15">
       <c r="A137" s="10" t="s">
         <v>444</v>
       </c>
@@ -25647,8 +26211,9 @@
         <v>357</v>
       </c>
       <c r="N137" s="14"/>
-    </row>
-    <row r="138" spans="1:14">
+      <c r="O137" s="14"/>
+    </row>
+    <row r="138" spans="1:15">
       <c r="A138" s="10" t="s">
         <v>445</v>
       </c>
@@ -25681,8 +26246,9 @@
         <v>357</v>
       </c>
       <c r="N138" s="14"/>
-    </row>
-    <row r="139" spans="1:14">
+      <c r="O138" s="14"/>
+    </row>
+    <row r="139" spans="1:15">
       <c r="A139" s="10" t="s">
         <v>446</v>
       </c>
@@ -25715,8 +26281,9 @@
         <v>357</v>
       </c>
       <c r="N139" s="14"/>
-    </row>
-    <row r="140" spans="1:14">
+      <c r="O139" s="14"/>
+    </row>
+    <row r="140" spans="1:15">
       <c r="A140" s="10" t="s">
         <v>447</v>
       </c>
@@ -25749,8 +26316,9 @@
         <v>357</v>
       </c>
       <c r="N140" s="14"/>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140" s="14"/>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="10" t="s">
         <v>448</v>
       </c>
@@ -25785,8 +26353,9 @@
         <v>357</v>
       </c>
       <c r="N141" s="14"/>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141" s="14"/>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="10" t="s">
         <v>450</v>
       </c>
@@ -25819,8 +26388,9 @@
         <v>357</v>
       </c>
       <c r="N142" s="14"/>
-    </row>
-    <row r="143" spans="1:14">
+      <c r="O142" s="14"/>
+    </row>
+    <row r="143" spans="1:15">
       <c r="A143" s="10" t="s">
         <v>451</v>
       </c>
@@ -25853,8 +26423,9 @@
         <v>357</v>
       </c>
       <c r="N143" s="14"/>
-    </row>
-    <row r="144" spans="1:14" ht="24.75">
+      <c r="O143" s="14"/>
+    </row>
+    <row r="144" spans="1:15" ht="24.75">
       <c r="A144" s="10" t="s">
         <v>509</v>
       </c>
@@ -25889,8 +26460,9 @@
         <v>357</v>
       </c>
       <c r="N144" s="14"/>
-    </row>
-    <row r="145" spans="1:14" ht="24.75">
+      <c r="O144" s="14"/>
+    </row>
+    <row r="145" spans="1:15" ht="24.75">
       <c r="A145" s="10" t="s">
         <v>511</v>
       </c>
@@ -25925,8 +26497,9 @@
         <v>357</v>
       </c>
       <c r="N145" s="14"/>
-    </row>
-    <row r="146" spans="1:14" ht="24.75">
+      <c r="O145" s="14"/>
+    </row>
+    <row r="146" spans="1:15" ht="24.75">
       <c r="A146" s="10" t="s">
         <v>512</v>
       </c>
@@ -25961,8 +26534,9 @@
         <v>357</v>
       </c>
       <c r="N146" s="14"/>
-    </row>
-    <row r="147" spans="1:14" ht="24.75">
+      <c r="O146" s="14"/>
+    </row>
+    <row r="147" spans="1:15" ht="24.75">
       <c r="A147" s="10" t="s">
         <v>513</v>
       </c>
@@ -25997,8 +26571,9 @@
         <v>357</v>
       </c>
       <c r="N147" s="14"/>
-    </row>
-    <row r="148" spans="1:14" ht="24.75">
+      <c r="O147" s="14"/>
+    </row>
+    <row r="148" spans="1:15" ht="24.75">
       <c r="A148" s="10" t="s">
         <v>514</v>
       </c>
@@ -26033,8 +26608,9 @@
         <v>357</v>
       </c>
       <c r="N148" s="14"/>
-    </row>
-    <row r="149" spans="1:14" ht="24.75">
+      <c r="O148" s="14"/>
+    </row>
+    <row r="149" spans="1:15" ht="24.75">
       <c r="A149" s="10" t="s">
         <v>515</v>
       </c>
@@ -26069,8 +26645,9 @@
         <v>357</v>
       </c>
       <c r="N149" s="14"/>
-    </row>
-    <row r="150" spans="1:14" ht="24.75">
+      <c r="O149" s="14"/>
+    </row>
+    <row r="150" spans="1:15" ht="24.75">
       <c r="A150" s="10" t="s">
         <v>516</v>
       </c>
@@ -26105,8 +26682,9 @@
         <v>357</v>
       </c>
       <c r="N150" s="14"/>
-    </row>
-    <row r="151" spans="1:14" ht="24.75">
+      <c r="O150" s="14"/>
+    </row>
+    <row r="151" spans="1:15" ht="24.75">
       <c r="A151" s="10" t="s">
         <v>517</v>
       </c>
@@ -26141,8 +26719,9 @@
         <v>357</v>
       </c>
       <c r="N151" s="14"/>
-    </row>
-    <row r="152" spans="1:14" ht="24.75">
+      <c r="O151" s="14"/>
+    </row>
+    <row r="152" spans="1:15" ht="24.75">
       <c r="A152" s="10" t="s">
         <v>518</v>
       </c>
@@ -26177,8 +26756,9 @@
         <v>357</v>
       </c>
       <c r="N152" s="14"/>
-    </row>
-    <row r="153" spans="1:14" ht="24.75">
+      <c r="O152" s="14"/>
+    </row>
+    <row r="153" spans="1:15" ht="24.75">
       <c r="A153" s="10" t="s">
         <v>519</v>
       </c>
@@ -26213,8 +26793,9 @@
         <v>357</v>
       </c>
       <c r="N153" s="14"/>
-    </row>
-    <row r="154" spans="1:14">
+      <c r="O153" s="14"/>
+    </row>
+    <row r="154" spans="1:15">
       <c r="A154" s="10" t="s">
         <v>452</v>
       </c>
@@ -26247,8 +26828,9 @@
         <v>357</v>
       </c>
       <c r="N154" s="14"/>
-    </row>
-    <row r="155" spans="1:14">
+      <c r="O154" s="14"/>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" s="10" t="s">
         <v>453</v>
       </c>
@@ -26281,19 +26863,20 @@
         <v>357</v>
       </c>
       <c r="N155" s="14"/>
-    </row>
-    <row r="156" spans="1:14">
+      <c r="O155" s="14"/>
+    </row>
+    <row r="156" spans="1:15">
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:15">
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:15">
       <c r="E158" s="2"/>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:15">
       <c r="E159" s="2"/>
     </row>
   </sheetData>
@@ -26322,7 +26905,7 @@
     <col min="16" max="1022" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -26371,8 +26954,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="63" customFormat="1" ht="72">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="63" customFormat="1" ht="72">
       <c r="A2" s="61" t="s">
         <v>520</v>
       </c>
@@ -26409,6 +26995,7 @@
         <v>52</v>
       </c>
       <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -26418,7 +27005,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -26433,10 +27020,10 @@
     <col min="13" max="13" width="9.140625" style="64" customWidth="1"/>
     <col min="14" max="14" width="11.5703125" style="1" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" customWidth="1"/>
+    <col min="16" max="17" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="65" t="s">
         <v>30</v>
       </c>
@@ -26485,8 +27072,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="24">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="24">
       <c r="A2" s="48" t="s">
         <v>526</v>
       </c>
@@ -26511,8 +27101,9 @@
         <v>52</v>
       </c>
       <c r="P2" s="66"/>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="66"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="67" t="s">
         <v>529</v>
       </c>
@@ -26549,8 +27140,9 @@
       <c r="P3" s="66">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="66"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="68" t="s">
         <v>531</v>
       </c>
@@ -26589,8 +27181,9 @@
       <c r="P4" s="73">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" s="45" customFormat="1">
+      <c r="Q4" s="73"/>
+    </row>
+    <row r="5" spans="1:17" s="45" customFormat="1">
       <c r="A5" s="48" t="s">
         <v>535</v>
       </c>
@@ -26615,8 +27208,9 @@
         <v>52</v>
       </c>
       <c r="P5" s="66"/>
-    </row>
-    <row r="6" spans="1:16" ht="24">
+      <c r="Q5" s="66"/>
+    </row>
+    <row r="6" spans="1:17" ht="24">
       <c r="A6" s="74" t="s">
         <v>537</v>
       </c>
@@ -26641,8 +27235,9 @@
         <v>52</v>
       </c>
       <c r="P6" s="78"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="78"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="67" t="s">
         <v>539</v>
       </c>
@@ -26677,8 +27272,9 @@
         <v>52</v>
       </c>
       <c r="P7" s="66"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="66"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="67" t="s">
         <v>542</v>
       </c>
@@ -26715,8 +27311,9 @@
       <c r="P8" s="66">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="66"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="67" t="s">
         <v>545</v>
       </c>
@@ -26753,8 +27350,9 @@
       <c r="P9" s="66">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="24">
+      <c r="Q9" s="66"/>
+    </row>
+    <row r="10" spans="1:17" ht="24">
       <c r="A10" s="67" t="s">
         <v>1165</v>
       </c>
@@ -26793,8 +27391,9 @@
       <c r="P10" s="66">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="66"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="67" t="s">
         <v>546</v>
       </c>
@@ -26833,8 +27432,9 @@
         <v>52</v>
       </c>
       <c r="P11" s="66"/>
-    </row>
-    <row r="12" spans="1:16" ht="24">
+      <c r="Q11" s="66"/>
+    </row>
+    <row r="12" spans="1:17" ht="24">
       <c r="A12" s="48" t="s">
         <v>552</v>
       </c>
@@ -26859,10 +27459,12 @@
         <v>52</v>
       </c>
       <c r="P12" s="66"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="66"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="O13" s="64"/>
       <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -26891,7 +27493,7 @@
     <col min="16" max="1022" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -26940,8 +27542,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="79" t="s">
         <v>553</v>
       </c>
@@ -26978,6 +27583,7 @@
         <v>52</v>
       </c>
       <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -27003,7 +27609,7 @@
     <col min="16" max="1022" width="9.140625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -27052,8 +27658,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="80" t="s">
         <v>558</v>
       </c>
@@ -27076,8 +27685,9 @@
       <c r="P2" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="80" t="s">
         <v>559</v>
       </c>
@@ -27100,8 +27710,9 @@
       <c r="P3" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="80" t="s">
         <v>560</v>
       </c>
@@ -27124,8 +27735,9 @@
       <c r="P4" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="80" t="s">
         <v>561</v>
       </c>
@@ -27148,8 +27760,9 @@
       <c r="P5" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="80" t="s">
         <v>562</v>
       </c>
@@ -27170,8 +27783,9 @@
         <v>52</v>
       </c>
       <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="80" t="s">
         <v>563</v>
       </c>
@@ -27192,6 +27806,7 @@
         <v>52</v>
       </c>
       <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -27218,11 +27833,11 @@
     <col min="13" max="13" width="19.42578125" style="2" customWidth="1"/>
     <col min="14" max="14" width="12.5703125" style="1" customWidth="1"/>
     <col min="15" max="15" width="18.140625" style="45" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="45"/>
-    <col min="17" max="1022" width="9.140625" style="1"/>
+    <col min="16" max="17" width="9.140625" style="45"/>
+    <col min="18" max="1022" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -27271,8 +27886,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
         <v>564</v>
       </c>
@@ -27311,8 +27929,9 @@
       <c r="P2" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="10" t="s">
         <v>567</v>
       </c>
@@ -27349,8 +27968,9 @@
         <v>52</v>
       </c>
       <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="10" t="s">
         <v>570</v>
       </c>
@@ -27388,8 +28008,9 @@
         <v>52</v>
       </c>
       <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
         <v>571</v>
       </c>
@@ -27429,8 +28050,9 @@
         <v>52</v>
       </c>
       <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" ht="24">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" ht="24">
       <c r="A6" s="10" t="s">
         <v>573</v>
       </c>
@@ -27471,8 +28093,9 @@
       <c r="P6" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="24">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17" ht="24">
       <c r="A7" s="48" t="s">
         <v>576</v>
       </c>
@@ -27507,8 +28130,9 @@
         <v>52</v>
       </c>
       <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" ht="24">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17" ht="24">
       <c r="A8" s="10" t="s">
         <v>580</v>
       </c>
@@ -27547,8 +28171,9 @@
       <c r="P8" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
         <v>584</v>
       </c>
@@ -27587,8 +28212,9 @@
       <c r="P9" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="10" t="s">
         <v>587</v>
       </c>
@@ -27627,8 +28253,9 @@
       <c r="P10" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="24">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" ht="24">
       <c r="A11" s="10" t="s">
         <v>588</v>
       </c>
@@ -27665,8 +28292,9 @@
       <c r="P11" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="48" t="s">
         <v>592</v>
       </c>
@@ -27691,8 +28319,9 @@
       <c r="P12" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="10" t="s">
         <v>593</v>
       </c>
@@ -27731,8 +28360,9 @@
       <c r="P13" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="10" t="s">
         <v>595</v>
       </c>
@@ -27773,8 +28403,9 @@
       <c r="P14" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="10" t="s">
         <v>597</v>
       </c>
@@ -27811,8 +28442,9 @@
         <v>52</v>
       </c>
       <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="10" t="s">
         <v>598</v>
       </c>
@@ -27851,8 +28483,9 @@
       <c r="P16" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="85" t="s">
         <v>599</v>
       </c>
@@ -27893,8 +28526,9 @@
       <c r="P17" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="85" t="s">
         <v>601</v>
       </c>
@@ -27933,8 +28567,9 @@
       <c r="P18" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="10" t="s">
         <v>602</v>
       </c>
@@ -27971,8 +28606,9 @@
         <v>52</v>
       </c>
       <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="10" t="s">
         <v>603</v>
       </c>
@@ -28009,8 +28645,9 @@
         <v>52</v>
       </c>
       <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="10" t="s">
         <v>604</v>
       </c>
@@ -28051,8 +28688,9 @@
       <c r="P21" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="10" t="s">
         <v>607</v>
       </c>
@@ -28091,8 +28729,9 @@
         <v>52</v>
       </c>
       <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" ht="36">
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" ht="36">
       <c r="A23" s="10" t="s">
         <v>609</v>
       </c>
@@ -28131,8 +28770,9 @@
         <v>52</v>
       </c>
       <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" ht="24">
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" ht="24">
       <c r="A24" s="48" t="s">
         <v>614</v>
       </c>
@@ -28167,8 +28807,9 @@
       <c r="P24" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="10" t="s">
         <v>618</v>
       </c>
@@ -28205,8 +28846,9 @@
         <v>52</v>
       </c>
       <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="10" t="s">
         <v>619</v>
       </c>
@@ -28243,8 +28885,9 @@
         <v>52</v>
       </c>
       <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="10" t="s">
         <v>621</v>
       </c>
@@ -28281,8 +28924,9 @@
         <v>52</v>
       </c>
       <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="1:16" ht="12" customHeight="1">
+      <c r="Q27" s="14"/>
+    </row>
+    <row r="28" spans="1:17" ht="12" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>622</v>
       </c>
@@ -28319,8 +28963,9 @@
         <v>52</v>
       </c>
       <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="14"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="10" t="s">
         <v>623</v>
       </c>
@@ -28361,8 +29006,9 @@
       <c r="P29" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29" s="14"/>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="10" t="s">
         <v>624</v>
       </c>
@@ -28401,8 +29047,9 @@
         <v>52</v>
       </c>
       <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30" s="14"/>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="48" t="s">
         <v>626</v>
       </c>
@@ -28437,8 +29084,9 @@
       <c r="P31" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="24">
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17" ht="24">
       <c r="A32" s="48" t="s">
         <v>629</v>
       </c>
@@ -28473,8 +29121,9 @@
       <c r="P32" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="48" t="s">
         <v>630</v>
       </c>
@@ -28507,8 +29156,9 @@
         <v>52</v>
       </c>
       <c r="P33" s="14"/>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="10" t="s">
         <v>631</v>
       </c>
@@ -28545,8 +29195,9 @@
         <v>52</v>
       </c>
       <c r="P34" s="14"/>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="10" t="s">
         <v>632</v>
       </c>
@@ -28587,8 +29238,9 @@
       <c r="P35" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35" s="14"/>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="10" t="s">
         <v>633</v>
       </c>
@@ -28625,8 +29277,9 @@
         <v>52</v>
       </c>
       <c r="P36" s="14"/>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="10" t="s">
         <v>634</v>
       </c>
@@ -28665,8 +29318,9 @@
       <c r="P37" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37" s="14"/>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="85" t="s">
         <v>635</v>
       </c>
@@ -28707,8 +29361,9 @@
       <c r="P38" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" s="85" t="s">
         <v>636</v>
       </c>
@@ -28747,8 +29402,9 @@
       <c r="P39" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39" s="14"/>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="10" t="s">
         <v>637</v>
       </c>
@@ -28785,8 +29441,9 @@
         <v>52</v>
       </c>
       <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" s="10" t="s">
         <v>638</v>
       </c>
@@ -28823,8 +29480,9 @@
         <v>52</v>
       </c>
       <c r="P41" s="14"/>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" s="10" t="s">
         <v>639</v>
       </c>
@@ -28865,8 +29523,9 @@
       <c r="P42" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="10" t="s">
         <v>640</v>
       </c>
@@ -28905,8 +29564,9 @@
         <v>52</v>
       </c>
       <c r="P43" s="14"/>
-    </row>
-    <row r="44" spans="1:16" ht="36">
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17" ht="36">
       <c r="A44" s="10" t="s">
         <v>641</v>
       </c>
@@ -28945,8 +29605,9 @@
         <v>52</v>
       </c>
       <c r="P44" s="14"/>
-    </row>
-    <row r="45" spans="1:16" ht="24">
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17" ht="24">
       <c r="A45" s="48" t="s">
         <v>642</v>
       </c>
@@ -28981,8 +29642,9 @@
       <c r="P45" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="10" t="s">
         <v>643</v>
       </c>
@@ -29019,8 +29681,9 @@
         <v>52</v>
       </c>
       <c r="P46" s="14"/>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="10" t="s">
         <v>644</v>
       </c>
@@ -29057,8 +29720,9 @@
         <v>52</v>
       </c>
       <c r="P47" s="14"/>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="10" t="s">
         <v>645</v>
       </c>
@@ -29095,8 +29759,9 @@
         <v>52</v>
       </c>
       <c r="P48" s="14"/>
-    </row>
-    <row r="49" spans="1:16" ht="12" customHeight="1">
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17" ht="12" customHeight="1">
       <c r="A49" s="10" t="s">
         <v>646</v>
       </c>
@@ -29133,8 +29798,9 @@
         <v>52</v>
       </c>
       <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49" s="14"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50" s="10" t="s">
         <v>647</v>
       </c>
@@ -29175,8 +29841,9 @@
       <c r="P50" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:16">
+      <c r="Q50" s="14"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="A51" s="10" t="s">
         <v>648</v>
       </c>
@@ -29215,8 +29882,9 @@
         <v>52</v>
       </c>
       <c r="P51" s="14"/>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="Q51" s="14"/>
+    </row>
+    <row r="52" spans="1:17">
       <c r="A52" s="48" t="s">
         <v>649</v>
       </c>
@@ -29249,8 +29917,9 @@
       <c r="P52" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="24">
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="1:17" ht="24">
       <c r="A53" s="48" t="s">
         <v>650</v>
       </c>
@@ -29285,8 +29954,9 @@
       <c r="P53" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="14"/>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54" s="48" t="s">
         <v>651</v>
       </c>
@@ -29319,8 +29989,9 @@
         <v>52</v>
       </c>
       <c r="P54" s="14"/>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54" s="14"/>
+    </row>
+    <row r="55" spans="1:17">
       <c r="A55" s="10" t="s">
         <v>652</v>
       </c>
@@ -29357,8 +30028,9 @@
         <v>52</v>
       </c>
       <c r="P55" s="14"/>
-    </row>
-    <row r="56" spans="1:16" ht="24">
+      <c r="Q55" s="14"/>
+    </row>
+    <row r="56" spans="1:17" ht="24">
       <c r="A56" s="28" t="s">
         <v>353</v>
       </c>
@@ -29407,8 +30079,11 @@
       <c r="P56" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57" s="10" t="s">
         <v>653</v>
       </c>
@@ -29448,8 +30123,9 @@
       <c r="P57" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="24">
+      <c r="Q57" s="14"/>
+    </row>
+    <row r="58" spans="1:17" ht="24">
       <c r="A58" s="10" t="s">
         <v>656</v>
       </c>
@@ -29489,8 +30165,9 @@
       <c r="P58" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="24">
+      <c r="Q58" s="14"/>
+    </row>
+    <row r="59" spans="1:17" ht="24">
       <c r="A59" s="10" t="s">
         <v>657</v>
       </c>
@@ -29530,8 +30207,9 @@
       <c r="P59" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="24">
+      <c r="Q59" s="14"/>
+    </row>
+    <row r="60" spans="1:17" ht="24">
       <c r="A60" s="10" t="s">
         <v>658</v>
       </c>
@@ -29571,8 +30249,9 @@
       <c r="P60" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="24">
+      <c r="Q60" s="14"/>
+    </row>
+    <row r="61" spans="1:17" ht="24">
       <c r="A61" s="10" t="s">
         <v>659</v>
       </c>
@@ -29612,8 +30291,9 @@
       <c r="P61" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="24">
+      <c r="Q61" s="14"/>
+    </row>
+    <row r="62" spans="1:17" ht="24">
       <c r="A62" s="10" t="s">
         <v>660</v>
       </c>
@@ -29653,8 +30333,9 @@
       <c r="P62" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="24">
+      <c r="Q62" s="14"/>
+    </row>
+    <row r="63" spans="1:17" ht="24">
       <c r="A63" s="10" t="s">
         <v>661</v>
       </c>
@@ -29694,8 +30375,9 @@
       <c r="P63" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="24">
+      <c r="Q63" s="14"/>
+    </row>
+    <row r="64" spans="1:17" ht="24">
       <c r="A64" s="10" t="s">
         <v>662</v>
       </c>
@@ -29735,8 +30417,9 @@
       <c r="P64" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="24">
+      <c r="Q64" s="14"/>
+    </row>
+    <row r="65" spans="1:17" ht="24">
       <c r="A65" s="10" t="s">
         <v>663</v>
       </c>
@@ -29776,8 +30459,9 @@
       <c r="P65" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="36">
+      <c r="Q65" s="14"/>
+    </row>
+    <row r="66" spans="1:17" ht="36">
       <c r="A66" s="10" t="s">
         <v>664</v>
       </c>
@@ -29818,8 +30502,9 @@
       <c r="P66" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66" s="14"/>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" s="10" t="s">
         <v>667</v>
       </c>
@@ -29859,8 +30544,9 @@
       <c r="P67" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="24">
+      <c r="Q67" s="14"/>
+    </row>
+    <row r="68" spans="1:17" ht="24">
       <c r="A68" s="10" t="s">
         <v>668</v>
       </c>
@@ -29900,8 +30586,9 @@
       <c r="P68" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="24">
+      <c r="Q68" s="14"/>
+    </row>
+    <row r="69" spans="1:17" ht="24">
       <c r="A69" s="10" t="s">
         <v>669</v>
       </c>
@@ -29941,8 +30628,9 @@
       <c r="P69" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="24">
+      <c r="Q69" s="14"/>
+    </row>
+    <row r="70" spans="1:17" ht="24">
       <c r="A70" s="10" t="s">
         <v>670</v>
       </c>
@@ -29982,8 +30670,9 @@
       <c r="P70" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="24">
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17" ht="24">
       <c r="A71" s="10" t="s">
         <v>671</v>
       </c>
@@ -30023,8 +30712,9 @@
       <c r="P71" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="24">
+      <c r="Q71" s="14"/>
+    </row>
+    <row r="72" spans="1:17" ht="24">
       <c r="A72" s="10" t="s">
         <v>672</v>
       </c>
@@ -30064,8 +30754,9 @@
       <c r="P72" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="24">
+      <c r="Q72" s="14"/>
+    </row>
+    <row r="73" spans="1:17" ht="24">
       <c r="A73" s="10" t="s">
         <v>673</v>
       </c>
@@ -30105,8 +30796,9 @@
       <c r="P73" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="24">
+      <c r="Q73" s="14"/>
+    </row>
+    <row r="74" spans="1:17" ht="24">
       <c r="A74" s="10" t="s">
         <v>674</v>
       </c>
@@ -30146,8 +30838,9 @@
       <c r="P74" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="24">
+      <c r="Q74" s="14"/>
+    </row>
+    <row r="75" spans="1:17" ht="24">
       <c r="A75" s="10" t="s">
         <v>675</v>
       </c>
@@ -30187,8 +30880,9 @@
       <c r="P75" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" ht="36">
+      <c r="Q75" s="14"/>
+    </row>
+    <row r="76" spans="1:17" ht="36">
       <c r="A76" s="10" t="s">
         <v>676</v>
       </c>
@@ -30229,8 +30923,9 @@
       <c r="P76" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="14"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="10" t="s">
         <v>677</v>
       </c>
@@ -30269,8 +30964,9 @@
         <v>357</v>
       </c>
       <c r="P77" s="14"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77" s="14"/>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="10" t="s">
         <v>679</v>
       </c>
@@ -30311,8 +31007,9 @@
       <c r="P78" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78" s="14"/>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79" s="10" t="s">
         <v>680</v>
       </c>
@@ -30351,8 +31048,9 @@
         <v>357</v>
       </c>
       <c r="P79" s="14"/>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79" s="14"/>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" s="10" t="s">
         <v>681</v>
       </c>
@@ -30391,8 +31089,9 @@
         <v>357</v>
       </c>
       <c r="P80" s="14"/>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="Q80" s="14"/>
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81" s="10" t="s">
         <v>683</v>
       </c>
@@ -30431,8 +31130,9 @@
         <v>357</v>
       </c>
       <c r="P81" s="14"/>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="Q81" s="14"/>
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82" s="88" t="s">
         <v>684</v>
       </c>
@@ -30471,8 +31171,9 @@
         <v>357</v>
       </c>
       <c r="P82" s="14"/>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82" s="14"/>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83" s="10" t="s">
         <v>687</v>
       </c>
@@ -30511,8 +31212,9 @@
         <v>357</v>
       </c>
       <c r="P83" s="14"/>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83" s="14"/>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" s="10" t="s">
         <v>689</v>
       </c>
@@ -30549,8 +31251,9 @@
         <v>357</v>
       </c>
       <c r="P84" s="14"/>
-    </row>
-    <row r="85" spans="1:16">
+      <c r="Q84" s="14"/>
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85" s="10" t="s">
         <v>690</v>
       </c>
@@ -30589,8 +31292,9 @@
         <v>357</v>
       </c>
       <c r="P85" s="14"/>
-    </row>
-    <row r="86" spans="1:16">
+      <c r="Q85" s="14"/>
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86" s="10" t="s">
         <v>691</v>
       </c>
@@ -30631,8 +31335,9 @@
       <c r="P86" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86" s="14"/>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" s="10" t="s">
         <v>692</v>
       </c>
@@ -30671,8 +31376,9 @@
         <v>357</v>
       </c>
       <c r="P87" s="14"/>
-    </row>
-    <row r="88" spans="1:16">
+      <c r="Q87" s="14"/>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88" s="10" t="s">
         <v>693</v>
       </c>
@@ -30711,8 +31417,9 @@
         <v>357</v>
       </c>
       <c r="P88" s="14"/>
-    </row>
-    <row r="89" spans="1:16">
+      <c r="Q88" s="14"/>
+    </row>
+    <row r="89" spans="1:17">
       <c r="A89" s="10" t="s">
         <v>694</v>
       </c>
@@ -30751,8 +31458,9 @@
         <v>357</v>
       </c>
       <c r="P89" s="14"/>
-    </row>
-    <row r="90" spans="1:16">
+      <c r="Q89" s="14"/>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90" s="10" t="s">
         <v>695</v>
       </c>
@@ -30791,8 +31499,9 @@
         <v>357</v>
       </c>
       <c r="P90" s="14"/>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90" s="14"/>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91" s="10" t="s">
         <v>696</v>
       </c>
@@ -30831,8 +31540,9 @@
         <v>357</v>
       </c>
       <c r="P91" s="14"/>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91" s="14"/>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92" s="10" t="s">
         <v>697</v>
       </c>
@@ -30869,8 +31579,9 @@
         <v>357</v>
       </c>
       <c r="P92" s="14"/>
-    </row>
-    <row r="93" spans="1:16">
+      <c r="Q92" s="14"/>
+    </row>
+    <row r="93" spans="1:17">
       <c r="A93" s="10" t="s">
         <v>698</v>
       </c>
@@ -30909,8 +31620,9 @@
         <v>357</v>
       </c>
       <c r="P93" s="14"/>
-    </row>
-    <row r="94" spans="1:16">
+      <c r="Q93" s="14"/>
+    </row>
+    <row r="94" spans="1:17">
       <c r="A94" s="10" t="s">
         <v>700</v>
       </c>
@@ -30949,8 +31661,9 @@
       <c r="P94" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" spans="1:16">
+      <c r="Q94" s="14"/>
+    </row>
+    <row r="95" spans="1:17">
       <c r="A95" s="10" t="s">
         <v>702</v>
       </c>
@@ -30989,8 +31702,9 @@
         <v>357</v>
       </c>
       <c r="P95" s="14"/>
-    </row>
-    <row r="96" spans="1:16">
+      <c r="Q95" s="14"/>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96" s="10" t="s">
         <v>703</v>
       </c>
@@ -31029,8 +31743,9 @@
       <c r="P96" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" ht="24">
+      <c r="Q96" s="14"/>
+    </row>
+    <row r="97" spans="1:17" ht="24">
       <c r="A97" s="10" t="s">
         <v>704</v>
       </c>
@@ -31073,8 +31788,9 @@
       <c r="P97" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" ht="24">
+      <c r="Q97" s="14"/>
+    </row>
+    <row r="98" spans="1:17" ht="24">
       <c r="A98" s="10" t="s">
         <v>709</v>
       </c>
@@ -31115,8 +31831,9 @@
       <c r="P98" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" ht="24">
+      <c r="Q98" s="14"/>
+    </row>
+    <row r="99" spans="1:17" ht="24">
       <c r="A99" s="10" t="s">
         <v>713</v>
       </c>
@@ -31159,8 +31876,9 @@
       <c r="P99" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" ht="24">
+      <c r="Q99" s="14"/>
+    </row>
+    <row r="100" spans="1:17" ht="24">
       <c r="A100" s="10" t="s">
         <v>716</v>
       </c>
@@ -31201,8 +31919,9 @@
       <c r="P100" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" ht="24">
+      <c r="Q100" s="14"/>
+    </row>
+    <row r="101" spans="1:17" ht="24">
       <c r="A101" s="10" t="s">
         <v>720</v>
       </c>
@@ -31243,8 +31962,9 @@
       <c r="P101" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" ht="36">
+      <c r="Q101" s="14"/>
+    </row>
+    <row r="102" spans="1:17" ht="36">
       <c r="A102" s="10" t="s">
         <v>723</v>
       </c>
@@ -31285,8 +32005,9 @@
       <c r="P102" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" ht="24">
+      <c r="Q102" s="14"/>
+    </row>
+    <row r="103" spans="1:17" ht="24">
       <c r="A103" s="10" t="s">
         <v>726</v>
       </c>
@@ -31327,8 +32048,9 @@
       <c r="P103" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" ht="24">
+      <c r="Q103" s="14"/>
+    </row>
+    <row r="104" spans="1:17" ht="24">
       <c r="A104" s="10" t="s">
         <v>729</v>
       </c>
@@ -31369,8 +32091,9 @@
       <c r="P104" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" ht="24">
+      <c r="Q104" s="14"/>
+    </row>
+    <row r="105" spans="1:17" ht="24">
       <c r="A105" s="10" t="s">
         <v>732</v>
       </c>
@@ -31415,8 +32138,9 @@
       <c r="P105" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" ht="24">
+      <c r="Q105" s="14"/>
+    </row>
+    <row r="106" spans="1:17" ht="24">
       <c r="A106" s="10" t="s">
         <v>736</v>
       </c>
@@ -31457,8 +32181,9 @@
       <c r="P106" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="Q106" s="14"/>
+    </row>
+    <row r="107" spans="1:17">
       <c r="A107" s="10" t="s">
         <v>739</v>
       </c>
@@ -31497,8 +32222,9 @@
       <c r="P107" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" ht="24">
+      <c r="Q107" s="14"/>
+    </row>
+    <row r="108" spans="1:17" ht="24">
       <c r="A108" s="28" t="s">
         <v>741</v>
       </c>
@@ -31547,8 +32273,11 @@
       <c r="P108" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" ht="36">
+      <c r="Q108" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="36">
       <c r="A109" s="10" t="s">
         <v>742</v>
       </c>
@@ -31589,8 +32318,9 @@
       <c r="P109" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" ht="24">
+      <c r="Q109" s="14"/>
+    </row>
+    <row r="110" spans="1:17" ht="24">
       <c r="A110" s="10" t="s">
         <v>747</v>
       </c>
@@ -31633,8 +32363,9 @@
       <c r="P110" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" ht="24">
+      <c r="Q110" s="14"/>
+    </row>
+    <row r="111" spans="1:17" ht="24">
       <c r="A111" s="10" t="s">
         <v>750</v>
       </c>
@@ -31671,8 +32402,9 @@
       <c r="P111" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" ht="36">
+      <c r="Q111" s="14"/>
+    </row>
+    <row r="112" spans="1:17" ht="36">
       <c r="A112" s="10" t="s">
         <v>753</v>
       </c>
@@ -31715,8 +32447,9 @@
       <c r="P112" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:16">
+      <c r="Q112" s="14"/>
+    </row>
+    <row r="113" spans="1:17">
       <c r="A113" s="10" t="s">
         <v>755</v>
       </c>
@@ -31757,8 +32490,9 @@
       <c r="P113" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="114" spans="1:16">
+      <c r="Q113" s="14"/>
+    </row>
+    <row r="114" spans="1:17">
       <c r="A114" s="10" t="s">
         <v>758</v>
       </c>
@@ -31797,8 +32531,9 @@
         <v>132</v>
       </c>
       <c r="P114" s="14"/>
-    </row>
-    <row r="115" spans="1:16">
+      <c r="Q114" s="14"/>
+    </row>
+    <row r="115" spans="1:17">
       <c r="A115" s="10" t="s">
         <v>760</v>
       </c>
@@ -31837,8 +32572,9 @@
         <v>132</v>
       </c>
       <c r="P115" s="14"/>
-    </row>
-    <row r="116" spans="1:16" ht="36">
+      <c r="Q115" s="14"/>
+    </row>
+    <row r="116" spans="1:17" ht="36">
       <c r="A116" s="10" t="s">
         <v>762</v>
       </c>
@@ -31879,8 +32615,9 @@
       <c r="P116" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" ht="24">
+      <c r="Q116" s="14"/>
+    </row>
+    <row r="117" spans="1:17" ht="24">
       <c r="A117" s="10" t="s">
         <v>765</v>
       </c>
@@ -31921,8 +32658,9 @@
       <c r="P117" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="118" spans="1:16">
+      <c r="Q117" s="14"/>
+    </row>
+    <row r="118" spans="1:17">
       <c r="A118" s="10" t="s">
         <v>769</v>
       </c>
@@ -31963,8 +32701,9 @@
       <c r="P118" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" ht="24">
+      <c r="Q118" s="14"/>
+    </row>
+    <row r="119" spans="1:17" ht="24">
       <c r="A119" s="10" t="s">
         <v>771</v>
       </c>
@@ -32005,8 +32744,9 @@
       <c r="P119" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" ht="36">
+      <c r="Q119" s="14"/>
+    </row>
+    <row r="120" spans="1:17" ht="36">
       <c r="A120" s="10" t="s">
         <v>774</v>
       </c>
@@ -32047,8 +32787,9 @@
       <c r="P120" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" ht="24">
+      <c r="Q120" s="14"/>
+    </row>
+    <row r="121" spans="1:17" ht="24">
       <c r="A121" s="10" t="s">
         <v>775</v>
       </c>
@@ -32089,8 +32830,9 @@
       <c r="P121" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" ht="24">
+      <c r="Q121" s="14"/>
+    </row>
+    <row r="122" spans="1:17" ht="24">
       <c r="A122" s="10" t="s">
         <v>779</v>
       </c>
@@ -32131,8 +32873,9 @@
       <c r="P122" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="123" spans="1:16">
+      <c r="Q122" s="14"/>
+    </row>
+    <row r="123" spans="1:17">
       <c r="A123" s="10" t="s">
         <v>780</v>
       </c>
@@ -32173,8 +32916,9 @@
       <c r="P123" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" ht="48">
+      <c r="Q123" s="14"/>
+    </row>
+    <row r="124" spans="1:17" ht="48">
       <c r="A124" s="10" t="s">
         <v>782</v>
       </c>
@@ -32215,8 +32959,9 @@
       <c r="P124" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" ht="24">
+      <c r="Q124" s="14"/>
+    </row>
+    <row r="125" spans="1:17" ht="24">
       <c r="A125" s="10" t="s">
         <v>786</v>
       </c>
@@ -32257,8 +33002,9 @@
       <c r="P125" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:16">
+      <c r="Q125" s="14"/>
+    </row>
+    <row r="126" spans="1:17">
       <c r="A126" s="10" t="s">
         <v>788</v>
       </c>
@@ -32299,8 +33045,9 @@
       <c r="P126" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:16">
+      <c r="Q126" s="14"/>
+    </row>
+    <row r="127" spans="1:17">
       <c r="A127" s="10" t="s">
         <v>790</v>
       </c>
@@ -32337,8 +33084,9 @@
       <c r="P127" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:16">
+      <c r="Q127" s="14"/>
+    </row>
+    <row r="128" spans="1:17">
       <c r="A128" s="10" t="s">
         <v>792</v>
       </c>
@@ -32379,8 +33127,9 @@
       <c r="P128" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" ht="24">
+      <c r="Q128" s="14"/>
+    </row>
+    <row r="129" spans="1:17" ht="24">
       <c r="A129" s="10" t="s">
         <v>794</v>
       </c>
@@ -32419,8 +33168,9 @@
       <c r="P129" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" ht="36">
+      <c r="Q129" s="14"/>
+    </row>
+    <row r="130" spans="1:17" ht="36">
       <c r="A130" s="10" t="s">
         <v>796</v>
       </c>
@@ -32459,8 +33209,9 @@
       <c r="P130" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" ht="36">
+      <c r="Q130" s="14"/>
+    </row>
+    <row r="131" spans="1:17" ht="36">
       <c r="A131" s="10" t="s">
         <v>798</v>
       </c>
@@ -32501,8 +33252,9 @@
       <c r="P131" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="132" spans="1:16">
+      <c r="Q131" s="14"/>
+    </row>
+    <row r="132" spans="1:17">
       <c r="A132" s="10" t="s">
         <v>799</v>
       </c>
@@ -32543,8 +33295,9 @@
       <c r="P132" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="133" spans="1:16">
+      <c r="Q132" s="14"/>
+    </row>
+    <row r="133" spans="1:17">
       <c r="A133" s="10" t="s">
         <v>801</v>
       </c>
@@ -32583,8 +33336,9 @@
         <v>132</v>
       </c>
       <c r="P133" s="14"/>
-    </row>
-    <row r="134" spans="1:16">
+      <c r="Q133" s="14"/>
+    </row>
+    <row r="134" spans="1:17">
       <c r="A134" s="10" t="s">
         <v>803</v>
       </c>
@@ -32621,8 +33375,9 @@
       <c r="P134" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:16">
+      <c r="Q134" s="14"/>
+    </row>
+    <row r="135" spans="1:17">
       <c r="A135" s="10" t="s">
         <v>804</v>
       </c>
@@ -32661,8 +33416,9 @@
         <v>132</v>
       </c>
       <c r="P135" s="14"/>
-    </row>
-    <row r="136" spans="1:16" ht="36">
+      <c r="Q135" s="14"/>
+    </row>
+    <row r="136" spans="1:17" ht="36">
       <c r="A136" s="10" t="s">
         <v>806</v>
       </c>
@@ -32703,8 +33459,9 @@
       <c r="P136" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="137" spans="1:16">
+      <c r="Q136" s="14"/>
+    </row>
+    <row r="137" spans="1:17">
       <c r="A137" s="10" t="s">
         <v>807</v>
       </c>
@@ -32745,8 +33502,9 @@
       <c r="P137" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="138" spans="1:16">
+      <c r="Q137" s="14"/>
+    </row>
+    <row r="138" spans="1:17">
       <c r="A138" s="10" t="s">
         <v>808</v>
       </c>
@@ -32787,8 +33545,9 @@
       <c r="P138" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:16">
+      <c r="Q138" s="14"/>
+    </row>
+    <row r="139" spans="1:17">
       <c r="A139" s="10" t="s">
         <v>810</v>
       </c>
@@ -32825,8 +33584,9 @@
       <c r="P139" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:16">
+      <c r="Q139" s="14"/>
+    </row>
+    <row r="140" spans="1:17">
       <c r="A140" s="10" t="s">
         <v>811</v>
       </c>
@@ -32867,8 +33627,9 @@
       <c r="P140" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" ht="36">
+      <c r="Q140" s="14"/>
+    </row>
+    <row r="141" spans="1:17" ht="36">
       <c r="A141" s="10" t="s">
         <v>812</v>
       </c>
@@ -32909,8 +33670,9 @@
       <c r="P141" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="142" spans="1:16">
+      <c r="Q141" s="14"/>
+    </row>
+    <row r="142" spans="1:17">
       <c r="A142" s="10" t="s">
         <v>813</v>
       </c>
@@ -32949,8 +33711,9 @@
       <c r="P142" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:16">
+      <c r="Q142" s="14"/>
+    </row>
+    <row r="143" spans="1:17">
       <c r="A143" s="10" t="s">
         <v>814</v>
       </c>
@@ -32989,8 +33752,9 @@
       <c r="P143" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:16">
+      <c r="Q143" s="14"/>
+    </row>
+    <row r="144" spans="1:17">
       <c r="A144" s="10" t="s">
         <v>815</v>
       </c>
@@ -33031,8 +33795,9 @@
       <c r="P144" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" ht="24">
+      <c r="Q144" s="14"/>
+    </row>
+    <row r="145" spans="1:17" ht="24">
       <c r="A145" s="65" t="s">
         <v>817</v>
       </c>
@@ -33081,8 +33846,11 @@
       <c r="P145" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="146" spans="1:16">
+      <c r="Q145" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17">
       <c r="A146" s="40" t="s">
         <v>818</v>
       </c>
@@ -33115,8 +33883,9 @@
         <v>1188</v>
       </c>
       <c r="P146" s="14"/>
-    </row>
-    <row r="147" spans="1:16">
+      <c r="Q146" s="14"/>
+    </row>
+    <row r="147" spans="1:17">
       <c r="A147" s="40" t="s">
         <v>822</v>
       </c>
@@ -33141,8 +33910,9 @@
         <v>1188</v>
       </c>
       <c r="P147" s="14"/>
-    </row>
-    <row r="148" spans="1:16">
+      <c r="Q147" s="14"/>
+    </row>
+    <row r="148" spans="1:17">
       <c r="A148" s="40" t="s">
         <v>250</v>
       </c>
@@ -33175,8 +33945,9 @@
         <v>1188</v>
       </c>
       <c r="P148" s="14"/>
-    </row>
-    <row r="149" spans="1:16">
+      <c r="Q148" s="14"/>
+    </row>
+    <row r="149" spans="1:17">
       <c r="A149" s="40" t="s">
         <v>825</v>
       </c>
@@ -33209,8 +33980,9 @@
         <v>1188</v>
       </c>
       <c r="P149" s="14"/>
-    </row>
-    <row r="150" spans="1:16">
+      <c r="Q149" s="14"/>
+    </row>
+    <row r="150" spans="1:17">
       <c r="A150" s="40" t="s">
         <v>826</v>
       </c>
@@ -33235,8 +34007,9 @@
         <v>1188</v>
       </c>
       <c r="P150" s="14"/>
-    </row>
-    <row r="151" spans="1:16">
+      <c r="Q150" s="14"/>
+    </row>
+    <row r="151" spans="1:17">
       <c r="A151" s="40" t="s">
         <v>827</v>
       </c>
@@ -33275,8 +34048,9 @@
         <v>1188</v>
       </c>
       <c r="P151" s="14"/>
-    </row>
-    <row r="152" spans="1:16">
+      <c r="Q151" s="14"/>
+    </row>
+    <row r="152" spans="1:17">
       <c r="A152" s="40" t="s">
         <v>828</v>
       </c>
@@ -33309,8 +34083,9 @@
         <v>1188</v>
       </c>
       <c r="P152" s="14"/>
-    </row>
-    <row r="153" spans="1:16">
+      <c r="Q152" s="14"/>
+    </row>
+    <row r="153" spans="1:17">
       <c r="A153" s="40" t="s">
         <v>829</v>
       </c>
@@ -33335,8 +34110,9 @@
         <v>1188</v>
       </c>
       <c r="P153" s="14"/>
-    </row>
-    <row r="154" spans="1:16">
+      <c r="Q153" s="14"/>
+    </row>
+    <row r="154" spans="1:17">
       <c r="A154" s="40" t="s">
         <v>830</v>
       </c>
@@ -33369,8 +34145,9 @@
         <v>1188</v>
       </c>
       <c r="P154" s="14"/>
-    </row>
-    <row r="155" spans="1:16">
+      <c r="Q154" s="14"/>
+    </row>
+    <row r="155" spans="1:17">
       <c r="A155" s="40" t="s">
         <v>831</v>
       </c>
@@ -33395,8 +34172,9 @@
         <v>1188</v>
       </c>
       <c r="P155" s="14"/>
-    </row>
-    <row r="156" spans="1:16">
+      <c r="Q155" s="14"/>
+    </row>
+    <row r="156" spans="1:17">
       <c r="A156" s="40" t="s">
         <v>832</v>
       </c>
@@ -33421,8 +34199,9 @@
         <v>1188</v>
       </c>
       <c r="P156" s="14"/>
-    </row>
-    <row r="157" spans="1:16">
+      <c r="Q156" s="14"/>
+    </row>
+    <row r="157" spans="1:17">
       <c r="A157" s="40" t="s">
         <v>833</v>
       </c>
@@ -33447,6 +34226,7 @@
         <v>1188</v>
       </c>
       <c r="P157" s="14"/>
+      <c r="Q157" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271B74B7-C4C6-4E33-8098-20A5AB5D62BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C3775-BD01-4677-B3C4-B97284B998D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="17250" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20475" yWindow="3300" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6617" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6670" uniqueCount="1209">
   <si>
     <t>Patient Inputs</t>
   </si>
@@ -3757,6 +3757,48 @@
   </si>
   <si>
     <t>Thresholds</t>
+  </si>
+  <si>
+    <t>ArterialOxygenContent</t>
+  </si>
+  <si>
+    <t>ArteriovenousOxygenDifference</t>
+  </si>
+  <si>
+    <t>MixedVenousOxygenContent</t>
+  </si>
+  <si>
+    <t>OxygenDelivery</t>
+  </si>
+  <si>
+    <t>OxygenDeliveryToOxygenConsumptionRatio</t>
+  </si>
+  <si>
+    <t>Between 4:1 and 5:1</t>
+  </si>
+  <si>
+    <t>[900,1100]</t>
+  </si>
+  <si>
+    <t>ApparentOxygenConsumption</t>
+  </si>
+  <si>
+    <t>18-20 mL O2/dL blood = 18-20%</t>
+  </si>
+  <si>
+    <t>4-5 mL O2/dL blood = 4-5%</t>
+  </si>
+  <si>
+    <t>13-15 mL O2/dL blood = 13-15%</t>
+  </si>
+  <si>
+    <t>[0.18,0.20]</t>
+  </si>
+  <si>
+    <t>[0.04-0.05]</t>
+  </si>
+  <si>
+    <t>[0.13,0.15]</t>
   </si>
 </sst>
 </file>
@@ -13265,7 +13307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMH81"/>
+  <dimension ref="A1:AMH87"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.140625" style="1" customWidth="1"/>
@@ -13341,21 +13383,21 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
-        <v>44</v>
+        <v>1202</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
-        <v>47</v>
+      <c r="F2" s="8">
+        <v>250</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
@@ -13380,46 +13422,46 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>54</v>
-      </c>
+        <v>1195</v>
+      </c>
+      <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="8">
-        <v>1050</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>56</v>
-      </c>
+      <c r="F3" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8"/>
       <c r="I3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="8" t="s">
+        <v>1203</v>
+      </c>
       <c r="K3" s="12"/>
       <c r="L3" s="13"/>
       <c r="M3" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P3" s="14"/>
+      <c r="P3" s="14">
+        <v>2</v>
+      </c>
       <c r="Q3" s="14"/>
     </row>
-    <row r="4" spans="1:17" ht="24">
+    <row r="4" spans="1:17">
       <c r="A4" s="10" t="s">
-        <v>58</v>
+        <v>1196</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
@@ -13428,20 +13470,20 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>1207</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="4"/>
+      <c r="J4" s="8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="5" t="s">
         <v>50</v>
       </c>
@@ -13458,21 +13500,21 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="8">
-        <v>3617</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>64</v>
+      <c r="F5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8" t="s">
@@ -13485,60 +13527,58 @@
         <v>50</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P5" s="14"/>
+      <c r="P5" s="14">
+        <v>2</v>
+      </c>
       <c r="Q5" s="14"/>
     </row>
-    <row r="6" spans="1:17" ht="24">
+    <row r="6" spans="1:17">
       <c r="A6" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>66</v>
+        <v>53</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>69</v>
+      <c r="F6" s="8">
+        <v>1050</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="4"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
       <c r="M6" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P6" s="14">
-        <v>1</v>
-      </c>
+      <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" ht="24">
       <c r="A7" s="10" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
@@ -13546,19 +13586,21 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="8">
-        <v>0.13</v>
+      <c r="F7" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="I7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="4"/>
       <c r="M7" s="5" t="s">
         <v>50</v>
       </c>
@@ -13575,124 +13617,124 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8"/>
+        <v>3617</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="J8" s="8"/>
       <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="5"/>
+      <c r="N8" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="O8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="14">
-        <v>2</v>
-      </c>
+      <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17" ht="24">
       <c r="A9" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>66</v>
+      </c>
       <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="21"/>
+      <c r="K9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="4"/>
       <c r="M9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P9" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="14"/>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="12">
+    <row r="10" spans="1:17">
       <c r="A10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>82</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="22">
-        <f>Patient!C7*Patient!C11/100</f>
-        <v>826.44819998688286</v>
+      <c r="F10" s="8">
+        <v>0.13</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="12"/>
+        <v>73</v>
+      </c>
+      <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>84</v>
-      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="O10" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P10" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="14"/>
     </row>
-    <row r="11" spans="1:17" ht="24">
+    <row r="11" spans="1:17">
       <c r="A11" s="10" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
@@ -13700,27 +13742,23 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>87</v>
-      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="4"/>
+      <c r="J11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
       <c r="M11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="N11" s="5"/>
       <c r="O11" s="14" t="s">
         <v>52</v>
       </c>
@@ -13729,79 +13767,74 @@
       </c>
       <c r="Q11" s="14"/>
     </row>
-    <row r="12" spans="1:17" ht="27.75" customHeight="1">
+    <row r="12" spans="1:17" ht="24">
       <c r="A12" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>89</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="20" t="s">
-        <v>90</v>
+      <c r="F12" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="I12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="20" t="s">
+        <v>80</v>
+      </c>
       <c r="L12" s="21"/>
       <c r="M12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="O12" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P12" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="14"/>
     </row>
-    <row r="13" spans="1:17" ht="27.75" customHeight="1">
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="12">
       <c r="A13" s="10" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="23">
-        <f>Patient!C7*(1-Patient!C11/34)</f>
-        <v>3078.9246666177987</v>
+      <c r="F13" s="22">
+        <f>Patient!C7*Patient!C11/100</f>
+        <v>826.44819998688286</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>93</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H13" s="12"/>
       <c r="I13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="K13" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>96</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="L13" s="13"/>
       <c r="M13" s="5" t="s">
         <v>50</v>
       </c>
@@ -13811,72 +13844,92 @@
       <c r="O13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P13" s="14"/>
+      <c r="P13" s="14">
+        <v>1</v>
+      </c>
       <c r="Q13" s="14"/>
     </row>
-    <row r="14" spans="1:17" ht="24">
+    <row r="14" spans="1:17">
       <c r="A14" s="10" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>581</v>
-      </c>
+        <v>1197</v>
+      </c>
+      <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="26" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="26"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="5"/>
+      <c r="J14" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O14" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="48" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="10" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
+      <c r="F15" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P15" s="14">
+        <v>2</v>
+      </c>
       <c r="Q15" s="14"/>
     </row>
-    <row r="16" spans="1:17" ht="24">
+    <row r="16" spans="1:17">
       <c r="A16" s="10" t="s">
-        <v>97</v>
+        <v>1199</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8" t="s">
@@ -13885,20 +13938,20 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>87</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="8"/>
       <c r="I16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="4"/>
+      <c r="J16" s="8" t="s">
+        <v>1200</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="5" t="s">
         <v>50</v>
       </c>
@@ -13915,110 +13968,116 @@
     </row>
     <row r="17" spans="1:17" ht="24">
       <c r="A17" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>99</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22">
-        <f>(F10/0.000000000029)/(Patient!C7*1000)</f>
-        <v>5172413.793103449</v>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="21"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="4"/>
       <c r="M17" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="O17" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P17" s="14"/>
+      <c r="P17" s="14">
+        <v>2</v>
+      </c>
       <c r="Q17" s="14"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" ht="27.75" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
-        <v>103</v>
+      <c r="F18" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>105</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="H18" s="8"/>
       <c r="I18" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="13"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="21"/>
       <c r="M18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="O18" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="14"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" ht="27.75" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="20" t="s">
-        <v>107</v>
+      <c r="F19" s="23">
+        <f>Patient!C7*(1-Patient!C11/34)</f>
+        <v>3078.9246666177987</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="I19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="13"/>
+      <c r="J19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="M19" s="5" t="s">
         <v>50</v>
       </c>
@@ -14028,158 +14087,143 @@
       <c r="O19" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P19" s="14">
-        <v>1</v>
-      </c>
+      <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="24">
       <c r="A20" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+        <v>1169</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>113</v>
-      </c>
+        <v>1170</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="26"/>
       <c r="I20" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="26"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O20" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P20" s="14"/>
+      <c r="P20" s="14">
+        <v>1</v>
+      </c>
       <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="8" t="s">
-        <v>46</v>
-      </c>
+      <c r="A21" s="48" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="8">
-        <v>2.3E-3</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" s="12"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="26"/>
       <c r="K21" s="8"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="O21" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P21" s="14">
-        <v>5</v>
-      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" ht="24">
       <c r="A22" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="12"/>
+        <v>97</v>
+      </c>
+      <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="8">
-        <v>1.2999999999999999E-3</v>
+      <c r="F22" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="12"/>
+        <v>78</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="I22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="13"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="4"/>
       <c r="M22" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="O22" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="14"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" ht="24">
       <c r="A23" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="27">
-        <v>7000</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>120</v>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="22">
+        <f>(F13/0.000000000029)/(Patient!C7*1000)</f>
+        <v>5172413.793103449</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="L23" s="4"/>
+      <c r="J23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>52</v>
@@ -14187,86 +14231,70 @@
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
     </row>
-    <row r="24" spans="1:17" ht="24">
-      <c r="A24" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="56.25">
-      <c r="A25" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>128</v>
+    <row r="24" spans="1:17">
+      <c r="A24" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P24" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J25" s="18"/>
-      <c r="K25" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="L25" s="4"/>
+      <c r="F25" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="13"/>
       <c r="M25" s="5" t="s">
         <v>50</v>
       </c>
@@ -14274,41 +14302,39 @@
         <v>71</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="P25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="14"/>
     </row>
-    <row r="26" spans="1:17" ht="22.5">
-      <c r="A26" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="B26" s="18" t="s">
+    <row r="26" spans="1:17">
+      <c r="A26" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="18" t="s">
+      <c r="C26" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I26" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="18"/>
-      <c r="K26" s="32" t="s">
-        <v>135</v>
-      </c>
+      <c r="I26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="5" t="s">
         <v>50</v>
@@ -14317,248 +14343,248 @@
         <v>71</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="P26" s="14">
-        <v>1</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="P26" s="14"/>
       <c r="Q26" s="14"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>110</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B27" s="12"/>
       <c r="C27" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="L27" s="4"/>
+      <c r="F27" s="8">
+        <v>2.3E-3</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="12"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="13"/>
       <c r="M27" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="P27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>128</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B28" s="12"/>
       <c r="C28" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J28" s="17"/>
-      <c r="K28" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="L28" s="4"/>
+      <c r="F28" s="8">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="13"/>
       <c r="M28" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="O28" s="14" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="P28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:17" ht="36">
+    <row r="29" spans="1:17">
       <c r="A29" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>146</v>
+        <v>118</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
-      <c r="F29" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>148</v>
+      <c r="F29" s="27">
+        <v>7000</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>119</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="I29" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="17"/>
-      <c r="K29" s="8" t="s">
-        <v>150</v>
+      <c r="K29" s="16" t="s">
+        <v>121</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="P29" s="14">
-        <v>4</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
     </row>
     <row r="30" spans="1:17" ht="24">
-      <c r="A30" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="17" t="s">
+      <c r="A30" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="56.25">
+      <c r="A31" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J30" s="17"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="P30" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="14"/>
-    </row>
-    <row r="31" spans="1:17" ht="60">
-      <c r="A31" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>155</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="H31" s="17"/>
+      <c r="F31" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="18"/>
       <c r="I31" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J31" s="17"/>
-      <c r="K31" s="4"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="31" t="s">
+        <v>131</v>
+      </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="O31" s="14" t="s">
         <v>132</v>
       </c>
       <c r="P31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B32" s="17" t="s">
+    <row r="32" spans="1:17" ht="22.5">
+      <c r="A32" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="G32" s="26" t="s">
+      <c r="C32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="26" t="s">
+      <c r="H32" s="18" t="s">
         <v>113</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J32" s="17"/>
-      <c r="K32" s="4"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="32" t="s">
+        <v>135</v>
+      </c>
       <c r="L32" s="4"/>
       <c r="M32" s="5" t="s">
         <v>50</v>
@@ -14576,81 +14602,76 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>66</v>
+        <v>136</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="17" t="s">
-        <v>161</v>
+      <c r="F33" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="H33" s="17"/>
+        <v>112</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="I33" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J33" s="17"/>
-      <c r="K33" s="4" t="s">
-        <v>163</v>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="O33" s="14" t="s">
         <v>132</v>
       </c>
       <c r="P33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:17" ht="36.75">
+    <row r="34" spans="1:17">
       <c r="A34" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>110</v>
+        <v>141</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F34" s="14" t="str">
-        <f>IF(Patient!C7&lt;&gt;"Male",D34,E34)</f>
-        <v>[13.8,17.2]</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>15</v>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>143</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="17"/>
-      <c r="K34" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>169</v>
-      </c>
+      <c r="K34" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L34" s="4"/>
       <c r="M34" s="5" t="s">
         <v>50</v>
       </c>
@@ -14665,31 +14686,33 @@
       </c>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" ht="36">
       <c r="A35" s="10" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="26">
-        <v>0.40600000000000003</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="H35" s="26"/>
+      <c r="F35" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>149</v>
+      </c>
       <c r="I35" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J35" s="26"/>
-      <c r="K35" s="4" t="s">
-        <v>171</v>
+      <c r="J35" s="17"/>
+      <c r="K35" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5" t="s">
@@ -14702,15 +14725,15 @@
         <v>132</v>
       </c>
       <c r="P35" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q35" s="14"/>
     </row>
     <row r="36" spans="1:17" ht="24">
       <c r="A36" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B36" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>128</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -14718,22 +14741,20 @@
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="26" t="s">
-        <v>173</v>
+      <c r="F36" s="20" t="s">
+        <v>152</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" s="26" t="s">
-        <v>175</v>
+        <v>112</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="4" t="s">
-        <v>176</v>
-      </c>
+      <c r="J36" s="17"/>
+      <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="5" t="s">
         <v>50</v>
@@ -14745,13 +14766,13 @@
         <v>132</v>
       </c>
       <c r="P36" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" ht="60">
       <c r="A37" s="10" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>155</v>
@@ -14761,17 +14782,17 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
-      <c r="F37" s="26" t="s">
-        <v>178</v>
+      <c r="F37" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H37" s="26"/>
+        <v>157</v>
+      </c>
+      <c r="H37" s="17"/>
       <c r="I37" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J37" s="5"/>
+      <c r="J37" s="17"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="5" t="s">
@@ -14788,34 +14809,32 @@
       </c>
       <c r="Q37" s="14"/>
     </row>
-    <row r="38" spans="1:17" ht="24">
+    <row r="38" spans="1:17">
       <c r="A38" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>183</v>
+        <v>158</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>113</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="4" t="s">
-        <v>184</v>
-      </c>
+      <c r="J38" s="17"/>
+      <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="5" t="s">
         <v>50</v>
@@ -14827,82 +14846,87 @@
         <v>132</v>
       </c>
       <c r="P38" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="14"/>
     </row>
-    <row r="39" spans="1:17" ht="24">
+    <row r="39" spans="1:17">
       <c r="A39" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>110</v>
+        <v>160</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="F39" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="F39" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H39" s="17"/>
       <c r="I39" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="34" t="s">
-        <v>188</v>
+      <c r="J39" s="17"/>
+      <c r="K39" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>132</v>
       </c>
       <c r="P39" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="14"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" ht="36.75">
       <c r="A40" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="G40" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="H40" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="J40" s="36"/>
-      <c r="K40" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="L40" s="4"/>
+        <v>164</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F40" s="14" t="str">
+        <f>IF(Patient!C7&lt;&gt;"Male",D40,E40)</f>
+        <v>[13.8,17.2]</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" s="17"/>
+      <c r="K40" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="L40" s="21" t="s">
+        <v>169</v>
+      </c>
       <c r="M40" s="5" t="s">
         <v>50</v>
       </c>
@@ -14912,40 +14936,38 @@
       <c r="O40" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="P40" s="14"/>
+      <c r="P40" s="14">
+        <v>2</v>
+      </c>
       <c r="Q40" s="14"/>
     </row>
-    <row r="41" spans="1:17" ht="36">
+    <row r="41" spans="1:17">
       <c r="A41" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>66</v>
+        <v>170</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>155</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>194</v>
+      <c r="F41" s="26">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="H41" s="26"/>
       <c r="I41" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J41" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="L41" s="39" t="s">
-        <v>197</v>
-      </c>
+      <c r="J41" s="26"/>
+      <c r="K41" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L41" s="4"/>
       <c r="M41" s="5" t="s">
         <v>50</v>
       </c>
@@ -14956,128 +14978,120 @@
         <v>132</v>
       </c>
       <c r="P41" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="24">
-      <c r="A42" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G42" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="H42" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="I42" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P42" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>1194</v>
-      </c>
+      <c r="A42" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="L42" s="4"/>
+      <c r="M42" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="P42" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>200</v>
+        <v>177</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
-      <c r="F43" s="8">
-        <v>40</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="8"/>
+      <c r="F43" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43" s="26"/>
+      <c r="I43" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="5"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="O43" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P43" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="P43" s="14">
+        <v>4</v>
+      </c>
       <c r="Q43" s="14"/>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" ht="24">
       <c r="A44" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>200</v>
+        <v>180</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
-      <c r="F44" s="8">
-        <v>95</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>15</v>
+      <c r="F44" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>182</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="I44" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I44" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J44" s="8"/>
-      <c r="K44" s="4"/>
+      <c r="K44" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="L44" s="4"/>
       <c r="M44" s="5" t="s">
         <v>50</v>
@@ -15086,76 +15100,84 @@
         <v>71</v>
       </c>
       <c r="O44" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P44" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="P44" s="14">
+        <v>2</v>
+      </c>
       <c r="Q44" s="14"/>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" ht="24">
       <c r="A45" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>200</v>
+        <v>185</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="20">
-        <v>45</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>15</v>
+      <c r="F45" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="I45" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="I45" s="18" t="s">
         <v>49</v>
       </c>
       <c r="J45" s="8"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="34" t="s">
+        <v>188</v>
+      </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="O45" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P45" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="P45" s="14">
+        <v>3</v>
+      </c>
       <c r="Q45" s="14"/>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="20">
-        <v>40</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="4"/>
+        <v>189</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="G46" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46" s="36"/>
+      <c r="K46" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="L46" s="4"/>
       <c r="M46" s="5" t="s">
         <v>50</v>
@@ -15164,38 +15186,42 @@
         <v>71</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="P46" s="14"/>
       <c r="Q46" s="14"/>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" ht="36">
       <c r="A47" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>66</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="20">
-        <v>40</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="F47" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="H47" s="26"/>
+      <c r="I47" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="K47" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="L47" s="39" t="s">
+        <v>197</v>
+      </c>
       <c r="M47" s="5" t="s">
         <v>50</v>
       </c>
@@ -15203,53 +15229,69 @@
         <v>71</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P47" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="P47" s="14">
+        <v>2</v>
+      </c>
       <c r="Q47" s="14"/>
     </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="20">
-        <v>104</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N48" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O48" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
+    <row r="48" spans="1:17" ht="24">
+      <c r="A48" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="H48" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I48" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P48" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q48" s="9" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="10" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>200</v>
@@ -15288,7 +15330,7 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="10" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>200</v>
@@ -15299,13 +15341,13 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>49</v>
@@ -15325,149 +15367,126 @@
       <c r="P50" s="14"/>
       <c r="Q50" s="14"/>
     </row>
-    <row r="51" spans="1:17" ht="24">
-      <c r="A51" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q51" s="9" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="24">
-      <c r="A52" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="8"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="20">
+        <v>45</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J51" s="8"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="14"/>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>200</v>
+      </c>
       <c r="C52" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
-      <c r="F52" s="8" t="str">
-        <f>F4</f>
-        <v>7.2,
- [7.35,7.4]</v>
-      </c>
-      <c r="G52" s="8" t="str">
-        <f>G4</f>
-        <v>valentin2002icrp,  guyton2006medical</v>
-      </c>
-      <c r="H52" s="8" t="str">
-        <f>H4</f>
-        <v>p137                                 p384</v>
-      </c>
-      <c r="I52" s="8" t="str">
-        <f>I4</f>
-        <v>Y</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>1189</v>
-      </c>
+      <c r="F52" s="20">
+        <v>40</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52" s="8"/>
+      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="5" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O52" s="5" t="s">
-        <v>1185</v>
+      <c r="O52" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="P52" s="14"/>
       <c r="Q52" s="14"/>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>45</v>
+      <c r="A53" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>112</v>
+      <c r="F53" s="20">
+        <v>40</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J53" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="J53" s="8"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="5" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="N53" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O53" s="5" t="s">
-        <v>1185</v>
+      <c r="O53" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="14"/>
     </row>
     <row r="54" spans="1:17">
-      <c r="A54" s="40" t="s">
-        <v>218</v>
+      <c r="A54" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>200</v>
@@ -15477,38 +15496,36 @@
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="8">
-        <v>95</v>
+      <c r="F54" s="20">
+        <v>104</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>15</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J54" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="J54" s="8"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="5" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="N54" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O54" s="5" t="s">
-        <v>1185</v>
+      <c r="O54" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="P54" s="14"/>
       <c r="Q54" s="14"/>
     </row>
     <row r="55" spans="1:17">
-      <c r="A55" s="40" t="s">
-        <v>219</v>
+      <c r="A55" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>200</v>
@@ -15530,65 +15547,63 @@
       <c r="I55" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="J55" s="8"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="5" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="N55" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O55" s="5" t="s">
-        <v>1185</v>
+      <c r="O55" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="P55" s="14"/>
       <c r="Q55" s="14"/>
     </row>
-    <row r="56" spans="1:17" ht="24">
-      <c r="A56" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="8"/>
+    <row r="56" spans="1:17">
+      <c r="A56" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>200</v>
+      </c>
       <c r="C56" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
-      <c r="F56" s="8" t="s">
-        <v>86</v>
+      <c r="F56" s="8">
+        <v>45</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J56" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="J56" s="8"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="5" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O56" s="5" t="s">
-        <v>1185</v>
+      <c r="O56" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="P56" s="14"/>
       <c r="Q56" s="14"/>
     </row>
     <row r="57" spans="1:17" ht="24">
       <c r="A57" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>1</v>
@@ -15596,8 +15611,12 @@
       <c r="C57" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
+      <c r="D57" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="F57" s="9" t="s">
         <v>34</v>
       </c>
@@ -15635,262 +15654,282 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" ht="24">
       <c r="A58" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="14" t="str">
-        <f>F9</f>
-        <v>0.42,
-[0.4,0.5]</v>
-      </c>
-      <c r="G58" s="14" t="str">
-        <f>G9</f>
-        <v>guyton2006medical,
-valtin1995renal</v>
-      </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8" t="str">
+        <f>F7</f>
+        <v>7.2,
+ [7.35,7.4]</v>
+      </c>
+      <c r="G58" s="8" t="str">
+        <f>G7</f>
+        <v>valentin2002icrp,  guyton2006medical</v>
+      </c>
+      <c r="H58" s="8" t="str">
+        <f>H7</f>
+        <v>p137                                 p384</v>
+      </c>
+      <c r="I58" s="8" t="str">
+        <f>I7</f>
+        <v>Y</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>1189</v>
+      </c>
       <c r="L58" s="4"/>
       <c r="M58" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P58" s="14"/>
       <c r="Q58" s="14"/>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F59" s="14" t="str">
-        <f>IF(Patient!C2="Male",D59,E59)</f>
-        <v>[13.8,17.2]</v>
-      </c>
-      <c r="G59" s="14" t="str">
-        <f>G34</f>
-        <v>guyton2006medical</v>
-      </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J59" s="4"/>
+        <v>215</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P59" s="14"/>
       <c r="Q59" s="14"/>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="14" t="s">
-        <v>225</v>
+        <v>218</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8">
+        <v>95</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J60" s="4"/>
-      <c r="K60" s="41" t="s">
-        <v>227</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P60" s="14"/>
       <c r="Q60" s="14"/>
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="14" t="s">
-        <v>229</v>
+        <v>219</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8">
+        <v>40</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J61" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P61" s="14"/>
       <c r="Q61" s="14"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" ht="24">
       <c r="A62" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="42">
-        <v>8.9999999999999999E-8</v>
+        <v>85</v>
+      </c>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J62" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P62" s="14"/>
       <c r="Q62" s="14"/>
     </row>
-    <row r="63" spans="1:17">
-      <c r="A63" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="G63" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="H63" s="4"/>
-      <c r="I63" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="L63" s="4"/>
-      <c r="M63" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="N63" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O63" s="5" t="s">
-        <v>1186</v>
-      </c>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
+    <row r="63" spans="1:17" ht="24">
+      <c r="A63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P63" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="9" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" s="14" t="str">
-        <f>B17</f>
-        <v>ct/uL</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B64" s="4"/>
       <c r="C64" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="14">
-        <f>F17</f>
-        <v>5172413.793103449</v>
+      <c r="F64" s="14" t="str">
+        <f>F12</f>
+        <v>0.42,
+[0.4,0.5]</v>
       </c>
       <c r="G64" s="14" t="str">
-        <f>G17</f>
-        <v>guyton2006medical</v>
+        <f>G12</f>
+        <v>guyton2006medical,
+valtin1995renal</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="5" t="s">
@@ -15903,7 +15942,7 @@
         <v>221</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="O64" s="5" t="s">
         <v>1186</v>
@@ -15913,24 +15952,27 @@
     </row>
     <row r="65" spans="1:17">
       <c r="A65" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="44" t="str">
-        <f>B23</f>
-        <v>ct/uL</v>
+        <v>222</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="44">
-        <f>F23</f>
-        <v>7000</v>
-      </c>
-      <c r="G65" s="44" t="str">
-        <f>G23</f>
-        <v xml:space="preserve">guyton2006medical   </v>
+      <c r="D65" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" s="14" t="str">
+        <f>IF(Patient!C2="Male",D65,E65)</f>
+        <v>[13.8,17.2]</v>
+      </c>
+      <c r="G65" s="14" t="str">
+        <f>G40</f>
+        <v>guyton2006medical</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="5" t="s">
@@ -15951,62 +15993,48 @@
       <c r="P65" s="14"/>
       <c r="Q65" s="14"/>
     </row>
-    <row r="66" spans="1:17" ht="24">
-      <c r="A66" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I66" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K66" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M66" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N66" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O66" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P66" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q66" s="9" t="s">
-        <v>1194</v>
-      </c>
+    <row r="66" spans="1:17">
+      <c r="A66" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" s="4"/>
+      <c r="K66" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="L66" s="4"/>
+      <c r="M66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="N66" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="P66" s="14"/>
+      <c r="Q66" s="14"/>
     </row>
     <row r="67" spans="1:17">
       <c r="A67" s="40" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>110</v>
@@ -16016,13 +16044,11 @@
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
-      <c r="F67" s="14" t="str">
-        <f>F26</f>
-        <v>[4,5]</v>
-      </c>
-      <c r="G67" s="14" t="str">
-        <f>G26</f>
-        <v>valtin1995renal</v>
+      <c r="F67" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="5" t="s">
@@ -16032,30 +16058,38 @@
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="P67" s="14"/>
       <c r="Q67" s="14"/>
     </row>
     <row r="68" spans="1:17">
       <c r="A68" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="B68" s="4"/>
+        <v>231</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>232</v>
+      </c>
       <c r="C68" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="F68" s="42">
+        <v>8.9999999999999999E-8</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="I68" s="5" t="s">
         <v>49</v>
       </c>
@@ -16063,60 +16097,77 @@
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N68" s="5" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="14"/>
     </row>
     <row r="69" spans="1:17">
       <c r="A69" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="B69" s="4"/>
+        <v>234</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="C69" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="4"/>
+      <c r="F69" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="G69" s="43" t="s">
+        <v>236</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="K69" s="4" t="s">
+        <v>237</v>
+      </c>
       <c r="L69" s="4"/>
       <c r="M69" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N69" s="5" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="P69" s="14"/>
       <c r="Q69" s="14"/>
     </row>
     <row r="70" spans="1:17">
       <c r="A70" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="B70" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="B70" s="14" t="str">
+        <f>B23</f>
+        <v>ct/uL</v>
+      </c>
       <c r="C70" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="4"/>
+      <c r="F70" s="14">
+        <f>F23</f>
+        <v>5172413.793103449</v>
+      </c>
+      <c r="G70" s="14" t="str">
+        <f>G23</f>
+        <v>guyton2006medical</v>
+      </c>
       <c r="H70" s="4"/>
       <c r="I70" s="5" t="s">
         <v>49</v>
@@ -16125,38 +16176,37 @@
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N70" s="5" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="14"/>
     </row>
     <row r="71" spans="1:17">
       <c r="A71" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>66</v>
+        <v>118</v>
+      </c>
+      <c r="B71" s="44" t="str">
+        <f>B29</f>
+        <v>ct/uL</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
-      <c r="F71" s="14" t="str">
-        <f>F6</f>
-        <v>[9.0,18.0],
-[6.0,20.0]</v>
-      </c>
-      <c r="G71" s="14" t="str">
-        <f>G6</f>
-        <v>valtin1995renal,
-Deepakfirst</v>
+      <c r="F71" s="44">
+        <f>F29</f>
+        <v>7000</v>
+      </c>
+      <c r="G71" s="44" t="str">
+        <f>G29</f>
+        <v xml:space="preserve">guyton2006medical   </v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="5" t="s">
@@ -16166,68 +16216,90 @@
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N71" s="5" t="s">
         <v>71</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="P71" s="14"/>
       <c r="Q71" s="14"/>
     </row>
-    <row r="72" spans="1:17">
-      <c r="A72" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="14" t="str">
-        <f>F28</f>
-        <v>[44.08,52.1]</v>
-      </c>
-      <c r="G72" s="14" t="str">
-        <f>G28</f>
-        <v>cheuvront2014comparison</v>
-      </c>
-      <c r="H72" s="4"/>
-      <c r="I72" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="N72" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O72" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="P72" s="14"/>
-      <c r="Q72" s="14"/>
+    <row r="72" spans="1:17" ht="24">
+      <c r="A72" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P72" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q72" s="9" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="73" spans="1:17">
       <c r="A73" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="B73" s="14"/>
+        <v>239</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="C73" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="4"/>
+      <c r="F73" s="14" t="str">
+        <f>F32</f>
+        <v>[4,5]</v>
+      </c>
+      <c r="G73" s="14" t="str">
+        <f>G32</f>
+        <v>valtin1995renal</v>
+      </c>
       <c r="H73" s="4"/>
       <c r="I73" s="5" t="s">
         <v>49</v>
@@ -16249,23 +16321,16 @@
     </row>
     <row r="74" spans="1:17">
       <c r="A74" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>89</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="B74" s="4"/>
       <c r="C74" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G74" s="14" t="str">
-        <f>G27</f>
-        <v>valtin1995renal</v>
-      </c>
+      <c r="F74" s="14"/>
+      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="5" t="s">
         <v>49</v>
@@ -16287,24 +16352,16 @@
     </row>
     <row r="75" spans="1:17">
       <c r="A75" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>128</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="B75" s="4"/>
       <c r="C75" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="14" t="str">
-        <f>F30</f>
-        <v>[5.0,15.0]</v>
-      </c>
-      <c r="G75" s="14" t="str">
-        <f>G30</f>
-        <v>valtin1995renal</v>
-      </c>
+      <c r="F75" s="14"/>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="5" t="s">
         <v>49</v>
@@ -16326,22 +16383,16 @@
     </row>
     <row r="76" spans="1:17">
       <c r="A76" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>66</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B76" s="4"/>
       <c r="C76" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>91</v>
-      </c>
+      <c r="F76" s="14"/>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="5" t="s">
         <v>49</v>
@@ -16363,16 +16414,26 @@
     </row>
     <row r="77" spans="1:17">
       <c r="A77" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="B77" s="4"/>
+        <v>244</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="C77" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="4"/>
+      <c r="F77" s="14" t="str">
+        <f>F9</f>
+        <v>[9.0,18.0],
+[6.0,20.0]</v>
+      </c>
+      <c r="G77" s="14" t="str">
+        <f>G9</f>
+        <v>valtin1995renal,
+Deepakfirst</v>
+      </c>
       <c r="H77" s="4"/>
       <c r="I77" s="5" t="s">
         <v>49</v>
@@ -16394,23 +16455,23 @@
     </row>
     <row r="78" spans="1:17">
       <c r="A78" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="B78" s="18" t="s">
-        <v>89</v>
+        <v>245</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="14" t="s">
-        <v>254</v>
+      <c r="F78" s="14" t="str">
+        <f>F34</f>
+        <v>[44.08,52.1]</v>
       </c>
       <c r="G78" s="14" t="str">
-        <f>G38</f>
-        <v>Leeuwen2015laboratory,
-valtin1995renal</v>
+        <f>G34</f>
+        <v>cheuvront2014comparison</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="5" t="s">
@@ -16433,9 +16494,9 @@
     </row>
     <row r="79" spans="1:17">
       <c r="A79" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="B79" s="4"/>
+        <v>246</v>
+      </c>
+      <c r="B79" s="14"/>
       <c r="C79" s="5" t="s">
         <v>46</v>
       </c>
@@ -16464,29 +16525,28 @@
     </row>
     <row r="80" spans="1:17">
       <c r="A80" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="B80" s="18" t="s">
-        <v>110</v>
+        <v>247</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="14" t="str">
-        <f>F20</f>
-        <v>[6,8]</v>
+      <c r="F80" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G80" s="14" t="str">
-        <f>G20</f>
+        <f>G33</f>
         <v>valtin1995renal</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J80" s="14"/>
+      <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="5" t="s">
@@ -16501,24 +16561,240 @@
       <c r="P80" s="14"/>
       <c r="Q80" s="14"/>
     </row>
-    <row r="81" spans="15:15">
-      <c r="O81" s="45"/>
+    <row r="81" spans="1:17">
+      <c r="A81" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="14" t="str">
+        <f>F36</f>
+        <v>[5.0,15.0]</v>
+      </c>
+      <c r="G81" s="14" t="str">
+        <f>G36</f>
+        <v>valtin1995renal</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N81" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O81" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P81" s="14"/>
+      <c r="Q81" s="14"/>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H82" s="4"/>
+      <c r="I82" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N82" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O82" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P82" s="14"/>
+      <c r="Q82" s="14"/>
+    </row>
+    <row r="83" spans="1:17">
+      <c r="A83" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N83" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O83" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P83" s="14"/>
+      <c r="Q83" s="14"/>
+    </row>
+    <row r="84" spans="1:17">
+      <c r="A84" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="G84" s="14" t="str">
+        <f>G44</f>
+        <v>Leeuwen2015laboratory,
+valtin1995renal</v>
+      </c>
+      <c r="H84" s="4"/>
+      <c r="I84" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N84" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O84" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P84" s="14"/>
+      <c r="Q84" s="14"/>
+    </row>
+    <row r="85" spans="1:17">
+      <c r="A85" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N85" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O85" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P85" s="14"/>
+      <c r="Q85" s="14"/>
+    </row>
+    <row r="86" spans="1:17">
+      <c r="A86" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="14" t="str">
+        <f>F26</f>
+        <v>[6,8]</v>
+      </c>
+      <c r="G86" s="14" t="str">
+        <f>G26</f>
+        <v>valtin1995renal</v>
+      </c>
+      <c r="H86" s="4"/>
+      <c r="I86" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J86" s="14"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N86" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O86" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P86" s="14"/>
+      <c r="Q86" s="14"/>
+    </row>
+    <row r="87" spans="1:17">
+      <c r="O87" s="45"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L13" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="L34" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="L41" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="K60" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="O52" r:id="rId5" xr:uid="{77CFD383-FFBB-43C3-9719-6C8925AAAF78}"/>
-    <hyperlink ref="O53" r:id="rId6" xr:uid="{FC8D543E-EB3E-4309-9928-49CA2DE8AE52}"/>
-    <hyperlink ref="O54" r:id="rId7" xr:uid="{DBD15686-F216-4EDA-9421-9DE799BC92F4}"/>
-    <hyperlink ref="O55" r:id="rId8" xr:uid="{8D9A9D3D-AD62-4201-ACA3-FDDCAEB5E9FC}"/>
-    <hyperlink ref="O56" r:id="rId9" xr:uid="{0042DED4-84E3-45EF-B81A-33C49E246FFA}"/>
-    <hyperlink ref="O58" r:id="rId10" xr:uid="{20112368-58A2-4555-8B18-514CF165C0FC}"/>
-    <hyperlink ref="O59:O65" r:id="rId11" display="CBC@120s" xr:uid="{20D8E90A-E850-443A-BB57-0CD158AC0414}"/>
-    <hyperlink ref="O67" r:id="rId12" xr:uid="{0318CE1E-6F08-4524-A904-03D995DB5DB1}"/>
-    <hyperlink ref="O68:O80" r:id="rId13" display="CMP@120s" xr:uid="{C869CBFA-5948-401B-822D-A99AAEA40075}"/>
+    <hyperlink ref="L19" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L40" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L47" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="K66" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="O58" r:id="rId5" xr:uid="{77CFD383-FFBB-43C3-9719-6C8925AAAF78}"/>
+    <hyperlink ref="O59" r:id="rId6" xr:uid="{FC8D543E-EB3E-4309-9928-49CA2DE8AE52}"/>
+    <hyperlink ref="O60" r:id="rId7" xr:uid="{DBD15686-F216-4EDA-9421-9DE799BC92F4}"/>
+    <hyperlink ref="O61" r:id="rId8" xr:uid="{8D9A9D3D-AD62-4201-ACA3-FDDCAEB5E9FC}"/>
+    <hyperlink ref="O62" r:id="rId9" xr:uid="{0042DED4-84E3-45EF-B81A-33C49E246FFA}"/>
+    <hyperlink ref="O64" r:id="rId10" xr:uid="{20112368-58A2-4555-8B18-514CF165C0FC}"/>
+    <hyperlink ref="O65:O71" r:id="rId11" display="CBC@120s" xr:uid="{20D8E90A-E850-443A-BB57-0CD158AC0414}"/>
+    <hyperlink ref="O73" r:id="rId12" xr:uid="{0318CE1E-6F08-4524-A904-03D995DB5DB1}"/>
+    <hyperlink ref="O74:O86" r:id="rId13" display="CMP@120s" xr:uid="{C869CBFA-5948-401B-822D-A99AAEA40075}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C3775-BD01-4677-B3C4-B97284B998D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AC0127-FEB7-48AF-AE43-6E91CF4DACFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20475" yWindow="3300" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18765" yWindow="4260" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -3780,9 +3780,6 @@
     <t>[900,1100]</t>
   </si>
   <si>
-    <t>ApparentOxygenConsumption</t>
-  </si>
-  <si>
     <t>18-20 mL O2/dL blood = 18-20%</t>
   </si>
   <si>
@@ -3799,6 +3796,9 @@
   </si>
   <si>
     <t>[0.13,0.15]</t>
+  </si>
+  <si>
+    <t>ClinicalOxygenConsumption</t>
   </si>
 </sst>
 </file>
@@ -13383,18 +13383,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>14</v>
-      </c>
+        <v>1195</v>
+      </c>
+      <c r="B2" s="8"/>
       <c r="C2" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
-      <c r="F2" s="8">
-        <v>250</v>
+      <c r="F2" s="2" t="s">
+        <v>1205</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>15</v>
@@ -13403,7 +13401,9 @@
       <c r="I2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>1202</v>
+      </c>
       <c r="K2" s="12"/>
       <c r="L2" s="13"/>
       <c r="M2" s="5" t="s">
@@ -13422,7 +13422,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="10" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="8" t="s">
         <v>1206</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -13461,27 +13461,27 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="10" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B4" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C4" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8" t="s">
-        <v>1207</v>
+        <v>47</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>1204</v>
-      </c>
+      <c r="J4" s="8"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="5" t="s">
@@ -13500,23 +13500,25 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="8"/>
+      <c r="F5" s="8">
+        <v>1050</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="I5" s="8" t="s">
         <v>49</v>
       </c>
@@ -13527,177 +13529,173 @@
         <v>50</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P5" s="14">
-        <v>2</v>
-      </c>
+      <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" ht="24">
       <c r="A6" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="8">
-        <v>1050</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>56</v>
+      <c r="F6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P6" s="14"/>
+      <c r="P6" s="14">
+        <v>2</v>
+      </c>
       <c r="Q6" s="14"/>
     </row>
-    <row r="7" spans="1:17" ht="24">
+    <row r="7" spans="1:17">
       <c r="A7" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="8" t="s">
-        <v>59</v>
+      <c r="F7" s="8">
+        <v>3617</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H7" s="8"/>
       <c r="I7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="4"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
       <c r="M7" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="14">
-        <v>2</v>
-      </c>
+      <c r="P7" s="14"/>
       <c r="Q7" s="14"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" ht="24">
       <c r="A8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="8">
-        <v>3617</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="8"/>
+      <c r="F8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="I8" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13"/>
+      <c r="K8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="4"/>
       <c r="M8" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="14"/>
+      <c r="P8" s="14">
+        <v>1</v>
+      </c>
       <c r="Q8" s="14"/>
     </row>
-    <row r="9" spans="1:17" ht="24">
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>66</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="F9" s="8">
+        <v>0.13</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="4"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>52</v>
       </c>
       <c r="P9" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
@@ -13706,24 +13704,22 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N10" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="N10" s="5"/>
       <c r="O10" s="14" t="s">
         <v>52</v>
       </c>
@@ -13734,31 +13730,35 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="8"/>
+        <v>1208</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8"/>
+        <v>250</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="J11" s="8"/>
       <c r="K11" s="12"/>
       <c r="L11" s="13"/>
       <c r="M11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="5"/>
+      <c r="N11" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="O11" s="14" t="s">
         <v>52</v>
       </c>
@@ -13860,7 +13860,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>15</v>
@@ -13870,7 +13870,7 @@
         <v>49</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="13"/>
@@ -15665,20 +15665,20 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8" t="str">
-        <f>F7</f>
+        <f>F6</f>
         <v>7.2,
  [7.35,7.4]</v>
       </c>
       <c r="G58" s="8" t="str">
-        <f>G7</f>
+        <f>G6</f>
         <v>valentin2002icrp,  guyton2006medical</v>
       </c>
       <c r="H58" s="8" t="str">
-        <f>H7</f>
+        <f>H6</f>
         <v>p137                                 p384</v>
       </c>
       <c r="I58" s="8" t="str">
-        <f>I7</f>
+        <f>I6</f>
         <v>Y</v>
       </c>
       <c r="J58" s="4" t="s">
@@ -16425,12 +16425,12 @@
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="14" t="str">
-        <f>F9</f>
+        <f>F8</f>
         <v>[9.0,18.0],
 [6.0,20.0]</v>
       </c>
       <c r="G77" s="14" t="str">
-        <f>G9</f>
+        <f>G8</f>
         <v>valtin1995renal,
 Deepakfirst</v>
       </c>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AC0127-FEB7-48AF-AE43-6E91CF4DACFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0EF5D0-CF4A-4CA9-BCE4-CBF453498BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18765" yWindow="4260" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18420" yWindow="3915" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -3792,13 +3792,13 @@
     <t>[0.18,0.20]</t>
   </si>
   <si>
-    <t>[0.04-0.05]</t>
-  </si>
-  <si>
     <t>[0.13,0.15]</t>
   </si>
   <si>
     <t>ClinicalOxygenConsumption</t>
+  </si>
+  <si>
+    <t>[0.04,0.05]</t>
   </si>
 </sst>
 </file>
@@ -13431,7 +13431,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>15</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="10" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>14</v>
@@ -13860,7 +13860,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>15</v>

--- a/data/human/adult/validation/SystemValidationData.xlsx
+++ b/data/human/adult/validation/SystemValidationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEE00C0-82DE-41C1-8440-323DE0D8DAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45ECEB53-8FFA-45EC-BFAC-0D7B86DA64C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
     <sheet name="RespiratoryExpandedLungs" sheetId="12" r:id="rId12"/>
     <sheet name="Tissue" sheetId="11" r:id="rId13"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId14"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -48,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7003" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7005" uniqueCount="1250">
   <si>
     <t>Patient Inputs</t>
   </si>
@@ -4632,52 +4629,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Patient"/>
-      <sheetName val="Blood Chemistry"/>
-      <sheetName val="Cardiovascular"/>
-      <sheetName val="CardiovascularExpandedLungs"/>
-      <sheetName val="CardiovascularComputationalLife"/>
-      <sheetName val="Endocrine"/>
-      <sheetName val="Energy"/>
-      <sheetName val="Gastrointestinal"/>
-      <sheetName val="Nervous"/>
-      <sheetName val="Renal"/>
-      <sheetName val="Respiratory"/>
-      <sheetName val="RespiratoryExpandedLungs"/>
-      <sheetName val="Tissue"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="55">
-          <cell r="F55">
-            <v>8.4000000000000005E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -16004,7 +15955,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1552AE4F-8EDA-4B53-A93F-ABC6B36E30F3}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -16022,7 +15973,7 @@
     <col min="15" max="15" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -16071,8 +16022,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="67" t="s">
         <v>1230</v>
       </c>
@@ -16085,7 +16039,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="122">
-        <f>(K2/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K2/100*Respiratory!$F$56)*1000</f>
         <v>3.3801600000000001</v>
       </c>
       <c r="G2" s="51" t="s">
@@ -16112,8 +16066,9 @@
       <c r="P2" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="67" t="s">
         <v>1229</v>
       </c>
@@ -16126,7 +16081,7 @@
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="122">
-        <f>(K3/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K3/100*Respiratory!$F$56)*1000</f>
         <v>3.7111200000000006</v>
       </c>
       <c r="G3" s="51" t="s">
@@ -16153,8 +16108,9 @@
       <c r="P3" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="67" t="s">
         <v>1228</v>
       </c>
@@ -16167,7 +16123,7 @@
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="122">
-        <f>(K4/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K4/100*Respiratory!$F$56)*1000</f>
         <v>4.1806799999999997</v>
       </c>
       <c r="G4" s="51" t="s">
@@ -16194,8 +16150,9 @@
       <c r="P4" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="67" t="s">
         <v>1227</v>
       </c>
@@ -16208,7 +16165,7 @@
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="122">
-        <f>(K5/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K5/100*Respiratory!$F$56)*1000</f>
         <v>4.9534800000000008</v>
       </c>
       <c r="G5" s="51" t="s">
@@ -16235,8 +16192,9 @@
       <c r="P5" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="67" t="s">
         <v>1226</v>
       </c>
@@ -16249,7 +16207,7 @@
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
       <c r="F6" s="122">
-        <f>(K6/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K6/100*Respiratory!$F$56)*1000</f>
         <v>4.8980399999999999</v>
       </c>
       <c r="G6" s="51" t="s">
@@ -16276,8 +16234,9 @@
       <c r="P6" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="67" t="s">
         <v>1225</v>
       </c>
@@ -16290,7 +16249,7 @@
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="122">
-        <f>(K7/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K7/100*Respiratory!$F$56)*1000</f>
         <v>4.4293200000000006</v>
       </c>
       <c r="G7" s="51" t="s">
@@ -16317,8 +16276,9 @@
       <c r="P7" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="67" t="s">
         <v>1224</v>
       </c>
@@ -16331,7 +16291,7 @@
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="122">
-        <f>(K8/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K8/100*Respiratory!$F$56)*1000</f>
         <v>5.0635200000000005</v>
       </c>
       <c r="G8" s="51" t="s">
@@ -16358,8 +16318,9 @@
       <c r="P8" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="67" t="s">
         <v>1223</v>
       </c>
@@ -16372,7 +16333,7 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="122">
-        <f>(K9/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K9/100*Respiratory!$F$56)*1000</f>
         <v>5.3121600000000004</v>
       </c>
       <c r="G9" s="51" t="s">
@@ -16399,8 +16360,9 @@
       <c r="P9" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="67" t="s">
         <v>1222</v>
       </c>
@@ -16413,7 +16375,7 @@
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="122">
-        <f>(K10/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K10/100*Respiratory!$F$56)*1000</f>
         <v>5.4230400000000003</v>
       </c>
       <c r="G10" s="51" t="s">
@@ -16440,8 +16402,9 @@
       <c r="P10" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="67" t="s">
         <v>1221</v>
       </c>
@@ -16454,7 +16417,7 @@
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="122">
-        <f>(K11/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K11/100*Respiratory!$F$56)*1000</f>
         <v>5.1744000000000012</v>
       </c>
       <c r="G11" s="51" t="s">
@@ -16481,8 +16444,9 @@
       <c r="P11" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="67" t="s">
         <v>1220</v>
       </c>
@@ -16495,7 +16459,7 @@
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="122">
-        <f>(K12/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K12/100*Respiratory!$F$56)*1000</f>
         <v>5.2021199999999999</v>
       </c>
       <c r="G12" s="51" t="s">
@@ -16522,8 +16486,9 @@
       <c r="P12" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="67" t="s">
         <v>1219</v>
       </c>
@@ -16536,7 +16501,7 @@
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
       <c r="F13" s="122">
-        <f>(K13/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K13/100*Respiratory!$F$56)*1000</f>
         <v>5.3676000000000004</v>
       </c>
       <c r="G13" s="51" t="s">
@@ -16563,8 +16528,9 @@
       <c r="P13" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="67" t="s">
         <v>1218</v>
       </c>
@@ -16577,7 +16543,7 @@
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="122">
-        <f>(K14/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K14/100*Respiratory!$F$56)*1000</f>
         <v>5.1189600000000004</v>
       </c>
       <c r="G14" s="51" t="s">
@@ -16604,8 +16570,9 @@
       <c r="P14" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="67" t="s">
         <v>1217</v>
       </c>
@@ -16618,7 +16585,7 @@
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="122">
-        <f>(K15/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K15/100*Respiratory!$F$56)*1000</f>
         <v>4.4293200000000006</v>
       </c>
       <c r="G15" s="51" t="s">
@@ -16645,8 +16612,9 @@
       <c r="P15" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="67" t="s">
         <v>1216</v>
       </c>
@@ -16659,7 +16627,7 @@
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
       <c r="F16" s="122">
-        <f>(K16/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K16/100*Respiratory!$F$56)*1000</f>
         <v>5.0089200000000007</v>
       </c>
       <c r="G16" s="51" t="s">
@@ -16686,8 +16654,9 @@
       <c r="P16" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="67" t="s">
         <v>1215</v>
       </c>
@@ -16700,7 +16669,7 @@
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="122">
-        <f>(K17/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K17/100*Respiratory!$F$56)*1000</f>
         <v>4.6771199999999995</v>
       </c>
       <c r="G17" s="51" t="s">
@@ -16727,8 +16696,9 @@
       <c r="P17" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="67" t="s">
         <v>1214</v>
       </c>
@@ -16741,7 +16711,7 @@
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="122">
-        <f>(K18/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K18/100*Respiratory!$F$56)*1000</f>
         <v>4.1252399999999998</v>
       </c>
       <c r="G18" s="51" t="s">
@@ -16768,8 +16738,9 @@
       <c r="P18" s="66">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="67" t="s">
         <v>1213</v>
       </c>
@@ -16782,7 +16753,7 @@
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
       <c r="F19" s="122">
-        <f>(K19/100*[1]Respiratory!$F$55)*1000</f>
+        <f>(K19/100*Respiratory!$F$56)*1000</f>
         <v>3.5456400000000001</v>
       </c>
       <c r="G19" s="51" t="s">
@@ -16809,6 +16780,7 @@
       <c r="P19" s="66">
         <v>4</v>
       </c>
+      <c r="Q19" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28928,7 +28900,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A288E4-2A5B-49C3-8F74-67B83EE55504}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.5703125" customWidth="1"/>
@@ -28946,7 +28918,7 @@
     <col min="15" max="15" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -28995,8 +28967,11 @@
       <c r="P1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="9" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="10" t="s">
         <v>1249</v>
       </c>
@@ -29034,8 +29009,9 @@
         <v>356</v>
       </c>
       <c r="P2" s="14"/>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="10" t="s">
         <v>1248</v>
       </c>
@@ -29073,8 +29049,9 @@
         <v>356</v>
       </c>
       <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="10" t="s">
         <v>1247</v>
       </c>
@@ -29112,8 +29089,9 @@
         <v>356</v>
       </c>
       <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
         <v>1246</v>
       </c>
@@ -29151,8 +29129,9 @@
         <v>356</v>
       </c>
       <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="10" t="s">
         <v>1245</v>
       </c>
@@ -29190,8 +29169,9 @@
         <v>356</v>
       </c>
       <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="10" t="s">
         <v>1244</v>
       </c>
@@ -29229,8 +29209,9 @@
         <v>356</v>
       </c>
       <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="10" t="s">
         <v>1243</v>
       </c>
@@ -29268,8 +29249,9 @@
         <v>356</v>
       </c>
       <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
         <v>1242</v>
       </c>
@@ -29307,8 +29289,9 @@
         <v>356</v>
       </c>
       <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="10" t="s">
         <v>1241</v>
       </c>
@@ -29346,8 +29329,9 @@
         <v>356</v>
       </c>
       <c r="P10" s="14"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="10" t="s">
         <v>1240</v>
       </c>
@@ -29385,8 +29369,9 @@
         <v>356</v>
       </c>
       <c r="P11" s="14"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="10" t="s">
         <v>1239</v>
       </c>
@@ -29424,8 +29409,9 @@
         <v>356</v>
       </c>
       <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="10" t="s">
         <v>1238</v>
       </c>
@@ -29463,8 +29449,9 @@
         <v>356</v>
       </c>
       <c r="P13" s="14"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="10" t="s">
         <v>1237</v>
       </c>
@@ -29502,8 +29489,9 @@
         <v>356</v>
       </c>
       <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="10" t="s">
         <v>1236</v>
       </c>
@@ -29541,8 +29529,9 @@
         <v>356</v>
       </c>
       <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="10" t="s">
         <v>1235</v>
       </c>
@@ -29580,8 +29569,9 @@
         <v>356</v>
       </c>
       <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="10" t="s">
         <v>1234</v>
       </c>
@@ -29619,8 +29609,9 @@
         <v>356</v>
       </c>
       <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="14"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="10" t="s">
         <v>1233</v>
       </c>
@@ -29658,8 +29649,9 @@
         <v>356</v>
       </c>
       <c r="P18" s="14"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="10" t="s">
         <v>1232</v>
       </c>
@@ -29697,6 +29689,7 @@
         <v>356</v>
       </c>
       <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
